--- a/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
+++ b/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arjen/kDrive/Obsidian/Literature Review MDIM/05_coding/atlas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E329DE31-167B-724A-8519-E8D88B991807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="236">
   <si>
     <t>Code</t>
   </si>
@@ -149,6 +144,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Legal: Privacy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Legal: Restrictions</t>
     </r>
   </si>
@@ -180,7 +186,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Agreement</t>
+      <t>Challenge: Organizational: Absence of agreement</t>
     </r>
   </si>
   <si>
@@ -196,7 +202,166 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Capacity</t>
+      <t>Challenge: Organizational: Cultural Differences</t>
+    </r>
+  </si>
+  <si>
+    <t>Literature:
+Scholl &amp; Klischewski (2007) (noted as collabrative)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Diversity</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Organizational interoperability challenge arising from persistent differences in organizational structures, roles, responsibilities, and management processes across public administrations, which hinder alignment and increase the effort required for interoperability.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Lack of Architecture</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Lack of Collaboration</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Lack of Expertise</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Defintion:
+Organizational interoperability challenge arising from insufficient domain, semantic, or technical expertise required to design, implement, interpret, and sustain interoperability solutions, including structured semantic data, ontologies, and linked data. complexity issues and lack in ability of people and organizations to cope with complex issues </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Lack of Governance</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Organizational interoperability challenge arising from the absence of explicit governance, ownership, or managerial steering for semantic interoperability, resulting in semantic issues being handled ad hoc within technical or business silos. Like: misaligned or incompatible business processes that prevent end‑to‑end service delivery (Scholl &amp; Klischewski 2007), unclear distribution of roles, responsibilities or decision rights and lack of coordination mechanisms, collaboration structures or shared governance arrangements
+Literature:
+Scholl &amp; Klischewski (2007) (noted as managerial)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Lack of implementation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Lack of Support</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Little Awareness</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Little or no Instrumentarium</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Organizational interoperability challenge arising from the absence or insufficient availability of appropriate tools, methods, and operational practices required to design, implement, manage, or apply interoperability and semantic solutions.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: No Availability of data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Overhead Costs</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Organizational interoperability challenge caused by the coordination, governance, and management overhead required to align multiple organizations, processes, and responsibilities, where the organizational effort itself becomes a bottleneck to interoperability. 
+Zou gezien kunnen worden als een capaciteitsprobleem dat ontstaat door de inzet op interoperabiliteit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Shortage in capacity</t>
     </r>
   </si>
   <si>
@@ -204,99 +369,6 @@
 Organizational interoperability challenge arising from insufficient structural capacity, including lack of time, funding, staffing, or institutional support to implement and sustain interoperability solutions.
 Literature:
 Scholl &amp; Klischewski (2007)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Culture</t>
-    </r>
-  </si>
-  <si>
-    <t>Literature:
-Scholl &amp; Klischewski (2007) (noted as collabrative)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Diversity</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Organizational interoperability challenge arising from persistent differences in organizational structures, roles, responsibilities, and management processes across public administrations, which hinder alignment and increase the effort required for interoperability.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Expertise</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Defintion:
-Organizational interoperability challenge arising from insufficient domain, semantic, or technical expertise required to design, implement, interpret, and sustain interoperability solutions, including structured semantic data, ontologies, and linked data. complexity issues and lack in ability of people and organizations to cope with complex issues </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Governance</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Organizational interoperability challenge arising from the absence of explicit governance, ownership, or managerial steering for semantic interoperability, resulting in semantic issues being handled ad hoc within technical or business silos. Like: misaligned or incompatible business processes that prevent end‑to‑end service delivery (Scholl &amp; Klischewski 2007), unclear distribution of roles, responsibilities or decision rights and lack of coordination mechanisms, collaboration structures or shared governance arrangements
-Literature:
-Scholl &amp; Klischewski (2007) (noted as managerial)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Instrumentarium</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Organizational interoperability challenge arising from the absence or insufficient availability of appropriate tools, methods, and operational practices required to design, implement, manage, or apply interoperability and semantic solutions.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Overhead</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Organizational interoperability challenge caused by the coordination, governance, and management overhead required to align multiple organizations, processes, and responsibilities, where the organizational effort itself becomes a bottleneck to interoperability. 
-Zou gezien kunnen worden als een capaciteitsprobleem dat ontstaat door de inzet op interoperabiliteit</t>
   </si>
   <si>
     <r>
@@ -399,6 +471,43 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Semantic: Instability of Meaning</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Lack of Semantic Standards</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Lack of shared Syntax</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Semantic interoperability challenge arising when semantic models or information artefacts are expressed using different representation or formal languages, such that their structures or constructs are not directly comparable without explicit translation or mapping. (Euzenat &amp; Shvaiko 2013, p37)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Semantic: Metadata Insufficiency</t>
     </r>
   </si>
@@ -430,12 +539,19 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Syntax</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Semantic interoperability challenge arising when semantic models or information artefacts are expressed using different representation or formal languages, such that their structures or constructs are not directly comparable without explicit translation or mapping. (Euzenat &amp; Shvaiko 2013, p37)</t>
+      <t>Challenge: Semantic: Redundant and repeated data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Semantic Complexity and Scale</t>
+    </r>
   </si>
   <si>
     <r>
@@ -486,6 +602,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Technical: Genral Technical Limitations</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Technical: Incompatible Technique</t>
     </r>
   </si>
@@ -521,7 +648,18 @@
   </si>
   <si>
     <t>Definition:
-Failures in syntactic validation, schema conformance, or machine-level processability of exchanged data</t>
+Failures in syntactic validation, schema conformance, or machine-level processability of exchanged data. Also Query languages fall into this category</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Technical: Security issues</t>
+    </r>
   </si>
   <si>
     <r>
@@ -554,36 +692,6 @@
   </si>
   <si>
     <t>Remark</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-A requirement is a normative statement that specifies a necessary property, condition, or capability that a solution, artifact, or approach must satisfy in order to adequately address one or more identified challenges. Requirements articulate what must be fulfilled, rather than how it should be implemented, and serve as evaluative criteria for design and assessment. (Hevner 2004, Gregor, S., &amp; Jones, D. 2007)
-Inclusion criteria:
-•The statement is prescriptive or normative, expressed in terms of necessity or obligation.
-•The requirement is explicitly linked to one or more identified challenges.
-•The formulation is solution-independent and does not prescribe a specific technology, method, or architecture.
-•The requirement defines a property, constraint, or capability that can be used for evaluation or comparison.
-•The requirement is formulated at an abstract or generic level, applicable across cases or contexts.
-Exclusion criteria:
-•Concrete design choices, implementation details, or technical specifications.
-•Descriptions of existing systems or practices without normative intent.
-•Desired outcomes or benefits that are not translated into necessary conditions.
-•General principles or values that lack operational relevance or evaluative function.
-•Challenges or problem statements that do not specify what must be satisfied.</t>
-  </si>
-  <si>
-    <t>Requirements</t>
   </si>
   <si>
     <r>
@@ -621,6 +729,48 @@
 </t>
   </si>
   <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Legal: Clear Copyright and Licensing Statements</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+All copyrightable data and metadata must include clear and explicitly stated copyright status and licensing conditions that define rights of use, reuse permissions, legal restrictions, and applicable conditions. These statements must be sufficiently precise and standardized to ensure that downstream users can unambiguously determine what is legally permitted.
+Clear copyright and licensing conditions are defined here as explicit and accessible statements that specify ownership, applicable license, scope of permitted reuse, and any legal limitations associated with the data or metadata resource.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•A specific license is attached to data or metadata.
+•Copyright status is explicitly declared.
+•Reuse permissions and restrictions are clearly defined.
+•Legal conditions for reuse are stated in an accessible manner.
+•Open licenses are recommended or mandated for semantic artefacts.
+•Standardized expressions of rights statements are required.
+Exclusion Criteria:
+Do not code when:
+•Terms of service are described without clarifying copyright or licensing.
+•Licensing statements are vague, implicit, or inconsistently formulated.
+Literature:
+•FAIR R1.1 (Wilkinson et al., 2016): “(Meta)data are released with a clear and accessible data usage license.”
+•EOSC Interoperability Framework (2021–2023): requirement for clear statements of rights, open licenses for semantic artefacts, and explicit legal conditions for reuse.
+•Creative Commons (2019): standardized open licensing frameworks supporting interoperable reuse.
+•Wimmer et al. (2018): legal interoperability as a component of federated data ecosystems.
+Links to EIF Recommendation 2:  “Publish the data you own as open data unless certain restrictions apply.”
+Links to EIF Recommendation 39:  Match each base registry with appropriate metadata including the description of its content, service assurance and responsibilities, the type of master data it keeps, conditions of access and the relevant licences, terminology, a glossary, and information about any master data it uses from other base registries.
+Links to EIF Recommendation 41:  Establish procedures and processes to integrate the opening of data in your common business processes, working routines, and in the development of new information systems.
+EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.
+Links to EIF Recommendation 43:  Communicate clearly the right to access and reuse open data. The legal regimes for facilitating access and reuse, such as licences, should be standardised as much as possible.
+</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -652,7 +802,8 @@
 Theoretical Grounding:
 Regulatory governance theory distinguishes rule-setting from monitoring and sanctioning functions. Effective regulation requires credible enforcement mechanisms to ensure compliance with established rules (Baldwin, Cave, &amp; Lodge, 2012).
 Responsive regulation theory emphasizes that enforcement instruments, ranging from incentives to penalties, are necessary to secure sustained adherence in complex governance environments (Ayres &amp; Braithwaite, 1992).
-Interoperability research similarly indicates that non-binding standards often fail to produce consistent cross-organizational alignment, whereas mandatory regimes supported by compliance strategies improve implementation outcomes (European Commission, 2017; Ojo, Janowski, &amp; Estevez, 2009).</t>
+Interoperability research similarly indicates that non-binding standards often fail to produce consistent cross-organizational alignment, whereas mandatory regimes supported by compliance strategies improve implementation outcomes (European Commission, 2017; Ojo, Janowski, &amp; Estevez, 2009).
+EIF: Recommendadtiom 1: “Ensure that national interoperability frameworks and interoperability strategies are aligned with the EIF and, if needed, tailor and extend them to address the national context and needs.”</t>
   </si>
   <si>
     <r>
@@ -662,32 +813,35 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Legal: Institutional Legal Mandate</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Institutional Legal Mandate refers to the requirement that a formally established and legally authorized institution must be designated to coordinate, govern, or oversee interoperability initiatives.
-This requirement asserts that interoperability is promoted when a competent authority is explicitly mandated by law to define responsibilities, provide coordination, and ensure coherence across organizational or jurisdictional boundaries. The focus is on the necessity of legally grounded institutional authority as an enabling condition for sustainable interoperability.
+      <t>Requirement: Legal: Public Policy for Interoperability</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Public Policy for Interoperability refers to the requirement that formally adopted governmental policy instruments must articulate, prioritize, and structurally support interoperability objectives across public administrations.
+This requirement asserts that sustainable interoperability depends on the existence of officially endorsed policy frameworks, strategies, or governmental programs that define objectives, principles, and coordination priorities for interoperability.
+Such policy instruments may include national digital strategies, interoperability frameworks, administrative agreements, governmental programs, or ministerial policy directives. They provide strategic direction and coordination without necessarily constituting binding statutory law.
+The defining characteristic of this requirement is the existence of an officially adopted governmental policy instrument that explicitly frames interoperability as a policy objective or structural priority.
 Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•A legally established coordinating body or competent authority.
-•A formal mandate assigned by statute or regulation to oversee interoperability.
-•Clearly defined legal competences and responsibilities for interoperability governance.
-•A designated authority responsible for harmonization, standard-setting, or cross-domain coordination.
-•Legal recognition of an institution empowered to resolve cross-organizational conflicts related to data exchange.
-The formulation must express necessity or obligation and remain independent of specific implementation mechanisms.
+Code when a source explicitly requires that interoperability depends on:
+•A formally adopted governmental interoperability strategy.
+•An official digital or data policy framework endorsing interoperability.
+•A government-approved roadmap or program mandating interoperability objectives.
+•Cross-ministerial or cross-level policy agreements guiding interoperability.
+•Policy directives that prioritize or structurally embed interoperability in public administration.
+The requirement must concern formally adopted governmental policy, not informal coordination.
 Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•The general existence of legislation without reference to a mandated institution.
-•Technical or semantic standards without institutional authorization.
-•Voluntary governance arrangements lacking formal legal mandate.
-•Enforcement instruments such as penalties or incentives, unless linked to the existence of a legally mandated authority.
-•Informal coordination networks without statutory grounding.
+Do not code when the text concerns:
+•Binding statutory or regulatory law (belongs under Statutory and Regulatory Basis).
+•A legally mandated authority (belongs under Statutory Interoperability Authority).
+•Enforcement or sanctioning mechanisms.
+•Organizational governance structures without policy-level endorsement.
+•Voluntary community frameworks without formal governmental adoption.
 Theoretical Grounding:
-Regulatory governance theory distinguishes rule-setting from institutional mandate and enforcement. Institutional mandate concerns the legally defined authority assigned to specific bodies to coordinate or regulate collective action (Baldwin, Cave, &amp; Lodge, 2012).
-Institutional theory emphasizes that formally established authority structures provide legitimacy, stability, and coordination capacity across organizational boundaries (Scott, 2014). In public-sector interoperability contexts, governance frameworks and clearly allocated responsibilities are consistently identified as critical success factors (European Commission, 2017).
-Empirical studies on e-government interoperability highlight the importance of legally mandated coordinating bodies for achieving sustained cross-organizational alignment (Kubicek &amp; Cimander, 2009; Sharma &amp; Panigrahi, 2011). Without such mandate, interoperability efforts tend to remain fragmented or voluntary.</t>
+Public governance theory distinguishes between statutory rule-making and policy instruments as strategic steering mechanisms (Baldwin, Cave, &amp; Lodge, 2012).
+The European Interoperability Framework (European Commission, 2017) emphasizes that interoperability requires political commitment and policy endorsement in addition to legal and technical measures.
+Multi-level governance research highlights that strategic governmental policy direction reduces fragmentation and provides coordination signals across administrative domains.
+</t>
   </si>
   <si>
     <r>
@@ -697,13 +851,15 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Legal: Legal Frameworks</t>
+      <t>Requirement: Legal: Public Regulation for Interoperability</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">Definition:
-Legal Frameworks refer to the requirement that an adequate and coherent body of binding legal norms must exist and be aligned in order to enable or improve interoperability. This requirement specifies that interoperable solutions depend on clear, consistent, and compatible statutory provisions governing data exchange, data processing, privacy, access rights, accountability, and liability. Without such legal alignment, interoperability efforts remain structurally constrained regardless of technical or semantic solutions.
-The requirement concerns the necessity of a supportive and harmonized legal environment as a precondition for sustainable interoperability.
+Public Regulation for Interoperability refers to the requirement that binding legal norms, enacted through formal legislative or regulatory instruments, must provide a clear and coherent legal foundation for interoperability arrangements.
+This requirement asserts that interoperable data exchange and cross-organizational coordination depend on explicit statutory authorization and regulatory alignment. Relevant legal instruments include primary legislation (acts of parliament), delegated legislation (e.g., governmental decrees, AMvB), ministerial regulations, and other binding regulatory measures.
+The defining characteristic is the necessity of a legally valid and harmonized body of binding norms that authorizes, structures, and constrains data exchange, data processing, privacy protection, access rights, accountability, and liability.
+Without such statutory and regulatory clarity, interoperability initiatives remain structurally limited regardless of technical or semantic adequacy.
 Inclusion Criteria:
 Use this code when the requirement states that interoperability requires:
 •The existence of a clear legal basis for data sharing or data reuse.
@@ -723,6 +879,7 @@
 The European Interoperability Framework identifies legal interoperability as a foundational condition for cross-administrative collaboration, emphasizing that aligned legal frameworks are required to remove barriers to data exchange (European Commission, 2017).
 Regulatory governance theory conceptualizes rule-setting as a prerequisite for coordinated action, distinguishing substantive legal norms from institutional mandate and enforcement (Baldwin, Cave, &amp; Lodge, 2012).
 Empirical research on semantic interoperability demonstrates that privacy law, authorization regimes, and accountability requirements function as structural boundary conditions; without legal clarity and compatibility, interoperability architectures cannot be sustainably implemented (Ojo, Janowski, &amp; Estevez, 2009).
+Links to EIF Recommendation 27:  Ensure that legislation is screened by means of ‘interoperability checks’, to identify any barriers to interoperability. When drafting legislation to establish a European public service, seek to make it consistent with relevant legislation, perform a ‘digital check’ and consider data protection requirements.
 ⸻
 </t>
   </si>
@@ -734,35 +891,71 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Semantic Construct Development and Maintenance refer to the requirement that public authorities must establish organizational arrangements to develop, refine, validate, and sustain shared semantic interoperability constructs over time.
-This requirement asserts that interoperability is promoted when structured or semi-structured procedures exist for creating and maintaining conceptual models, information models, ontologies, controlled vocabularies, reference data structures, and cross-domain mappings. The focus is not on the mere adoption of existing standards, but on the institutionalized capacity to generate, evolve, and harmonize shared meaning constructs within a public authority, across the public sector, and between Member States.
-These arrangements may include formal committees, expert working groups, consultation mechanisms, modeling guidelines, review cycles, and lifecycle governance processes ensuring that semantic constructs remain coherent, aligned, and up to date.
+      <t>Requirement: Legal: Statutory Interoperability Authority</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Statutory Interoperability Authority refers to the requirement that a legally established and formally authorized public body must be designated to coordinate, regulate, or oversee interoperability arrangements across organizational or jurisdictional boundaries.
+This requirement asserts that sustainable interoperability depends on the existence of a competent authority whose mandate is explicitly grounded in statute or regulation. The authority must possess clearly defined legal competences to assign responsibilities, ensure coherence, coordinate cross-domain alignment, and resolve conflicts related to data exchange or standardization.
+The defining characteristic of this requirement is the legal designation of an institutional authority with formally allocated powers in relation to interoperability.
 Inclusion Criteria:
 This requirement applies when the statement expresses that interoperability requires:
-• Organizational structures responsible for developing shared conceptual or information models.
-• Formal or informal procedures for creating and validating semantic constructs.
-• Working groups or expert communities managing ontologies or shared vocabularies.
-• Cross-organizational consultation in model development.
-• Structured review and update cycles for semantic artifacts.
-• Mapping governance between heterogeneous models.
-• Mechanisms for resolving conceptual inconsistencies across domains or jurisdictions.
-• Documented modeling principles or harmonization guidelines.
+•A legally established coordinating body or competent authority.
+•A formal mandate assigned by statute or regulation to oversee interoperability.
+•Clearly defined legal competences and responsibilities for interoperability governance.
+•A designated authority responsible for harmonization, standard-setting, or cross-domain coordination.
+•Legal recognition of an institution empowered to resolve cross-organizational conflicts related to data exchange.
+The formulation must express necessity or obligation and remain independent of specific implementation mechanisms.
 Exclusion Criteria:
 This requirement does not apply when the statement concerns:
-• Governance mandates without reference to semantic construct development.
-• Standard adoption without involvement in model development or evolution.
-• Purely technical data transformation mechanisms.
-• Ad hoc mappings created without institutional maintenance responsibility.
-• Isolated modeling exercises not embedded in organizational structures.
+•The general existence of legislation without reference to a mandated institution.
+•Technical or semantic standards without institutional authorization.
+•Voluntary governance arrangements lacking formal legal mandate.
+•Enforcement instruments such as penalties or incentives, unless linked to the existence of a legally mandated authority.
+•Informal coordination networks without statutory grounding.
 Theoretical Grounding:
-Organizational interoperability research emphasizes that sustainable interoperability requires institutionalized mechanisms for managing shared meaning structures rather than relying solely on static standards (Kubicek, Cimander, &amp; Scholl, 2011).
-Enterprise interoperability maturity models highlight the importance of coordinated development of conceptual and information models (Guédria, Naudet, &amp; Chen, 2008).
-The European Interoperability Framework (2017) underscores the need for documented business processes and harmonized data models as part of sustainable interoperability governance.</t>
+Regulatory governance theory distinguishes rule-setting from institutional mandate and enforcement. Institutional mandate concerns the legally defined authority assigned to specific bodies to coordinate or regulate collective action (Baldwin, Cave, &amp; Lodge, 2012).
+Institutional theory emphasizes that formally established authority structures provide legitimacy, stability, and coordination capacity across organizational boundaries (Scott, 2014). In public-sector interoperability contexts, governance frameworks and clearly allocated responsibilities are consistently identified as critical success factors (European Commission, 2017).
+Empirical studies on e-government interoperability highlight the importance of legally mandated coordinating bodies for achieving sustained cross-organizational alignment 
+Wimmer et al. (2018), however, specifically analyse “interoperability governance models” in Europe and identify concrete, legally mandated bodies required for this purpose, such as the National Digital Commissioner in the Netherlands. They further conclude that formal governing bodies (such as supervisory and preparatory bodies) are necessary to effectively enforce interoperability.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Organizational Requirements refer to normative statements asserting that organizational arrangements are necessary to achieve, enable, or improve interoperability.
+Such requirements indicate that interoperable collaboration depends on the establishment, alignment, or formalization of organizational structures, roles, processes, coordination mechanisms, and governance practices. The defining characteristic is that organizational measures are presented as necessary enabling conditions for sustained cross-organizational or cross-domain interoperability, beyond purely technical or legal provisions.
+Organizational Requirements concern the capability of organizations to coordinate activities, align business processes, allocate responsibilities, and manage shared semantic artefacts in a structured and durable manner.
+Inclusion Criteria:
+This requirement applies when the statement expresses that interoperability requires:
+•Clearly defined roles, responsibilities, or stewardship functions for shared data or semantic artefacts.
+•Alignment or harmonization of business processes across organizational boundaries.
+•Formal governance structures (e.g., boards, coordination bodies, working groups) overseeing interoperability.
+•Institutionalized collaboration mechanisms between agencies, sectors, or levels of government.
+•Agreed procedures for change management, versioning, and lifecycle management of shared models.
+•Capacity-building, knowledge management, or organizational learning mechanisms necessary for interoperability.
+Exclusion Criteria:
+This requirement does not apply when the statement concerns:
+•Technical standards, APIs, schemas, or infrastructure without reference to organizational coordination.
+•Legal mandates or statutory authorization without reference to organizational implementation structures.
+•Purely semantic alignment mechanisms (e.g., ontology matching) without organizational embedding.
+•Informal collaboration lacking structural or governance components.
+•Descriptions of existing organizational structures without asserting their necessity for interoperability.
+Theoretical Grounding:
+The European Interoperability Framework conceptualizes organizational interoperability as the alignment of business processes, responsibilities, and expectations necessary to achieve commonly agreed and mutually beneficial goals across public administrations (European Commission, 2017). Organizational alignment is thus positioned as a fundamental prerequisite for enabling semantic and technical collaboration.
+Interoperability governance literature further specifies that sustainable interoperability requires an enabling framework with defined institutional roles, managerial processes, and steering functions (Wimmer, Boneva, &amp; di Giacomo, 2018). Without these structured governance functions to manage change and assure the sustainability of shared semantic enablers, interoperability artefacts risk fragmentation over time.
+Studies on semantic interoperability emphasize that organizational and governance factors—such as clear stewardship, aligned collaboration processes, and defined communities of interest—function as structural boundary conditions and are at least as critical to achieving interoperability as technical requirements (Ojo, Janowski, &amp; Estevez, 2009). Furthermore, e-government research demonstrates that an overwhelming focus on the purely functional and technical side drastically increases the risk of failure, as technical systems are ultimately subordinated to the organizational and social processes of information sharing (Scholl, 2005). These findings robustly support the view that organizational measures function as necessary enabling conditions for achieving and maintaining interoperability.</t>
   </si>
   <si>
     <r>
@@ -797,7 +990,8 @@
 Theoretical Grounding:
 Organizational capability theory highlights the importance of institutionalized skills and routines for sustained coordination (Rauffet, da Cunha, &amp; Bernard, 2009).
 Enterprise architecture research demonstrates that interoperability depends on structured capability development (Hjort-Madsen, 2006).
-The European Interoperability Framework (2017) emphasizes training and change management as preconditions for interoperability.</t>
+The European Interoperability Framework (2017) emphasizes training and change management as preconditions for interoperability.
+EOSC: “expertise and skills related to semantics”</t>
   </si>
   <si>
     <r>
@@ -807,83 +1001,331 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Cross-Boundary Integration and Strategic Alignment</t>
+      <t>Requirement: Organizational: Clear Terms and Conditions of Use</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">Definition:
-Cross-Boundary Integration and Structural Alignment refer to the requirement that public authorities must establish structural arrangements enabling interoperability across organizational, sectoral, administrative, and national boundaries.
-This requirement asserts that interoperability is promoted when organizations are institutionally configured to operate in coordinated cross-domain environments, including alignment with national strategies, cross-sector frameworks, and cross-border arrangements. The focus is on structural alignment beyond a single organizational context, ensuring that interoperability mechanisms function coherently across levels of government and between Member States.
-This includes alignment with overarching digital strategies, cross-border service infrastructures, and mechanisms enabling consistent implementation of shared principles such as the Once-Only Principle.
+Interoperability services must be accompanied by clearly documented terms and conditions of use, including acceptable use policies and service-level agreements (SLAs), that define rights, obligations, liabilities, and performance expectations for users and providers within the ecosystem.
+Terms and conditions of use are defined here as formally specified legal and operational documents governing access to and use of services such as catalogues, registries of semantic artefacts, alignment services, and semantic mediation systems.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Acceptable use policies are documented for interoperability services.
+•Service-level agreements define availability, reliability, or performance commitments.
+•Legal conditions for accessing catalogues, registries, or alignment services are specified.
+•Usage rights, restrictions, or liabilities are clearly articulated.
+•Terms governing the use of semantic alignment or mediation systems are formally described.
+Exclusion Criteria:
+Do not code when:
+•Only technical accessibility is discussed without legal or usage conditions.
+•Governance roles are described without formal user-facing conditions.
+•Licensing of data is discussed without reference to service-level obligations.
+•Informal or implicit norms of use are assumed without documentation.
+Literature:
+•EOSC Interoperability Framework (2021–2023): requirement for clear terms, acceptable use policies, and SLAs in federated interoperability services.
+•FAIR A1.2 (Wilkinson et al., 2016): accessibility may require authentication and authorization, implying explicit conditions of access.
+•Wimmer et al. (2018): interoperability governance requires formalized service agreements.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Collaboration</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Communuities of Interest and Collaboration</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Communities of Interest and Collaboration refer to the requirement that sustained semantic interoperability depends on the existence of structured, cross-organizational collaboration mechanisms that bring together relevant stakeholders around shared semantic artefacts, standards, and interoperability objectives.
+This requirement asserts that interoperability is promoted when formalized communities or collaborative networks exist in which domain experts, technical specialists, data stewards, policy actors, and governance representatives collectively develop, refine, align, and maintain shared semantic constructs. The focus is on institutionalized interaction structures that enable coordinated meaning-making and continuous alignment across organizational, sectoral, or jurisdictional boundaries.
+Communities of interest are defined here as organized and recurring collaboration forums or networks dedicated to the joint governance, development, or harmonization of interoperability-relevant artefacts.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Formal cross-organizational collaboration structures are established to support interoperability.
+•Multi-stakeholder communities are created to co-develop or maintain standards or semantic artefacts.
+•Regular coordination forums exist for resolving semantic inconsistencies.
+•Domain experts and technical experts are required to collaborate structurally.
+•Cross-sector or cross-border working groups are institutionalized.
+•Collaborative governance arrangements support shared model evolution.
+•Ongoing inter-organizational dialogue is mandated to sustain interoperability.
+Exclusion Criteria:
+Do not code when:
+•Informal communication between organizations is mentioned without institutional structure.
+•Governance authority is described without collaborative interaction mechanisms.
+•Technical integration occurs without stakeholder collaboration.
+•Temporary project groups are formed without sustained institutional embedding.
+•Legal mandates are specified without reference to collaborative practice.
+Theoretical Grounding:
+Organizational and semantic interoperability research emphasizes that sustained alignment of meaning requires structured interaction across institutional boundaries, for example through the forming of project groups and federations (Scholl &amp; Klischewski, 2007). Regulatory governance theory further demonstrates that shared rules and interpretations stabilize through the ongoing discourse within 'epistemic' and 'interpretive communities' (Baldwin, Cave, &amp; Lodge, 2012). In practice, the successful development and maintenance of shared semantic artefacts strongly relies on such community-based repositories and cross-sectoral communities (EOSC, 2021; European Commission, 2017).
+EIF Recommendation 32:  Support the establishment of sector-specific and cross-sectoral communities that aim to create open information specifications and encourage relevant communities to share their results on national and European platforms.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Compliance Mechanismes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Organizational Compliance refers to the requirement that public authorities must establish internal mechanisms to ensure consistent adherence to agreed interoperability standards, semantic artefacts, governance procedures, and operational rules.
+This requirement asserts that interoperability is promoted when organizations actively monitor, verify, and enforce conformity with adopted standards and shared specifications within their own structures and processes. The focus is on institutionalized internal adherence mechanisms rather than on external legal enforcement.
+Organizational compliance is defined here as the structured capacity of an organization to ensure that interoperability-related obligations are consistently implemented in operational systems, data practices, and administrative routines.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Organizations must ensure internal adherence to agreed standards or semantic artefacts.
+•Conformance checks or validation procedures are institutionalized within the organization.
+•Internal audit or quality control mechanisms verify compliance with interoperability agreements.
+•Compliance responsibilities are assigned to specific roles or units.
+•Monitoring mechanisms assess whether standards are correctly implemented in practice.
+•Organizations are required to demonstrate conformity with interoperability frameworks.
+Exclusion Criteria:
+Do not code when:
+•Legal enforcement mechanisms such as penalties or statutory sanctions are described (belongs under Legal: Compliance and Enforcement Mechanisms).
+•Governance structures are described without reference to adherence monitoring.
+•Voluntary or informal commitment to standards is mentioned without structured verification.
+•Technical validation mechanisms are discussed solely at infrastructure level without organizational responsibility.
+•Evaluation or feedback mechanisms focus on learning without compliance verification.
+Theoretical Grounding:
+Organizational control theory distinguishes between formal rule-setting and internal compliance mechanisms that ensure consistent implementation (Baldwin, Cave, &amp; Lodge, 2012).
+Wimmer et al. (2018) explicitly define “Interoperability Governance” as a mechanism that provides the functions and structures required to control and monitor whether objectives are achieved and whether compliance with standards is ensured.
+The European Interoperability Framework (European Commission, 2017) highlights monitoring and conformity assessment as organizational conditions for sustainable cross-government interoperability.
+In design science research, artifact instantiation requires organizational embedding and verification to ensure that prescribed constructs are enacted as intended (Hevner et al., 2004).
+EOSC: “interoperability certification mechanisms for service providers,”
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Evaluation and Feedback Mechanisms</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Evaluation and Feedback Mechanisms refer to the requirement that public authorities must institutionalize structured processes to assess, review, and iteratively improve interoperability arrangements over time.
+This requirement asserts that interoperability is sustained when organizations systematically evaluate whether adopted standards, semantic artefacts, governance arrangements, and aligned processes function as intended in practice, and when evaluation outcomes inform corrective action, refinement, or redesign.
+Evaluation and feedback mechanisms are defined here as formalized procedures that generate evidence about interoperability performance and feed that evidence back into governance, operational practice, or artefact evolution.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Interoperability arrangements must be periodically reviewed or assessed.
+•Monitoring systems evaluate the effectiveness or maturity of interoperability.
+•Metrics or performance indicators measure interoperability outcomes.
+•Structured review cycles exist for standards, models, or governance frameworks.
+•Evaluation findings must trigger revision, refinement, or redesign.
+•Mechanisms detect semantic drift, misalignment, or unintended consequences.
+•Feedback loops connect operational experience to policy or model updates.
+Exclusion Criteria:
+Do not code when:
+•The statement concerns internal adherence verification only (belongs under Organizational: Compliance).
+•Legal enforcement or sanctioning mechanisms are described (belongs under Legal: Compliance and Enforcement).
+•Governance authority is described without evaluation processes.
+•Initial design or development of standards is discussed without review cycles.
+•Informal feedback is mentioned without institutionalized mechanisms.
+•Technical validation is described solely at system level without organizational review.
+Theoretical Grounding:
+Measuring, Benchmarking &amp; Improving (MB&amp;I) (Maheshwari &amp; Janssen, 2014): .
+The European Interoperability Framework (European Commission, 2017) stresses monitoring, benchmarking, and review processes as necessary for sustainable cross-government interoperability.
+EIF: Recommendation 19:  Evaluate the effectiveness and efficiency of different interoperability solutions and technological options considering user needs, proportionality and balance between costs and benefits.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Governance and Institutional Alignment</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Governance and Institutional Alignment refer to the requirement that public authorities must be organizationally structured to ensure the consistent application, monitoring, and maintenance of agreed interoperability standards and shared specifications.
+This requirement asserts that interoperability is promoted when formal governance arrangements, clearly defined roles, decision-making procedures, and data management capabilities are in place to operationalize existing standards in practice. The focus is not on the existence of standards themselves, but on the institutional capacity to implement, enforce, and sustain compliance within individual public organizations, across the public sector, and between Member States.
+Governance in this sense includes stewardship responsibilities, accountability mechanisms, structured coordination, and organizational embedding that ensure standards are actively used rather than merely adopted in principle.
 Inclusion Criteria:
 This requirement applies when the statement expresses that interoperability requires:
-• Institutional mechanisms enabling cross-organizational coordination.
-• Structural alignment across administrative levels.
-• Cross-border interoperability arrangements between Member States.
-• Alignment with national or supranational digital strategies.
-• Multilingual or cross-jurisdictional semantic coordination structures.
-• Integration into national or European digital gateways or shared infrastructures.
-• Mechanisms supporting once-only data exchange across authorities.
+•Organizational structures ensuring the application of agreed standards.
+•Clearly defined roles such as data owner, semantic steward, or compliance authority.
+•Processes for implementing, monitoring, and maintaining compliance with standards.
+•Data management capabilities supporting consistent interpretation and use of shared models.
+•Institutionalized coordination mechanisms ensuring adherence across departments or jurisdictions.
+•Formal mandates or governance frameworks embedding standards into operational practice.
+•Allocation of resources to sustain implementation and compliance efforts.
 Exclusion Criteria:
 This requirement does not apply when the statement concerns:
-• Internal organizational improvements without cross-boundary relevance.
-• Technical system connectivity without institutional alignment.
-• Purely legal obligations without structural integration mechanisms.
-• Informal cross-organizational collaboration lacking structural embedding.
-• Standard governance or process alignment limited to a single authority.
+•The mere existence or selection of standards without reference to their organizational application.
+•Purely technical integration or system architecture.
+•Legislative harmonization without operational governance arrangements.
+•Temporary project coordination without sustained institutional embedding.
+•Informal collaboration lacking defined roles, responsibilities, or accountability mechanisms.
 Theoretical Grounding:
-Interorganizational information integration research highlights that structural cross-boundary alignment is a prerequisite for digital government effectiveness (Pardo &amp; Tayi, 2007).
-Research on the Once-Only Principle shows that interoperability across administrations requires institutional coordination beyond technical exchange (Krimmer et al., 2017).
-The European Interoperability Framework (2017) positions cross-level and cross-border alignment as central to sustainable interoperability.
+Institutional governance theory emphasizes that durable coordination depends on formalized authority structures and accountability mechanisms (Pardo, Nam, &amp; Burke, 2012).
+Wimmer et al. (2018), however, specifically analyse “interoperability governance models” in Europe and identify concrete, legally mandated bodies required for this purpose, such as the National Digital Commissioner in the Netherlands. They further conclude that formal governing bodies (such as supervisory and preparatory bodies) are necessary to effectively enforce interoperability.
+The European Interoperability Framework (2017) highlights governance, coordination, and change management structures as prerequisites for sustained interoperability implementation.
+EOSC: “governance framework that will deal with interoperability across organisations and disciplines”
+EIF: Recommendation 20:  Ensure holistic governance of interoperability activities across administrative levels and sectors.
+EIF Recommendation 25:  Ensure interoperability and coordination over time when operating and delivering integrated public services by putting in place the necessary governance structure.
+EIF Recommendation 26:  Establish interoperability agreements in all layers, complemented by operational agreements and change management procedures.
+Links to EIF Recommendation 28:  Document your business processes using commonly accepted modelling techniques and agree on how these processes should be aligned to deliver a European public service.
+Links to EIF Recommendation 29:  Clarify and formalise your organisational relationships for establishing and operating European public services. 
+Links to EIF Recommendation 31:  Put in place an information management strategy at the highest possible level to avoid fragmentation and duplication. Management of metadata, master data and reference data should be prioritised.
 </t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Incentive Strategies</t>
+    </r>
+  </si>
+  <si>
     <t>Definition:
-Evaluation and Feedback Mechanisms refer to the requirement that public authorities institutionalize structured mechanisms to assess, monitor, and review the effectiveness, consistency, and compliance of interoperability arrangements over time.
-Interoperability is promoted when organizations systematically evaluate whether semantic constructs, standards, and aligned processes are functioning as intended in practice, and when findings from monitoring activities trigger corrective action, refinement, or redesign. The focus is on continuous assessment and adaptive learning, rather than on initial development, selection, or operational implementation.
-This requirement applies within individual public organizations, across administrative levels, and between Member States wherever sustained interoperability depends on feedback loops and structured review mechanisms.
+Incentive Strategy refers to the requirement that public authorities must establish structured motivational and alignment mechanisms that encourage organizations and stakeholders to adopt, implement, and sustain interoperability standards, semantic artefacts, and shared practices.
+This requirement asserts that interoperability is promoted when actors are provided with institutional, financial, reputational, or strategic incentives that make compliance with shared constructs beneficial or advantageous. The focus is on proactive alignment mechanisms that stimulate voluntary adherence and sustained participation, rather than on coercive legal enforcement.
+An incentive strategy is defined here as an intentionally designed set of mechanisms that align organizational behavior with interoperability objectives through positive or strategic reinforcement.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Financial incentives or funding conditions are linked to interoperability adoption.
+•Performance metrics or benchmarking influence organizational reputation.
+•Certification or recognition schemes reward interoperability compliance.
+•Access to shared infrastructure or services is conditional upon alignment.
+•Strategic benefits (e.g., efficiency gains, data access privileges) are structured to encourage adherence.
+•Participation in interoperability frameworks is supported by institutional rewards.
+•Incentive mechanisms are designed to stimulate collaboration or standard adoption.
+The requirement must concern motivational alignment mechanisms rather than mandatory compliance or sanctioning.
+Exclusion Criteria:
+Do not code when:
+•Legal penalties or sanctions are described (belongs under Legal: Compliance and Enforcement Mechanisms).
+•Internal monitoring mechanisms verify adherence without motivational instruments (belongs under Organizational: Compliance).
+•Governance authority is described without incentive alignment.
+•Voluntary cooperation is mentioned without structured incentive design.
+•Technical requirements are specified without behavioral alignment mechanisms.
+Theoretical Grounding:
+Institutional economics and regulatory governance theory distinguish between coercive enforcement and incentive-based regulatory strategies (Baldwin, Cave, &amp; Lodge, 2012).
+Interorganizational collaboration research demonstrates that sustained alignment often depends on incentive compatibility between participating actors (Pardo &amp; Tayi, 2007).
+The European Interoperability Framework (European Commission, 2017) highlights that policy alignment, funding conditions, and strategic coordination mechanisms can stimulate interoperability adoption across administrations.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Operational Use and Institutional Embedding</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Operational Use and Institutional Embedding of Semantic Constructs refer to the requirement that agreed semantic constructs, standards, and shared specifications are actively and consistently applied and reused in everyday organizational practice.
+Interoperability is promoted when semantic artifacts are not merely selected or governed, but systematically integrated into operational processes, information systems, service delivery routines, and decision-making procedures. The focus is on the effective enactment of constructs in real-world administrative workflows, ensuring that shared models shape how data are captured, interpreted, exchanged, and maintained.
+This requirement applies within single organizations and across organizational, sectoral, administrative, or national contexts wherever interoperability depends on sustained and consistent practical application.
 Inclusion Criteria:
 This requirement applies when interoperability requires:
-• Monitoring mechanisms assessing compliance with standards or semantic constructs.
-• Maturity assessments or interoperability performance evaluations.
-• Structured review cycles for models, standards, or cross-organizational arrangements.
-• Audit mechanisms detecting inconsistencies, conflicts, or semantic drift.
-• Feedback loops linking evaluation outcomes to revision or improvement processes.
-• Metrics measuring interoperability quality, coherence, or effectiveness.
-• Formal procedures for resolving detected conceptual or semantic conflicts.
+• Actual application of agreed information models in operational systems.
+• Routine use of shared vocabularies or taxonomies in data entry and processing.
+• Embedding of standards into software configurations or business rules.
+• Use of shared semantic constructs in decision-making or service provision.
+• Consistent interpretation of shared definitions in administrative practice.
+• Institutional enforcement of construct use in day-to-day operations.
+• Alignment between documented standards and actual operational behavior.
 Exclusion Criteria:
 This requirement does not apply when the statement concerns:
-• The initial development or selection of standards without reference to monitoring.
-• Governance authority without assessment or feedback mechanisms.
-• Incentive or performance structures without explicit evaluation processes.
-• Technical validation at infrastructure level without organizational review.
-• Informal feedback lacking institutionalized procedures.
+• Design or development of semantic constructs.
+• Selection or cataloguing of standards without operational application.
+• Governance roles without reference to practical enactment.
+• Monitoring or evaluation activities without reference to actual use.
+• Temporary pilot implementations without institutional embedding.
+• Purely technical connectivity without semantic enactment.
 Theoretical Grounding:
-Design science research emphasizes evaluation as an essential component of the build–evaluate cycle, ensuring artifacts are tested and refined in real contexts (Hevner et al., 2004).
-Organizational learning theory highlights the importance of feedback loops for sustained adaptation in complex institutional environments.
-Interoperability maturity research demonstrates that without structured assessment and corrective mechanisms, semantic divergence and implementation drift emerge over time.</t>
+In design science research, artifacts must be instantiated and used in organizational contexts to demonstrate utility (Hevner et al., 2004). The “build–evaluate” cycle presupposes actual use as the context in which relevance and performance emerge.
+Institutional theory emphasizes that formal artifacts only produce coordination effects when enacted through routinized organizational practice (Orlikowski, 2000). 
+Links to EIF Recommendation 34:  Use the conceptual model for European public services to design new services or reengineer existing ones and reuse, whenever possible, existing service and data components.
+EIF Recommendation 6:  Reuse and share solutions, and cooperate in the development of joint solutions when implementing European public services.
+EIF Recommendation 7:  Reuse and share information and data when implementing European public services, unless certain privacy or confidentiality restrictions apply.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Political Support</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Public Asset Orientation Toward Data</t>
+    </r>
   </si>
   <si>
     <t>Definition:
-Interoperability Governance and Accountability refer to the requirement that public authorities establish formal decision-making structures, roles, mandates, and oversight mechanisms to steer and coordinate interoperability-related activities.
-Interoperability is promoted when authority, responsibility, and accountability for standards, semantic constructs, implementation strategies, and compliance are clearly allocated and institutionally embedded. The focus is on who decides, who is responsible, and how coordinated direction and oversight are exercised, rather than on operational implementation. This applies within organizations, across sectors and administrative levels, and between Member States.
+Public Asset Orientation Toward Data refers to the requirement that public authorities institutionalize a normative understanding of data and information as strategic public assets whose value extends beyond their immediate administrative use.
+This requirement asserts that sustainable semantic interoperability depends on an organizational orientation in which data are perceived as shared, reusable, and durable public resources. Under this orientation, data are intentionally generated, documented, structured, and preserved in ways that anticipate reuse across organizational and domain boundaries.
+The focus is on the institutionalized perception and treatment of data as enduring public resources, rather than on specific governance mechanisms, legal mandates, or technical infrastructure.
 Inclusion Criteria:
-This requirement applies when interoperability requires:
-• Formal governance bodies overseeing interoperability strategies or frameworks.
-• Clearly defined roles such as data owner or semantic steward.
-• Decision-making procedures for adopting or prioritizing standards and initiatives.
-• Monitoring, reporting, or accountability mechanisms for interoperability performance.
-• Cross-organizational coordination or escalation mechanisms.
-• Allocation of resources linked to interoperability governance decisions.
+Code when a source explicitly requires that:
+•Data be perceived or treated as public assets.
+•Data management be guided by long-term public value considerations.
+•Data generation anticipate reuse beyond original administrative purpose.
+•Information be managed with cross-organizational or cross-domain applicability in mind.
+•Public authorities adopt a culture or principle of data-as-asset.
+•Data sharing and preservation are framed as intrinsic public responsibilities.
+•Administrative practices reflect recognition of data’s strategic and collective value.
+The emphasis must concern normative orientation toward data, not technical implementation details.
 Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-• Concrete operational use of standards in workflows or systems.
-• Technical infrastructure configuration without governance structures.
-• Process harmonization without explicit authority or accountability elements.
-• Legal mandates without organizational governance arrangements.
-• Capability development without decision rights or oversight structures.
+Do not code when:
+•Only specific governance structures or stewardship roles are described.
+•Legal authorization for data sharing is specified without asset framing.
+•Technical infrastructure requirements are discussed.
+•Data quality requirements are defined without reference to public value orientation.
+•Open data publication is mentioned without a broader data-as-asset principle.
 Theoretical Grounding:
-Institutional governance theory emphasizes that sustained coordination requires formal authority and accountability structures (Pardo, Nam, &amp; Burke, 2012). Organizational interoperability research shows that standards become effective only when embedded in governance arrangements that define decision rights and oversight (Kubicek, Cimander, &amp; Scholl, 2011).</t>
+The European Interoperability Framework frames data and information as public assets whose lifecycle management underpins interoperability.
+Public value theory conceptualizes government information as a strategic resource contributing to collective societal benefit rather than merely administrative efficiency (Dawes, 2008).
+Information governance literature distinguishes between transactional data handling and asset-oriented data management, emphasizing that cross-organizational reuse requires anticipatory structuring and preservation.
+Organizational theory further suggests that institutionalized cognitive frames shape how artefacts are designed and managed; treating data as assets influences modelling, documentation, and interoperability practices (Scott, 2014).
+EIF Recommendation 30:  Perceive data and information as a public asset that should be appropriately generated, collected, managed, shared, protected and preserved.</t>
   </si>
   <si>
     <r>
@@ -893,60 +1335,48 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Incentive and Performance Structures</t>
+      <t>Requirement: Organizational: Semantic Construct Design and Maintenance</t>
     </r>
   </si>
   <si>
     <t>Definition:
-Incentive and Performance Structures refer to the requirement that public authorities establish financial, strategic, and performance-related mechanisms that motivate, reward, or compel organizations and sub-organizations to adopt, implement, and sustain interoperability arrangements.
-Interoperability is promoted when compliance with shared standards, semantic constructs, and coordination frameworks is reinforced through budgetary allocation rules, funding conditions, performance indicators, portfolio management criteria, or accountability regimes. The focus is not on governance authority itself, but on the incentive logic that shapes organizational behavior and prioritization decisions.
-This requirement applies within individual public organizations, across sectors, across administrative levels, and between Member States wherever interoperability depends on sustained organizational commitment and resource allocation.
+Semantic Construct Design and Maintenance refer to the requirement that public authorities must establish structured processes for the systematic design, specification, revision, and long-term maintenance of shared semantic artefacts used for interoperability.
+This requirement asserts that interoperability is promoted when semantic constructs such as conceptual models, vocabularies, ontologies, taxonomies, metadata schemas, and reference data are deliberately engineered, formally documented, version-controlled, and periodically updated through institutionalized processes.
+Semantic construct design concerns the initial modeling and formalization of shared meaning. Maintenance concerns controlled evolution, including versioning, change management, impact analysis, and alignment with related artefacts over time.
+The focus is on lifecycle management of meaning-bearing artefacts as organizational responsibilities.
 Inclusion Criteria:
-This requirement applies when interoperability requires:
-• Financial incentives or funding conditions linked to standard adoption or compliance.
-• Performance indicators or KPIs measuring interoperability outcomes.
-• Budget allocation mechanisms prioritizing interoperable solutions.
-• Portfolio or investment governance rewarding cross-organizational alignment.
-• Sanctioning or corrective measures for non-compliance.
-• Strategic prioritization of interoperability within planning cycles.
-• Performance-based reporting mechanisms tied to interoperability goals.
+Code when a source explicitly requires that:
+•Shared semantic artefacts must be systematically designed or modeled.
+•Formal modeling methodologies are mandated for construct development.
+•Versioning and change management procedures exist for semantic artefacts.
+•Impact analysis is required before modifying shared definitions or models.
+•Maintenance procedures ensure semantic consistency over time.
+•Revision cycles are institutionalized for shared vocabularies or schemas.
+•Documentation standards govern the specification of semantic constructs.
+•Long-term stewardship responsibilities are assigned for construct upkeep.
 Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-• Formal governance structures without reference to incentive or performance mechanisms.
-• Operational implementation of standards without motivational or funding components.
-• Capability development without linkage to performance or resource allocation.
-• Legal mandates without performance or incentive structures.
-• General political commitment without structural reinforcement mechanisms.
+Do not code when:
+•Standards are merely selected or adopted without reference to their design or maintenance.
+•Operational use of constructs is described without lifecycle management.
+•Governance authority is mentioned without reference to artefact design or evolution.
+•Evaluation mechanisms are described without connection to construct revision.
+•Technical encoding formats are specified without organizational responsibility for construct development.
+•Informal updates occur without institutionalized change procedures.
 Theoretical Grounding:
-Institutional theory highlights that formal rules alone are insufficient; incentive and performance structures shape organizational behavior and strategic prioritization. Governance research demonstrates that resource allocation and performance measurement mechanisms strongly influence cross-organizational coordination outcomes. Interoperability studies indicate that adoption gaps often persist when standards lack financial, strategic, or performance-based reinforcement mechanisms.</t>
-  </si>
-  <si>
-    <t>Definition:
-Process Alignment and Formalization refer to the requirement that operational processes, decision procedures, and coordination routines within and across public authorities must be explicitly defined, harmonized, and institutionalized to prevent conceptual and semantic misalignment.
-This requirement asserts that interoperability is promoted when organizations follow aligned and documented procedures for activities such as standard development, model change management, data exchange, validation, quality control, and compliance review. The focus is on the structural alignment of how work is performed, not merely on the existence of governance roles or standards.
-Process alignment may apply within a single public organization, across multiple authorities within a Member State, or between Member States, where consistent procedures are necessary to ensure coherent interpretation and implementation of shared specifications.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-• Harmonized business processes across organizations or administrative levels.
-• Shared procedures for developing, adopting, or updating standards.
-• Structured change management processes with cross-organizational coordination.
-• Aligned data submission, validation, or quality assurance procedures.
-• Standardized documentation or modeling practices.
-• Joint decision-making cycles or review mechanisms.
-• Formalized escalation, dispute resolution, or alignment procedures.
-• Consistent lifecycle management processes across authorities.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-• The definition of governance roles or mandates without reference to operational procedures.
-• The existence or selection of standards without reference to aligned processes.
-• Purely technical orchestration of systems.
-• Legal harmonization without operational alignment.
-• Internal optimization of processes that has no cross-boundary relevance.
-• Informal coordination not embedded in structured procedures.
-Theoretical Grounding:
-Process integration research emphasizes that interoperability depends on alignment of administrative and operational procedures rather than solely on shared technical artifacts (Scholl &amp; Klischewski, 2007).
-Organizational interoperability measurement approaches identify harmonized processes and structured coordination routines as core maturity dimensions (Maheshwari &amp; Janssen, 2012).
-The European Interoperability Framework (2017) explicitly recommends documenting and aligning business processes to enable cross-organizational and cross-border interoperability.</t>
+Ontology engineering literature emphasizes the need for formalized development methodologies and controlled evolution processes to prevent semantic drift (Guarino, 1998; Euzenat &amp; Shvaiko, 2013).
+Interoperability governance research shows that uncontrolled modification of shared artefacts leads to divergence and fragmentation across organizations (Kubicek, Cimander, &amp; Scholl, 2011).
+The European Interoperability Framework (European Commission, 2017) and EOSC highlight lifecycle governance and maintenance of shared semantic artefacts as critical for sustainable cross-domain interoperability.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Standardization and Semantic Control</t>
+    </r>
   </si>
   <si>
     <t>Definition:
@@ -970,7 +1400,11 @@
 •Ad hoc mappings or translations not institutionally governed.
 •General references to “using standards” without structured control mechanisms.
 Theoretical Grounding:
-Interoperability maturity research highlights that structured governance of shared artifacts is necessary for sustained organizational alignment (Guédria, Naudet, &amp; Chen, 2008). Holistic interoperability assessment literature emphasizes systematic control across administrative levels and contexts (Da Silva Serapião Leal, Guédria, &amp; Panetto, 2019). The European Interoperability Framework (2017) calls for structured selection, monitoring, and compliance processes for standards and specifications in cross-government and cross-border settings.</t>
+Interoperability governance research highlights that structured management and sustained governance of shared artifacts across administrative levels is necessary to maintain alignment and ensure sustainability (Wimmer, Boneva, &amp; di Giacomo, 2018). Federated ecosystem literature emphasizes the critical need for common repositories of semantic artifacts backed by clear governance frameworks and systematic monitoring procedures (EOSC, 2021; Wimmer et al., 2018). Furthermore, the European Interoperability Framework (2017) calls for structured selection, monitoring, and compliance processes for standards and specifications in cross-government and cross-border settings:
+EIF Recommendation 21: Put in place processes to select relevant standards and specifications, evaluate them, monitor their implementation, check compliance and test their interoperability.
+EIF Recommendation 22: Use a structured, transparent, objective and common approach to assessing and selecting standards and specifications. Take into account relevant EU recommendations and seek to make the approach consistent across borders.
+EIF Recommendation 23: Consult relevant catalogues of standards, specifications and guidelines at national and EU level, in accordance with your NIF and relevant DIFs, when procuring and developing ICT solutions.
+EIF Recommendation 24: Actively participate in standardisation work relevant to your needs to ensure your requirements are met.</t>
   </si>
   <si>
     <r>
@@ -980,8 +1414,36 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Undecided</t>
-    </r>
+      <t>Requirement: Organizational: Structural Process Alignment</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Structural and Procedural Alignment refers to the requirement that public authorities institutionalize coherent organizational structures and aligned operational procedures to enable interoperability.
+Interoperability is promoted when organizations are structurally configured and procedurally aligned to operate in coordinated multi-level and cross-domain environments, within a single authority and across organizational, sectoral, administrative, or national boundaries. This includes integration into national or supranational strategies and infrastructures, as well as harmonized business processes, change management routines, and coordinated lifecycle management of shared semantic assets.
+Inclusion Criteria:
+This requirement applies when interoperability is said to require:
+• Institutional coordination across organizational or administrative boundaries.
+• Structural alignment across local, regional, national, or supranational levels.
+• Cross-border interoperability arrangements.
+• Alignment with national or European digital strategies or infrastructures.
+• Harmonized business processes within or across authorities.
+• Shared procedures for standard development, adoption, and change management.
+• Aligned data submission, validation, or quality assurance procedures.
+• Standardized documentation, review, or lifecycle management practices.
+• Formalized joint decision-making or escalation mechanisms.
+Exclusion Criteria:
+This requirement does not apply when the statement concerns:
+• Internal improvements without broader coordination relevance.
+• Purely technical connectivity.
+• Legal mandates without structural or procedural embedding.
+• Governance roles without operational alignment.
+• Selection of standards without coordinated implementation.
+• Informal, non-institutionalized collaboration.
+Theoretical Grounding:
+Interorganizational integration research demonstrates that interoperability depends on structural coordination beyond technical exchange (Pardo &amp; Tayi, 2007). Process integration studies show that misaligned administrative routines undermine interoperability (Scholl &amp; Klischewski, 2007). Organizational interoperability maturity models identify harmonized processes and institutionalized coordination as core dimensions (Maheshwari &amp; Janssen, 2014).
+Scholl (2005). In “Interoperability in e-Government: More than Just Smart Middleware,” Scholl argues unequivocally that purely technical middleware is insufficient. He emphasizes that information exchange between public agencies encounters deliberately erected organizational barriers, and that rigorous alignment of organizational and social processes is required for interoperability to succeed.
+The European Interoperability Framework (European Commission, 2017) positions structural and procedural alignment as foundational conditions for sustainable public-sector interoperability.</t>
   </si>
   <si>
     <r>
@@ -995,6 +1457,36 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Semantic requirements are the normative conditions that data, metadata, and semantic artefacts must satisfy in order to ensure shared meaning, interpretability, traceability, and reliable reuse across organizational, disciplinary, or system boundaries.
+They extend the FAIR principles (Wilkinson et al., 2016), including their elaboration in FAIR 2.0, and are further operationalized within federated infrastructures such as EOSC. Semantic requirements concern the explicit articulation of meaning, the use of shared semantic standards, structured and persistent metadata, formal representation syntax, documented provenance, and adequate data quality.
+Semantic requirements operate at the level of meaning and interpretation. They ensure that data exchanged across systems can be consistently understood beyond their original production context and can be responsibly integrated and reused.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•The meaning of data or metadata must be clearly specified or described.
+•Shared vocabularies, ontologies, or semantic standards are required.
+•Metadata are structurally defined to support interpretation.
+•Provenance information is required to reconstruct origin or transformation history.
+•Data quality adequacy is mandated to ensure reliable interpretation.
+•Formal representation syntax is required to encode semantic artefacts.
+•Semantic artefacts must be maintained or governed to ensure cross-community interpretability.
+•Ecosystem-level semantic consistency (e.g., EOSC common semantic artefacts) is required.
+Exclusion Criteria:
+Do not code when:
+•Only technical connectivity or communication protocols are described without semantic implications.
+•Organizational governance mechanisms are discussed without reference to meaning or interpretation.
+•Legal conditions (e.g., licensing) are described without semantic relevance.
+•Discovery, indexing, or accessibility mechanisms are specified without reference to meaning.
+•Data quality improvement processes are described without connection to semantic interpretability.
+Literature:
+•FAIR Guiding Principles (Wilkinson et al., 2016):
+•FAIR 2.0 (Vogt et al., 2024): distinction between entity-level and proposition-level interoperability; emphasis on semantic artefact alignment and cross-schema mappings.
+•EOSC Interoperability Framework (2021–2023): requirement for common semantic artefacts, shared metadata standards, federation mechanisms, sustainability of semantic infrastructures, and cross-community interpretability.
+•Guarino (1998): ontological commitment and explicit semantic specification in information systems.
+•Euzenat &amp; Shvaiko (2013): ontology matching and semantic alignment as core interoperability mechanisms.
+•Peristeras et al. (2009): conceptual and semantic layers of interoperability in model-driven architectures.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1002,8 +1494,655 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Requirement: Semantic: Adequate Data Quality</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data resources must meet explicitly defined and domain-appropriate quality criteria in order to support reliable interpretation, integration, and reuse across organizational or system boundaries. Data quality is understood as the degree to which data are fit for their intended interoperable use.
+Adequate data quality includes, as contextually relevant, dimensions such as accuracy, completeness, consistency, timeliness, validity, and coherence with domain constraints.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data conform to defined quality criteria or validation rules.
+•Data satisfy accuracy, completeness, or consistency thresholds.
+•Formal validation, conformance testing, or quality assurance mechanisms are mandated.
+•Data are required to be “fit for purpose” in an interoperable context.
+•Semantic consistency with defined domain constraints is required.
+Exclusion Criteria:
+Do not code when:
+•Only documentation of quality (without requirement of adequacy) is discussed.
+•Governance or provenance mechanisms are mentioned without reference to quality performance.
+•Quality improvement processes are described without normative quality criteria.
+•Accessibility or metadata richness is discussed without reference to intrinsic data quality.
+Literature:
+•FAIR R1 (Wilkinson et al., 2016): metadata must describe attributes relevant to reuse, implicitly presupposing adequacy for reuse.
+•Wang &amp; Strong (1996): data quality dimensions and “fitness for use” framework.
+•Batini &amp; Scannapieco (2016): methodological foundations of data quality management.
+•FAIR 2.0 (Vogt et al., 2024) further strengthens this perspective by introducing an explicit extension (Principle R1.4), which requires metadata to specify the certainty level of semantic content in order to enable trustworthy reuse, thereby formulating a concrete requirement for adequate data and metadata quality within semantic networks.
+EIF Recommendation 40:  Create and follow data quality assurance plans for base registries and related master data.
+EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Existence and Use of Domain-Relevant Semantic Standards</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+For semantic interoperability to be achieved, domain-relevant semantic standards must exist and be explicitly referenced in the specification, modeling, or representation of data and metadata. These standards provide shared conceptual definitions, constraints, and semantic structures recognized within a disciplinary, sectoral, or institutional community.
+Domain-relevant semantic standards are defined here as formally specified and publicly documented conceptual models, vocabularies, ontologies, or reference schemas that structure meaning within a particular domain of practice.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data or metadata reference recognized domain-specific semantic standards.
+•Sectoral ontologies, vocabularies, or reference models are used or mandated.
+•Domain-level conceptual harmonization is grounded in formally defined standards.
+•Interoperability is supported through alignment with community-endorsed semantic artefacts.
+Exclusion Criteria:
+Do not code when:
+•Conceptual models are organization-specific without external recognition.
+•Standards are mentioned only generically without domain specification.
+•Alignment concerns only technical formats or transport protocols.
+•Informal consensus or practice is referenced without formal standardization.
+Literature:
+•FAIR R1.3 (Wilkinson et al., 2016): use of community standards for metadata and data.
+•Peristeras et al. (2009), in “Model-driven eGovernment Interoperability,” provide a comprehensive analysis of domain-specific semantic standards—such as the Governance Enterprise Architecture (GEA)—and ontologies designed to standardize e-government, thereby offering a strong empirical and theoretical foundation for requiring domain-relevant semantic standards within the public sector.
+•Wimmer et al. (2018): governance and institutionalization of interoperability standards.
+•Guarino (1998): formal ontologies as shared domain conceptualizations.
+•EOSC: “common semantic artefacts across communities”
+Links to EIF Recommendation 4:  Give preference to open specifications, taking due account of the coverage of functional needs, maturity and market support and innovation.
+EIF Recommendation 7:  Reuse and share information and data when implementing European public services, unless certain privacy or confidentiality restrictions apply.
+Links to EIF: Recommendation 9:  Ensure data portability, namely that data is easily transferable between systems and applications supporting the implementation and evolution of European public services without unjustified restrictions, if legally possible. 
+EIF Recommendation 33:  Use open specifications, where available, to ensure technical interoperability when establishing European public services.
+Links to EIF Recommendation 34:  Use the conceptual model for European public services to design new services or reengineer existing ones and reuse, whenever possible, existing service and data components.
+Links to EIF Recommendation 35:  Decide on a common scheme for interconnecting loosely coupled service components and put in place and maintain the necessary infrastructure for establishing and maintaining European public services.
+Links to EIF Recommendation 38:  Develop interfaces with base registries and authoritative sources of information, publish the semantic and technical means and documentation needed for others to connect and reuse available information.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Existence of Meta-data</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Explicit Provenance Documentation</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be accompanied by structured and sufficiently detailed documentation of their origin, creation process, transformation history, and responsible actors. Provenance information must enable reconstruction of how a data resource came into existence and how it has been modified over time.
+Provenance is defined here as the formally recorded account of the source, production context, processing steps, and custodianship of a data resource, such that its reliability, interpretation, and suitability for reuse can be assessed.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•The origin or source system of data is documented.
+•Creation dates, modification dates, or version histories are recorded.
+•Transformations, aggregations, or processing steps are specified.
+•Responsible individuals, organizations, or systems are identified.
+•Provenance information is linked to the corresponding data or metadata resource.
+Exclusion Criteria:
+Do not code when:
+•Only general statements about data reliability are made without documented lineage.
+•Quality characteristics are described without reference to origin or transformation history (this belongs under the data quality code).
+•Governance roles are discussed without documenting data lineage.
+•Metadata are present but do not include origin or transformation information.
+Literature:
+•FAIR R1.2 (Wilkinson et al., 2016): (meta)data are associated with detailed provenance.
+•Buneman, Khanna &amp; Tan (2001): data provenance in databases.
+•Moreau &amp; Missier (2013): W3C PROV model and formal provenance representation.
+•Wang &amp; Strong (1996): fitness for use requires knowledge of origin and production context.
+•Peristeras et al. (2009): cross-domain interoperability requires traceability of information sources.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Formal and Shared Syntax for Knowledge Representation</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be expressed using formally defined, publicly specified, and widely recognized syntactic languages for knowledge representation, in order to ensure structurally consistent and interoperable encoding of meaning across systems.
+Syntax is defined here as the formally specified structure and grammar through which information and semantic constructs are represented. The requirement concerns the use of shared and standardized representation languages that enable consistent parsing, validation, and exchange of semantically structured information.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data or metadata are represented using formally specified syntactic languages (e.g., RDF, OWL, XML Schema).
+•Representation languages are publicly documented and standardized.
+•Semantic artefacts (e.g., ontologies, vocabularies) are encoded in shared formal syntaxes.
+•Structural constraints or schemas are formally defined.
+Exclusion Criteria:
+Do not code when:
+•Meaning is expressed solely through natural language or free text without formal structure.
+•Proprietary or undocumented syntactic formats are used.
+•Conceptual alignment is discussed without reference to formal representation syntax.
+•Only technical transport protocols are specified without representation structure.
+Literature:
+•FAIR I1, I2, R1.3 (Wilkinson et al., 2016): use of formal, accessible, shared representation languages and vocabularies.
+•Guarino (1998): formal ontology and the role of explicit representation structures in information systems.
+•Euzenat &amp; Shvaiko (2013): ontology matching presupposes formally structured representations.
+•Peristeras et al. (2009): syntactic interoperability as prerequisite for semantic interoperability.
+EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Modelling Flexibility</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Mutlilingual Representation</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Multilingual Semantic Representation refers to the requirement that information systems, data models, and semantic artefacts must support representation and interpretation of information across multiple natural languages in order to enable cross-border and cross-community interoperability.
+This requirement asserts that semantic interoperability in multi-lingual governance contexts depends on the capability to represent, link, and present concepts, labels, and descriptive information in more than one language, while preserving conceptual equivalence and interpretive consistency.
+The focus is not merely on user-interface translation, but on structurally embedding multilingual support within semantic artefacts and system architectures so that meaning remains stable across linguistic contexts.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Information systems support multiple natural languages.
+•Semantic artefacts include multilingual labels or descriptions.
+•Conceptual models accommodate language-specific representations.
+•Cross-border services provide multilingual data interpretation.
+•Controlled vocabularies include multilingual equivalents.
+•Multilingual metadata are mandated.
+•Concept identifiers are separated from language-specific labels.
+•Language support is treated as a structural interoperability requirement.
+Exclusion Criteria:
+Do not code when:
+•Only front-end user interface translation is mentioned without semantic implications.
+•Accessibility for persons with disabilities is discussed without linguistic representation.
+•Legal translation requirements are described without system-level semantic embedding.
+•Cultural adaptation is referenced without structured multilingual representation.
+•Data are translated informally without controlled semantic linkage.
+Theoretical Grounding:
+Ontology and vocabulary engineering literature distinguishes between language-independent conceptual identifiers and language-dependent lexicalizations, highlighting the importance of separating concept identity from linguistic expression (Guarino, 1998).
+Multilingual terminology management research shows that semantic interoperability across jurisdictions requires controlled vocabularies with multilingual correspondences to prevent interpretive drift.
+EIF Recommendation 16:  Use information systems and technical architectures that cater for multilingualism when establishing a European public service. Decide on the level of multilingualism support based on the needs of the expected users.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Rich and Accurate Conceptual Description</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Data and metadata must be described with a plurality of accurate, relevant, and sufficiently detailed attributes that make their meaning understandable within and beyond their original context of production. Descriptions must be precise enough to prevent misinterpretation and to support consistent use across organizational or disciplinary boundaries.
+This requirement concerns the substantive adequacy and clarity of descriptive attributes, rather than the formalization of conceptual models.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data or metadata are richly described with multiple relevant attributes.
+•Descriptions include contextual qualifiers necessary for correct interpretation (e.g., scope, units, temporal coverage, intended meaning).
+•Definitions are accurate, non-ambiguous, and sufficiently detailed for reuse.
+•Descriptive attributes reduce interpretive variability across contexts.
+Exclusion Criteria:
+Do not code when:
+•Descriptions are minimal, generic, or underspecified.
+•Terminology is used without clarification of meaning.
+•Only syntactic schema structures are defined without descriptive attributes.
+•Conceptual modeling is required in a formal ontological sense (this belongs under syntactic or semantic standard codes).
+Literature:
+•FAIR R1 (Wilkinson et al., 2016): meta(data) are richly described with a plurality of accurate and relevant attributes.
+•Park (2006): semantic interoperability requires sufficiently detailed descriptive information to reduce interpretive ambiguity.
+•Peristeras et al. (2009): interoperability depends on shared and sufficiently specified information structures.
+•Batini &amp; Scannapieco (2016): completeness and adequacy as core dimensions of information quality.
+•EOSC: “common explicit definitions” + “clear and precise definitions for the concepts” + “Every semantic artefact that is being maintained in EOSC must have sufficient associated documentation”
+Links to EIF Recommendation 38:  Develop interfaces with base registries and authoritative sources of information, publish the semantic and technical means and documentation needed for others to connect and reuse available information.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Semantic Mapping and Alignment capabilities</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Semantic Mapping and Alignment Capabilities refer to the requirement that an interoperability ecosystem must enable the formal specification, representation, and maintenance of explicit correspondences between heterogeneous semantic artefacts in order to achieve semantic interoperability across systems, domains, or jurisdictions.
+This requirement asserts that when multiple conceptual models, vocabularies, ontologies, or metadata schemas coexist, interoperability depends on the capability to establish structured semantic relationships—such as equivalence, subsumption, or transformation rules—between their respective constructs.
+The focus is on the availability and institutionalization of alignment mechanisms that relate distinct artefacts after their independent development. It concerns post hoc semantic correspondence rather than ex ante modelling harmonization.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Correspondences between heterogeneous semantic artefacts must be specified.
+•Ontologies or schemas must be aligned to enable interoperability.
+•Cross-schema mappings or crosswalks are required.
+•Transformation rules between semantic representations must be defined.
+•Equivalence, subsumption, or refinement relationships between constructs must be formally represented.
+•Legacy and target models must be related through structured alignment artefacts.
+•Semantic mediation relies on formally specified mapping relationships.
+•Multi-standard environments require semantic correspondence mechanisms.
+Exclusion Criteria:
+Do not code when:
+•A single shared semantic model is mandated (belongs under Semantic Modelling Alignment).
+•Only syntactic format conversion is described without semantic correspondence.
+•Modelling guidelines are harmonized at design stage.
+•Governance of standard selection is discussed without mapping.
+•Runtime technical infrastructure is described without reference to semantic correspondences.
+•Informal interpretation between artefacts is mentioned without explicit mapping artefacts.
+Theoretical Grounding:
+Ontology alignment literature defines alignment as the establishment of formal correspondences between entities of distinct ontologies to enable interoperability (Euzenat &amp; Shvaiko, 2013).
+Model-driven interoperability research demonstrates that heterogeneous conceptual models require explicit relational mappings to prevent semantic ambiguity (Peristeras et al., 2009).
+The FAIR principles, particularly I1–I2 and R1.3 (Wilkinson et al., 2016), imply the necessity of semantic compatibility across standards, while FAIR 2.0 emphasizes interoperability in multi-standard environments requiring schema crosswalks.
+Ontology engineering theory highlights that explicit ontological commitment and formal correspondence specification are prerequisites for meaningful integration across conceptual systems (Guarino, 1998).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Semantic Modelling Alignment</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Semantic Modelling Alignment refers to the requirement that participating actors adopt and apply a shared conceptualization approach, modelling methodology, naming conventions, abstraction principles, and structural design logic when developing semantic artefacts.
+This requirement asserts that semantic interoperability is strengthened when semantic artefacts are engineered according to harmonized modelling strategies across organizational, sectoral, or jurisdictional boundaries. The objective is to prevent structural divergence and conceptual inconsistency at design time, thereby reducing interpretive ambiguity and minimizing the need for subsequent mapping or mediation.
+Semantic modelling alignment concerns ex ante harmonization of modelling practice rather than post hoc correspondence between heterogeneous artefacts. It focuses on methodological convergence in how meaning is constructed, structured, and formalized.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Participating actors adopt a common conceptual modelling methodology.
+•Agreed abstraction levels or modelling granularity are defined.
+•Common structuring principles govern entity, attribute, and relation design.
+•Modelling guidelines or design rules are harmonized across organizations.
+•Conceptual modelling follows a shared reference architecture or meta-model.
+•Model development is coordinated to ensure structural coherence.
+•A unified modelling grammar or pattern language is prescribed.
+•Divergent modelling approaches are to be avoided through harmonized design principles.
+The emphasis must be on harmonization of modelling strategy at design stage, not on technical encoding or legal authorization.
+Exclusion Criteria:
+Do not code when:
+•The statement concerns post hoc mapping or cross-schema alignment (belongs under Semantic: Alignment and Mapping Capability).
+•Only syntactic representation formats are specified (belongs under Formal and Shared Syntax).
+•Governance structures are described without modelling methodology.
+•A single shared artefact is mandated without reference to modelling principles.
+•Informal conceptual agreement is mentioned without structured modelling strategy.
+•Technical tooling is discussed without methodological alignment.
+•Data quality requirements are specified without reference to modelling approach.
+Theoretical Grounding:
+•FAIR 2.0 (Vogt et al., 2024): emphasizes interoperability across semantic layers and the need to support mappings and cross-schema interoperability in heterogeneous environments.
+•FAIR I1–I2, R1.3 (Wilkinson et al., 2016): formal languages, shared vocabularies, and community standards as prerequisites, but not sufficient in multi-standard contexts.
+•Euzenat &amp; Shvaiko (2013): alignment as explicit correspondences between ontologies enabling interoperability.
+•Ontology engineering research emphasizes that shared ontological commitments and explicit modelling principles are necessary to ensure semantic coherence across systems (Guarino, 1998).
+•Model-driven interoperability literature demonstrates that structural divergence often originates from inconsistent modelling strategies rather than absence of mapping mechanisms (Peristeras et al., 2009).
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Structured and Independently Accessible Metadata</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data resources must be accompanied by formally structured metadata that provide explicit descriptions of their content, context, structure, provenance, and conditions of use. These metadata must remain retrievable independently of the data objects they describe.
+Metadata are defined here as structured representations about data resources that enable identification, interpretation, evaluation, and responsible reuse across organizational or institutional boundaries. Metadata include descriptive, contextual, semantic, and governance-relevant information.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data resources are described using a formally defined metadata schema or model.
+•Metadata provide contextual information necessary for correct interpretation (e.g., scope, temporal coverage, conceptual definitions).
+•Metadata document provenance, custodianship, versioning, or usage conditions.
+•Metadata remain available even when the underlying data are restricted, archived, or no longer accessible.
+•Metadata are explicitly linked to the data resources they describe.
+Exclusion Criteria:
+Do not code when:
+•Descriptive information is informal, narrative, or ad hoc without structural specification.
+•Contextual information is embedded implicitly in data without explicit modeling.
+•Metadata are mentioned only as optional documentation without normative requirement.
+•Only technical storage formats are specified without requirement for structured description.
+Literature:
+•FAIR F2, F3, A2 (Wilkinson et al., 2016): rich metadata, explicit linkage to data, and persistence of metadata even if data are unavailable.
+•Guarino (1998): formal ontology and explicit conceptual specification in information systems.
+•Guizzardi &amp; Guarino (2024): ontological unpacking and semantic explicitness.
+•Peristeras et al. (2009): model-driven interoperability and structured metadata as enablers of cross-domain integration.
+EIF. Recommendation 39:  Match each base registry with appropriate metadata including the description of its content, service assurance and responsibilities, the type of master data it keeps, conditions of access and the relevant licences, terminology, a glossary, and information about any master data it uses from other base registries.
+EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Requirement: Technical</t>
     </r>
+  </si>
+  <si>
+    <t>Definition:
+Technical requirements are the normative conditions that data, metadata, semantic artefacts, and interoperability services must satisfy in order to enable reliable exchange, retrieval, discovery, and sustained operation across heterogeneous systems and organizational boundaries.
+They operationalize the technical layer of interoperability by specifying conditions for persistent identification, standardized access protocols, searchable indexing infrastructures, common metadata standards, shared semantic tooling, and sustainable infrastructure components.
+Grounded in the FAIR principles (Wilkinson et al., 2016), extended in FAIR 2.0, and contextualized in federated ecosystems such as EOSC, technical requirements ensure that interoperability is not merely conceptual but infrastructurally and operationally feasible.
+Technical requirements concern the structural, protocol-level, infrastructural, and architectural conditions under which semantic and organizational interoperability can function.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Persistent and globally unique identifiers are used.
+•Data or metadata are accessible via standardized and documented communication protocols.
+•Searchable catalogues, registries, or indexing infrastructures are established.
+•Federation or harvesting mechanisms interconnect distributed repositories.
+•A shared metadata standard (with governed profiling mechanisms) is defined.
+•Common tooling is provided for semantic artefact creation and maintenance.
+•Infrastructure components ensure sustained availability and continuity of services.
+•Architectural building blocks are defined to support cross-system interoperability.
+Exclusion Criteria:
+Do not code when:
+•Only meaning, conceptual definitions, or semantic alignment are discussed without technical implementation implications (belongs under Semantic).
+•Governance, institutional arrangements, or legal frameworks are described without infrastructural or protocol-level implications.
+•Licensing or copyright conditions are specified without technical relevance.
+•Data quality criteria are defined without reference to technical enablement.
+Literature:
+•FAIR Guiding Principles (Wilkinson et al., 2016):
+•FAIR 2.0 (Vogt et al., 2024): entity-level and proposition-level interoperability requiring technical schema crosswalks and interoperable services.
+•EOSC Interoperability Framework (2021–2023):
+•Peristeras et al. (2009): technical interoperability as standardized communication and model-driven architectural capability.
+•Wimmer et al. (2018): technical and infrastructural foundations of interoperability governance.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Existence of Shared Technical Standards</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Existence of Shared Technical Standards refers to the requirement that interoperable public services must rely on commonly agreed and publicly available technical specifications—preferably open specifications—to ensure compatibility of systems, interfaces, protocols, and infrastructural components across organizational and jurisdictional boundaries.
+This requirement asserts that technical interoperability depends on the availability and adoption of shared standards governing communication protocols, data exchange formats, interface definitions, security mechanisms, and infrastructural interaction patterns.
+The focus is on the presence and use of open, consensus-based technical specifications that enable predictable system-level interoperability, independent of vendor-specific implementations.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Open specifications be used for interoperability.
+•Common technical standards govern system interfaces or protocols.
+•Shared communication or transport standards are mandated.
+•Interoperability relies on standardized technical formats.
+•Technical compatibility across systems is ensured through agreed standards.
+•Vendor-neutral technical specifications are required.
+•Public services must adopt commonly recognized ICT standards.
+•Cross-border technical interoperability depends on open specifications.
+Exclusion Criteria:
+Do not code when:
+•Only semantic standards or vocabularies are discussed (belongs under Semantic).
+•Governance of standard selection processes is described without technical specification content (belongs under Organizational: Standardization and Semantic Control).
+•Legal mandates for standard adoption are discussed without technical focus.
+•Technical tooling is mentioned without reference to shared standards.
+•Interface design is described without standardized specification.
+Theoretical Grounding:
+The European Interoperability Framework emphasizes the use of open specifications to guarantee technical interoperability and reduce vendor lock-in.
+Technical interoperability literature identifies shared standards for communication, data formats, and interface definitions as foundational preconditions for cross-system compatibility (Peristeras et al., 2009).
+EIF Recommendation 33:  Use open specifications, where available, to ensure technical interoperability when establishing European public services.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Findable, Searchable and Visible</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be structured, registered, and indexed in interoperable discovery infrastructures such that they can be located across organizational and community boundaries. Findability requires not only local indexing but also clearly defined protocols and architectural building blocks that enable federation and harvesting of catalogues and semantic artefact registries.
+Findability is defined here as the ecosystem-level capability to systematically discover data, metadata, and semantic artefacts through searchable resources and federated discovery mechanisms.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data or metadata are registered in searchable catalogues, repositories, or registries.
+•Indexing mechanisms support structured and queryable discovery.
+•Discovery infrastructures allow cross-community or cross-domain search.
+•Federation or harvesting protocols are defined to interconnect multiple catalogues.
+•Architectural components enable interoperability between distributed metadata or semantic artefact registries.
+Exclusion Criteria:
+Do not code when:
+•Only direct retrieval via known identifiers is described without indexing.
+•Discovery is limited to manual browsing or informal exchange.
+•Metadata richness is required without searchable registration.
+•Technical APIs are specified without indexing or discovery functionality.
+•Local cataloguing exists without federated interoperability mechanisms.
+Literature:
+•FAIR F4 (Wilkinson et al., 2016): meta(data) are registered or indexed in a searchable resource.
+•FAIR F2 (Wilkinson et al., 2016): rich metadata as prerequisite for effective discovery.
+•EOSC Interoperability Framework (2021–2023): need for federated discovery, harvesting protocols, and architectural building blocks for semantic artefact catalogues.
+•Peristeras et al. (2009): interoperability requires structured information infrastructures enabling cross-domain discovery.
+Links to EIF: Recommendation 5:  Ensure internal visibility and provide external interfaces for European public services.
+Links to EIF Recommendation 44:  Put in place catalogues of public services, public data, and interoperability solutions and use common models for describing them.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Persistent and Globally Unique Identification</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition
+All data objects, metadata records, and semantic artefacts must be assigned globally unique, persistent, and resolvable identifiers to enable stable reference, citation, and machine-mediated linking across systems and domains.
+Inclusion Criteria:
+•Explicit requirement for persistent identifiers (e.g., URI, DOI, Handle).
+•Machine-resolvable identifiers.
+•Explicit linkage between identifiers of data and associated metadata.
+Exclusion Criteria
+•Local, system-internal, or temporary identifiers.
+•Identifiers without persistence guarantees.
+•Implicit references without global uniqueness.
+Literature:
+•FAIR F1, F3, A1 (Wilkinson et al., 2016).
+•Guarino (1998), formal ontology and stable reference.
+•Peristeras et al. (2009), model-driven interoperability and identity management.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Presence of Common Semantic Tooling</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+A federated or multi-domain ecosystem must provide and promote common, principled tooling for the creation, maintenance, governance, and use of semantic artefacts such as ontologies and metadata schemas. Such tooling must support formally specified representation models and ensure structural and semantic consistency across communities.
+Common semantic tooling is defined here as a shared set of methods, platforms, and modeling environments that enable interoperable development and lifecycle management of semantic artefacts, thereby reducing heterogeneity in representation practices.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Shared tools or platforms are established for ontology or metadata schema development.
+•Formal modeling environments are mandated to ensure semantic precision.
+•Tooling supports versioning, governance, or controlled evolution of semantic artefacts.
+•Heterogeneity in representation practices is addressed through harmonized tool support.
+•Formal semantic representation is preferred over informal or purely diagrammatic modeling.
+Exclusion Criteria:
+Do not code when:
+•Only the existence of semantic standards is discussed without tooling support.
+•Individual communities independently select tools without coordination.
+•UML or other diagrammatic models are mentioned without requirement for formal semantic rigor.
+•Governance structures are described without reference to technical tooling.
+Literature:
+•EOSC Interoperability Framework (2021–2023): need for principled approaches and common tooling for semantic artefact management.
+•FAIR I1, I2 (Wilkinson et al., 2016): use of formal, shared knowledge representation languages.
+•Guarino (1998): importance of formal ontology in information systems.
+•Euzenat &amp; Shvaiko (2013): ontology engineering and alignment require formal representation support.
+•Wimmer et al. (2018): governance and infrastructure for interoperable semantic artefacts.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Security and Privacy</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Security and Privacy Assurance Framework refers to the requirement that interoperable public services must operate within a coherent framework of technical, organizational, and procedural safeguards that ensure secure, trustworthy, and legally compliant data exchange across administrative boundaries.
+This requirement asserts that sustainable interoperability depends on systematically defined security and privacy principles, risk-based protection measures, access control mechanisms, and trusted identity and authentication services. Secure interoperability requires not only technical controls but also structured processes and governance arrangements that manage risks and ensure compliance with relevant legislation.
+The focus is on the structured integration of security and privacy into interoperability architectures and service design, rather than on isolated technical safeguards.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•A common security and privacy framework be defined.
+•Secure and trustworthy data exchange mechanisms be established.
+•Access control or authorization mechanisms be implemented.
+•Privacy protection be embedded in interoperability architectures.
+•Risk management processes guide service security measures.
+•Trust services (e.g., eID, electronic signatures, trust services) be used to secure interactions.
+•Security measures be tailored to service-specific risk profiles.
+•Authoritative data sources implement controlled access mechanisms.
+•Data exchange comply with relevant privacy and security legislation.
+Exclusion Criteria:
+Do not code when:
+•Only legal data protection obligations are discussed without architectural or process implications (belongs under Legal: Public Regulation for Interoperability).
+•Generic references to “trust” are made without security mechanisms.
+•Technical encryption mechanisms are described in isolation without framework context.
+•Organizational governance roles are described without security focus.
+•Data quality or provenance is discussed without privacy or protection implications.
+Theoretical Grounding:
+EIF: Recommendation 15:  Define a common security and privacy framework and establish processes for public services to ensure secure and trustworthy data exchange between public administrations and in interactions with citizens and businesses.
+EIF. Recommendation 37:  Make authoritative sources of information available to others while implementing access and control mechanisms to ensure security and privacy in accordance with the relevant legislation.
+EIF Recommendation 46:  Consider the specific security and privacy requirements and identify measures for the provision of each public service according to risk management plans.
+EIF Recommendation 47:  Use trust services according to the Regulation on eID and Trust Services as mechanisms that ensure secure and protected data exchange in public services.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Standardized and Formally Governed Accessibility</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Data and metadata must be retrievable through standardized, documented, and interoperable communication protocols that ensure predictable access conditions across organizational and technical boundaries. Where access restrictions apply, authentication and authorization mechanisms must be explicitly specified and governed.
+Accessibility is defined here as the formally regulated capacity to retrieve data or metadata through stable and documented access mechanisms that are independent of ad hoc arrangements.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Data or metadata are accessible via standardized and documented communication protocols.
+•Access mechanisms are openly specified and stable over time.
+•Authentication and authorization procedures are formally described where required.
+•Access conditions, restrictions, or licensing constraints are explicitly articulated.
+•Retrieval does not depend on informal or discretionary arrangements between parties.
+Exclusion Criteria:
+Do not code when:
+•Access is limited to manual request or informal exchange.
+•Access mechanisms are undocumented or proprietary without specification.
+•Retrieval depends solely on organizational discretion without formal protocol.
+•Only internal system connectivity is described without cross-boundary accessibility requirement.
+Literature;
+•FAIR A1, A1.1, A1.2 (Wilkinson et al., 2016): data retrievable by standardized protocols, open and universally implementable, with authentication and authorization where necessary.
+•Peristeras et al. (2009): technical interoperability as standardized communication capability in model-driven architectures.
+•Wimmer et al. (2018): interoperability frameworks and cross-organizational governance of access.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Sustainable and Trusted Infrastructure for Data Availability</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+A federated data ecosystem must include stable, trusted, and sustainably governed infrastructure components that ensure the long-term availability, accessibility, and operational continuity of data and metadata services across communities and domains.
+Infrastructure components are defined here as the technical services, repositories, registries, storage systems, identifier services, and access mechanisms that enable persistent data publication, retrieval, and maintenance over time.
+This requirement operationalizes trust not as a normative claim but as the presence of technically and institutionally supported infrastructure that ensures continuity of service.
+Inclusion Criteria:
+Code when a source explicitly requires that:
+•Persistent repositories or registries are established to host data and metadata.
+•Infrastructure components provide long-term storage and availability guarantees.
+•Service continuity or operational sustainability is mandated.
+•Federated infrastructures ensure cross-community interoperability.
+•Trustworthiness is linked to the presence of certified, governed, or monitored technical services.
+Exclusion Criteria:
+Do not code when:
+•Trust is discussed only in social or reputational terms without infrastructure implications.
+•Sustainability is mentioned without reference to operational technical components.
+•Governance structures are described without technical service provision.
+•Data sharing is discussed without specifying infrastructural support mechanisms.
+Literature:
+•EOSC Interoperability Framework (European Open Science Cloud Association, 2021–2023): trusted and sustainable service ecosystem.
+•FAIR A principles (Wilkinson et al., 2016): accessibility requires stable retrieval mechanisms.
+•Wimmer et al. (2018): interoperability frameworks require sustainable infrastructural arrangements.
+•Peristeras et al. (2009): technical interoperability depends on institutionalized service infrastructures.
+•EOSC: “common reference repositories” + “EOSC should provide support for the maintenance of a repository of semantic artefacts, and a governance framework” 
+EIF Recommendation 6:  Reuse and share solutions, and cooperate in the development of joint solutions when implementing European public services.
+Links to EIF Recommendation 35:  Decide on a common scheme for interconnecting loosely coupled service components and put in place and maintain the necessary infrastructure for establishing and maintaining European public services.
+Links to EIF Recommendation 36:  Develop a shared infrastructure of reusable services and information sources that can be used by all public administrations.
+Links to EIF Recommendation 37:  Make authoritative sources of information available to others while implementing access and control mechanisms to ensure security and privacy in accordance with the relevant legislation.
+Links to EIF Recommendation 38:  Develop interfaces with base registries and authoritative sources of information, publish the semantic and technical means and documentation needed for others to connect and reuse available information.
+Links to EIF Recommendation 39:  Match each base registry with appropriate metadata including the description of its content, service assurance and responsibilities, the type of master data it keeps, conditions of access and the relevant licences, terminology, a glossary, and information about any master data it uses from other base registries.
+Links to EIF Recommendation 44:  Put in place catalogues of public services, public data, and interoperability solutions and use common models for describing them.
+</t>
   </si>
   <si>
     <r>
@@ -1132,7 +2271,7 @@
     </r>
   </si>
   <si>
-    <t>Definition:
+    <t xml:space="preserve">Definition:
 A governance paradigm in which multiple autonomous actors retain authority over their own semantic models, while interoperability is achieved through explicit coordination mechanisms such as shared reference models, mappings, or jointly governed agreements.
 Inclusion criteria
 •Participating actors maintain semantic autonomy.
@@ -1146,7 +2285,8 @@
 •No governance mechanisms exist to coordinate meaning across actors.
 •Interoperability is limited to syntactic or technical compatibility.
 Literature:
-Kubicek 2008 (Governance of interoperability in intergovernmental services: Towards an empirical taxonomy), Scholl and Kischewski 2007</t>
+Kubicek 2008 (Governance of interoperability in intergovernmental services: Towards an empirical taxonomy), Scholl and Kischewski 2007
+</t>
   </si>
   <si>
     <r>
@@ -1338,7 +2478,7 @@
     </r>
   </si>
   <si>
-    <t>Definition:
+    <t xml:space="preserve">Definition:
 Interoperability is achieved through an intermediary mediation logic that reconciles semantic heterogeneity between autonomous models by relying on explicit semantic mappings and executing translation or transformation operations. Mapping provides the declarative specification of semantic correspondences, while translation operationalizes these correspondences through data or message transformation. Together, they constitute a mediation-based interoperability mechanism.
 Inclusion criteria:
 - An explicit mediation logic is present that enables interoperability between heterogeneous semantic models.
@@ -1357,7 +2497,20 @@
    - Euzenat, J. &amp; Shvaiko, P. (2013). Ontology Matching.
    - Doan, A., Halevy, A. &amp; Ives, Z. (2012). Principles of Data Integration.
    - Wache, H. et al. (2001). Ontology-Based Integration of Information — A Survey of Existing Approaches.
-   - Guarino, N. (1998). Formal Ontology and Information Systems.</t>
+   - Guarino, N. (1998). Formal Ontology and Information Systems.
+Vogt Fair2.0: “The federated interoperability approach, on the other hand, assumes that data formats and  schemata have to be adapted dynamically instead of having a predefined super metamodel.” 
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Interoperability Mechanism: Rule-based</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1395,7 +2548,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
+    <t>Definition:
 Situations in which all participating parties commit to a single, comprehensive semantic reality that defines domain concepts, relationships, and constraints across use cases and organizational boundaries.
 Inclusion criteria:
 •One unified semantic or conceptual model governs all participants.
@@ -1409,7 +2562,19 @@
 Literature:
 • Uschold &amp; Gruninger
 • Wache et al. 
-• Kubicek </t>
+• Kubicek 
+In Fair 2.0 by Vogt this level of interoperability is a form of “schema interoperability”</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Level of Shared Meaning: Shared identifiers</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1434,7 +2599,19 @@
 •Purely terminological artifacts without semantic definitions.
 •Upper ontologies or domain-independent foundational models.
 •Claims of full semantic unification across all domains or actors.
-</t>
+Literature:
+In Fair 2.0 by Vogt this level of interoperability is a form of “schema interoperability” on the Core Elements only </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Level of Shared Meaning: Shared Metadata</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1457,7 +2634,9 @@
 Exclusion criteria
 •Explicit definitions of concepts or data elements.
 •Shared semantic models, reference models, or mappings with semantic intent.
-•Constraints or relationships that define conceptual meaning.</t>
+•Constraints or relationships that define conceptual meaning.
+Literature:
+FAIR 2.0 Vogt</t>
   </si>
   <si>
     <r>
@@ -1471,7 +2650,7 @@
     </r>
   </si>
   <si>
-    <t>Definition:
+    <t xml:space="preserve">Definition:
 Situations in which actors adopt a shared upper ontology consisting of a coherent set of foundational entities and explicitly defined relations, forming a unified ontological framework that constrains and aligns multiple domain models.
 Inclusion criteria:
 •An explicit upper or foundational ontology is adopted.
@@ -1482,7 +2661,42 @@
 •Abstract terms are listed without explicit relations.
 •High-level concepts are used informally or heuristically.
 •The artifact functions primarily as a vocabulary, classification, metadata schema, or architectural guideline.
-•Semantic agreement is limited to a single domain or use case..</t>
+•Semantic agreement is limited to a single domain or use case..
+Literature:
+In Fair 2.0 by Vogt this level of interoperability is a form of “schema interoperability” on the Upper semantic realisty only </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: RDF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: UML</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1675,6 +2889,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Type: Agreements</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Type: Assessment tools and Evaluation</t>
     </r>
   </si>
@@ -1720,6 +2945,28 @@
 - Assessment or evaluation instruments whose primary function is measurement rather than guidance or structuring.
 Literature:
 (European Commission EIF Solution Finder), </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Type: Consensus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Type: Documentation</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1840,6 +3087,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Type: Query based</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Type: Semantic Assets</t>
     </r>
   </si>
@@ -1888,30 +3146,21 @@
 Literature:
 (European Commission EIF Solution Finder),  </t>
   </si>
-  <si>
-    <t>Requirement: Organizational: Evaluation and Feedback Mechanisms</t>
-  </si>
-  <si>
-    <t>Requirement: Organizational: Governance and Institutional Alignment</t>
-  </si>
-  <si>
-    <t>Requirement: Organizational: Process Alignment and Formalization</t>
-  </si>
-  <si>
-    <t>Requirement: Organizational: Semantic Construct Design and Maintenance</t>
-  </si>
-  <si>
-    <t>Requirement: Organizational: Standardization and Semantic Control</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1962,23 +3211,121 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2286,1074 +3633,1590 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF9CA26-1573-4495-AACA-80E5993A745D}">
-  <dimension ref="A1:E83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ef851959-c551-42c2-8a62-0ed41916ab49}">
+  <dimension ref="A1:E130"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="77" customWidth="1"/>
-    <col min="2" max="2" width="255.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="1" max="1" width="80.42857142857143" customWidth="1"/>
+    <col min="2" max="2" width="255.71428571428572" customWidth="1"/>
+    <col min="3" max="3" width="14.285714285714286" customWidth="1"/>
+    <col min="4" max="4" width="14.428571428571429" customWidth="1"/>
+    <col min="5" max="5" width="14.285714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="14.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" ht="14.25">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5" ht="14.25">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" ht="14.25">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" ht="14.25">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" ht="14.25">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" ht="14.25">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" ht="14.25">
+      <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" ht="14.25">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" ht="14.25">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" ht="14.25">
+      <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" ht="14.25">
+      <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="B12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" ht="14.25">
+      <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" ht="14.25">
+      <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" ht="14.25">
+      <c r="A15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.25">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="14.25">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" ht="14.25">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" ht="14.25">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" ht="14.25">
+      <c r="A20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="14.25">
+      <c r="A21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" ht="14.25">
+      <c r="A22" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" ht="14.25">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" ht="14.25">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" ht="14.25">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" ht="14.25">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" ht="14.25">
+      <c r="A27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5" ht="14.25">
+      <c r="A28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5" ht="14.25">
+      <c r="A29" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="14.25">
+      <c r="A30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" ht="14.25">
+      <c r="A31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="14.25">
+      <c r="A32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="14.25">
+      <c r="A33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" ht="14.25">
+      <c r="A34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" ht="14.25">
+      <c r="A35" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="14.25">
+      <c r="A36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="14.25">
+      <c r="A37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="14.25">
+      <c r="A38" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" ht="14.25">
+      <c r="A39" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" ht="14.25">
+      <c r="A40" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" ht="14.25">
+      <c r="A41" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A30" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" ht="14.25">
+      <c r="A42" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" ht="14.25">
+      <c r="A43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" ht="14.25">
+      <c r="A44" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A32" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A37" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" ht="14.25">
+      <c r="A45" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A40" s="1" t="s">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" ht="14.25">
+      <c r="A46" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" ht="14.25">
+      <c r="A47" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A41" s="1" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" ht="14.25">
+      <c r="A48" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A42" s="1" t="s">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" ht="14.25">
+      <c r="A49" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A43" s="2" t="s">
+      <c r="B49" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" ht="14.25">
+      <c r="A50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" ht="14.25">
+      <c r="A51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" ht="14.25">
+      <c r="A52" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5" ht="14.25">
+      <c r="A53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5" ht="14.25">
+      <c r="A54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5" ht="14.25">
+      <c r="A55" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5" ht="14.25">
+      <c r="A56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5" ht="14.25">
+      <c r="A57" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5" ht="14.25">
+      <c r="A58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5" ht="14.25">
+      <c r="A59" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5" ht="14.25">
+      <c r="A60" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5" ht="14.25">
+      <c r="A61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5" ht="14.25">
+      <c r="A62" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5" ht="14.25">
+      <c r="A63" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" ht="14.25">
+      <c r="A64" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5" ht="14.25">
+      <c r="A65" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5" ht="14.25">
+      <c r="A66" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5" ht="14.25">
+      <c r="A67" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5" ht="14.25">
+      <c r="A68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:5" ht="14.25">
+      <c r="A69" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5" ht="14.25">
+      <c r="A70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5" ht="14.25">
+      <c r="A71" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5" ht="14.25">
+      <c r="A72" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5" ht="14.25">
+      <c r="A73" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5" ht="14.25">
+      <c r="A74" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="1:5" ht="14.25">
+      <c r="A75" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5" ht="14.25">
+      <c r="A76" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5" ht="14.25">
+      <c r="A77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5" ht="14.25">
+      <c r="A78" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5" ht="14.25">
+      <c r="A79" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" ht="14.25">
+      <c r="A80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5" ht="14.25">
+      <c r="A81" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" ht="14.25">
+      <c r="A82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" ht="14.25">
+      <c r="A83" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" ht="14.25">
+      <c r="A84" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" ht="14.25">
+      <c r="A85" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" ht="14.25">
+      <c r="A86" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5" ht="14.25">
+      <c r="A87" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" ht="14.25">
+      <c r="A88" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A44" s="2" t="s">
+      <c r="C88" s="2"/>
+      <c r="D88" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5" ht="14.25">
+      <c r="A89" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
+      <c r="B89" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A48" s="2" t="s">
+    </row>
+    <row r="90" spans="1:5" ht="14.25">
+      <c r="A90" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" s="1"/>
-    </row>
-    <row r="49" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A49" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A50" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A51" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A52" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A53" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A54" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A55" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A56" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A57" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A58" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A59" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A60" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A61" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A62" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-    </row>
-    <row r="63" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A63" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A64" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A65" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A66" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A67" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A68" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A69" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A70" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A71" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A72" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A73" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A74" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A75" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A76" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A77" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A78" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A79" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A80" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A81" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A82" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="14" x14ac:dyDescent="0.15">
-      <c r="A83" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1" t="s">
-        <v>97</v>
+      <c r="B90" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="14.25">
+      <c r="A91" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="14.25">
+      <c r="A92" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="14.25">
+      <c r="A93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="14.25">
+      <c r="A94" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="14.25">
+      <c r="A95" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="14.25">
+      <c r="A96" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="14.25">
+      <c r="A97" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="14.25">
+      <c r="A98" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="14.25">
+      <c r="A99" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5" ht="14.25">
+      <c r="A100" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="14.25">
+      <c r="A101" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" spans="1:5" ht="14.25">
+      <c r="A102" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="14.25">
+      <c r="A103" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="14.25">
+      <c r="A104" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+    </row>
+    <row r="105" spans="1:5" ht="14.25">
+      <c r="A105" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="14.25">
+      <c r="A106" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+    </row>
+    <row r="107" spans="1:5" ht="14.25">
+      <c r="A107" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="14.25">
+      <c r="A108" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="14.25">
+      <c r="A109" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+    </row>
+    <row r="110" spans="1:5" ht="14.25">
+      <c r="A110" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+    </row>
+    <row r="111" spans="1:5" ht="14.25">
+      <c r="A111" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+    </row>
+    <row r="112" spans="1:5" ht="14.25">
+      <c r="A112" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="14.25">
+      <c r="A113" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="14.25">
+      <c r="A114" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="14.25">
+      <c r="A115" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="14.25">
+      <c r="A116" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="14.25">
+      <c r="A117" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="14.25">
+      <c r="A118" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="14.25">
+      <c r="A119" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+    </row>
+    <row r="120" spans="1:5" ht="14.25">
+      <c r="A120" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="14.25">
+      <c r="A121" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="14.25">
+      <c r="A122" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5" ht="14.25">
+      <c r="A123" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="1:5" ht="14.25">
+      <c r="A124" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="14.25">
+      <c r="A125" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="E125" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="14.25">
+      <c r="A126" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="14.25">
+      <c r="A127" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="14.25">
+      <c r="A128" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+    </row>
+    <row r="129" spans="1:5" ht="14.25">
+      <c r="A129" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="14.25">
+      <c r="A130" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
+++ b/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="285">
   <si>
     <t>Code</t>
   </si>
@@ -43,20 +43,14 @@
     </r>
   </si>
   <si>
-    <t>Definition: 
-Legal interoperability concerns the extent to which binding legal instruments enable, constrain, or structurally condition interoperability across domains and organizations.
-Inclusion:
-- Legal_Incompability Varying or incompatible legal requirements. such as conflicting legislative requirements that hinder data exchange (Weber 2019)
-- Legal_Restrictions or jurisdictional restrictions on data access, storage or reuse. Including privacy restrictions. 
-- Legal_Licensing incompatible licensing regimes or data ownership rules
-  - Legal_Clarity Lack of legal clarity regarding responsibilities, rights or liabilities in shared-service arrangements. _Supported by Scholl &amp; Klischewski (2007)_
-  - Legal_instability This subtype concerns situations where laws, regulations, or policy criteria are subject to frequent modification, reinterpretation, or re-scoping, thereby undermining shared understandings, durable semantic agreements, and stable implementation practices.
-  - Legal_Overhead Legal interoperability challenge arising from the juridical and governance burden of establishing, negotiating, and maintaining multilateral agreements to mandate shared standards, where the agreement process itself becomes a bottleneck to interoperability. _Supported by Kubicek, Cimander &amp; Scholl (2011)_
-Exclusion:
-  - semantic or technical challenges not rooted in law
-  - organizational misalignment unrelated to regulatory constraints
-Literature:
-Scholl &amp; Klischewski (2007)</t>
+    <t>Definition:
+Header category. Legal interoperability concerns the extent to which binding legal instruments enable, constrain or structurally condition interoperability across domains and organizations. Use the subcodes for actual coding; this header should not be applied directly to fragments.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code; not used for fragment-level coding.</t>
   </si>
   <si>
     <t>Challenges</t>
@@ -74,7 +68,21 @@
   </si>
   <si>
     <t>Definition:
-Lack of legal clarity regarding responsibilities, rights or liabilities in shared-service arrangements. Supported by Scholl &amp; Klischewski (2007)</t>
+Lack of legal clarity regarding responsibilities, rights, or liabilities in shared‐service or cross‐organizational arrangements.
+Inclusion Criteria:
+1. Ambiguous statutory responsibilities for shared services.
+2. Unclear allocation of legal liability between data providers and reusers.
+3. Vague or contested rights of use.
+Exclusion Criteria:
+1. Conflict between legal regimes (use Incompatibility).
+2. Restrictions on access (use Restrictions).
+Example Quotations:
+1. “Legal validity of the data models is not fully verified... birth of a person should be proved by a certificate issued by a legal verified competent authority...”
+2. “Due to a lack of a common understanding and also due to potential legal issues in the various countries, tackling this series of mapping and disambiguation issues poses a non-trivial challenge...”
+Notes:
+Distinguish from Restrictions: Clarity is about ambiguity, Restrictions is about prohibition
+Literature:
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -89,7 +97,21 @@
   </si>
   <si>
     <t>Definition:
-Varying or incompatible legal requirements. such as conflicting legislative requirements that hinder data exchange (Weber 2019)</t>
+Conflicts or incompatibilities between legal requirements across jurisdictions, sectors, or policy domains that hinder data exchange.
+Inclusion Criteria:
+1. Conflicting legislation across borders.
+2. Mismatched policy requirements between sectors.
+3. Misaligned regulatory regimes hindering reuse.
+Exclusion Criteria:
+1. Restrictions limiting access in a single jurisdiction (use Restrictions).
+2. Licensing conflicts (use Licensing).
+Example Quotations:
+1. “The legislation and policies incompatibility, data inconsistencies, semi-structured information, data heterogeneity, and the lack of common vocabularies also concern the digital government sector.”
+2. “Varying legislation or policy at national level.”
+Literature:
+• Weber (2019)
+• Incompatibility implies two or more conflicting legal regimes
+• Restrictions implies a single barrier</t>
   </si>
   <si>
     <r>
@@ -103,8 +125,19 @@
     </r>
   </si>
   <si>
-    <t>Definition: 
-This subtype concerns situations where laws, regulations, or policy criteria are subject to frequent modification, reinterpretation, or re-scoping, thereby undermining shared understandings, durable semantic agreements, and stable implementation practices.</t>
+    <t>Definition:
+Frequent modification, reinterpretation, or re‐scoping of laws, regulations, or policy criteria, undermining shared understandings and durable semantic agreements.
+Inclusion Criteria:
+1. Repeated legislative change disrupting agreed semantics.
+2. Re-scoping of regulations forcing re-modelling.
+3. Reinterpretation of legal concepts after agreement.
+Exclusion Criteria:
+1. One-off legal change without persistent disruption.
+2. Policy aspiration without legal status.
+Example Quotations:
+1. “Even if terminology and processes are successfully standardized, the risk remains that standards will be altered after their imposition to suit various environments...”
+Notes:
+Distinguish from Incompatibility: Instability is temporal volatility within one regime, Incompatibility is conflict across regimes.</t>
   </si>
   <si>
     <r>
@@ -119,7 +152,18 @@
   </si>
   <si>
     <t>Definition:
-Incompatible licensing regimes or data ownership rules</t>
+Incompatible licensing regimes or unclear data ownership rules that hinder reuse across organizations or jurisdictions.
+Inclusion Criteria:
+1. Conflicting open data licenses.
+2. Restrictive license conditions blocking reuse.
+3. Ownership disputes preventing sharing.
+Exclusion Criteria:
+1. General copyright concerns without license focus (use Restrictions).
+2. Privacy restrictions (use Restrictions).
+Example Quotations:
+1. “A number of organisational and legal challenges remain. There is still a diversity of license conditions between countries...”
+Notes:
+Sub‐dimension of legal interoperability targeting the licensing instrument specifically.</t>
   </si>
   <si>
     <r>
@@ -134,7 +178,17 @@
   </si>
   <si>
     <t>Definition:
-Legal interoperability challenge arising from the juridical and governance burden of establishing, negotiating, and maintaining multilateral agreements to mandate shared standards, where the agreement process itself becomes a bottleneck to interoperability. Supported by Kubicek, Cimander &amp; Scholl (2011)</t>
+Juridical and governance burden of establishing, negotiating, and maintaining multilateral legal agreements to mandate shared standards, where the legal process itself becomes a bottleneck.
+Inclusion Criteria:
+1. Lengthy treaty or regulation negotiations.
+2. Repeated re-negotiation of legal arrangements.
+3. Disproportionate legal effort relative to interoperability gain.
+Exclusion Criteria:
+1. General organizational overhead (use Organizational: Overhead Costs).
+Example Quotations:
+1. “A great deal of experience has been gained by public administrations through its implementation. Due to its complexity and wide scope, this is taking place in a stepwise manner...”
+Literature:
+• Kubicek, Cimander &amp; Scholl (2011)</t>
   </si>
   <si>
     <r>
@@ -148,6 +202,25 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Privacy and personal‐data protection obligations, derived from data protection law (such as the GDPR), that constrain the collection, sharing, processing, or reuse of data identifying or relating to individuals; the primary aim of the constraint is the protection of personal data and individual privacy rights, not generic confidentiality or commercial protection.
+Inclusion Criteria:
+1. Restrictions traceable to data protection law (GDPR, national equivalents).
+2. Constraints rooted in protection of identifiable individuals.
+3. Requirements for purpose limitation, minimisation, lawful basis, or consent affecting interoperability.
+4. Pseudonymisation or anonymisation obligations limiting reuse.
+Exclusion Criteria:
+1. Generic confidentiality not aimed at personal data (use Restrictions).
+2. Commercial or state secrecy regimes (use Restrictions).
+3. Licensing terms (use Licensing).
+4. Ambiguity in liability or responsibility (use Clarity).
+5. Technical security weaknesses without legal grounding (use Technical: Security Issues).
+Example Quotations:
+1. “Some of these challenges were discussed by Alshehab et al. in their study, which summarized these challenges as the lack of awareness of privacy and security...”
+Notes:
+Privacy is distinct from Restrictions in legal source and protective object: privacy law operates from the rights of natural persons, whereas Restrictions cover all other access or reuse limitations rooted in jurisdictional or statutory law. When in doubt, ask whether the limitation exists primarily to protect identifiable individuals; if yes, code Privacy.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -159,8 +232,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Jurisdictional restrictions on data access, storage or reuse. Including privacy restrictions. </t>
+    <t>Definition:
+Jurisdictional or statutory restrictions on data access, storage, sharing, or reuse other than those primarily aimed at protecting personal data; for example confidentiality of state security data, classification regimes, commercial confidentiality, statutory access limitations, or sectoral disclosure prohibitions.
+Inclusion Criteria:
+1. Confidentiality regulations blocking access (non‐privacy).
+2. Classification or state security regimes.
+3. Commercial confidentiality limitations.
+4. Statutory disclosure prohibitions in a single jurisdiction.
+Exclusion Criteria:
+1. Conflicts between legal regimes (use Incompatibility).
+2. License terms specifically (use Licensing).
+3. Ambiguity rather than prohibition (use Clarity).
+4. Restrictions specifically protecting personal data or individual privacy (use Privacy).
+Example Quotations:
+1. “Data-sharing was also hampered by cultural and institutional barriers, including closed or non-existent data policies.”
+Notes:
+Boundary with Privacy: Privacy is reserved for restrictions whose primary aim is protection of personal data and individual privacy rights; Restrictions covers all other access or reuse limitations.</t>
   </si>
   <si>
     <r>
@@ -174,9 +261,17 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">
-Literature:
-EIF, Scholl &amp; Klischewski (2007)</t>
+    <t>Definition:
+Header category. Organizational interoperability challenges concern persistent misalignments in roles, structures, processes, governance, capacity, and culture that hinder cross‐organizational interoperability.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• EIF
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -190,9 +285,19 @@
     </r>
   </si>
   <si>
-    <t>Defintion:
-Organizational interoperability challenge arising from the absence of shared organizational agreements on the interpretation and use of semantic concepts across public service providers, despite the availability of common models or standards. Dit betreft afspraken over organisatorische eenheden heen. 
-Zou overlap met #ORG_Governance kunnen hebben omdat het een tekort aan governance afspraken betekent</t>
+    <t>Definition:
+Absence of shared organizational agreements on the interpretation, use, or governance of semantic constructs, processes, or data, despite the availability of common models or standards.
+Inclusion Criteria:
+1. Missing administrative consensus on use of a shared model.
+2. Lack of formal agreement among partners about implementation.
+3. Standards adopted in name but without operational agreement.
+Exclusion Criteria:
+1. Lack of governance structures (use Lack of Governance).
+2. Voluntary collaboration that simply did not occur (use Lack of Collaboration).
+Example Quotations:
+1. “Lack of semantic agreement at the administrative level of public service providers — for example, the object Address has an attribute, AdminUnitL2...”
+Notes:
+Boundary with Lack of Governance: Absence of Agreement is the missing consensus, Lack of Governance is the missing structural mechanism.</t>
   </si>
   <si>
     <r>
@@ -206,8 +311,20 @@
     </r>
   </si>
   <si>
-    <t>Literature:
-Scholl &amp; Klischewski (2007) (noted as collabrative)</t>
+    <t>Definition:
+Differences in organizational, professional, or sectoral culture, norms, values, or attitudes that hinder interoperability collaboration.
+Inclusion Criteria:
+1. Divergent professional norms across sectors.
+2. Cultural barriers to information sharing.
+3. Differing attitudes toward openness across administrations.
+Exclusion Criteria:
+1. Structural differences in roles or processes (use Diversity).
+2. Lack of formal coordination (use Lack of Governance).
+Example Quotations:
+1. “Data-sharing was also hampered by cultural and institutional barriers, including closed or non-existent data policies.”
+2. “In order to develop technical solutions for interoperability, one must understand the politics that were involved in its negotiation.”
+Literature:
+• Scholl &amp; Klischewski (2007), labelled as collaborative challenge</t>
   </si>
   <si>
     <r>
@@ -217,12 +334,34 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Organizational: Data Fragmentation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Organizational: Diversity</t>
     </r>
   </si>
   <si>
     <t>Definition:
-Organizational interoperability challenge arising from persistent differences in organizational structures, roles, responsibilities, and management processes across public administrations, which hinder alignment and increase the effort required for interoperability.</t>
+Persistent differences in organizational structures, roles, responsibilities, hierarchies, and management processes across public administrations, hindering interoperability alignment.
+Inclusion Criteria:
+1. Structural fragmentation of administrations.
+2. Diverging role definitions across organizations.
+3. Misaligned management processes preventing alignment.
+Exclusion Criteria:
+1. Cultural or attitudinal differences (use Cultural Differences).
+2. Lack of governance arrangements specifically (use Lack of Governance).
+Example Quotations:
+1. “As 80% of the informational needs are related to geographic location and spatial data often uses domain specific standards, address information is scattered on different information systems.”
+Notes:
+Diversity is structural; Cultural Differences is normative and attitudinal.</t>
   </si>
   <si>
     <r>
@@ -236,6 +375,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Absence or insufficient maturity of an enterprise or interoperability architecture at organizational, sectoral, or jurisdictional level, leading to ad hoc integration and fragmented technical-organizational design.
+Inclusion Criteria:
+1. Missing enterprise architecture for cross-organizational services.
+2. Absence of architectural patterns for shared services.
+3. Scarcity of web-oriented architecture for data exchange.
+Exclusion Criteria:
+1. Technical incompatibility specifically (use Technical: Incompatible Technique).
+2. Lack of governance separately (use Lack of Governance).
+Example Quotations:
+1. “Due to interoperability problems, including adequate semantic standards and scarcity of web-oriented architecture, private partners struggle to reuse Public Sector Information.”
+Notes:
+Newly defined; sits between organizational and technical layer because architecture is an organizational capability with technical manifestations.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -247,6 +401,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Absence of operational cooperation, joint action, or coordination between actors needed to implement or sustain interoperability, even when governance structures may exist.
+Inclusion Criteria:
+1. Stakeholders failing to engage in joint development.
+2. Coordination not happening despite mandate.
+3. Silos preventing operational cooperation.
+Exclusion Criteria:
+1. Missing governance arrangements (use Lack of Governance).
+2. Cultural reasons for not collaborating (use Cultural Differences).
+Example Quotations:
+1. “The evaluation highlighted some ongoing challenges that include the need for coordination on multiple levels, as well as a more profound role of the private sector.”
+Notes:
+Closely related to Lack of Governance; here the focus is operational cooperation between actors, not the structural arrangement.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -258,8 +427,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Defintion:
-Organizational interoperability challenge arising from insufficient domain, semantic, or technical expertise required to design, implement, interpret, and sustain interoperability solutions, including structured semantic data, ontologies, and linked data. complexity issues and lack in ability of people and organizations to cope with complex issues </t>
+    <t>Definition:
+Insufficient domain, semantic, technical, or interoperability expertise required to design, implement, interpret, and sustain interoperability solutions, including ontologies and linked data.
+Inclusion Criteria:
+1. Insufficient ontology engineering skills.
+2. Inability to interpret structured semantic data.
+3. Difficulty coping with semantic complexity.
+Exclusion Criteria:
+1. Insufficient time, funding or staffing (use Shortage in Capacity).
+2. Absence of tools or methods (use Little or no Instrumentarium).
+Example Quotations:
+1. “A key problem to be solved in FinnONTO was that large cross-domain thesauri, especially the General Finnish Thesaurus YSA, could not anymore be maintained easily...”
+Notes:
+Together with Shortage in Capacity and Little or no Instrumentarium, this forms the capacity sub-cluster.</t>
   </si>
   <si>
     <r>
@@ -274,9 +454,18 @@
   </si>
   <si>
     <t>Definition:
-Organizational interoperability challenge arising from the absence of explicit governance, ownership, or managerial steering for semantic interoperability, resulting in semantic issues being handled ad hoc within technical or business silos. Like: misaligned or incompatible business processes that prevent end‑to‑end service delivery (Scholl &amp; Klischewski 2007), unclear distribution of roles, responsibilities or decision rights and lack of coordination mechanisms, collaboration structures or shared governance arrangements
-Literature:
-Scholl &amp; Klischewski (2007) (noted as managerial)</t>
+Absence of explicit governance arrangements, ownership, or managerial steering for interoperability, leading to ad hoc handling within technical or business silos and unclear allocation of decision rights.
+Inclusion Criteria:
+1. Unclear ownership of shared semantic artefacts.
+2. Missing decision rights or escalation mechanisms.
+3. Misaligned business processes due to absent governance.
+Exclusion Criteria:
+1. Failure of operational cooperation while structures exist (use Lack of Collaboration).
+2. Substantive missing agreements on interpretation (use Absence of Agreement).
+Example Quotations:
+1. “The FinnONTO initiative pointed out that lots of redundant work had been done in developing the thesauri in Finland as they shared lots similar concepts...”
+Literature:
+• Scholl &amp; Klischewski (2007), labelled managerial</t>
   </si>
   <si>
     <r>
@@ -290,6 +479,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Adoption of standards, models, or interoperability arrangements remains nominal or partial, with insufficient operational implementation in everyday processes and systems.
+Inclusion Criteria:
+1. Standards adopted on paper but not operationalized.
+2. Pilots that fail to scale.
+3. Documented intentions without operational uptake.
+Exclusion Criteria:
+1. Quality issues in implementation (use Data Quality).
+2. Absence of agreement preceding implementation (use Absence of Agreement).
+Example Quotations:
+1. “It has to be mentioned, that there are several serious problem areas, like documentation (intelligibility), implementation, quality of interoperability...”
+Notes:
+Newly defined; complements Operational Use and Institutional Embedding (a Requirement).</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -301,6 +505,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Insufficient political, executive, or stakeholder backing required to authorize, fund, sustain, or legitimize interoperability initiatives.
+Inclusion Criteria:
+1. Missing political endorsement.
+2. Lack of executive sponsorship.
+3. Stakeholder resistance to adoption.
+Exclusion Criteria:
+1. Absence of formal governance (use Lack of Governance).
+2. Funding and staffing constraints (use Shortage in Capacity).
+Example Quotations:
+1. “OSLO applied a generic process and methodology and provided practical insights on how to overcome the encountered hurdles: political support and adoption...”
+Notes:
+Newly defined; relates inversely to the Requirement: Organizational: Political Support.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -312,6 +531,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Limited awareness, understanding, or recognition among relevant actors of the importance, methods, or benefits of interoperability and shared semantic artefacts.
+Inclusion Criteria:
+1. Stakeholders unaware of available standards.
+2. Decision makers unfamiliar with interoperability concepts.
+3. Organizations not recognizing data as a shared concern.
+Exclusion Criteria:
+1. Lack of training capacity (use Lack of Expertise).
+2. Cultural resistance (use Cultural Differences).
+Example Quotations:
+1. “This ontology building, however, is not being undertaken by Geoconnections, the Canadian federal body responsible for spatial data infrastructure. Instead, isolated initiatives...”
+Notes:
+Newly defined; precedes Lack of Expertise as a precondition: awareness must exist before expertise is sought.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -324,7 +558,18 @@
   </si>
   <si>
     <t>Definition:
-Organizational interoperability challenge arising from the absence or insufficient availability of appropriate tools, methods, and operational practices required to design, implement, manage, or apply interoperability and semantic solutions.</t>
+Absence or insufficient availability of appropriate tools, methods, or operational practices required to design, implement, manage, or apply interoperability and semantic solutions.
+Inclusion Criteria:
+1. Missing modelling tools.
+2. Inadequate methods for semantic alignment.
+3. Absence of operational templates and patterns.
+Exclusion Criteria:
+1. Insufficient skills to use existing tools (use Lack of Expertise).
+2. Insufficient infrastructure investments (use Shortage in Capacity).
+Example Quotations:
+1. “While the varying levels of access to technological means (and thus e-education) is another soft challenge.”
+Notes:
+Capacity dimension complement to Lack of Expertise (people) and Shortage in Capacity (resources).</t>
   </si>
   <si>
     <r>
@@ -338,6 +583,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Relevant data are not available to relevant actors due to organizational decisions, gaps in collection, or absence of publication mechanisms, irrespective of legal or technical permissibility.
+Inclusion Criteria:
+1. Data exist but are not published.
+2. Required datasets simply not collected.
+3. Insufficient release of needed data.
+Exclusion Criteria:
+1. Legal restrictions blocking access (use Legal: Restrictions).
+2. Findability problems (use Technical: Findable, Searchable and Visible as inverse).
+Example Quotations:
+1. “Looking back twenty years to the 1990s, the accessibility and online sharing of public sector data were minimal...”
+Notes:
+Newly defined; an organizational antecedent to technical findability.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -350,8 +610,18 @@
   </si>
   <si>
     <t>Definition:
-Organizational interoperability challenge caused by the coordination, governance, and management overhead required to align multiple organizations, processes, and responsibilities, where the organizational effort itself becomes a bottleneck to interoperability. 
-Zou gezien kunnen worden als een capaciteitsprobleem dat ontstaat door de inzet op interoperabiliteit</t>
+Coordination, governance, and management overhead required to align multiple organizations, processes, and responsibilities, where the organizational effort itself becomes a bottleneck to interoperability.
+Inclusion Criteria:
+1. Excessive coordination meetings without progress.
+2. High agreement maintenance costs.
+3. Disproportionate effort relative to benefit.
+Exclusion Criteria:
+1. Legal negotiation overhead (use Legal: Overhead).
+2. Insufficient resources to begin with (use Shortage in Capacity).
+Example Quotations:
+1. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
+Notes:
+Distinguishable from Shortage in Capacity: Overhead is the cost of coordination effort itself, not the absence of resources.</t>
   </si>
   <si>
     <r>
@@ -361,14 +631,36 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Organizational: Personal biases</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Organizational: Shortage in capacity</t>
     </r>
   </si>
   <si>
     <t>Definition:
-Organizational interoperability challenge arising from insufficient structural capacity, including lack of time, funding, staffing, or institutional support to implement and sustain interoperability solutions.
-Literature:
-Scholl &amp; Klischewski (2007)</t>
+Insufficient structural capacity, including lack of time, funding, staffing, or institutional support, to implement and sustain interoperability solutions.
+Inclusion Criteria:
+1. Insufficient funding for interoperability projects.
+2. Understaffed interoperability units.
+3. Insufficient sustained institutional support.
+Exclusion Criteria:
+1. Skill gaps (use Lack of Expertise).
+2. Tool gaps (use Little or no Instrumentarium).
+Example Quotations:
+1. “A mundane challenge of developing large domain ontologies, at least in Finland, is how to convince the funding organizations, year after year, that this never-ending task is essential...”
+Notes:
+Capacity dimension complement to Expertise and Instrumentarium
+Literature:
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -382,23 +674,17 @@
     </r>
   </si>
   <si>
-    <t>Definition: 
-Semantic interoperability concerns the shared interpretation and consistent meaning of data across organisations. Challenges arise when the underlying conceptual structures, meaning assumptions or representational conventions diverge across domains.
-Inclusion:
-- Syntax Challenges: Semantic interoperability challenge arising when semantic models or information artefacts are expressed using different representation or formal languages, such that their structures or constructs are not directly comparable without explicit translation or mapping. (Euzenat &amp; Shvaiko 2013, p37)
-  - Underspecified Meaning: Semantic interoperability challenge arising when relevant concepts, properties, or relations are insufficiently, or not at all, conceptualized or left implicit, such that the meaning of data or information artefacts cannot be reliably interpreted or related to real-world phenomena. This includes situations where semantic content remains embedded in unstructured, weakly structured, or fragmented representations. _Guarino, N. (1998). Formal ontology and information systems_. (Euzenat &amp; Shvaiko 2013, p38)
-  - ConceptualDivergence: Semantic interoperability challenge arising from differences in how entities, attributes, or relations are conceptualized, such that modeling assumptions about meaning, granularity, or scope are misaligned, even when referring to comparable phenomena. This includes non-equivalence caused by mismatched levels of abstraction and divergent meaning structures that lead to inconsistent interpretation, rather than differences between problem domains as such. Vogt (2024), (Euzenat &amp; Shvaiko 2013, p38)
-  - Data Heterogeneity: Semantic interoperability challenge arising when problem domains differ in applications, scope, boundaries, or underlying assumptions, such that meanings are not directly comparable or transferable across domains. These differences exist independently of whether domains are explicitly conceptualized or remain implicit. When persistent, such heterogeneity contributes to the formation of semantic silos.
-  - Expressiveness Limit: Semantic interoperability challenge arising from limitations in the expressive power or representational adequacy of ontology-based formalisms, where formal structures such as class hierarchies cannot fully or faithfully capture complex, fuzzy, or context-dependent meanings.
-  - DataQuality Semantic interoperability challenge arising when data contain errors or otherwise fail to accurately convey their intended meaning, resulting in inconsistent interpretation, reduced usability, or loss of conceptual fidelity across contexts (Vogt, 2024).
-  - Multi Language: Semantic interoperability challenge arising from differences in natural languages (ie. English, Dutch or Swedish) used to label, describe, or document data and models, leading to ambiguity, translation loss, or inconsistent interpretation across linguistic contexts. 
-  - Metadata Insufficiency: Semantic interoperability challenge arising when metadata are incomplete, inaccurate, or missing, such that the meaning, context, or constraints of data cannot be reliably understood or interpreted. [^aliDevelopmentInteroperableOpen2024]  
-Exclusion:
-  - purely technical issues concerning formats, APIs or protocols
-  - legal constraints not affecting meaning
-  - organizational constraints not affecting meaning
-Literature:
-EIF, Scholl &amp; Klischewski (2007) (noted as collabrative)</t>
+    <t>Definition:
+Header category. Semantic interoperability challenges concern the shared interpretation and consistent meaning of data across organisations. Challenges arise when conceptual structures, meaning assumptions, or representational conventions diverge across domains or contexts.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• EIF
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -412,9 +698,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Semantic interoperability challenge arising from differences in how entities, attributes, or relations are conceptualized, such that modeling assumptions about meaning, granularity, or scope are misaligned, even when referring to comparable phenomena. This includes non-equivalence caused by mismatched levels of abstraction and divergent meaning structures that lead to inconsistent interpretation, rather than differences between problem domains as such. Vogt (2024), (Euzenat &amp; Shvaiko 2013, p38)
-</t>
+    <t>Definition:
+Differences in how entities, attributes, or relations are conceptualized across actors, such that modelling assumptions about meaning, granularity, or scope are misaligned even when referring to comparable phenomena. Includes mismatched abstraction levels and divergent meaning structures.
+Inclusion Criteria:
+1. Different conceptualization of the same phenomenon.
+2. Mismatched abstraction levels.
+3. Divergent semantic granularity.
+4. Homonym or synonym conflicts in models.
+Exclusion Criteria:
+1. Differences across distinct domains (use Data Heterogenity).
+2. Insufficient or implicit conceptualization (use Underspecified Meaning).
+3. Different formal languages used (use Lack of shared Syntax).
+Example Quotations:
+1. “However, in practice one also has to deal with national level issues and data available that are represented using national languages, data models, vocabularies...”
+2. “Public Sector Information is often modelled from a single perspective and therefore cannot be integrated with other information sources...”
+Notes:
+Boundary with Data Heterogenity: Conceptual Divergence is about the conceptualization of comparable phenomena, Data Heterogenity is about differences between distinct problem domains
+Literature:
+• Vogt (2024)
+• Euzenat &amp; Shvaiko (2013, p38)</t>
   </si>
   <si>
     <r>
@@ -429,7 +731,19 @@
   </si>
   <si>
     <t>Definition:
-Semantic interoperability challenge arising when problem domains differ in applications, scope, boundaries, or underlying assumptions, such that meanings are not directly comparable or transferable across domains. These differences exist independently of whether domains are explicitly conceptualized or remain implicit. When persistent, such heterogeneity contributes to the formation of semantic silos.</t>
+Differences across problem domains in applications, scope, boundaries, or underlying assumptions, such that meanings are not directly comparable or transferable across domains. When persistent, contributes to semantic silos.
+Inclusion Criteria:
+1. Cross-domain meaning mismatches.
+2. Heterogeneous formats and structures across sectors.
+3. Address fragmentation across multiple registries.
+Exclusion Criteria:
+1. Comparable phenomena conceptualized differently within one domain (use Conceptual Divergence).
+2. Errors in data (use Data Quality).
+Example Quotations:
+1. “The obstacles: (i) address data fragmentation (ii) heterogeneous address data formats and (iii) a lack of common identifiers.”
+2. “The European Commission wanted to overcome the fragmentation of the address data.”
+Notes:
+Heterogenity refers to distinct domains; Conceptual Divergence refers to differing conceptualizations of comparable phenomena.</t>
   </si>
   <si>
     <r>
@@ -444,9 +758,20 @@
   </si>
   <si>
     <t>Definition:
-Semantic interoperability challenge arising when data contain errors or otherwise fail to accurately convey their intended meaning, resulting in inconsistent interpretation, reduced usability, or loss of conceptual fidelity across contexts (Vogt, 2024).
-Literature:
-Scholl &amp; Klischewski (2007) (noted as collabrative)</t>
+Data contain errors or otherwise fail to accurately convey their intended meaning, resulting in inconsistent interpretation, reduced usability, or loss of conceptual fidelity across contexts.
+Inclusion Criteria:
+1. Errors degrading semantic interpretation.
+2. Incomplete or inaccurate data hindering meaning.
+3. Loss of conceptual fidelity through transformation.
+Exclusion Criteria:
+1. Heterogeneity across domains (use Data Heterogenity).
+2. Missing metadata (use Metadata Insufficiency).
+Example Quotations:
+1. “When developing ontology-based applications in FinnONTO, much of the time of the developers was 'wasted' in cleaning and aligning the data from different organizations for interoperability.”
+2. “What the underlying data actually means is not always clear and issues of Big Data quality, such as completeness, veracity, skewness, uncertainty, fuzziness, and errors of data arise.”
+Literature:
+• Vogt (2024)
+• Scholl &amp; Klischewski (2007), labelled collaborative</t>
   </si>
   <si>
     <r>
@@ -461,7 +786,18 @@
   </si>
   <si>
     <t>Definition:
-Semantic interoperability challenge arising from limitations in the expressive power or representational adequacy of ontology-based formalisms, where formal structures such as class hierarchies cannot fully or faithfully capture complex, fuzzy, or context-dependent meanings.</t>
+Limitations in the expressive power or representational adequacy of ontology-based formalisms, where formal structures cannot fully capture complex, fuzzy, or context-dependent meanings.
+Inclusion Criteria:
+1. Class hierarchies cannot represent the needed nuances.
+2. Formal language insufficient for fuzzy categories.
+3. Context dependency lost in formal representation.
+Exclusion Criteria:
+1. Insufficient formalization at all (use Underspecified Meaning).
+2. Different formal languages used (use Lack of shared Syntax).
+Example Quotations:
+1. “As ISA limits itself to an address-as-an-attribute, certain properties of structured addresses are missing in the Core Location Vocabulary. Most noteworthy is address position...”
+Notes:
+The formal language exists but is too limited; not absence of formalization.</t>
   </si>
   <si>
     <r>
@@ -475,6 +811,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Instability or fluidity of meaning over time, such that previously agreed semantic content shifts, drifts, or is reinterpreted, undermining sustained interoperability.
+Inclusion Criteria:
+1. Concept drift in evolving domains.
+2. Reinterpretation of agreed terms.
+3. Fluid digital data eroding stable meaning.
+Exclusion Criteria:
+1. Differences in meaning at one point in time (use Conceptual Divergence).
+2. Changes in legal definitions (use Legal: Instability).
+Example Quotations:
+1. “This view fails to take into account the changes wrought by digital data, which are fluid, unstable, and mobile.”
+Notes:
+Newly defined; the temporal dimension of semantic challenges.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -486,6 +837,22 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Absence or insufficient maturity of agreed semantic standards (vocabularies, ontologies, code lists, reference models) within a domain or jurisdiction, leaving meaning unanchored across actors.
+Inclusion Criteria:
+1. No agreed vocabulary in a domain.
+2. Sectoral standards do not exist or are immature.
+3. Lack of common reference models.
+Exclusion Criteria:
+1. Standards exist but are underspecified (use Underspecified Meaning).
+2. Standards exist but in different formal languages (use Lack of shared Syntax).
+3. Standards exist but vary across organizations (use Conceptual Divergence).
+Example Quotations:
+1. “Due to interoperability problems, including adequate semantic standards and scarcity of web-oriented architecture, private partners struggle to reuse Public Sector Information.”
+Notes:
+Newly defined and distinguished from Underspecified Meaning: Lack of Semantic Standards is the absence of standards, Underspecified Meaning is insufficient explicit conceptualization within available representations.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -498,7 +865,18 @@
   </si>
   <si>
     <t>Definition:
-Semantic interoperability challenge arising when semantic models or information artefacts are expressed using different representation or formal languages, such that their structures or constructs are not directly comparable without explicit translation or mapping. (Euzenat &amp; Shvaiko 2013, p37)</t>
+Semantic models or information artefacts are expressed using different representation or formal languages, such that their structures or constructs are not directly comparable without explicit translation or mapping.
+Inclusion Criteria:
+1. Models in different formal languages (e.g., RDF vs UML).
+2. Different schema languages prevent direct comparison.
+3. Heterogeneous syntactic encodings.
+Exclusion Criteria:
+1. Substantive conceptual differences (use Conceptual Divergence).
+2. Absence of any standards (use Lack of Semantic Standards).
+Example Quotations:
+1. “Back in the 1990s, there were several barriers... different data policies, encodings, formats and semantics, to name a few.”
+Literature:
+• Euzenat &amp; Shvaiko (2013, p37)</t>
   </si>
   <si>
     <r>
@@ -512,9 +890,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Semantic interoperability challenge arising when metadata are incomplete, inaccurate, or missing, such that the meaning, context, or constraints of data cannot be reliably understood or interpreted.
-</t>
+    <t>Definition:
+Metadata are incomplete, inaccurate, or missing, such that the meaning, context, or constraints of data cannot be reliably understood or interpreted.
+Inclusion Criteria:
+1. Missing provenance.
+2. Absent context descriptions.
+3. Inaccurate metadata records.
+Exclusion Criteria:
+1. Quality of the data itself (use Data Quality).
+2. Absent semantic standards (use Lack of Semantic Standards).
+Example Quotations:
+1. “When re-using public sector information, until now Postbuzz had to look-up the coordinates... Because of a lack of context, the developers of Postbuzz missed out this valuable clue.”
+Notes:
+The receiving system lacks the descriptive context needed to interpret data.</t>
   </si>
   <si>
     <r>
@@ -528,8 +916,17 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Semantic interoperability challenge arising from differences in natural languages (ie. English, Dutch or Swedish) used to label, describe, or document data and models, leading to ambiguity, translation loss, or inconsistent interpretation across linguistic contexts. </t>
+    <t>Definition:
+Differences in natural languages used to label, describe, or document data and models, leading to ambiguity, translation loss, or inconsistent interpretation across linguistic contexts.
+Inclusion Criteria:
+1. Multilingual labels with translation loss.
+2. Ambiguity arising from cross-language documentation.
+3. Inconsistent interpretation across language communities.
+Exclusion Criteria:
+1. Conceptual differences not rooted in language (use Conceptual Divergence).
+2. Insufficient documentation generally (use Metadata Insufficiency).
+Notes:
+Currently no quotations in the dataset; consider whether this code earns its place. Retain provisionally because EU multi-language context is structurally relevant to the research scope.</t>
   </si>
   <si>
     <r>
@@ -543,6 +940,22 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Same or near-identical data are produced and maintained in multiple places, leading to inconsistency, drift, and resource waste; a downstream symptom of organizational and semantic misalignment.
+Inclusion Criteria:
+1. Shadow databases.
+2. Duplicate data across registries.
+3. Inconsistent copies of authoritative data.
+Exclusion Criteria:
+1. Underlying organizational misalignment (use Organizational: Lack of Governance).
+2. Conceptual differences (use Conceptual Divergence).
+Example Quotations:
+1. “A lack of interoperable information products at local level, has led to redundant and repeated data.”
+2. “The processes that drive these products are often digitalized in separate systems. Due to this, shadow databases arise...”
+Notes:
+Newly defined; often co-occurs with Lack of Governance and Conceptual Divergence as a symptom.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -554,6 +967,22 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+The intrinsic complexity and scale of semantic models or domains exceeds the capacity to represent, maintain, or interpret them coherently, leading to fragmentation or untractable mappings.
+Inclusion Criteria:
+1. Very large ontologies that cannot be maintained.
+2. Fine-grained classifications that fragment communities.
+3. Scale of mappings between models that is intractable.
+Exclusion Criteria:
+1. Insufficient skills (use Lack of Expertise).
+2. Quality issues (use Data Quality).
+Example Quotations:
+1. “Clearly, the higher the resolution of the study, the greater the number of categories that emerge. Both scientific and social pressures bear on classification.”
+2. “Classification systems are, by definition, not complete.”
+Notes:
+Newly defined; addresses the scale-induced semantic challenges that the original codebook did not name.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -566,7 +995,20 @@
   </si>
   <si>
     <t>Definition:
-Semantic interoperability challenge arising when relevant concepts, properties, or relations are insufficiently, or not at all, conceptualized or left implicit, such that the meaning of data or information artefacts cannot be reliably interpreted or related to real-world phenomena. This includes situations where semantic content remains embedded in unstructured, weakly structured, or fragmented representations. (Guarino, N. (1998). Formal ontology and information systems) (Euzenat &amp; Shvaiko 2013, p38)</t>
+Relevant concepts, properties, or relations are insufficiently or not at all conceptualized or left implicit, such that the meaning of data or information artefacts cannot be reliably interpreted. Includes situations where semantic content remains in unstructured or weakly structured representations.
+Inclusion Criteria:
+1. Implicit semantics in free text.
+2. Concepts referenced but not defined.
+3. Unstructured representation hampering interpretation.
+Exclusion Criteria:
+1. Standards do not exist at all (use Lack of Semantic Standards).
+2. Standards exist but are too limited (use Expressiveness Limit).
+Example Quotations:
+1. “What the underlying data actually means is not always clear and issues of Big Data quality, such as completeness, veracity, skewness, uncertainty, fuzziness, and errors of data arise.”
+2. “We have learned that the formal structure of addresses is difficult to understand.”
+Literature:
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013, p38)</t>
   </si>
   <si>
     <r>
@@ -580,19 +1022,16 @@
     </r>
   </si>
   <si>
-    <t>Definition
-Technical interoperability concerns the ability of applications and underlying infrastructures to connect systems and services in a reliable and machine-processable manner. It covers the technical mechanisms that enable data presentation, exchange, and integration, including interface specifications, interconnection services, data integration services, and secure communication protocols. Technical challenges arise when these mechanisms are fragmented, incompatible, or insufficiently implemented, thereby obstructing effective system-to-system interoperability.
-Inclusion criteria:
-- Technical Incompatibilities: incompatibilities in system architectures, platforms, or infrastructure, including constraints imposed by legacy systems
-- Interface absence: partial adoption, or inconsistent implementation of shared technical standards for data exchange, interfaces, or services
-- Transport limitations:  limitations in discoverability, data transport, service connectivity, authentication, or authorization mechanisms that hinder secure and stable communication
-- Failures in machine readability: failures in syntactic validation, schema conformance, or machine-level processability of exchanged data
-Exclusion criteria:
-- differences in meaning, interpretation, or conceptualisation of data elements or structures (semantic layer)
-- misalignment of organisational roles, responsibilities, workflows, or governance arrangements (organisational layer)
-- legal or policy constraints that restrict data exchange independently of technical feasibility
-Literature:
-Scholl &amp; Klischewski (2007)</t>
+    <t>Definition:
+Header category. Technical interoperability challenges concern the ability of applications and underlying infrastructures to connect systems and services in a reliable and machine-processable manner.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -602,10 +1041,35 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Technical: Different encoding and font types</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Technical: Genral Technical Limitations</t>
     </r>
   </si>
   <si>
+    <t>Definition:
+Generic or composite technical limitations that do not cleanly fall into one specific subcode but jointly hinder system-to-system interoperability.
+Inclusion Criteria:
+1. Composite technical barriers without single dominant cause.
+2. Multiple technical limitations described jointly.
+Exclusion Criteria:
+1. Specific incompatibilities (use Incompatible Technique).
+2. Specific interface or transport problems (use Interfacing or Transportation).
+Example Quotations:
+1. “Back in the 1990s, there were several barriers for accessing and using the spatial data and information necessary for environmental management...”
+Notes:
+Use sparingly; prefer the more specific subcodes whenever possible. Note: original spelling 'Genral' corrected to 'General'.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -613,12 +1077,34 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Challenge: Technical: Identification and authentication issues</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Challenge: Technical: Incompatible Technique</t>
     </r>
   </si>
   <si>
     <t>Definition:
-incompatibilities in system architectures, platforms, or infrastructure, including constraints imposed by legacy systems</t>
+Incompatibilities in system architectures, platforms, or infrastructure, including constraints imposed by legacy systems.
+Inclusion Criteria:
+1. Legacy system constraints.
+2. Platform incompatibilities.
+3. Architectural lock-in preventing exchange.
+Exclusion Criteria:
+1. Missing or inconsistent shared standards (use Interfacing Problems).
+2. Validation failures (use Machine Readability problems).
+Example Quotations:
+1. “The infrastructure should adapt to changing technological trends... encoding of data through GeoJSON, or JSON-LD...”
+Literature:
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -633,7 +1119,18 @@
   </si>
   <si>
     <t>Definition:
-Absence, partial adoption, or inconsistent implementation of shared technical standards for data exchange, interfaces, or services</t>
+Absence, partial adoption, or inconsistent implementation of shared technical standards for data exchange, interfaces, or services.
+Inclusion Criteria:
+1. Missing API standards.
+2. Inconsistent interface profiles.
+3. Partial conformance to OGC services.
+Exclusion Criteria:
+1. Architectural mismatches (use Incompatible Technique).
+2. Transport-layer issues (use Transportation Problems).
+Example Quotations:
+1. “In general the discoverability of geospatial data on the web remains a challenge. Being based on OGC standards, data in INSPIRE is accessed through the interaction with different services...”
+Notes:
+Boundary with Incompatible Technique: Interfacing concerns the interface contract; Incompatible Technique concerns the underlying platform/architecture.</t>
   </si>
   <si>
     <r>
@@ -648,7 +1145,18 @@
   </si>
   <si>
     <t>Definition:
-Failures in syntactic validation, schema conformance, or machine-level processability of exchanged data. Also Query languages fall into this category</t>
+Failures in syntactic validation, schema conformance, or machine-level processability of exchanged data, including query language limitations.
+Inclusion Criteria:
+1. Parsing failures.
+2. Schema validation errors.
+3. Query language unsuited to the data.
+Exclusion Criteria:
+1. Conceptual issues affecting interpretation (use Semantic: Underspecified Meaning).
+2. Format incompatibility (use Interfacing Problems).
+Example Quotations:
+1. “The infrastructure should adapt to changing technological trends... establishment of RESTful web services, use of asynchronous event-based architectures...”
+Notes:
+Includes query languages.</t>
   </si>
   <si>
     <r>
@@ -662,6 +1170,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Technical security limitations including authentication weaknesses, authorization gaps, integrity risks, and confidentiality threats hindering trustworthy data exchange.
+Inclusion Criteria:
+1. Weak authentication mechanisms.
+2. Authorization gaps blocking sharing.
+3. Confidentiality risks limiting interoperability.
+Exclusion Criteria:
+1. Privacy law obligations (use Legal: Restrictions).
+2. Trust frameworks at organizational level (use Org: Lack of Governance).
+Example Quotations:
+1. “Some of these challenges were discussed by Alshehab et al. in their study, which summarized these challenges as the lack of awareness... and security.”
+Notes:
+Newly defined; complements Requirement: Technical: Security and Privacy.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -674,7 +1197,18 @@
   </si>
   <si>
     <t>Definition:
-Limitations in discoverability, data transport, service connectivity, authentication, or authorization mechanisms that hinder secure and stable communication</t>
+Limitations in discoverability, data transport, service connectivity, authentication, or authorization mechanisms that hinder secure and stable communication across systems.
+Inclusion Criteria:
+1. Unstable connectivity.
+2. Failures in service discovery.
+3. Authentication mechanisms blocking transport.
+Exclusion Criteria:
+1. Format-level interfacing problems (use Interfacing Problems).
+2. Pure security limitations (use Security Issues).
+Example Quotations:
+1. “The infrastructure should adapt to changing technological trends. In that respect, new guidance may be produced...”
+Notes:
+Original definition retained.</t>
   </si>
   <si>
     <r>
@@ -688,12 +1222,49 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Cross-cutting metadata code used to capture the substantive domain or context of the coded fragment (e.g., addresses, healthcare, environmental policy, geospatial, e-government), independent of the analytical Challenge/Requirement/Solution dimensions.
+Inclusion Criteria:
+1. Identification of the substantive domain referenced.
+2. Sectoral, thematic, or jurisdictional context.
+Exclusion Criteria:
+1. Use only as cross-cutting metadata; not in place of analytical codes.
+2. Do not use for the abstract analytical category.
+Example Quotations:
+1. “Linked domain ontologies of the original KOKO ontology cloud.”
+Notes:
+Highest-frequency code in dataset (146 quotations). Definition added; previously empty. Recommend using as a multi-value tag with the domain string in a free-text comment in ATLAS.ti.</t>
+  </si>
+  <si>
     <t>Imported annotation</t>
   </si>
   <si>
+    <t>Definition:
+Meta-code reserved for annotations imported from other coding systems or external sources during data ingestion. Use as a flag, not as an analytical category.
+Inclusion Criteria:
+1. Annotations carried over from previous coding rounds.
+2. External annotations imported with the document.
+Exclusion Criteria:
+1. Substantive analytical observations (use Remark).
+Notes:
+System / housekeeping code. Consider whether to retain or replace with a metadata field.</t>
+  </si>
+  <si>
     <t>Remark</t>
   </si>
   <si>
+    <t>Definition:
+Meta-code for the researcher's analytical remark, observation, or interpretive note attached to a fragment, distinct from the application of substantive codes.
+Inclusion Criteria:
+1. Researcher commentary on a fragment.
+2. Methodological notes.
+3. Observations about author intent or framing.
+Exclusion Criteria:
+1. Direct application of a substantive Challenge, Requirement, or Solution.
+Notes:
+System code; use sparingly to avoid blurring with substantive codes.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -705,28 +1276,14 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Legal Requirements refer to normative statements asserting that legal measures are necessary to achieve, enable, or improve interoperability.
-Such requirements indicate that interoperable collaboration depends on the establishment, alignment, or clarification of binding legal arrangements. These may include statutory authorization for data exchange, legally defined responsibilities, harmonized legislation across domains, or formal legal safeguards ensuring lawful and accountable information sharing. The defining characteristic is that legal measures are presented as necessary enabling conditions for interoperability.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•A clear legal basis for data sharing or data reuse.
-•Formal legal authorization for cross-organizational or cross-sector information exchange.
-•Harmonization or alignment of legislation to remove legal barriers.
-•Legally defined roles, competences, or accountability structures supporting collaboration.
-•Binding legal safeguards ensuring lawful, transparent, and secure data processing.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•Technical standards, architectures, or semantic alignment mechanisms without reference to legal necessity.
-•Organizational coordination mechanisms lacking formal legal grounding.
-•Specific enforcement instruments such as penalties or incentives, unless framed as part of a broader legal necessity.
-•Descriptions of existing legislation without asserting that legal measures are required.
-•General values or policy aspirations that are not translated into concrete legal conditions.
-Theoretical Grounding:
-Interoperability research identifies legal interoperability as a foundational dimension alongside technical and organizational layers. The European Interoperability Framework emphasizes that legislation must enable rather than obstruct collaboration between public administrations (European Commission, 2017).
-Regulatory governance theory conceptualizes formal legal arrangements as prerequisites for coordinated action because they define permissible conduct and allocate authority (Baldwin, Cave, &amp; Lodge, 2012).
-Empirical studies in semantic interoperability demonstrate that fragmented or unclear legal provisions constitute structural barriers to interoperability, irrespective of technical readiness (Ojo, Janowski, &amp; Estevez, 2009). These findings support the view that legal measures function as necessary enabling conditions.
-</t>
+    <t>Definition:
+Header category. Legal Requirements refer to normative statements asserting that legal measures are necessary to achieve, enable, or improve interoperability.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code.</t>
   </si>
   <si>
     <t>Requirements</t>
@@ -743,32 +1300,23 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-All copyrightable data and metadata must include clear and explicitly stated copyright status and licensing conditions that define rights of use, reuse permissions, legal restrictions, and applicable conditions. These statements must be sufficiently precise and standardized to ensure that downstream users can unambiguously determine what is legally permitted.
-Clear copyright and licensing conditions are defined here as explicit and accessible statements that specify ownership, applicable license, scope of permitted reuse, and any legal limitations associated with the data or metadata resource.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•A specific license is attached to data or metadata.
-•Copyright status is explicitly declared.
-•Reuse permissions and restrictions are clearly defined.
-•Legal conditions for reuse are stated in an accessible manner.
-•Open licenses are recommended or mandated for semantic artefacts.
-•Standardized expressions of rights statements are required.
-Exclusion Criteria:
-Do not code when:
-•Terms of service are described without clarifying copyright or licensing.
-•Licensing statements are vague, implicit, or inconsistently formulated.
-Literature:
-•FAIR R1.1 (Wilkinson et al., 2016): “(Meta)data are released with a clear and accessible data usage license.”
-•EOSC Interoperability Framework (2021–2023): requirement for clear statements of rights, open licenses for semantic artefacts, and explicit legal conditions for reuse.
-•Creative Commons (2019): standardized open licensing frameworks supporting interoperable reuse.
-•Wimmer et al. (2018): legal interoperability as a component of federated data ecosystems.
-Links to EIF Recommendation 2:  “Publish the data you own as open data unless certain restrictions apply.”
-Links to EIF Recommendation 39:  Match each base registry with appropriate metadata including the description of its content, service assurance and responsibilities, the type of master data it keeps, conditions of access and the relevant licences, terminology, a glossary, and information about any master data it uses from other base registries.
-Links to EIF Recommendation 41:  Establish procedures and processes to integrate the opening of data in your common business processes, working routines, and in the development of new information systems.
-EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.
-Links to EIF Recommendation 43:  Communicate clearly the right to access and reuse open data. The legal regimes for facilitating access and reuse, such as licences, should be standardised as much as possible.
-</t>
+    <t>Definition:
+All copyrightable data and metadata must include clear and explicitly stated copyright status and licensing conditions that define rights of use, reuse permissions, legal restrictions, and applicable conditions.
+Inclusion Criteria:
+1. Specific licenses attached.
+2. Standardized rights statements.
+3. Open licenses for semantic artefacts.
+Exclusion Criteria:
+1. Vague or implicit licensing.
+2. Service-level agreements (use Clear Terms and Conditions of Use).
+Example Quotations:
+1. “Adopting this data policy approach is often a consequence of collaboration established between public administrations that decide to share the costs...”
+Literature:
+• FAIR R1.1
+• EOSC IF
+• CC
+• Wimmer (2018)
+• Links to EIF 2, 39, 41, 42, 43</t>
   </si>
   <si>
     <r>
@@ -783,27 +1331,20 @@
   </si>
   <si>
     <t>Definition:
-Compliance and Enforcement Mechanisms refer to the requirement that formal mechanisms must exist to ensure adherence to interoperability-related legal and regulatory arrangements.
-This requirement asserts that interoperability is promoted when binding rules are supported by monitoring, oversight, incentives, and sanctioning instruments that ensure consistent application across organizations or jurisdictions. The focus is on the necessity of credible enforcement and compliance structures as enabling conditions for effective and sustained interoperability.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•Mandatory compliance with interoperability-related legal or regulatory provisions.
-•Monitoring, audit, or reporting mechanisms ensuring adherence to agreed rules.
-•Sanctioning instruments, penalties, or corrective measures for non-compliance.
-•Incentive schemes encouraging conformity with interoperability obligations.
-•Formal compliance strategies or accountability mechanisms supporting rule observance.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•The existence of legislation without reference to enforcement or compliance.
-•The establishment of a legally mandated authority without reference to enforcement functions.
-•Voluntary coordination mechanisms lacking binding force.
-•Technical validation mechanisms unless explicitly framed as regulatory compliance instruments.
-•General references to “trust” or “commitment” without institutionalized enforcement structures.
-Theoretical Grounding:
-Regulatory governance theory distinguishes rule-setting from monitoring and sanctioning functions. Effective regulation requires credible enforcement mechanisms to ensure compliance with established rules (Baldwin, Cave, &amp; Lodge, 2012).
-Responsive regulation theory emphasizes that enforcement instruments, ranging from incentives to penalties, are necessary to secure sustained adherence in complex governance environments (Ayres &amp; Braithwaite, 1992).
-Interoperability research similarly indicates that non-binding standards often fail to produce consistent cross-organizational alignment, whereas mandatory regimes supported by compliance strategies improve implementation outcomes (European Commission, 2017; Ojo, Janowski, &amp; Estevez, 2009).
-EIF: Recommendadtiom 1: “Ensure that national interoperability frameworks and interoperability strategies are aligned with the EIF and, if needed, tailor and extend them to address the national context and needs.”</t>
+Formal mechanisms must exist to ensure adherence to interoperability-related legal and regulatory arrangements through monitoring, oversight, incentives, and sanctioning instruments.
+Inclusion Criteria:
+1. Mandatory compliance regimes.
+2. Audit and reporting mechanisms.
+3. Sanctions for non-compliance.
+Exclusion Criteria:
+1. Internal organizational adherence (use Organizational: Compliance Mechanisms).
+2. Voluntary coordination.
+Example Quotations:
+1. “As a Directive, the legal obligations did not come into force immediately but had to be transposed into national law.”
+Literature:
+• Baldwin et al. (2012)
+• Ayres &amp; Braithwaite (1992)
+• EIF Recommendation 1</t>
   </si>
   <si>
     <r>
@@ -813,35 +1354,36 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Requirement: Legal: Information serves as legal evidence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Requirement: Legal: Public Policy for Interoperability</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Public Policy for Interoperability refers to the requirement that formally adopted governmental policy instruments must articulate, prioritize, and structurally support interoperability objectives across public administrations.
-This requirement asserts that sustainable interoperability depends on the existence of officially endorsed policy frameworks, strategies, or governmental programs that define objectives, principles, and coordination priorities for interoperability.
-Such policy instruments may include national digital strategies, interoperability frameworks, administrative agreements, governmental programs, or ministerial policy directives. They provide strategic direction and coordination without necessarily constituting binding statutory law.
-The defining characteristic of this requirement is the existence of an officially adopted governmental policy instrument that explicitly frames interoperability as a policy objective or structural priority.
-Inclusion Criteria:
-Code when a source explicitly requires that interoperability depends on:
-•A formally adopted governmental interoperability strategy.
-•An official digital or data policy framework endorsing interoperability.
-•A government-approved roadmap or program mandating interoperability objectives.
-•Cross-ministerial or cross-level policy agreements guiding interoperability.
-•Policy directives that prioritize or structurally embed interoperability in public administration.
-The requirement must concern formally adopted governmental policy, not informal coordination.
-Exclusion Criteria:
-Do not code when the text concerns:
-•Binding statutory or regulatory law (belongs under Statutory and Regulatory Basis).
-•A legally mandated authority (belongs under Statutory Interoperability Authority).
-•Enforcement or sanctioning mechanisms.
-•Organizational governance structures without policy-level endorsement.
-•Voluntary community frameworks without formal governmental adoption.
-Theoretical Grounding:
-Public governance theory distinguishes between statutory rule-making and policy instruments as strategic steering mechanisms (Baldwin, Cave, &amp; Lodge, 2012).
-The European Interoperability Framework (European Commission, 2017) emphasizes that interoperability requires political commitment and policy endorsement in addition to legal and technical measures.
-Multi-level governance research highlights that strategic governmental policy direction reduces fragmentation and provides coordination signals across administrative domains.
-</t>
+    <t>Definition:
+Formally adopted governmental policy instruments must articulate, prioritize, and structurally support interoperability objectives across public administrations.
+Inclusion Criteria:
+1. National digital strategy mandates interoperability.
+2. Cross-ministerial interoperability programs.
+3. Policy directives prioritizing interoperability.
+Exclusion Criteria:
+1. Statutory law specifically (use Public Regulation).
+2. Voluntary frameworks without governmental adoption.
+Example Quotations:
+1. “The Flemish Government launched an interoperability programme: Open Standards for Linked Organisations (OSLO).”
+Literature:
+• EIF (2017)
+• Baldwin et al. (2012)
+• Distinct from Public Regulation in that it covers strategic policy without the binding force of statute</t>
   </si>
   <si>
     <r>
@@ -855,33 +1397,20 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Public Regulation for Interoperability refers to the requirement that binding legal norms, enacted through formal legislative or regulatory instruments, must provide a clear and coherent legal foundation for interoperability arrangements.
-This requirement asserts that interoperable data exchange and cross-organizational coordination depend on explicit statutory authorization and regulatory alignment. Relevant legal instruments include primary legislation (acts of parliament), delegated legislation (e.g., governmental decrees, AMvB), ministerial regulations, and other binding regulatory measures.
-The defining characteristic is the necessity of a legally valid and harmonized body of binding norms that authorizes, structures, and constrains data exchange, data processing, privacy protection, access rights, accountability, and liability.
-Without such statutory and regulatory clarity, interoperability initiatives remain structurally limited regardless of technical or semantic adequacy.
-Inclusion Criteria:
-Use this code when the requirement states that interoperability requires:
-•The existence of a clear legal basis for data sharing or data reuse.
-•Harmonization or alignment of legislation across domains or jurisdictions.
-•Removal of contradictory or fragmented statutory provisions that obstruct data exchange.
-•Explicit legal authorization for cross-organizational or cross-sector information exchange.
-•Legal certainty as a condition for implementing interoperable systems.
-The requirement must be normative and expressed as necessary for enabling or strengthening interoperability.
-Exclusion Criteria:
-Do not use this code when the text refers to:
-•The establishment of a legally mandated authority or coordinating institution.
-•Enforcement mechanisms such as penalties, audits, or incentive schemes.
-•Technical or semantic alignment measures without reference to substantive law.
-•Descriptions of existing legislation without stating its necessity for interoperability.
-•Organizational coordination mechanisms that are not grounded in formal law.
-Theoretical Grounding:
-The European Interoperability Framework identifies legal interoperability as a foundational condition for cross-administrative collaboration, emphasizing that aligned legal frameworks are required to remove barriers to data exchange (European Commission, 2017).
-Regulatory governance theory conceptualizes rule-setting as a prerequisite for coordinated action, distinguishing substantive legal norms from institutional mandate and enforcement (Baldwin, Cave, &amp; Lodge, 2012).
-Empirical research on semantic interoperability demonstrates that privacy law, authorization regimes, and accountability requirements function as structural boundary conditions; without legal clarity and compatibility, interoperability architectures cannot be sustainably implemented (Ojo, Janowski, &amp; Estevez, 2009).
-Links to EIF Recommendation 27:  Ensure that legislation is screened by means of ‘interoperability checks’, to identify any barriers to interoperability. When drafting legislation to establish a European public service, seek to make it consistent with relevant legislation, perform a ‘digital check’ and consider data protection requirements.
-⸻
-</t>
+    <t>Definition:
+Binding legal norms enacted through formal legislative or regulatory instruments must provide a clear and coherent legal foundation for interoperability arrangements.
+Inclusion Criteria:
+1. Clear legal basis for data sharing.
+2. Harmonized legislation across jurisdictions.
+3. Statutory authorization for cross-organizational exchange.
+Exclusion Criteria:
+1. Strategic policy instruments (use Public Policy).
+2. Institutional mandates (use Statutory Interoperability Authority).
+Example Quotations:
+1. “The legal framework has been set by the Directive (2007/2/EC) and interdependent legal acts.”
+Literature:
+• EIF Recommendation 27
+• Baldwin et al. (2012)</t>
   </si>
   <si>
     <r>
@@ -895,31 +1424,20 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Statutory Interoperability Authority refers to the requirement that a legally established and formally authorized public body must be designated to coordinate, regulate, or oversee interoperability arrangements across organizational or jurisdictional boundaries.
-This requirement asserts that sustainable interoperability depends on the existence of a competent authority whose mandate is explicitly grounded in statute or regulation. The authority must possess clearly defined legal competences to assign responsibilities, ensure coherence, coordinate cross-domain alignment, and resolve conflicts related to data exchange or standardization.
-The defining characteristic of this requirement is the legal designation of an institutional authority with formally allocated powers in relation to interoperability.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•A legally established coordinating body or competent authority.
-•A formal mandate assigned by statute or regulation to oversee interoperability.
-•Clearly defined legal competences and responsibilities for interoperability governance.
-•A designated authority responsible for harmonization, standard-setting, or cross-domain coordination.
-•Legal recognition of an institution empowered to resolve cross-organizational conflicts related to data exchange.
-The formulation must express necessity or obligation and remain independent of specific implementation mechanisms.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•The general existence of legislation without reference to a mandated institution.
-•Technical or semantic standards without institutional authorization.
-•Voluntary governance arrangements lacking formal legal mandate.
-•Enforcement instruments such as penalties or incentives, unless linked to the existence of a legally mandated authority.
-•Informal coordination networks without statutory grounding.
-Theoretical Grounding:
-Regulatory governance theory distinguishes rule-setting from institutional mandate and enforcement. Institutional mandate concerns the legally defined authority assigned to specific bodies to coordinate or regulate collective action (Baldwin, Cave, &amp; Lodge, 2012).
-Institutional theory emphasizes that formally established authority structures provide legitimacy, stability, and coordination capacity across organizational boundaries (Scott, 2014). In public-sector interoperability contexts, governance frameworks and clearly allocated responsibilities are consistently identified as critical success factors (European Commission, 2017).
-Empirical studies on e-government interoperability highlight the importance of legally mandated coordinating bodies for achieving sustained cross-organizational alignment 
-Wimmer et al. (2018), however, specifically analyse “interoperability governance models” in Europe and identify concrete, legally mandated bodies required for this purpose, such as the National Digital Commissioner in the Netherlands. They further conclude that formal governing bodies (such as supervisory and preparatory bodies) are necessary to effectively enforce interoperability.
-</t>
+    <t>Definition:
+A legally established and formally authorized public body must be designated to coordinate, regulate, or oversee interoperability arrangements across organizational or jurisdictional boundaries.
+Inclusion Criteria:
+1. Legally mandated coordinating body.
+2. Statutory authority with interoperability competence.
+3. Designated regulator for interoperability.
+Exclusion Criteria:
+1. Voluntary coordinating bodies (use Communities of Interest).
+2. Internal organizational governance (use Governance and Institutional Alignment).
+Example Quotations:
+1. “Two groups of stakeholders were identified: Legally Mandated Organisations (LMOs) and Spatial Data Interest Community (SDIC).”
+Literature:
+• Wimmer et al. (2018)
+• Scott (2014)</t>
   </si>
   <si>
     <r>
@@ -934,28 +1452,18 @@
   </si>
   <si>
     <t>Definition:
-Organizational Requirements refer to normative statements asserting that organizational arrangements are necessary to achieve, enable, or improve interoperability.
-Such requirements indicate that interoperable collaboration depends on the establishment, alignment, or formalization of organizational structures, roles, processes, coordination mechanisms, and governance practices. The defining characteristic is that organizational measures are presented as necessary enabling conditions for sustained cross-organizational or cross-domain interoperability, beyond purely technical or legal provisions.
-Organizational Requirements concern the capability of organizations to coordinate activities, align business processes, allocate responsibilities, and manage shared semantic artefacts in a structured and durable manner.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•Clearly defined roles, responsibilities, or stewardship functions for shared data or semantic artefacts.
-•Alignment or harmonization of business processes across organizational boundaries.
-•Formal governance structures (e.g., boards, coordination bodies, working groups) overseeing interoperability.
-•Institutionalized collaboration mechanisms between agencies, sectors, or levels of government.
-•Agreed procedures for change management, versioning, and lifecycle management of shared models.
-•Capacity-building, knowledge management, or organizational learning mechanisms necessary for interoperability.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•Technical standards, APIs, schemas, or infrastructure without reference to organizational coordination.
-•Legal mandates or statutory authorization without reference to organizational implementation structures.
-•Purely semantic alignment mechanisms (e.g., ontology matching) without organizational embedding.
-•Informal collaboration lacking structural or governance components.
-•Descriptions of existing organizational structures without asserting their necessity for interoperability.
-Theoretical Grounding:
-The European Interoperability Framework conceptualizes organizational interoperability as the alignment of business processes, responsibilities, and expectations necessary to achieve commonly agreed and mutually beneficial goals across public administrations (European Commission, 2017). Organizational alignment is thus positioned as a fundamental prerequisite for enabling semantic and technical collaboration.
-Interoperability governance literature further specifies that sustainable interoperability requires an enabling framework with defined institutional roles, managerial processes, and steering functions (Wimmer, Boneva, &amp; di Giacomo, 2018). Without these structured governance functions to manage change and assure the sustainability of shared semantic enablers, interoperability artefacts risk fragmentation over time.
-Studies on semantic interoperability emphasize that organizational and governance factors—such as clear stewardship, aligned collaboration processes, and defined communities of interest—function as structural boundary conditions and are at least as critical to achieving interoperability as technical requirements (Ojo, Janowski, &amp; Estevez, 2009). Furthermore, e-government research demonstrates that an overwhelming focus on the purely functional and technical side drastically increases the risk of failure, as technical systems are ultimately subordinated to the organizational and social processes of information sharing (Scholl, 2005). These findings robustly support the view that organizational measures function as necessary enabling conditions for achieving and maintaining interoperability.</t>
+Header category. Organizational Requirements refer to normative statements asserting that organizational arrangements are necessary to achieve, enable, or improve interoperability.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• EIF
+• Wimmer et al. (2018)
+• Scholl (2005)
+• Ojo et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -970,28 +1478,22 @@
   </si>
   <si>
     <t>Definition:
-Capability and Learning Infrastructure refer to the requirement that sustainable semantic interoperability necessitates institutionalized competencies, professional roles, and structured learning mechanisms.
-This requirement asserts that interoperability is promoted when organizations develop and maintain human capacities, defined expertise profiles, and knowledge-sharing structures that enable consistent semantic implementation. The focus is on capability-building as a structural enabler of semantic coherence.
-Inclusion Criteria:
-This requirement applies when the statement expresses that semantic interoperability requires:
-•Formal interoperability training programs.
-•Defined competency profiles or learning frameworks.
-•Professionalization of semantic or interoperability roles.
-•Institutionalized knowledge-sharing mechanisms.
-•Access to interoperability knowledge bases.
-•Long-term capacity-building strategies.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•General ICT training unrelated to interoperability.
-•Technical tool deployment without capacity development.
-•Temporary project staffing solutions.
-•Individual expertise without institutional embedding.
-•Generic references to awareness without structured learning systems.
-Theoretical Grounding:
-Organizational capability theory highlights the importance of institutionalized skills and routines for sustained coordination (Rauffet, da Cunha, &amp; Bernard, 2009).
-Enterprise architecture research demonstrates that interoperability depends on structured capability development (Hjort-Madsen, 2006).
-The European Interoperability Framework (2017) emphasizes training and change management as preconditions for interoperability.
-EOSC: “expertise and skills related to semantics”</t>
+Sustainable interoperability necessitates institutionalized competencies, professional roles, and structured learning mechanisms that enable consistent semantic implementation.
+Inclusion Criteria:
+1. Formal interoperability training.
+2. Defined competency profiles.
+3. Knowledge-sharing platforms.
+4. Long-term capacity-building.
+Exclusion Criteria:
+1. Generic ICT training.
+2. Individual expertise without institutional embedding.
+Example Quotations:
+1. “Collaboration is also reflected in the development and sharing of reusable tools to facilitate implementation. The use of thematic platforms helps to share implementation experiences...”
+Literature:
+• Rauffet et al. (2009)
+• Hjort-Madsen (2006)
+• EIF (2017)
+• EOSC</t>
   </si>
   <si>
     <r>
@@ -1005,27 +1507,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Interoperability services must be accompanied by clearly documented terms and conditions of use, including acceptable use policies and service-level agreements (SLAs), that define rights, obligations, liabilities, and performance expectations for users and providers within the ecosystem.
-Terms and conditions of use are defined here as formally specified legal and operational documents governing access to and use of services such as catalogues, registries of semantic artefacts, alignment services, and semantic mediation systems.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Acceptable use policies are documented for interoperability services.
-•Service-level agreements define availability, reliability, or performance commitments.
-•Legal conditions for accessing catalogues, registries, or alignment services are specified.
-•Usage rights, restrictions, or liabilities are clearly articulated.
-•Terms governing the use of semantic alignment or mediation systems are formally described.
-Exclusion Criteria:
-Do not code when:
-•Only technical accessibility is discussed without legal or usage conditions.
-•Governance roles are described without formal user-facing conditions.
-•Licensing of data is discussed without reference to service-level obligations.
-•Informal or implicit norms of use are assumed without documentation.
-Literature:
-•EOSC Interoperability Framework (2021–2023): requirement for clear terms, acceptable use policies, and SLAs in federated interoperability services.
-•FAIR A1.2 (Wilkinson et al., 2016): accessibility may require authentication and authorization, implying explicit conditions of access.
-•Wimmer et al. (2018): interoperability governance requires formalized service agreements.
-</t>
+    <t>Definition:
+Interoperability services must be accompanied by clearly documented terms and conditions of use, including acceptable use policies and service-level agreements (SLAs).
+Inclusion Criteria:
+1. Documented acceptable use policies.
+2. Defined SLAs.
+3. Clear usage rights and restrictions.
+Exclusion Criteria:
+1. Data licensing (use Legal: Clear Copyright and Licensing).
+2. Implicit norms of use.
+Literature:
+• EOSC IF
+• FAIR A1.2
+• Wimmer (2018)
+• No quotations yet
+• retained because the requirement is widely emphasized in cited literature</t>
   </si>
   <si>
     <r>
@@ -1039,6 +1535,25 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Generic collaboration requirement: interoperability requires that relevant actors, including domain experts, technical specialists, public administrations, citizens, and businesses, actively work together, share knowledge, and align their efforts. Use this code for statements that emphasise the need for collaboration as such, without specifying institutional structures, formalised communities, or sustained governance arrangements.
+Inclusion Criteria:
+1. Calls for collaboration between government, industry, researchers, citizens.
+2. Need for joint working between domain and technical experts.
+3. Generic invocations of cooperation as a precondition for interoperability.
+Exclusion Criteria:
+1. Structured, sustained, multi‐stakeholder collaboration with institutional embedding (use Communities of Interest and Collaboration).
+2. Internal organisational coordination (use Governance and Institutional Alignment).
+3. Process alignment across organisations (use Structural Process Alignment).
+Example Quotations:
+1. “Finally, they concluded the article by highlighting the need for collaboration between government agencies, IT professionals, researchers, and citizens to overcome the challenges...”
+2. “They also emphasize the need for effective collaboration between domain experts and technical specialists to develop accurate and useful ontologies.”
+Notes:
+Boundary with Communities of Interest and Collaboration: Collaboration is the generic call for working together; Communities of Interest is the institutionalised, sustained collaboration via formal structures.
+Literature:
+• When the source describes formal working groups, sector forums, or governance bodies, use the latter</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1051,28 +1566,25 @@
   </si>
   <si>
     <t>Definition:
-Communities of Interest and Collaboration refer to the requirement that sustained semantic interoperability depends on the existence of structured, cross-organizational collaboration mechanisms that bring together relevant stakeholders around shared semantic artefacts, standards, and interoperability objectives.
-This requirement asserts that interoperability is promoted when formalized communities or collaborative networks exist in which domain experts, technical specialists, data stewards, policy actors, and governance representatives collectively develop, refine, align, and maintain shared semantic constructs. The focus is on institutionalized interaction structures that enable coordinated meaning-making and continuous alignment across organizational, sectoral, or jurisdictional boundaries.
-Communities of interest are defined here as organized and recurring collaboration forums or networks dedicated to the joint governance, development, or harmonization of interoperability-relevant artefacts.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Formal cross-organizational collaboration structures are established to support interoperability.
-•Multi-stakeholder communities are created to co-develop or maintain standards or semantic artefacts.
-•Regular coordination forums exist for resolving semantic inconsistencies.
-•Domain experts and technical experts are required to collaborate structurally.
-•Cross-sector or cross-border working groups are institutionalized.
-•Collaborative governance arrangements support shared model evolution.
-•Ongoing inter-organizational dialogue is mandated to sustain interoperability.
-Exclusion Criteria:
-Do not code when:
-•Informal communication between organizations is mentioned without institutional structure.
-•Governance authority is described without collaborative interaction mechanisms.
-•Technical integration occurs without stakeholder collaboration.
-•Temporary project groups are formed without sustained institutional embedding.
-•Legal mandates are specified without reference to collaborative practice.
-Theoretical Grounding:
-Organizational and semantic interoperability research emphasizes that sustained alignment of meaning requires structured interaction across institutional boundaries, for example through the forming of project groups and federations (Scholl &amp; Klischewski, 2007). Regulatory governance theory further demonstrates that shared rules and interpretations stabilize through the ongoing discourse within 'epistemic' and 'interpretive communities' (Baldwin, Cave, &amp; Lodge, 2012). In practice, the successful development and maintenance of shared semantic artefacts strongly relies on such community-based repositories and cross-sectoral communities (EOSC, 2021; European Commission, 2017).
-EIF Recommendation 32:  Support the establishment of sector-specific and cross-sectoral communities that aim to create open information specifications and encourage relevant communities to share their results on national and European platforms.</t>
+Sustained semantic interoperability depends on structured cross-organizational collaboration mechanisms that bring together stakeholders around shared semantic artefacts, standards, and interoperability objectives.
+Inclusion Criteria:
+1. Formal cross-organizational collaboration structures.
+2. Multi-stakeholder communities co-developing standards.
+3. Institutionalized working groups.
+4. Cross-sector or cross-border forums.
+Exclusion Criteria:
+1. Informal communication.
+2. Temporary project groups without institutional embedding.
+3. Legal mandates without collaborative practice.
+Example Quotations:
+1. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
+2. “Stakeholders, who participated in the development and implementation process, have a sense of stewardship of the results.”
+Notes:
+ABSORBS: Requirement: Organizational: Collaboration. The original 'Collaboration' code is empirically a subset of this code; recommend folding all quotes here. Note: original spelling 'Communuities' corrected to 'Communities'
+Literature:
+• EIF Recommendation 32
+• Scholl &amp; Klischewski (2007)
+• Baldwin et al. (2012)</t>
   </si>
   <si>
     <r>
@@ -1086,32 +1598,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Organizational Compliance refers to the requirement that public authorities must establish internal mechanisms to ensure consistent adherence to agreed interoperability standards, semantic artefacts, governance procedures, and operational rules.
-This requirement asserts that interoperability is promoted when organizations actively monitor, verify, and enforce conformity with adopted standards and shared specifications within their own structures and processes. The focus is on institutionalized internal adherence mechanisms rather than on external legal enforcement.
-Organizational compliance is defined here as the structured capacity of an organization to ensure that interoperability-related obligations are consistently implemented in operational systems, data practices, and administrative routines.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Organizations must ensure internal adherence to agreed standards or semantic artefacts.
-•Conformance checks or validation procedures are institutionalized within the organization.
-•Internal audit or quality control mechanisms verify compliance with interoperability agreements.
-•Compliance responsibilities are assigned to specific roles or units.
-•Monitoring mechanisms assess whether standards are correctly implemented in practice.
-•Organizations are required to demonstrate conformity with interoperability frameworks.
-Exclusion Criteria:
-Do not code when:
-•Legal enforcement mechanisms such as penalties or statutory sanctions are described (belongs under Legal: Compliance and Enforcement Mechanisms).
-•Governance structures are described without reference to adherence monitoring.
-•Voluntary or informal commitment to standards is mentioned without structured verification.
-•Technical validation mechanisms are discussed solely at infrastructure level without organizational responsibility.
-•Evaluation or feedback mechanisms focus on learning without compliance verification.
-Theoretical Grounding:
-Organizational control theory distinguishes between formal rule-setting and internal compliance mechanisms that ensure consistent implementation (Baldwin, Cave, &amp; Lodge, 2012).
-Wimmer et al. (2018) explicitly define “Interoperability Governance” as a mechanism that provides the functions and structures required to control and monitor whether objectives are achieved and whether compliance with standards is ensured.
-The European Interoperability Framework (European Commission, 2017) highlights monitoring and conformity assessment as organizational conditions for sustainable cross-government interoperability.
-In design science research, artifact instantiation requires organizational embedding and verification to ensure that prescribed constructs are enacted as intended (Hevner et al., 2004).
-EOSC: “interoperability certification mechanisms for service providers,”
-</t>
+    <t>Definition:
+Public authorities must establish internal mechanisms to ensure consistent adherence to agreed interoperability standards, semantic artefacts, governance procedures, and operational rules.
+Inclusion Criteria:
+1. Internal conformance checks.
+2. Internal audit or quality control on adherence.
+3. Compliance roles assigned within organization.
+Exclusion Criteria:
+1. Legal sanctions (use Legal: Compliance and Enforcement).
+2. Evaluation/feedback for learning (use Evaluation and Feedback Mechanisms).
+Example Quotations:
+1. “The 7th star is given to a data publication, if the publication includes some kind of evaluation that the data actually conforms to the provided schemas...”
+Notes:
+Note: original spelling 'Mechanismes' corrected
+Literature:
+• Baldwin et al. (2012)
+• Wimmer et al. (2018)
+• EIF (2017)
+• Hevner et al. (2004)
+• EOSC</t>
   </si>
   <si>
     <r>
@@ -1125,32 +1630,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Evaluation and Feedback Mechanisms refer to the requirement that public authorities must institutionalize structured processes to assess, review, and iteratively improve interoperability arrangements over time.
-This requirement asserts that interoperability is sustained when organizations systematically evaluate whether adopted standards, semantic artefacts, governance arrangements, and aligned processes function as intended in practice, and when evaluation outcomes inform corrective action, refinement, or redesign.
-Evaluation and feedback mechanisms are defined here as formalized procedures that generate evidence about interoperability performance and feed that evidence back into governance, operational practice, or artefact evolution.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Interoperability arrangements must be periodically reviewed or assessed.
-•Monitoring systems evaluate the effectiveness or maturity of interoperability.
-•Metrics or performance indicators measure interoperability outcomes.
-•Structured review cycles exist for standards, models, or governance frameworks.
-•Evaluation findings must trigger revision, refinement, or redesign.
-•Mechanisms detect semantic drift, misalignment, or unintended consequences.
-•Feedback loops connect operational experience to policy or model updates.
-Exclusion Criteria:
-Do not code when:
-•The statement concerns internal adherence verification only (belongs under Organizational: Compliance).
-•Legal enforcement or sanctioning mechanisms are described (belongs under Legal: Compliance and Enforcement).
-•Governance authority is described without evaluation processes.
-•Initial design or development of standards is discussed without review cycles.
-•Informal feedback is mentioned without institutionalized mechanisms.
-•Technical validation is described solely at system level without organizational review.
-Theoretical Grounding:
-Measuring, Benchmarking &amp; Improving (MB&amp;I) (Maheshwari &amp; Janssen, 2014): .
-The European Interoperability Framework (European Commission, 2017) stresses monitoring, benchmarking, and review processes as necessary for sustainable cross-government interoperability.
-EIF: Recommendation 19:  Evaluate the effectiveness and efficiency of different interoperability solutions and technological options considering user needs, proportionality and balance between costs and benefits.
-</t>
+    <t>Definition:
+Public authorities must institutionalize structured processes to assess, review, and iteratively improve interoperability arrangements over time, with feedback loops connecting operational experience to governance and artefact evolution.
+Inclusion Criteria:
+1. Periodic review of interoperability arrangements.
+2. Performance metrics and indicators.
+3. Mechanisms detecting semantic drift.
+4. Feedback loops to policy or artefact updates.
+Exclusion Criteria:
+1. Internal compliance verification only (use Compliance Mechanisms).
+2. Legal sanctioning.
+Example Quotations:
+1. “The mid-term evaluation of the status of the Directive's implementation was carried out in 2014.”
+2. “The European Commission is supporting this community by coordinating the INSPIRE Thematic Clusters Platform.”
+Literature:
+• Maheshwari &amp; Janssen (2014)
+• EIF Recommendation 19</t>
   </si>
   <si>
     <r>
@@ -1164,38 +1659,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Governance and Institutional Alignment refer to the requirement that public authorities must be organizationally structured to ensure the consistent application, monitoring, and maintenance of agreed interoperability standards and shared specifications.
-This requirement asserts that interoperability is promoted when formal governance arrangements, clearly defined roles, decision-making procedures, and data management capabilities are in place to operationalize existing standards in practice. The focus is not on the existence of standards themselves, but on the institutional capacity to implement, enforce, and sustain compliance within individual public organizations, across the public sector, and between Member States.
-Governance in this sense includes stewardship responsibilities, accountability mechanisms, structured coordination, and organizational embedding that ensure standards are actively used rather than merely adopted in principle.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•Organizational structures ensuring the application of agreed standards.
-•Clearly defined roles such as data owner, semantic steward, or compliance authority.
-•Processes for implementing, monitoring, and maintaining compliance with standards.
-•Data management capabilities supporting consistent interpretation and use of shared models.
-•Institutionalized coordination mechanisms ensuring adherence across departments or jurisdictions.
-•Formal mandates or governance frameworks embedding standards into operational practice.
-•Allocation of resources to sustain implementation and compliance efforts.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•The mere existence or selection of standards without reference to their organizational application.
-•Purely technical integration or system architecture.
-•Legislative harmonization without operational governance arrangements.
-•Temporary project coordination without sustained institutional embedding.
-•Informal collaboration lacking defined roles, responsibilities, or accountability mechanisms.
-Theoretical Grounding:
-Institutional governance theory emphasizes that durable coordination depends on formalized authority structures and accountability mechanisms (Pardo, Nam, &amp; Burke, 2012).
-Wimmer et al. (2018), however, specifically analyse “interoperability governance models” in Europe and identify concrete, legally mandated bodies required for this purpose, such as the National Digital Commissioner in the Netherlands. They further conclude that formal governing bodies (such as supervisory and preparatory bodies) are necessary to effectively enforce interoperability.
-The European Interoperability Framework (2017) highlights governance, coordination, and change management structures as prerequisites for sustained interoperability implementation.
-EOSC: “governance framework that will deal with interoperability across organisations and disciplines”
-EIF: Recommendation 20:  Ensure holistic governance of interoperability activities across administrative levels and sectors.
-EIF Recommendation 25:  Ensure interoperability and coordination over time when operating and delivering integrated public services by putting in place the necessary governance structure.
-EIF Recommendation 26:  Establish interoperability agreements in all layers, complemented by operational agreements and change management procedures.
-Links to EIF Recommendation 28:  Document your business processes using commonly accepted modelling techniques and agree on how these processes should be aligned to deliver a European public service.
-Links to EIF Recommendation 29:  Clarify and formalise your organisational relationships for establishing and operating European public services. 
-Links to EIF Recommendation 31:  Put in place an information management strategy at the highest possible level to avoid fragmentation and duplication. Management of metadata, master data and reference data should be prioritised.
-</t>
+    <t>Definition:
+Public authorities must be organizationally structured to ensure the consistent application, monitoring, and maintenance of agreed interoperability standards through formal governance arrangements, defined roles, and decision procedures.
+Inclusion Criteria:
+1. Stewardship roles for shared data.
+2. Decision-making procedures for interoperability.
+3. Formal governance frameworks.
+4. Allocation of resources for sustained implementation.
+Exclusion Criteria:
+1. Mere existence of standards.
+2. Legal mandates without operational governance.
+3. Informal collaboration without accountability.
+Example Quotations:
+1. “In order to overcome these challenges, strong coordination was needed between stakeholders at European and national levels.”
+2. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
+Literature:
+• Pardo et al. (2012)
+• Wimmer et al. (2018)
+• EIF Recommendations 20, 25, 26, 28, 29, 31
+• EOSC</t>
   </si>
   <si>
     <r>
@@ -1210,30 +1692,21 @@
   </si>
   <si>
     <t>Definition:
-Incentive Strategy refers to the requirement that public authorities must establish structured motivational and alignment mechanisms that encourage organizations and stakeholders to adopt, implement, and sustain interoperability standards, semantic artefacts, and shared practices.
-This requirement asserts that interoperability is promoted when actors are provided with institutional, financial, reputational, or strategic incentives that make compliance with shared constructs beneficial or advantageous. The focus is on proactive alignment mechanisms that stimulate voluntary adherence and sustained participation, rather than on coercive legal enforcement.
-An incentive strategy is defined here as an intentionally designed set of mechanisms that align organizational behavior with interoperability objectives through positive or strategic reinforcement.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Financial incentives or funding conditions are linked to interoperability adoption.
-•Performance metrics or benchmarking influence organizational reputation.
-•Certification or recognition schemes reward interoperability compliance.
-•Access to shared infrastructure or services is conditional upon alignment.
-•Strategic benefits (e.g., efficiency gains, data access privileges) are structured to encourage adherence.
-•Participation in interoperability frameworks is supported by institutional rewards.
-•Incentive mechanisms are designed to stimulate collaboration or standard adoption.
-The requirement must concern motivational alignment mechanisms rather than mandatory compliance or sanctioning.
-Exclusion Criteria:
-Do not code when:
-•Legal penalties or sanctions are described (belongs under Legal: Compliance and Enforcement Mechanisms).
-•Internal monitoring mechanisms verify adherence without motivational instruments (belongs under Organizational: Compliance).
-•Governance authority is described without incentive alignment.
-•Voluntary cooperation is mentioned without structured incentive design.
-•Technical requirements are specified without behavioral alignment mechanisms.
-Theoretical Grounding:
-Institutional economics and regulatory governance theory distinguish between coercive enforcement and incentive-based regulatory strategies (Baldwin, Cave, &amp; Lodge, 2012).
-Interorganizational collaboration research demonstrates that sustained alignment often depends on incentive compatibility between participating actors (Pardo &amp; Tayi, 2007).
-The European Interoperability Framework (European Commission, 2017) highlights that policy alignment, funding conditions, and strategic coordination mechanisms can stimulate interoperability adoption across administrations.</t>
+Public authorities must establish structured motivational and alignment mechanisms that encourage organizations and stakeholders to adopt, implement, and sustain interoperability standards.
+Inclusion Criteria:
+1. Funding linked to interoperability adoption.
+2. Performance benchmarking influencing reputation.
+3. Certification or recognition schemes.
+4. Strategic benefits structured to encourage adherence.
+Exclusion Criteria:
+1. Legal sanctions (use Legal: Compliance and Enforcement).
+2. Internal monitoring (use Compliance Mechanisms).
+Example Quotations:
+1. “The collaboration between experts in Member States' public and private sectors, software solution providers, open source communities...”
+Literature:
+• Baldwin et al. (2012)
+• Pardo &amp; Tayi (2007)
+• EIF (2017)</t>
   </si>
   <si>
     <r>
@@ -1247,34 +1720,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Operational Use and Institutional Embedding of Semantic Constructs refer to the requirement that agreed semantic constructs, standards, and shared specifications are actively and consistently applied and reused in everyday organizational practice.
-Interoperability is promoted when semantic artifacts are not merely selected or governed, but systematically integrated into operational processes, information systems, service delivery routines, and decision-making procedures. The focus is on the effective enactment of constructs in real-world administrative workflows, ensuring that shared models shape how data are captured, interpreted, exchanged, and maintained.
-This requirement applies within single organizations and across organizational, sectoral, administrative, or national contexts wherever interoperability depends on sustained and consistent practical application.
-Inclusion Criteria:
-This requirement applies when interoperability requires:
-• Actual application of agreed information models in operational systems.
-• Routine use of shared vocabularies or taxonomies in data entry and processing.
-• Embedding of standards into software configurations or business rules.
-• Use of shared semantic constructs in decision-making or service provision.
-• Consistent interpretation of shared definitions in administrative practice.
-• Institutional enforcement of construct use in day-to-day operations.
-• Alignment between documented standards and actual operational behavior.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-• Design or development of semantic constructs.
-• Selection or cataloguing of standards without operational application.
-• Governance roles without reference to practical enactment.
-• Monitoring or evaluation activities without reference to actual use.
-• Temporary pilot implementations without institutional embedding.
-• Purely technical connectivity without semantic enactment.
-Theoretical Grounding:
-In design science research, artifacts must be instantiated and used in organizational contexts to demonstrate utility (Hevner et al., 2004). The “build–evaluate” cycle presupposes actual use as the context in which relevance and performance emerge.
-Institutional theory emphasizes that formal artifacts only produce coordination effects when enacted through routinized organizational practice (Orlikowski, 2000). 
-Links to EIF Recommendation 34:  Use the conceptual model for European public services to design new services or reengineer existing ones and reuse, whenever possible, existing service and data components.
-EIF Recommendation 6:  Reuse and share solutions, and cooperate in the development of joint solutions when implementing European public services.
-EIF Recommendation 7:  Reuse and share information and data when implementing European public services, unless certain privacy or confidentiality restrictions apply.
-</t>
+    <t>Definition:
+Agreed semantic constructs, standards, and shared specifications must be actively and consistently applied and reused in everyday organizational practice, embedded into operational processes, systems, and decision-making.
+Inclusion Criteria:
+1. Routine use of shared vocabularies in data entry.
+2. Embedding of standards into software configurations.
+3. Use of shared constructs in service delivery.
+4. Alignment between documented standards and actual behavior.
+Exclusion Criteria:
+1. Selection or cataloguing of standards without operational application.
+2. Pilot implementations without institutional embedding.
+Example Quotations:
+1. “The Address Registry is deployed on a cloud infrastructure: Microsoft Azure. All the components are available as runnable services using Docker.”
+Literature:
+• Hevner et al. (2004)
+• Orlikowski (2000)
+• EIF Recommendations 6, 7, 34</t>
   </si>
   <si>
     <r>
@@ -1288,6 +1749,22 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Sustained interoperability requires explicit political support, including endorsement, sponsorship, and ongoing legitimization by elected and executive decision makers.
+Inclusion Criteria:
+1. Political endorsement of interoperability initiatives.
+2. Executive sponsorship at ministerial level.
+3. Continuous political backing for sustained programmes.
+Exclusion Criteria:
+1. Legal mandates without political backing (use Public Policy).
+2. Internal organizational sponsorship without political dimension (use Governance).
+Example Quotations:
+1. “Political support is essential, for collecting sponsoring and gaining authority and engagement.”
+2. “Both the bottom-up and top-down approach were important to create the necessary political support.”
+Notes:
+Newly defined; complement to Challenge: Organizational: Lack of Support.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1300,32 +1777,21 @@
   </si>
   <si>
     <t>Definition:
-Public Asset Orientation Toward Data refers to the requirement that public authorities institutionalize a normative understanding of data and information as strategic public assets whose value extends beyond their immediate administrative use.
-This requirement asserts that sustainable semantic interoperability depends on an organizational orientation in which data are perceived as shared, reusable, and durable public resources. Under this orientation, data are intentionally generated, documented, structured, and preserved in ways that anticipate reuse across organizational and domain boundaries.
-The focus is on the institutionalized perception and treatment of data as enduring public resources, rather than on specific governance mechanisms, legal mandates, or technical infrastructure.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data be perceived or treated as public assets.
-•Data management be guided by long-term public value considerations.
-•Data generation anticipate reuse beyond original administrative purpose.
-•Information be managed with cross-organizational or cross-domain applicability in mind.
-•Public authorities adopt a culture or principle of data-as-asset.
-•Data sharing and preservation are framed as intrinsic public responsibilities.
-•Administrative practices reflect recognition of data’s strategic and collective value.
-The emphasis must concern normative orientation toward data, not technical implementation details.
-Exclusion Criteria:
-Do not code when:
-•Only specific governance structures or stewardship roles are described.
-•Legal authorization for data sharing is specified without asset framing.
-•Technical infrastructure requirements are discussed.
-•Data quality requirements are defined without reference to public value orientation.
-•Open data publication is mentioned without a broader data-as-asset principle.
-Theoretical Grounding:
-The European Interoperability Framework frames data and information as public assets whose lifecycle management underpins interoperability.
-Public value theory conceptualizes government information as a strategic resource contributing to collective societal benefit rather than merely administrative efficiency (Dawes, 2008).
-Information governance literature distinguishes between transactional data handling and asset-oriented data management, emphasizing that cross-organizational reuse requires anticipatory structuring and preservation.
-Organizational theory further suggests that institutionalized cognitive frames shape how artefacts are designed and managed; treating data as assets influences modelling, documentation, and interoperability practices (Scott, 2014).
-EIF Recommendation 30:  Perceive data and information as a public asset that should be appropriately generated, collected, managed, shared, protected and preserved.</t>
+Public authorities must institutionalize a normative understanding of data and information as strategic public assets whose value extends beyond their immediate administrative use.
+Inclusion Criteria:
+1. Data treated as public assets.
+2. Long-term public value considerations.
+3. Anticipation of cross-organizational reuse.
+4. Data sharing framed as a public responsibility.
+Exclusion Criteria:
+1. Specific governance structures (use Governance and Institutional Alignment).
+2. Open data publication mentioned without asset framing.
+Literature:
+• Dawes (2008)
+• Scott (2014)
+• EIF Recommendation 30
+• No quotations in current dataset
+• retained because of strong theoretical grounding</t>
   </si>
   <si>
     <r>
@@ -1340,32 +1806,23 @@
   </si>
   <si>
     <t>Definition:
-Semantic Construct Design and Maintenance refer to the requirement that public authorities must establish structured processes for the systematic design, specification, revision, and long-term maintenance of shared semantic artefacts used for interoperability.
-This requirement asserts that interoperability is promoted when semantic constructs such as conceptual models, vocabularies, ontologies, taxonomies, metadata schemas, and reference data are deliberately engineered, formally documented, version-controlled, and periodically updated through institutionalized processes.
-Semantic construct design concerns the initial modeling and formalization of shared meaning. Maintenance concerns controlled evolution, including versioning, change management, impact analysis, and alignment with related artefacts over time.
-The focus is on lifecycle management of meaning-bearing artefacts as organizational responsibilities.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Shared semantic artefacts must be systematically designed or modeled.
-•Formal modeling methodologies are mandated for construct development.
-•Versioning and change management procedures exist for semantic artefacts.
-•Impact analysis is required before modifying shared definitions or models.
-•Maintenance procedures ensure semantic consistency over time.
-•Revision cycles are institutionalized for shared vocabularies or schemas.
-•Documentation standards govern the specification of semantic constructs.
-•Long-term stewardship responsibilities are assigned for construct upkeep.
-Exclusion Criteria:
-Do not code when:
-•Standards are merely selected or adopted without reference to their design or maintenance.
-•Operational use of constructs is described without lifecycle management.
-•Governance authority is mentioned without reference to artefact design or evolution.
-•Evaluation mechanisms are described without connection to construct revision.
-•Technical encoding formats are specified without organizational responsibility for construct development.
-•Informal updates occur without institutionalized change procedures.
-Theoretical Grounding:
-Ontology engineering literature emphasizes the need for formalized development methodologies and controlled evolution processes to prevent semantic drift (Guarino, 1998; Euzenat &amp; Shvaiko, 2013).
-Interoperability governance research shows that uncontrolled modification of shared artefacts leads to divergence and fragmentation across organizations (Kubicek, Cimander, &amp; Scholl, 2011).
-The European Interoperability Framework (European Commission, 2017) and EOSC highlight lifecycle governance and maintenance of shared semantic artefacts as critical for sustainable cross-domain interoperability.</t>
+Public authorities must establish structured processes for the systematic design, specification, revision, and long-term maintenance of shared semantic artefacts used for interoperability.
+Inclusion Criteria:
+1. Formal modeling methodologies for construct development.
+2. Versioning and change management procedures.
+3. Impact analysis before changes.
+4. Long-term stewardship responsibilities.
+Exclusion Criteria:
+1. Mere selection of standards (use Standardization and Semantic Control).
+2. Operational use without lifecycle management (use Operational Use).
+Example Quotations:
+1. “This was achieved by implementing a process and methodology for developing semantic agreements, based on the ISA methodology.”
+Literature:
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013)
+• Kubicek et al. (2011)
+• EIF
+• EOSC</t>
   </si>
   <si>
     <r>
@@ -1380,31 +1837,22 @@
   </si>
   <si>
     <t>Definition:
-Standardization and Semantic Control refer to the requirement that public authorities, individually, across government, and across Member States, must systematically govern the selection, adoption, documentation, versioning, alignment, and compliance monitoring of interoperability-relevant artifacts.
-This requirement asserts that sustainable interoperability is promoted when structured and institutionalized procedures exist to manage meaning-bearing and coordination-enabling artifacts, including conceptual models, vocabularies, taxonomies, metadata schemes, reference data, process specifications, and interoperability frameworks. The focus is on organizational and inter-organizational control mechanisms that prevent uncontrolled divergence of definitions and specifications within a single public body, across organizations, and between jurisdictions, thereby ensuring semantic stability over time.
-Inclusion Criteria:
-This requirement applies when the statement expresses that interoperability requires:
-•Structured procedures for selecting standards, specifications, or shared artifacts.
-•Alignment with national, sectoral, or EU-level catalogues, reference models, or frameworks.
-•Metadata or reference data governance arrangements.
-•Formal versioning and change governance of information models or shared artifacts.
-•Compliance assessment or conformity testing of adopted artifacts.
-•Systematic documentation and lifecycle management of interoperability-relevant artifacts.
-•Mechanisms ensuring consistency of definitions across departments, organizations, or Member States.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-•Purely technical infrastructure or protocol standards without governance of shared meaning.
-•Legislative rule-setting without reference to governance of shared artifacts.
-•Informal or voluntary use of standards without structured oversight or lifecycle management.
-•Isolated modeling exercises lacking organizational or cross-organizational embedding.
-•Ad hoc mappings or translations not institutionally governed.
-•General references to “using standards” without structured control mechanisms.
-Theoretical Grounding:
-Interoperability governance research highlights that structured management and sustained governance of shared artifacts across administrative levels is necessary to maintain alignment and ensure sustainability (Wimmer, Boneva, &amp; di Giacomo, 2018). Federated ecosystem literature emphasizes the critical need for common repositories of semantic artifacts backed by clear governance frameworks and systematic monitoring procedures (EOSC, 2021; Wimmer et al., 2018). Furthermore, the European Interoperability Framework (2017) calls for structured selection, monitoring, and compliance processes for standards and specifications in cross-government and cross-border settings:
-EIF Recommendation 21: Put in place processes to select relevant standards and specifications, evaluate them, monitor their implementation, check compliance and test their interoperability.
-EIF Recommendation 22: Use a structured, transparent, objective and common approach to assessing and selecting standards and specifications. Take into account relevant EU recommendations and seek to make the approach consistent across borders.
-EIF Recommendation 23: Consult relevant catalogues of standards, specifications and guidelines at national and EU level, in accordance with your NIF and relevant DIFs, when procuring and developing ICT solutions.
-EIF Recommendation 24: Actively participate in standardisation work relevant to your needs to ensure your requirements are met.</t>
+Public authorities must systematically govern the selection, adoption, documentation, versioning, alignment, and compliance monitoring of interoperability-relevant artefacts across organizations and jurisdictions.
+Inclusion Criteria:
+1. Selection processes for standards.
+2. Alignment with national or EU catalogues.
+3. Reference data governance.
+4. Versioning and change governance.
+Exclusion Criteria:
+1. Purely technical infrastructure (use Technical: Existence of Shared Technical Standards).
+2. Legislative rule-setting (use Public Regulation).
+Example Quotations:
+1. “This has led to a demand for stable, governed data standards.”
+2. “While implementing the address vocabulary, we stumbled on competing international semantic standards and difficult choices on how to extend them to fit the local context.”
+Literature:
+• Wimmer et al. (2018)
+• EOSC
+• EIF Recommendations 21, 22, 23, 24</t>
   </si>
   <si>
     <r>
@@ -1419,31 +1867,24 @@
   </si>
   <si>
     <t>Definition:
-Structural and Procedural Alignment refers to the requirement that public authorities institutionalize coherent organizational structures and aligned operational procedures to enable interoperability.
-Interoperability is promoted when organizations are structurally configured and procedurally aligned to operate in coordinated multi-level and cross-domain environments, within a single authority and across organizational, sectoral, administrative, or national boundaries. This includes integration into national or supranational strategies and infrastructures, as well as harmonized business processes, change management routines, and coordinated lifecycle management of shared semantic assets.
-Inclusion Criteria:
-This requirement applies when interoperability is said to require:
-• Institutional coordination across organizational or administrative boundaries.
-• Structural alignment across local, regional, national, or supranational levels.
-• Cross-border interoperability arrangements.
-• Alignment with national or European digital strategies or infrastructures.
-• Harmonized business processes within or across authorities.
-• Shared procedures for standard development, adoption, and change management.
-• Aligned data submission, validation, or quality assurance procedures.
-• Standardized documentation, review, or lifecycle management practices.
-• Formalized joint decision-making or escalation mechanisms.
-Exclusion Criteria:
-This requirement does not apply when the statement concerns:
-• Internal improvements without broader coordination relevance.
-• Purely technical connectivity.
-• Legal mandates without structural or procedural embedding.
-• Governance roles without operational alignment.
-• Selection of standards without coordinated implementation.
-• Informal, non-institutionalized collaboration.
-Theoretical Grounding:
-Interorganizational integration research demonstrates that interoperability depends on structural coordination beyond technical exchange (Pardo &amp; Tayi, 2007). Process integration studies show that misaligned administrative routines undermine interoperability (Scholl &amp; Klischewski, 2007). Organizational interoperability maturity models identify harmonized processes and institutionalized coordination as core dimensions (Maheshwari &amp; Janssen, 2014).
-Scholl (2005). In “Interoperability in e-Government: More than Just Smart Middleware,” Scholl argues unequivocally that purely technical middleware is insufficient. He emphasizes that information exchange between public agencies encounters deliberately erected organizational barriers, and that rigorous alignment of organizational and social processes is required for interoperability to succeed.
-The European Interoperability Framework (European Commission, 2017) positions structural and procedural alignment as foundational conditions for sustainable public-sector interoperability.</t>
+Public authorities must institutionalize coherent organizational structures and aligned operational procedures to enable interoperability across organizational, sectoral, administrative, or national boundaries.
+Inclusion Criteria:
+1. Institutional coordination across boundaries.
+2. Harmonized business processes.
+3. Aligned data submission and validation procedures.
+4. Joint decision-making mechanisms.
+Exclusion Criteria:
+1. Internal improvements without coordination relevance.
+2. Purely technical connectivity.
+3. Informal collaboration.
+Example Quotations:
+1. “The streamlined data governance approach leads to the establishment of an efficient governance structure. In some cases, such as the Dutch 'public geo datasets at your service – PDOK'...”
+Literature:
+• Pardo &amp; Tayi (2007)
+• Scholl &amp; Klischewski (2007)
+• Maheshwari &amp; Janssen (2014)
+• Scholl (2005)
+• EIF (2017)</t>
   </si>
   <si>
     <r>
@@ -1458,33 +1899,20 @@
   </si>
   <si>
     <t>Definition:
-Semantic requirements are the normative conditions that data, metadata, and semantic artefacts must satisfy in order to ensure shared meaning, interpretability, traceability, and reliable reuse across organizational, disciplinary, or system boundaries.
-They extend the FAIR principles (Wilkinson et al., 2016), including their elaboration in FAIR 2.0, and are further operationalized within federated infrastructures such as EOSC. Semantic requirements concern the explicit articulation of meaning, the use of shared semantic standards, structured and persistent metadata, formal representation syntax, documented provenance, and adequate data quality.
-Semantic requirements operate at the level of meaning and interpretation. They ensure that data exchanged across systems can be consistently understood beyond their original production context and can be responsibly integrated and reused.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•The meaning of data or metadata must be clearly specified or described.
-•Shared vocabularies, ontologies, or semantic standards are required.
-•Metadata are structurally defined to support interpretation.
-•Provenance information is required to reconstruct origin or transformation history.
-•Data quality adequacy is mandated to ensure reliable interpretation.
-•Formal representation syntax is required to encode semantic artefacts.
-•Semantic artefacts must be maintained or governed to ensure cross-community interpretability.
-•Ecosystem-level semantic consistency (e.g., EOSC common semantic artefacts) is required.
-Exclusion Criteria:
-Do not code when:
-•Only technical connectivity or communication protocols are described without semantic implications.
-•Organizational governance mechanisms are discussed without reference to meaning or interpretation.
-•Legal conditions (e.g., licensing) are described without semantic relevance.
-•Discovery, indexing, or accessibility mechanisms are specified without reference to meaning.
-•Data quality improvement processes are described without connection to semantic interpretability.
-Literature:
-•FAIR Guiding Principles (Wilkinson et al., 2016):
-•FAIR 2.0 (Vogt et al., 2024): distinction between entity-level and proposition-level interoperability; emphasis on semantic artefact alignment and cross-schema mappings.
-•EOSC Interoperability Framework (2021–2023): requirement for common semantic artefacts, shared metadata standards, federation mechanisms, sustainability of semantic infrastructures, and cross-community interpretability.
-•Guarino (1998): ontological commitment and explicit semantic specification in information systems.
-•Euzenat &amp; Shvaiko (2013): ontology matching and semantic alignment as core interoperability mechanisms.
-•Peristeras et al. (2009): conceptual and semantic layers of interoperability in model-driven architectures.</t>
+Header category. Semantic requirements are the normative conditions that data, metadata, and semantic artefacts must satisfy to ensure shared meaning, interpretability, traceability, and reliable reuse across boundaries.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• FAIR
+• FAIR 2.0
+• EOSC
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013)
+• Peristeras et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -1499,28 +1927,23 @@
   </si>
   <si>
     <t>Definition:
-Data resources must meet explicitly defined and domain-appropriate quality criteria in order to support reliable interpretation, integration, and reuse across organizational or system boundaries. Data quality is understood as the degree to which data are fit for their intended interoperable use.
-Adequate data quality includes, as contextually relevant, dimensions such as accuracy, completeness, consistency, timeliness, validity, and coherence with domain constraints.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data conform to defined quality criteria or validation rules.
-•Data satisfy accuracy, completeness, or consistency thresholds.
-•Formal validation, conformance testing, or quality assurance mechanisms are mandated.
-•Data are required to be “fit for purpose” in an interoperable context.
-•Semantic consistency with defined domain constraints is required.
-Exclusion Criteria:
-Do not code when:
-•Only documentation of quality (without requirement of adequacy) is discussed.
-•Governance or provenance mechanisms are mentioned without reference to quality performance.
-•Quality improvement processes are described without normative quality criteria.
-•Accessibility or metadata richness is discussed without reference to intrinsic data quality.
-Literature:
-•FAIR R1 (Wilkinson et al., 2016): metadata must describe attributes relevant to reuse, implicitly presupposing adequacy for reuse.
-•Wang &amp; Strong (1996): data quality dimensions and “fitness for use” framework.
-•Batini &amp; Scannapieco (2016): methodological foundations of data quality management.
-•FAIR 2.0 (Vogt et al., 2024) further strengthens this perspective by introducing an explicit extension (Principle R1.4), which requires metadata to specify the certainty level of semantic content in order to enable trustworthy reuse, thereby formulating a concrete requirement for adequate data and metadata quality within semantic networks.
-EIF Recommendation 40:  Create and follow data quality assurance plans for base registries and related master data.
-EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.</t>
+Data resources must meet explicitly defined and domain-appropriate quality criteria to support reliable interpretation, integration, and reuse.
+Inclusion Criteria:
+1. Conformance to quality criteria.
+2. Accuracy, completeness, consistency thresholds.
+3. Validation and quality assurance mechanisms.
+4. Fitness for purpose in interoperable context.
+Exclusion Criteria:
+1. Documentation of quality without normative criteria.
+2. Provenance only (use Explicit Provenance Documentation).
+Literature:
+• FAIR R1
+• Wang &amp; Strong (1996)
+• Batini &amp; Scannapieco (2016)
+• FAIR 2.0
+• EIF Recommendations 40, 42
+• No quotations yet
+• retained because of strong theoretical grounding</t>
   </si>
   <si>
     <r>
@@ -1534,35 +1957,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-For semantic interoperability to be achieved, domain-relevant semantic standards must exist and be explicitly referenced in the specification, modeling, or representation of data and metadata. These standards provide shared conceptual definitions, constraints, and semantic structures recognized within a disciplinary, sectoral, or institutional community.
-Domain-relevant semantic standards are defined here as formally specified and publicly documented conceptual models, vocabularies, ontologies, or reference schemas that structure meaning within a particular domain of practice.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data or metadata reference recognized domain-specific semantic standards.
-•Sectoral ontologies, vocabularies, or reference models are used or mandated.
-•Domain-level conceptual harmonization is grounded in formally defined standards.
-•Interoperability is supported through alignment with community-endorsed semantic artefacts.
-Exclusion Criteria:
-Do not code when:
-•Conceptual models are organization-specific without external recognition.
-•Standards are mentioned only generically without domain specification.
-•Alignment concerns only technical formats or transport protocols.
-•Informal consensus or practice is referenced without formal standardization.
-Literature:
-•FAIR R1.3 (Wilkinson et al., 2016): use of community standards for metadata and data.
-•Peristeras et al. (2009), in “Model-driven eGovernment Interoperability,” provide a comprehensive analysis of domain-specific semantic standards—such as the Governance Enterprise Architecture (GEA)—and ontologies designed to standardize e-government, thereby offering a strong empirical and theoretical foundation for requiring domain-relevant semantic standards within the public sector.
-•Wimmer et al. (2018): governance and institutionalization of interoperability standards.
-•Guarino (1998): formal ontologies as shared domain conceptualizations.
-•EOSC: “common semantic artefacts across communities”
-Links to EIF Recommendation 4:  Give preference to open specifications, taking due account of the coverage of functional needs, maturity and market support and innovation.
-EIF Recommendation 7:  Reuse and share information and data when implementing European public services, unless certain privacy or confidentiality restrictions apply.
-Links to EIF: Recommendation 9:  Ensure data portability, namely that data is easily transferable between systems and applications supporting the implementation and evolution of European public services without unjustified restrictions, if legally possible. 
-EIF Recommendation 33:  Use open specifications, where available, to ensure technical interoperability when establishing European public services.
-Links to EIF Recommendation 34:  Use the conceptual model for European public services to design new services or reengineer existing ones and reuse, whenever possible, existing service and data components.
-Links to EIF Recommendation 35:  Decide on a common scheme for interconnecting loosely coupled service components and put in place and maintain the necessary infrastructure for establishing and maintaining European public services.
-Links to EIF Recommendation 38:  Develop interfaces with base registries and authoritative sources of information, publish the semantic and technical means and documentation needed for others to connect and reuse available information.
-</t>
+    <t>Definition:
+Domain-relevant semantic standards must exist and be explicitly referenced in the specification, modeling, or representation of data and metadata.
+Inclusion Criteria:
+1. Reference to domain-specific standards.
+2. Sectoral ontologies or vocabularies mandated.
+3. Domain conceptual harmonization through standards.
+Exclusion Criteria:
+1. Organization-specific models without external recognition.
+2. Generic technical standards (use Technical: Existence of Shared Technical Standards).
+Example Quotations:
+1. “This has led to a demand for stable, governed data standards.”
+2. “The Directive does not require a collection of new data, instead existing data should be transformed to fit agreed data models.”
+Literature:
+• FAIR R1.3
+• Peristeras et al. (2009)
+• Wimmer et al. (2018)
+• Guarino (1998)
+• EOSC
+• EIF Recommendations 4, 7, 9, 33, 34, 35, 38</t>
   </si>
   <si>
     <r>
@@ -1576,6 +1989,19 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Data resources must be accompanied by metadata, irrespective of structuring or independence; this is the precondition for the more demanding requirement of structured and independently accessible metadata.
+Inclusion Criteria:
+1. Presence of any metadata for data resources.
+2. Documented existence of metadata.
+Exclusion Criteria:
+1. Structured metadata accessible independently (use Structured and Independently Accessible Metadata).
+Example Quotations:
+1. “The Directive does not require a collection of new data, instead existing data should be transformed to fit agreed data models.”
+Notes:
+Newly defined as a baseline precondition. Note: original spelling 'Meta-data' standardized to 'Metadata'.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1588,27 +2014,24 @@
   </si>
   <si>
     <t>Definition:
-Data and metadata must be accompanied by structured and sufficiently detailed documentation of their origin, creation process, transformation history, and responsible actors. Provenance information must enable reconstruction of how a data resource came into existence and how it has been modified over time.
-Provenance is defined here as the formally recorded account of the source, production context, processing steps, and custodianship of a data resource, such that its reliability, interpretation, and suitability for reuse can be assessed.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•The origin or source system of data is documented.
-•Creation dates, modification dates, or version histories are recorded.
-•Transformations, aggregations, or processing steps are specified.
-•Responsible individuals, organizations, or systems are identified.
-•Provenance information is linked to the corresponding data or metadata resource.
-Exclusion Criteria:
-Do not code when:
-•Only general statements about data reliability are made without documented lineage.
-•Quality characteristics are described without reference to origin or transformation history (this belongs under the data quality code).
-•Governance roles are discussed without documenting data lineage.
-•Metadata are present but do not include origin or transformation information.
-Literature:
-•FAIR R1.2 (Wilkinson et al., 2016): (meta)data are associated with detailed provenance.
-•Buneman, Khanna &amp; Tan (2001): data provenance in databases.
-•Moreau &amp; Missier (2013): W3C PROV model and formal provenance representation.
-•Wang &amp; Strong (1996): fitness for use requires knowledge of origin and production context.
-•Peristeras et al. (2009): cross-domain interoperability requires traceability of information sources.</t>
+Data and metadata must be accompanied by structured and sufficiently detailed documentation of their origin, creation process, transformation history, and responsible actors.
+Inclusion Criteria:
+1. Documented data origin.
+2. Recorded transformation steps.
+3. Identified responsible actors.
+4. Lineage linked to resources.
+Exclusion Criteria:
+1. General reliability claims without lineage.
+2. Quality without origin information.
+Example Quotations:
+1. “The Model of the Flemish Address Register applies the W3C PROV ontology for modeling provenance.”
+2. “Core Objects contain provenance information, which defines when the information was registered and for which period of time it is valid.”
+Literature:
+• FAIR R1.2
+• Buneman et al. (2001)
+• Moreau &amp; Missier (2013)
+• Wang &amp; Strong (1996)
+• Peristeras et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -1623,26 +2046,22 @@
   </si>
   <si>
     <t>Definition:
-Data and metadata must be expressed using formally defined, publicly specified, and widely recognized syntactic languages for knowledge representation, in order to ensure structurally consistent and interoperable encoding of meaning across systems.
-Syntax is defined here as the formally specified structure and grammar through which information and semantic constructs are represented. The requirement concerns the use of shared and standardized representation languages that enable consistent parsing, validation, and exchange of semantically structured information.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data or metadata are represented using formally specified syntactic languages (e.g., RDF, OWL, XML Schema).
-•Representation languages are publicly documented and standardized.
-•Semantic artefacts (e.g., ontologies, vocabularies) are encoded in shared formal syntaxes.
-•Structural constraints or schemas are formally defined.
-Exclusion Criteria:
-Do not code when:
-•Meaning is expressed solely through natural language or free text without formal structure.
-•Proprietary or undocumented syntactic formats are used.
-•Conceptual alignment is discussed without reference to formal representation syntax.
-•Only technical transport protocols are specified without representation structure.
-Literature:
-•FAIR I1, I2, R1.3 (Wilkinson et al., 2016): use of formal, accessible, shared representation languages and vocabularies.
-•Guarino (1998): formal ontology and the role of explicit representation structures in information systems.
-•Euzenat &amp; Shvaiko (2013): ontology matching presupposes formally structured representations.
-•Peristeras et al. (2009): syntactic interoperability as prerequisite for semantic interoperability.
-EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.</t>
+Data and metadata must be expressed using formally defined, publicly specified, and widely recognized syntactic languages for knowledge representation.
+Inclusion Criteria:
+1. Use of RDF, OWL, XML Schema or similar.
+2. Public documentation of representation languages.
+3. Formal structural constraints.
+Exclusion Criteria:
+1. Free text without formal structure.
+2. Proprietary or undocumented syntactic formats.
+Example Quotations:
+1. “When someone looks up a URI, provide useful information, using the standards RDF and SPARQL.”
+Literature:
+• FAIR I1, I2, R1.3
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013)
+• Peristeras et al. (2009)
+• EIF Recommendation 42</t>
   </si>
   <si>
     <r>
@@ -1656,6 +2075,22 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Semantic models and modelling environments must allow for context-sensitive variation and extension without breaking interoperability, in order to accommodate divergent and evolving domain requirements.
+Inclusion Criteria:
+1. Extension mechanisms in shared models.
+2. Application profiles built on top of core models.
+3. Allowance for jurisdictional or sectoral variation.
+Exclusion Criteria:
+1. Strict conformance regimes that prohibit variation (use Conformance-based mechanism for related solution context).
+2. Ad hoc undocumented modelling differences.
+Example Quotations:
+1. “Analyzing the situation at ECDC it became clear, that implementing simply a rigorous data modeling rule set plus introducing obligatory mappings is insufficient...”
+2. “The core data models as contained in the legal framework can be extended, following the rules defined by the generic conceptual model.”
+Notes:
+Newly defined; complement of Semantic Modelling Alignment, addressing how flexibility is institutionalized.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1668,30 +2103,21 @@
   </si>
   <si>
     <t>Definition:
-Multilingual Semantic Representation refers to the requirement that information systems, data models, and semantic artefacts must support representation and interpretation of information across multiple natural languages in order to enable cross-border and cross-community interoperability.
-This requirement asserts that semantic interoperability in multi-lingual governance contexts depends on the capability to represent, link, and present concepts, labels, and descriptive information in more than one language, while preserving conceptual equivalence and interpretive consistency.
-The focus is not merely on user-interface translation, but on structurally embedding multilingual support within semantic artefacts and system architectures so that meaning remains stable across linguistic contexts.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Information systems support multiple natural languages.
-•Semantic artefacts include multilingual labels or descriptions.
-•Conceptual models accommodate language-specific representations.
-•Cross-border services provide multilingual data interpretation.
-•Controlled vocabularies include multilingual equivalents.
-•Multilingual metadata are mandated.
-•Concept identifiers are separated from language-specific labels.
-•Language support is treated as a structural interoperability requirement.
-Exclusion Criteria:
-Do not code when:
-•Only front-end user interface translation is mentioned without semantic implications.
-•Accessibility for persons with disabilities is discussed without linguistic representation.
-•Legal translation requirements are described without system-level semantic embedding.
-•Cultural adaptation is referenced without structured multilingual representation.
-•Data are translated informally without controlled semantic linkage.
-Theoretical Grounding:
-Ontology and vocabulary engineering literature distinguishes between language-independent conceptual identifiers and language-dependent lexicalizations, highlighting the importance of separating concept identity from linguistic expression (Guarino, 1998).
-Multilingual terminology management research shows that semantic interoperability across jurisdictions requires controlled vocabularies with multilingual correspondences to prevent interpretive drift.
-EIF Recommendation 16:  Use information systems and technical architectures that cater for multilingualism when establishing a European public service. Decide on the level of multilingualism support based on the needs of the expected users.</t>
+Information systems, data models, and semantic artefacts must support representation and interpretation of information across multiple natural languages, preserving conceptual equivalence.
+Inclusion Criteria:
+1. Multilingual labels in semantic artefacts.
+2. Concept identifiers separated from labels.
+3. Multilingual metadata mandated.
+Exclusion Criteria:
+1. UI translation only.
+2. Informal translation without semantic linkage.
+Example Quotations:
+1. “All the semantics included in the legal text have been translated into 24 languages and are now accessible via the INSPIRE registry service.”
+Notes:
+Note: original spelling 'Mutlilingual' corrected
+Literature:
+• Guarino (1998)
+• EIF Recommendation 16</t>
   </si>
   <si>
     <r>
@@ -1705,29 +2131,24 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Data and metadata must be described with a plurality of accurate, relevant, and sufficiently detailed attributes that make their meaning understandable within and beyond their original context of production. Descriptions must be precise enough to prevent misinterpretation and to support consistent use across organizational or disciplinary boundaries.
-This requirement concerns the substantive adequacy and clarity of descriptive attributes, rather than the formalization of conceptual models.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data or metadata are richly described with multiple relevant attributes.
-•Descriptions include contextual qualifiers necessary for correct interpretation (e.g., scope, units, temporal coverage, intended meaning).
-•Definitions are accurate, non-ambiguous, and sufficiently detailed for reuse.
-•Descriptive attributes reduce interpretive variability across contexts.
-Exclusion Criteria:
-Do not code when:
-•Descriptions are minimal, generic, or underspecified.
-•Terminology is used without clarification of meaning.
-•Only syntactic schema structures are defined without descriptive attributes.
-•Conceptual modeling is required in a formal ontological sense (this belongs under syntactic or semantic standard codes).
-Literature:
-•FAIR R1 (Wilkinson et al., 2016): meta(data) are richly described with a plurality of accurate and relevant attributes.
-•Park (2006): semantic interoperability requires sufficiently detailed descriptive information to reduce interpretive ambiguity.
-•Peristeras et al. (2009): interoperability depends on shared and sufficiently specified information structures.
-•Batini &amp; Scannapieco (2016): completeness and adequacy as core dimensions of information quality.
-•EOSC: “common explicit definitions” + “clear and precise definitions for the concepts” + “Every semantic artefact that is being maintained in EOSC must have sufficient associated documentation”
-Links to EIF Recommendation 38:  Develop interfaces with base registries and authoritative sources of information, publish the semantic and technical means and documentation needed for others to connect and reuse available information.
-</t>
+    <t>Definition:
+Data and metadata must be described with a plurality of accurate, relevant, and sufficiently detailed attributes that make their meaning understandable within and beyond their original context.
+Inclusion Criteria:
+1. Multiple relevant descriptive attributes.
+2. Contextual qualifiers (scope, units, temporal coverage).
+3. Definitions accurate and non-ambiguous.
+Exclusion Criteria:
+1. Minimal or generic descriptions.
+2. Formal ontological modelling specifically (use Semantic Standards or Modelling Alignment).
+Example Quotations:
+1. “Linked address data provides context information via the dereferenceable address identifiers (URIs) including a reference to the vocabulary...”
+Literature:
+• FAIR R1
+• Park (2006)
+• Peristeras et al. (2009)
+• Batini &amp; Scannapieco (2016)
+• EOSC
+• EIF Recommendation 38</t>
   </si>
   <si>
     <r>
@@ -1742,32 +2163,23 @@
   </si>
   <si>
     <t>Definition:
-Semantic Mapping and Alignment Capabilities refer to the requirement that an interoperability ecosystem must enable the formal specification, representation, and maintenance of explicit correspondences between heterogeneous semantic artefacts in order to achieve semantic interoperability across systems, domains, or jurisdictions.
-This requirement asserts that when multiple conceptual models, vocabularies, ontologies, or metadata schemas coexist, interoperability depends on the capability to establish structured semantic relationships—such as equivalence, subsumption, or transformation rules—between their respective constructs.
-The focus is on the availability and institutionalization of alignment mechanisms that relate distinct artefacts after their independent development. It concerns post hoc semantic correspondence rather than ex ante modelling harmonization.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Correspondences between heterogeneous semantic artefacts must be specified.
-•Ontologies or schemas must be aligned to enable interoperability.
-•Cross-schema mappings or crosswalks are required.
-•Transformation rules between semantic representations must be defined.
-•Equivalence, subsumption, or refinement relationships between constructs must be formally represented.
-•Legacy and target models must be related through structured alignment artefacts.
-•Semantic mediation relies on formally specified mapping relationships.
-•Multi-standard environments require semantic correspondence mechanisms.
-Exclusion Criteria:
-Do not code when:
-•A single shared semantic model is mandated (belongs under Semantic Modelling Alignment).
-•Only syntactic format conversion is described without semantic correspondence.
-•Modelling guidelines are harmonized at design stage.
-•Governance of standard selection is discussed without mapping.
-•Runtime technical infrastructure is described without reference to semantic correspondences.
-•Informal interpretation between artefacts is mentioned without explicit mapping artefacts.
-Theoretical Grounding:
-Ontology alignment literature defines alignment as the establishment of formal correspondences between entities of distinct ontologies to enable interoperability (Euzenat &amp; Shvaiko, 2013).
-Model-driven interoperability research demonstrates that heterogeneous conceptual models require explicit relational mappings to prevent semantic ambiguity (Peristeras et al., 2009).
-The FAIR principles, particularly I1–I2 and R1.3 (Wilkinson et al., 2016), imply the necessity of semantic compatibility across standards, while FAIR 2.0 emphasizes interoperability in multi-standard environments requiring schema crosswalks.
-Ontology engineering theory highlights that explicit ontological commitment and formal correspondence specification are prerequisites for meaningful integration across conceptual systems (Guarino, 1998).</t>
+An interoperability ecosystem must enable the formal specification, representation, and maintenance of explicit correspondences between heterogeneous semantic artefacts (post hoc alignment).
+Inclusion Criteria:
+1. Cross-schema mappings or crosswalks.
+2. Equivalence, subsumption, transformation rules.
+3. Semantic mediation via formal mappings.
+4. Multi-standard environments requiring correspondence.
+Exclusion Criteria:
+1. Single shared model mandated (use Semantic Modelling Alignment).
+2. Syntactic format conversion only.
+Example Quotations:
+1. “In order to achieve a feasible model, and to benefit from the best of both worlds, the Flemish Government has adapted the ISA address towards INSPIRE.”
+Literature:
+• Euzenat &amp; Shvaiko (2013)
+• Peristeras et al. (2009)
+• FAIR I1-I2 and R1.3
+• FAIR 2.0
+• Guarino (1998)</t>
   </si>
   <si>
     <r>
@@ -1781,37 +2193,25 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Semantic Modelling Alignment refers to the requirement that participating actors adopt and apply a shared conceptualization approach, modelling methodology, naming conventions, abstraction principles, and structural design logic when developing semantic artefacts.
-This requirement asserts that semantic interoperability is strengthened when semantic artefacts are engineered according to harmonized modelling strategies across organizational, sectoral, or jurisdictional boundaries. The objective is to prevent structural divergence and conceptual inconsistency at design time, thereby reducing interpretive ambiguity and minimizing the need for subsequent mapping or mediation.
-Semantic modelling alignment concerns ex ante harmonization of modelling practice rather than post hoc correspondence between heterogeneous artefacts. It focuses on methodological convergence in how meaning is constructed, structured, and formalized.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Participating actors adopt a common conceptual modelling methodology.
-•Agreed abstraction levels or modelling granularity are defined.
-•Common structuring principles govern entity, attribute, and relation design.
-•Modelling guidelines or design rules are harmonized across organizations.
-•Conceptual modelling follows a shared reference architecture or meta-model.
-•Model development is coordinated to ensure structural coherence.
-•A unified modelling grammar or pattern language is prescribed.
-•Divergent modelling approaches are to be avoided through harmonized design principles.
-The emphasis must be on harmonization of modelling strategy at design stage, not on technical encoding or legal authorization.
-Exclusion Criteria:
-Do not code when:
-•The statement concerns post hoc mapping or cross-schema alignment (belongs under Semantic: Alignment and Mapping Capability).
-•Only syntactic representation formats are specified (belongs under Formal and Shared Syntax).
-•Governance structures are described without modelling methodology.
-•A single shared artefact is mandated without reference to modelling principles.
-•Informal conceptual agreement is mentioned without structured modelling strategy.
-•Technical tooling is discussed without methodological alignment.
-•Data quality requirements are specified without reference to modelling approach.
-Theoretical Grounding:
-•FAIR 2.0 (Vogt et al., 2024): emphasizes interoperability across semantic layers and the need to support mappings and cross-schema interoperability in heterogeneous environments.
-•FAIR I1–I2, R1.3 (Wilkinson et al., 2016): formal languages, shared vocabularies, and community standards as prerequisites, but not sufficient in multi-standard contexts.
-•Euzenat &amp; Shvaiko (2013): alignment as explicit correspondences between ontologies enabling interoperability.
-•Ontology engineering research emphasizes that shared ontological commitments and explicit modelling principles are necessary to ensure semantic coherence across systems (Guarino, 1998).
-•Model-driven interoperability literature demonstrates that structural divergence often originates from inconsistent modelling strategies rather than absence of mapping mechanisms (Peristeras et al., 2009).
-</t>
+    <t>Definition:
+Participating actors must adopt and apply a shared conceptualization approach, modelling methodology, naming conventions, and structural design logic when developing semantic artefacts (ex ante alignment).
+Inclusion Criteria:
+1. Common conceptual modelling methodology.
+2. Agreed abstraction levels and granularity.
+3. Harmonized modelling guidelines.
+4. Shared reference architecture or meta-model.
+Exclusion Criteria:
+1. Post hoc mapping (use Semantic Mapping and Alignment).
+2. Syntactic format choice only.
+3. Single shared artefact without modelling principles.
+Example Quotations:
+1. “The base registries are part of a semantic coherent system of uniform identified base-objects and relations, which are in line with the OSLO-standards.”
+Literature:
+• FAIR 2.0 (Vogt et al. 2024)
+• FAIR I1-I2, R1.3
+• Euzenat &amp; Shvaiko (2013)
+• Guarino (1998)
+• Peristeras et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -1826,28 +2226,23 @@
   </si>
   <si>
     <t>Definition:
-Data resources must be accompanied by formally structured metadata that provide explicit descriptions of their content, context, structure, provenance, and conditions of use. These metadata must remain retrievable independently of the data objects they describe.
-Metadata are defined here as structured representations about data resources that enable identification, interpretation, evaluation, and responsible reuse across organizational or institutional boundaries. Metadata include descriptive, contextual, semantic, and governance-relevant information.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data resources are described using a formally defined metadata schema or model.
-•Metadata provide contextual information necessary for correct interpretation (e.g., scope, temporal coverage, conceptual definitions).
-•Metadata document provenance, custodianship, versioning, or usage conditions.
-•Metadata remain available even when the underlying data are restricted, archived, or no longer accessible.
-•Metadata are explicitly linked to the data resources they describe.
-Exclusion Criteria:
-Do not code when:
-•Descriptive information is informal, narrative, or ad hoc without structural specification.
-•Contextual information is embedded implicitly in data without explicit modeling.
-•Metadata are mentioned only as optional documentation without normative requirement.
-•Only technical storage formats are specified without requirement for structured description.
-Literature:
-•FAIR F2, F3, A2 (Wilkinson et al., 2016): rich metadata, explicit linkage to data, and persistence of metadata even if data are unavailable.
-•Guarino (1998): formal ontology and explicit conceptual specification in information systems.
-•Guizzardi &amp; Guarino (2024): ontological unpacking and semantic explicitness.
-•Peristeras et al. (2009): model-driven interoperability and structured metadata as enablers of cross-domain integration.
-EIF. Recommendation 39:  Match each base registry with appropriate metadata including the description of its content, service assurance and responsibilities, the type of master data it keeps, conditions of access and the relevant licences, terminology, a glossary, and information about any master data it uses from other base registries.
-EIF Recommendation 42:  Publish open data in machine-readable, non-proprietary formats. Ensure that open data is accompanied by high quality, machine-readable metadata in non-proprietary formats, including a description of their content, the way data is collected and its level of quality and the licence terms under which it is made available. The use of common vocabularies for expressing metadata is recommended.</t>
+Data resources must be accompanied by formally structured metadata that provide explicit descriptions of their content, context, structure, provenance, and conditions of use, retrievable independently of the data they describe.
+Inclusion Criteria:
+1. Formally defined metadata schema.
+2. Contextual metadata for interpretation.
+3. Metadata documenting provenance and usage conditions.
+4. Metadata persistent even when data are restricted.
+Exclusion Criteria:
+1. Informal narrative documentation.
+2. Implicit context embedded in data.
+Example Quotations:
+1. “Member States ensure that metadata are created for the spatial data sets and services corresponding to one or more of the INSPIRE themes.”
+Literature:
+• FAIR F2, F3, A2
+• Guarino (1998)
+• Guizzardi &amp; Guarino (2024)
+• Peristeras et al. (2009)
+• EIF Recommendations 39, 42</t>
   </si>
   <si>
     <r>
@@ -1862,32 +2257,19 @@
   </si>
   <si>
     <t>Definition:
-Technical requirements are the normative conditions that data, metadata, semantic artefacts, and interoperability services must satisfy in order to enable reliable exchange, retrieval, discovery, and sustained operation across heterogeneous systems and organizational boundaries.
-They operationalize the technical layer of interoperability by specifying conditions for persistent identification, standardized access protocols, searchable indexing infrastructures, common metadata standards, shared semantic tooling, and sustainable infrastructure components.
-Grounded in the FAIR principles (Wilkinson et al., 2016), extended in FAIR 2.0, and contextualized in federated ecosystems such as EOSC, technical requirements ensure that interoperability is not merely conceptual but infrastructurally and operationally feasible.
-Technical requirements concern the structural, protocol-level, infrastructural, and architectural conditions under which semantic and organizational interoperability can function.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Persistent and globally unique identifiers are used.
-•Data or metadata are accessible via standardized and documented communication protocols.
-•Searchable catalogues, registries, or indexing infrastructures are established.
-•Federation or harvesting mechanisms interconnect distributed repositories.
-•A shared metadata standard (with governed profiling mechanisms) is defined.
-•Common tooling is provided for semantic artefact creation and maintenance.
-•Infrastructure components ensure sustained availability and continuity of services.
-•Architectural building blocks are defined to support cross-system interoperability.
-Exclusion Criteria:
-Do not code when:
-•Only meaning, conceptual definitions, or semantic alignment are discussed without technical implementation implications (belongs under Semantic).
-•Governance, institutional arrangements, or legal frameworks are described without infrastructural or protocol-level implications.
-•Licensing or copyright conditions are specified without technical relevance.
-•Data quality criteria are defined without reference to technical enablement.
-Literature:
-•FAIR Guiding Principles (Wilkinson et al., 2016):
-•FAIR 2.0 (Vogt et al., 2024): entity-level and proposition-level interoperability requiring technical schema crosswalks and interoperable services.
-•EOSC Interoperability Framework (2021–2023):
-•Peristeras et al. (2009): technical interoperability as standardized communication and model-driven architectural capability.
-•Wimmer et al. (2018): technical and infrastructural foundations of interoperability governance.</t>
+Header category. Technical requirements are the normative conditions that data, metadata, semantic artefacts, and interoperability services must satisfy to enable reliable exchange, retrieval, discovery, and sustained operation across heterogeneous systems and organizational boundaries.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• FAIR
+• FAIR 2.0
+• EOSC
+• Peristeras et al. (2009)
+• Wimmer et al. (2018)</t>
   </si>
   <si>
     <r>
@@ -1902,30 +2284,20 @@
   </si>
   <si>
     <t>Definition:
-Existence of Shared Technical Standards refers to the requirement that interoperable public services must rely on commonly agreed and publicly available technical specifications—preferably open specifications—to ensure compatibility of systems, interfaces, protocols, and infrastructural components across organizational and jurisdictional boundaries.
-This requirement asserts that technical interoperability depends on the availability and adoption of shared standards governing communication protocols, data exchange formats, interface definitions, security mechanisms, and infrastructural interaction patterns.
-The focus is on the presence and use of open, consensus-based technical specifications that enable predictable system-level interoperability, independent of vendor-specific implementations.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Open specifications be used for interoperability.
-•Common technical standards govern system interfaces or protocols.
-•Shared communication or transport standards are mandated.
-•Interoperability relies on standardized technical formats.
-•Technical compatibility across systems is ensured through agreed standards.
-•Vendor-neutral technical specifications are required.
-•Public services must adopt commonly recognized ICT standards.
-•Cross-border technical interoperability depends on open specifications.
-Exclusion Criteria:
-Do not code when:
-•Only semantic standards or vocabularies are discussed (belongs under Semantic).
-•Governance of standard selection processes is described without technical specification content (belongs under Organizational: Standardization and Semantic Control).
-•Legal mandates for standard adoption are discussed without technical focus.
-•Technical tooling is mentioned without reference to shared standards.
-•Interface design is described without standardized specification.
-Theoretical Grounding:
-The European Interoperability Framework emphasizes the use of open specifications to guarantee technical interoperability and reduce vendor lock-in.
-Technical interoperability literature identifies shared standards for communication, data formats, and interface definitions as foundational preconditions for cross-system compatibility (Peristeras et al., 2009).
-EIF Recommendation 33:  Use open specifications, where available, to ensure technical interoperability when establishing European public services.</t>
+Interoperable public services must rely on commonly agreed and publicly available technical specifications, preferably open, to ensure compatibility of systems, interfaces, protocols, and infrastructural components.
+Inclusion Criteria:
+1. Open specifications for interoperability.
+2. Common technical standards for interfaces.
+3. Standardized communication protocols.
+4. Vendor-neutral technical specifications.
+Exclusion Criteria:
+1. Semantic standards (use Semantic: Existence and Use of Domain-Relevant Semantic Standards).
+2. Governance of selection (use Standardization and Semantic Control).
+Example Quotations:
+1. “INSPIRE metadata are based on the well-established EN ISO 19115 and EN ISO 19119 standards.”
+Literature:
+• EIF Recommendation 33
+• Peristeras et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -1940,29 +2312,23 @@
   </si>
   <si>
     <t>Definition:
-Data and metadata must be structured, registered, and indexed in interoperable discovery infrastructures such that they can be located across organizational and community boundaries. Findability requires not only local indexing but also clearly defined protocols and architectural building blocks that enable federation and harvesting of catalogues and semantic artefact registries.
-Findability is defined here as the ecosystem-level capability to systematically discover data, metadata, and semantic artefacts through searchable resources and federated discovery mechanisms.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data or metadata are registered in searchable catalogues, repositories, or registries.
-•Indexing mechanisms support structured and queryable discovery.
-•Discovery infrastructures allow cross-community or cross-domain search.
-•Federation or harvesting protocols are defined to interconnect multiple catalogues.
-•Architectural components enable interoperability between distributed metadata or semantic artefact registries.
-Exclusion Criteria:
-Do not code when:
-•Only direct retrieval via known identifiers is described without indexing.
-•Discovery is limited to manual browsing or informal exchange.
-•Metadata richness is required without searchable registration.
-•Technical APIs are specified without indexing or discovery functionality.
-•Local cataloguing exists without federated interoperability mechanisms.
-Literature:
-•FAIR F4 (Wilkinson et al., 2016): meta(data) are registered or indexed in a searchable resource.
-•FAIR F2 (Wilkinson et al., 2016): rich metadata as prerequisite for effective discovery.
-•EOSC Interoperability Framework (2021–2023): need for federated discovery, harvesting protocols, and architectural building blocks for semantic artefact catalogues.
-•Peristeras et al. (2009): interoperability requires structured information infrastructures enabling cross-domain discovery.
-Links to EIF: Recommendation 5:  Ensure internal visibility and provide external interfaces for European public services.
-Links to EIF Recommendation 44:  Put in place catalogues of public services, public data, and interoperability solutions and use common models for describing them.</t>
+Data and metadata must be structured, registered, and indexed in interoperable discovery infrastructures such that they can be located across organizational and community boundaries, including federation and harvesting protocols.
+Inclusion Criteria:
+1. Searchable catalogues, repositories, registries.
+2. Indexing supporting structured queries.
+3. Federation or harvesting protocols.
+4. Cross-community discovery infrastructures.
+Exclusion Criteria:
+1. Direct retrieval by known identifiers only.
+2. Manual browsing only.
+3. Local cataloguing without federation.
+Example Quotations:
+1. “Easy to find what geographic information is available, how it can be used to meet particular needs, and under which conditions it can be acquired and used.”
+Literature:
+• FAIR F4, F2
+• EOSC IF
+• Peristeras et al. (2009)
+• EIF Recommendations 5, 44</t>
   </si>
   <si>
     <r>
@@ -1972,24 +2338,37 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Requirement: Technical: Integration of services and applications</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Requirement: Technical: Persistent and Globally Unique Identification</t>
     </r>
   </si>
   <si>
-    <t>Definition
-All data objects, metadata records, and semantic artefacts must be assigned globally unique, persistent, and resolvable identifiers to enable stable reference, citation, and machine-mediated linking across systems and domains.
-Inclusion Criteria:
-•Explicit requirement for persistent identifiers (e.g., URI, DOI, Handle).
-•Machine-resolvable identifiers.
-•Explicit linkage between identifiers of data and associated metadata.
-Exclusion Criteria
-•Local, system-internal, or temporary identifiers.
-•Identifiers without persistence guarantees.
-•Implicit references without global uniqueness.
-Literature:
-•FAIR F1, F3, A1 (Wilkinson et al., 2016).
-•Guarino (1998), formal ontology and stable reference.
-•Peristeras et al. (2009), model-driven interoperability and identity management.</t>
+    <t>Definition:
+All data objects, metadata records, and semantic artefacts must be assigned globally unique, persistent, and resolvable identifiers to enable stable reference, citation, and machine-mediated linking.
+Inclusion Criteria:
+1. Persistent identifiers (URI, DOI, Handle).
+2. Machine-resolvable identifiers.
+3. Explicit linkage between data and metadata identifiers.
+Exclusion Criteria:
+1. Local or temporary identifiers.
+2. Identifiers without persistence guarantees.
+Example Quotations:
+1. “A base registry reuses the identifiers of the base-objects in other base registries.”
+2. “All addresses and streets were given a universally unique identifier which can be looked up via the web.”
+Literature:
+• FAIR F1, F3, A1
+• Guarino (1998)
+• Peristeras et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -2004,27 +2383,22 @@
   </si>
   <si>
     <t>Definition:
-A federated or multi-domain ecosystem must provide and promote common, principled tooling for the creation, maintenance, governance, and use of semantic artefacts such as ontologies and metadata schemas. Such tooling must support formally specified representation models and ensure structural and semantic consistency across communities.
-Common semantic tooling is defined here as a shared set of methods, platforms, and modeling environments that enable interoperable development and lifecycle management of semantic artefacts, thereby reducing heterogeneity in representation practices.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Shared tools or platforms are established for ontology or metadata schema development.
-•Formal modeling environments are mandated to ensure semantic precision.
-•Tooling supports versioning, governance, or controlled evolution of semantic artefacts.
-•Heterogeneity in representation practices is addressed through harmonized tool support.
-•Formal semantic representation is preferred over informal or purely diagrammatic modeling.
-Exclusion Criteria:
-Do not code when:
-•Only the existence of semantic standards is discussed without tooling support.
-•Individual communities independently select tools without coordination.
-•UML or other diagrammatic models are mentioned without requirement for formal semantic rigor.
-•Governance structures are described without reference to technical tooling.
-Literature:
-•EOSC Interoperability Framework (2021–2023): need for principled approaches and common tooling for semantic artefact management.
-•FAIR I1, I2 (Wilkinson et al., 2016): use of formal, shared knowledge representation languages.
-•Guarino (1998): importance of formal ontology in information systems.
-•Euzenat &amp; Shvaiko (2013): ontology engineering and alignment require formal representation support.
-•Wimmer et al. (2018): governance and infrastructure for interoperable semantic artefacts.</t>
+A federated or multi-domain ecosystem must provide and promote common, principled tooling for the creation, maintenance, governance, and use of semantic artefacts such as ontologies and metadata schemas.
+Inclusion Criteria:
+1. Shared tools for ontology development.
+2. Formal modelling environments.
+3. Versioning and governance support tooling.
+Exclusion Criteria:
+1. Standards without tooling support (use Existence of Shared Technical Standards).
+2. Independent tool selection without coordination.
+Literature:
+• EOSC IF
+• FAIR I1, I2
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013)
+• Wimmer et al. (2018)
+• No quotations yet
+• retained because of theoretical grounding</t>
   </si>
   <si>
     <r>
@@ -2039,32 +2413,17 @@
   </si>
   <si>
     <t>Definition:
-Security and Privacy Assurance Framework refers to the requirement that interoperable public services must operate within a coherent framework of technical, organizational, and procedural safeguards that ensure secure, trustworthy, and legally compliant data exchange across administrative boundaries.
-This requirement asserts that sustainable interoperability depends on systematically defined security and privacy principles, risk-based protection measures, access control mechanisms, and trusted identity and authentication services. Secure interoperability requires not only technical controls but also structured processes and governance arrangements that manage risks and ensure compliance with relevant legislation.
-The focus is on the structured integration of security and privacy into interoperability architectures and service design, rather than on isolated technical safeguards.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•A common security and privacy framework be defined.
-•Secure and trustworthy data exchange mechanisms be established.
-•Access control or authorization mechanisms be implemented.
-•Privacy protection be embedded in interoperability architectures.
-•Risk management processes guide service security measures.
-•Trust services (e.g., eID, electronic signatures, trust services) be used to secure interactions.
-•Security measures be tailored to service-specific risk profiles.
-•Authoritative data sources implement controlled access mechanisms.
-•Data exchange comply with relevant privacy and security legislation.
-Exclusion Criteria:
-Do not code when:
-•Only legal data protection obligations are discussed without architectural or process implications (belongs under Legal: Public Regulation for Interoperability).
-•Generic references to “trust” are made without security mechanisms.
-•Technical encryption mechanisms are described in isolation without framework context.
-•Organizational governance roles are described without security focus.
-•Data quality or provenance is discussed without privacy or protection implications.
-Theoretical Grounding:
-EIF: Recommendation 15:  Define a common security and privacy framework and establish processes for public services to ensure secure and trustworthy data exchange between public administrations and in interactions with citizens and businesses.
-EIF. Recommendation 37:  Make authoritative sources of information available to others while implementing access and control mechanisms to ensure security and privacy in accordance with the relevant legislation.
-EIF Recommendation 46:  Consider the specific security and privacy requirements and identify measures for the provision of each public service according to risk management plans.
-EIF Recommendation 47:  Use trust services according to the Regulation on eID and Trust Services as mechanisms that ensure secure and protected data exchange in public services.</t>
+Interoperable public services must operate within a coherent framework of technical, organizational, and procedural safeguards that ensure secure, trustworthy, and legally compliant data exchange.
+Inclusion Criteria:
+1. Common security and privacy framework.
+2. Trust services (eID, e-signatures).
+3. Risk-based protection measures.
+4. Embedded privacy in interoperability architectures.
+Exclusion Criteria:
+1. Pure legal data protection (use Legal: Restrictions).
+2. Generic trust references without mechanisms.
+Literature:
+• EIF Recommendations 15, 37, 46, 47</t>
   </si>
   <si>
     <r>
@@ -2078,27 +2437,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Data and metadata must be retrievable through standardized, documented, and interoperable communication protocols that ensure predictable access conditions across organizational and technical boundaries. Where access restrictions apply, authentication and authorization mechanisms must be explicitly specified and governed.
-Accessibility is defined here as the formally regulated capacity to retrieve data or metadata through stable and documented access mechanisms that are independent of ad hoc arrangements.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Data or metadata are accessible via standardized and documented communication protocols.
-•Access mechanisms are openly specified and stable over time.
-•Authentication and authorization procedures are formally described where required.
-•Access conditions, restrictions, or licensing constraints are explicitly articulated.
-•Retrieval does not depend on informal or discretionary arrangements between parties.
-Exclusion Criteria:
-Do not code when:
-•Access is limited to manual request or informal exchange.
-•Access mechanisms are undocumented or proprietary without specification.
-•Retrieval depends solely on organizational discretion without formal protocol.
-•Only internal system connectivity is described without cross-boundary accessibility requirement.
-Literature;
-•FAIR A1, A1.1, A1.2 (Wilkinson et al., 2016): data retrievable by standardized protocols, open and universally implementable, with authentication and authorization where necessary.
-•Peristeras et al. (2009): technical interoperability as standardized communication capability in model-driven architectures.
-•Wimmer et al. (2018): interoperability frameworks and cross-organizational governance of access.
-</t>
+    <t>Definition:
+Data and metadata must be retrievable through standardized, documented, and interoperable communication protocols that ensure predictable access conditions across organizational and technical boundaries.
+Inclusion Criteria:
+1. Documented standardized access protocols.
+2. Stable access mechanisms.
+3. Formally specified authentication and authorization.
+Exclusion Criteria:
+1. Manual or informal access.
+2. Undocumented or proprietary mechanisms.
+Example Quotations:
+1. “Geospatial data is made available 'online first', thus unlocking it as is for further use.”
+Literature:
+• FAIR A1, A1.1, A1.2
+• Peristeras et al. (2009)
+• Wimmer et al. (2018)</t>
   </si>
   <si>
     <r>
@@ -2112,37 +2465,35 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-A federated data ecosystem must include stable, trusted, and sustainably governed infrastructure components that ensure the long-term availability, accessibility, and operational continuity of data and metadata services across communities and domains.
-Infrastructure components are defined here as the technical services, repositories, registries, storage systems, identifier services, and access mechanisms that enable persistent data publication, retrieval, and maintenance over time.
-This requirement operationalizes trust not as a normative claim but as the presence of technically and institutionally supported infrastructure that ensures continuity of service.
-Inclusion Criteria:
-Code when a source explicitly requires that:
-•Persistent repositories or registries are established to host data and metadata.
-•Infrastructure components provide long-term storage and availability guarantees.
-•Service continuity or operational sustainability is mandated.
-•Federated infrastructures ensure cross-community interoperability.
-•Trustworthiness is linked to the presence of certified, governed, or monitored technical services.
-Exclusion Criteria:
-Do not code when:
-•Trust is discussed only in social or reputational terms without infrastructure implications.
-•Sustainability is mentioned without reference to operational technical components.
-•Governance structures are described without technical service provision.
-•Data sharing is discussed without specifying infrastructural support mechanisms.
-Literature:
-•EOSC Interoperability Framework (European Open Science Cloud Association, 2021–2023): trusted and sustainable service ecosystem.
-•FAIR A principles (Wilkinson et al., 2016): accessibility requires stable retrieval mechanisms.
-•Wimmer et al. (2018): interoperability frameworks require sustainable infrastructural arrangements.
-•Peristeras et al. (2009): technical interoperability depends on institutionalized service infrastructures.
-•EOSC: “common reference repositories” + “EOSC should provide support for the maintenance of a repository of semantic artefacts, and a governance framework” 
-EIF Recommendation 6:  Reuse and share solutions, and cooperate in the development of joint solutions when implementing European public services.
-Links to EIF Recommendation 35:  Decide on a common scheme for interconnecting loosely coupled service components and put in place and maintain the necessary infrastructure for establishing and maintaining European public services.
-Links to EIF Recommendation 36:  Develop a shared infrastructure of reusable services and information sources that can be used by all public administrations.
-Links to EIF Recommendation 37:  Make authoritative sources of information available to others while implementing access and control mechanisms to ensure security and privacy in accordance with the relevant legislation.
-Links to EIF Recommendation 38:  Develop interfaces with base registries and authoritative sources of information, publish the semantic and technical means and documentation needed for others to connect and reuse available information.
-Links to EIF Recommendation 39:  Match each base registry with appropriate metadata including the description of its content, service assurance and responsibilities, the type of master data it keeps, conditions of access and the relevant licences, terminology, a glossary, and information about any master data it uses from other base registries.
-Links to EIF Recommendation 44:  Put in place catalogues of public services, public data, and interoperability solutions and use common models for describing them.
-</t>
+    <t>Definition:
+A federated data ecosystem must include stable, trusted, and sustainably governed infrastructure components that ensure long-term availability, accessibility, and operational continuity.
+Inclusion Criteria:
+1. Persistent repositories.
+2. Long-term availability guarantees.
+3. Federated infrastructures for cross-community interoperability.
+4. Certified or governed technical services.
+Exclusion Criteria:
+1. Trust as social claim only.
+2. Governance without technical service provision.
+Example Quotations:
+1. “The Address Registry is deployed on a cloud infrastructure: Microsoft Azure. All the components are available as runnable services using Docker.”
+Literature:
+• EOSC IF
+• FAIR A
+• Wimmer et al. (2018)
+• Peristeras et al. (2009)
+• EIF Recommendations 6, 35, 36, 37, 38, 39, 44</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Technical Interconnection</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2156,21 +2507,19 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-An analytical code used to classify solutions according to the governance logic by which semantic authority, decision-making, coordination, and accountability are organized in the design, maintenance, and evolution of semantic interoperability solutions.
-This code captures how meaning is governed, rather than what technical mechanisms are used or what functional outcomes are achieved.
-Inclusion criteria:
-•The solution description addresses who defines, controls, or legitimizes semantic assets (e.g., data models, vocabularies, standards).
-•Governance arrangements for semantic decision-making are explicitly or implicitly described.
-•The solution makes assumptions about authority, coordination, autonomy, or participation in relation to semantic interoperability.
-•The distribution of semantic control across actors, organizations, or communities can be inferred from the text.
-Exclusion criteria:
-•The text focuses exclusively on technical implementation details (e.g., APIs, data formats, algorithms) without reference to governance or authority.
-•Interoperability is described solely in semantic, syntactic or infrastructural terms.
-•No assumptions about decision-making, control, or responsibility for semantic assets can be identified.
-•The solution concerns operational deployment without addressing how semantic meaning is defined or maintained.
-Literature:
-Kubicek 2008 (Governance of interoperability in intergovernmental services: Towards an empirical taxonomy), Scholl and Kischewski 2007, Grunninger 2007 en Bontas </t>
+    <t>Definition:
+Header category. Analytical dimension classifying solutions according to the governance logic by which semantic authority, decision-making, coordination, and accountability are organized.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• Kubicek (2008)
+• Scholl &amp; Klischewski (2007)
+• Bontas
+• Gruninger</t>
   </si>
   <si>
     <t>Solutions</t>
@@ -2187,21 +2536,21 @@
     </r>
   </si>
   <si>
-    <t>Definition
-A governance paradigm in which semantic definitions, data models, vocabularies, or interoperability rules are authoritatively defined and controlled by a single central entity, and participating actors are required to conform to these definitions.
-Inclusion criteria
-•Semantic assets are defined by a single authoritative body.
-•Compliance with centrally defined semantics is mandatory or expected.
-•Semantic change, maintenance, and versioning are governed top-down.
-•Interoperability is achieved primarily through standardization and uniformity.
-•Local semantic variation is restricted or discouraged.
-Exclusion criteria
-•Semantic definitions are jointly negotiated by multiple autonomous actors.
-•Interoperability relies on mappings, mediation, or alignment rather than conformance.
-•Governance authority is distributed or shared.
-•Semantic meaning emerges through community consensus.
-Literature:
-Kubicek 2008 (Governance of interoperability in intergovernmental services: Towards an empirical taxonomy), Scholl and Kischewski 2007</t>
+    <t>Definition:
+A governance paradigm in which semantic definitions, data models, vocabularies, or interoperability rules are authoritatively defined and controlled by a single central entity, with mandatory conformance.
+Inclusion Criteria:
+1. Single authoritative body defines artefacts.
+2. Mandatory compliance with central definitions.
+3. Top-down semantic governance.
+Exclusion Criteria:
+1. Multiple actors retaining authority (use Federated).
+2. Bottom-up community processes (use Community Based).
+Example Quotations:
+1. “The new agency launched the programme OSLO that focuses on the semantic interoperability level...”
+2. “The Danish Address Programme is a sub-programme of the Basic Data Programme...”
+Literature:
+• Kubicek (2008)
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -2217,19 +2566,18 @@
   <si>
     <t>Definition:
 A governance paradigm in which semantic definitions and interoperability practices emerge through collective, bottom-up processes within a community of practice, rather than through formal hierarchical authority.
-Inclusion criteria:
-•Semantic meaning is shaped through community consensus or shared practice.
-•Governance relies on participation, deliberation, and social norms.
-•Formal hierarchical authority is limited or absent.
-•Semantic assets evolve iteratively through community use.
-•Legitimacy derives from adoption rather than enforcement.
-Exclusion criteria:
-•Semantic definitions are imposed by a formal authority.
-•Participation is symbolic or consultative only.
-•Governance is primarily regulatory or contractual.
-•Community members have no influence over semantic evolution.
-Literature:
-Bontas, Grunninger 2008</t>
+Inclusion Criteria:
+1. Bottom-up community consensus.
+2. Participation, deliberation, social norms.
+3. Iterative semantic evolution.
+Exclusion Criteria:
+1. Top-down imposed semantics (use Central).
+2. Multi-paradigm combinations (use Hybrid).
+Example Quotations:
+1. “The OSLO-program, which started as a grassroots initiative at the level of the local governments...”
+Literature:
+• Bontas
+• Gruninger (2008)</t>
   </si>
   <si>
     <r>
@@ -2245,19 +2593,17 @@
   <si>
     <t>Definition:
 A governance paradigm in which semantic definitions and interoperability decisions are made independently by individual actors, without shared governance structures or coordination mechanisms.
-Inclusion criteria:
-•Each actor defines and manages its own semantics independently.
-•No shared semantic governance or coordination mechanisms exist.
-•Interoperability is ad hoc, bilateral, or project-specific.
-•Semantic meaning is implicit, undocumented, or locally defined.
-•Responsibility for semantic alignment is externalized to implementers.
-Exclusion criteria:
-•Any form of shared semantic governance is present.
-•Alignment mechanisms are explicitly defined or institutionalized.
-•Semantic coordination is designed beyond local scope.
-•Semantic assets are jointly maintained.
-Literature:
-Kubicek 2008 (Governance of interoperability in intergovernmental services: Towards an empirical taxonomy),</t>
+Inclusion Criteria:
+1. Each actor manages own semantics.
+2. No shared governance or coordination.
+3. Ad hoc bilateral interoperability.
+Exclusion Criteria:
+1. Federated coordination present (use Federated).
+2. Joint maintenance of artefacts.
+Literature:
+• Kubicek (2008)
+• No quotations yet
+• retained for analytical completeness</t>
   </si>
   <si>
     <r>
@@ -2271,22 +2617,22 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
+    <t>Definition:
 A governance paradigm in which multiple autonomous actors retain authority over their own semantic models, while interoperability is achieved through explicit coordination mechanisms such as shared reference models, mappings, or jointly governed agreements.
-Inclusion criteria
-•Participating actors maintain semantic autonomy.
-•Interoperability is achieved through negotiated alignment rather than imposed uniformity.
-•Explicit coordination mechanisms (e.g. mappings, mediators, reference models) are defined.
-•Governance arrangements support shared or joint decision-making.
-•Semantic heterogeneity is explicitly acknowledged and managed.
-Exclusion criteria
-•A single authority dictates semantic definitions.
-•Semantic alignment occurs only locally or implicitly.
-•No governance mechanisms exist to coordinate meaning across actors.
-•Interoperability is limited to syntactic or technical compatibility.
-Literature:
-Kubicek 2008 (Governance of interoperability in intergovernmental services: Towards an empirical taxonomy), Scholl and Kischewski 2007
-</t>
+Inclusion Criteria:
+1. Actors retain semantic autonomy.
+2. Explicit coordination mechanisms.
+3. Negotiated alignment.
+4. Shared or joint governance.
+Exclusion Criteria:
+1. Single authoritative body (use Central).
+2. No coordination mechanisms (use Decentral).
+Example Quotations:
+1. “The implementation, due to its ambition and wide scope, follows a progressive approach, according to different National and European levels of priority.”
+2. “Member states were represented by the INSPIRE committee and appointed national contact points.”
+Literature:
+• Kubicek (2008)
+• Scholl &amp; Klischewski (2007)</t>
   </si>
   <si>
     <r>
@@ -2302,17 +2648,18 @@
   <si>
     <t>Definition:
 A governance paradigm in which multiple governance logics coexist, combining elements of central, federated, community-based, and/or decentralized approaches within a single solution or ecosystem.
-Inclusion criteria:
-•Multiple governance paradigms are explicitly combined.
-•Different layers, phases, or components follow different governance logics.
-•Governance trade-offs are consciously designed and articulated.
-•No single governance paradigm fully dominates semantic control.
-Exclusion criteria:
-•One governance paradigm clearly dominates across the solution.
-•Apparent hybridity results from ambiguity or lack of documentation.
-•Governance arrangements are implicit rather than intentional.
-Literature:
-Kubicek 2008, Grunninger 2008</t>
+Inclusion Criteria:
+1. Multiple governance paradigms explicitly combined.
+2. Different layers, phases, or components follow different logics.
+3. Trade-offs consciously articulated.
+Exclusion Criteria:
+1. One paradigm dominates clearly.
+2. Apparent hybridity from ambiguity rather than design.
+Example Quotations:
+1. “Two groups of stakeholders were identified: Legally Mandated Organisations (LMOs) and Spatial Data Interest Community (SDIC).”
+Literature:
+• Kubicek (2008)
+• Gruninger (2008)</t>
   </si>
   <si>
     <r>
@@ -2327,20 +2674,18 @@
   </si>
   <si>
     <t>Definition:
-An analytical code used to classify solutions according to the primary mechanism through which interoperability between heterogeneous semantic models, systems, or organizations is realised. The code captures the operational logic of alignment, reconciliation, or coordination, rather than the artefact used or the authority governing it.
-Inclusion criteria:
-- The solution description specifies or implies how heterogeneity is handled.
-- The operational logic of achieving interoperability can be identified.
-- The mechanism concerns semantic or informational alignment rather than mere technical connectivity.
-Exclusion criteria:
-- Descriptions limited to artefact types without alignment logic.
-- Pure governance arrangements without operational mechanisms.
-- Transport, protocol, or infrastructure mechanisms without semantic impact.
-Literature:
-   ◦ Kubicek, H. (2009). Governance of Interoperability in Intergovernmental Services.
-   ◦ Wache, H. et al. (2001). Ontology-Based Integration of Information — A Survey of Existing Approaches.
-   ◦ Doan, A., Halevy, A. &amp; Ives, Z. (2012). Principles of Data Integration.
-   ◦ Wimmer, M.A., Boneva, R. &amp; di Giacomo, D. (2018). Interoperability Governance: A Definition and Insights from Case Studies in Europe.</t>
+Header category. Analytical dimension classifying solutions by the primary mechanism through which interoperability between heterogeneous semantic models, systems, or organizations is realised.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• Kubicek (2009)
+• Wache et al. (2001)
+• Doan et al. (2012)
+• Wimmer et al. (2018)</t>
   </si>
   <si>
     <r>
@@ -2354,25 +2699,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition
-Interoperability is achieved by requiring all participating actors or systems to conform to shared specifications, such as a canonical data models, reference ontologies, or mandatory standards. Semantic heterogeneity is eliminated ex ante through uniform adoption.
-Inclusion criteria:
-- Authoritative semantic artefacts are defined for all users.
-- Compliance with the shared model is required or expected.
-- Local variation is restricted or tightly governed.
-- Interoperability depends on uniform interpretation.
-Exclusion criteria:
-- Solutions relying on mappings or mediation between distinct models.
-- Approaches that preserve local semantic autonomy.
-- Ad hoc bilateral alignment.
-Examples:
-- Common Data Models mandated for reporting.
-- Canonical data schemas imposed across organizations.
-Lliterature:
-   - Wache, H., Vögele, T., Visser, U., Stuckenschmidt, H., Schuster, G., Neumann, H. and Hübner, S. (2001). Ontology-Based Integration of Information — A Survey of Existing Approaches.
-   - Guarino, N. (1998). Formal Ontology and Information Systems.
-   - Uschold, M. &amp; Gruninger, M. (2004). Ontologies and Semantics for Seamless Connectivity.
-</t>
+    <t>Definition:
+Interoperability is achieved by requiring all participating actors or systems to conform to shared specifications, such as canonical data models, reference ontologies, or mandatory standards. Heterogeneity is eliminated ex ante through uniform adoption.
+Inclusion Criteria:
+1. Authoritative semantic artefacts for all users.
+2. Compliance with shared model required.
+3. Local variation restricted.
+Exclusion Criteria:
+1. Mappings or mediation (use Mediation-based).
+2. Local autonomy preserved (use Identifier-based).
+Example Quotations:
+1. “A central goal of FinnONTO was to create an interlinked cloud of national ontologies based on existing thesauri...”
+Literature:
+• Wache et al. (2001)
+• Guarino (1998)
+• Uschold &amp; Gruninger (2004)</t>
   </si>
   <si>
     <r>
@@ -2386,23 +2727,24 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
+    <t>Definition:
 Interoperability is achieved by organizing and coordinating semantic practices across actors without enforcing shared models or explicit mappings. Alignment emerges through procedures, agreements, or governance processes.
-Inclusion criteria:
-- Interoperability relies on coordination rather than artefacts.
-- Semantic agreement is procedural or negotiated.
-- Local semantic autonomy is preserved.
-Exclusion criteria:
-- Formal semantic mappings or mediation infrastructures.
-- Mandatory standards or canonical models.
-- Purely technical exchange mechanisms.
-Examples:
-- Federated metadata registries.
-- Linked Data ecosystems based on shared identifiers.
-Literature:
-   - Wimmer, M.A., Boneva, R. &amp; di Giacomo, D. (2018). Interoperability Governance: A Definition and Insights from Case Studies in Europe.
-   - Kubicek, H. (2009). Governance of Interoperability in Intergovernmental Services.
-</t>
+Inclusion Criteria:
+1. Procedural rather than artefact-based alignment.
+2. Negotiated semantic agreement.
+3. Local semantic autonomy preserved.
+Exclusion Criteria:
+1. Formal mappings present (use Mediation-based).
+2. Mandatory standards (use Conformance-based).
+3. Pure technical exchange.
+Example Quotations:
+1. “The problem with this approach is that nailing down meaning is fraught. Negotiation is involved in the development of categories.”
+2. “This binding relation ensures a 'mapping' of a term's meaning from one value set across the ontology to any other value set.”
+Notes:
+Note: empirically thin in current dataset consider expanding sampling on this code
+Literature:
+• Wimmer et al. (2018)
+• Kubicek (2009)</t>
   </si>
   <si>
     <r>
@@ -2417,21 +2759,20 @@
   </si>
   <si>
     <t>Definition:
-Interoperability is achieved through a deliberate combination of two or more distinct interoperability mechanisms. Different mechanisms may apply at different layers, scopes, or phases.
-Inclusion criteria:
-- Multiple mechanisms are explicitly combined.
-- The combination is intentional and articulated.
-- No single mechanism dominates across the solution.
-Exclusion criteria:
-- Vague or accidental hybridity.
-- Multiple mechanisms mentioned without integration rationale.
-Examples:
-- Federated governance with mediation and local conformance.
-- Shared core models combined with mappings for extensions.
-Lliterature:
-    ◦ Wache, H. et al. (2001). Ontology-Based Integration of Information — A Survey of Existing Approaches.
-    ◦ Uschold, M. &amp; Gruninger, M. (2004). Ontologies and Semantics for Seamless Connectivity.
-    ◦ Doan, A. et al. (2012). Principles of Data Integration.</t>
+Interoperability is achieved through a deliberate combination of two or more distinct interoperability mechanisms applied at different layers, scopes, or phases.
+Inclusion Criteria:
+1. Multiple mechanisms explicitly combined.
+2. Combination intentional and articulated.
+3. No single dominant mechanism.
+Exclusion Criteria:
+1. Vague or accidental hybridity.
+2. Multiple mechanisms mentioned without integration rationale.
+Literature:
+• Wache et al. (2001)
+• Uschold &amp; Gruninger (2004)
+• Doan et al. (2012)
+• No quotations yet
+• retained for analytical completeness</t>
   </si>
   <si>
     <r>
@@ -2445,26 +2786,24 @@
     </r>
   </si>
   <si>
-    <t>Definition
-Interoperability is achieved through loose coupling by means of shared identifiers, metadata, and linking practices, without requiring semantic convergence, explicit mappings, or data transformation. Actors retain full semantic autonomy, while interoperability emerges from the ability to reference, discover, and relate distributed information resources.
-Inclusion criteria:
-- Interoperability relies on shared identifiers (e.g. URIs), metadata schemas, or linking principles.
-- Data remain at the source and are not transformed into a common schema.
-- Semantic alignment is limited to naming, referencing, or lightweight relationships.
-- The solution prioritizes scalability, openness, and autonomy over semantic precision.
-Exclusion criteria:
-- Explicit semantic mappings or mediation logic.
-- Mandatory adoption of shared conceptual models or ontologies.
-- Translation or transformation of data for semantic reconciliation.
-- Procedural coordination mechanisms aimed at negotiating meaning.
-Examples:
-- Linked Data ecosystems using shared vocabularies and URIs.
-- Federated metadata registries enabling dataset discovery across domains.
-- Open data portals relying on DCAT and SKOS for cross-dataset linking.
-Llterature:
-    ◦ Berners-Lee, T., Hendler, J. &amp; Lassila, O. (2001). The Semantic Web.
-    ◦ Euzenat, J. &amp; Shvaiko, P. (2013). Ontology Matching.
-    ◦ Doan, A. et al. (2012). Principles of Data Integration.</t>
+    <t>Definition:
+Interoperability is achieved through loose coupling by means of shared identifiers, metadata, and linking practices, without requiring semantic convergence, explicit mappings, or data transformation. Actors retain full semantic autonomy.
+Inclusion Criteria:
+1. Shared identifiers (URIs, DOIs).
+2. Federated metadata registries enabling discovery.
+3. Linked Data ecosystems with shared vocabularies.
+4. Linking without semantic convergence.
+Exclusion Criteria:
+1. Explicit semantic mappings (use Mediation-based).
+2. Mandatory canonical models (use Conformance-based).
+3. Procedural negotiation (use Coordination-based).
+Example Quotations:
+1. “A central goal of FinnONTO was to create an interlinked cloud of national ontologies.”
+Literature:
+• Berners-Lee et al. (2001)
+• Euzenat &amp; Shvaiko (2013)
+• Doan et al. (2012)
+• Conceptually adjacent to Solution Level of Shared Meaning: Shared identifiers, but operates at a different analytical layer (mechanism vs level)</t>
   </si>
   <si>
     <r>
@@ -2478,28 +2817,26 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Interoperability is achieved through an intermediary mediation logic that reconciles semantic heterogeneity between autonomous models by relying on explicit semantic mappings and executing translation or transformation operations. Mapping provides the declarative specification of semantic correspondences, while translation operationalizes these correspondences through data or message transformation. Together, they constitute a mediation-based interoperability mechanism.
-Inclusion criteria:
-- An explicit mediation logic is present that enables interoperability between heterogeneous semantic models.
-- Semantic correspondences (mappings or alignments) between models are defined or assumed.
-- Data or messages are transformed, interpreted, or reconciled based on these correspondences.
-- Local semantic models remain autonomous and are not replaced by a single canonical model.
-Exclusion criteria:
-- Mandatory conformance to a single shared or canonical semantic model.
-- Purely organizational coordination without semantic reconciliation.
-- Purely technical data transformation without an explicit semantic basis.
-Examples:
-- Ontology-based mediation architectures that use mappings to translate between domain models.
-- Semantic gateways or brokers that transform messages based on alignment rules.
-- Data integration platforms that mediate between multiple schemas via an intermediary semantic layer.
-Literature:
-   - Euzenat, J. &amp; Shvaiko, P. (2013). Ontology Matching.
-   - Doan, A., Halevy, A. &amp; Ives, Z. (2012). Principles of Data Integration.
-   - Wache, H. et al. (2001). Ontology-Based Integration of Information — A Survey of Existing Approaches.
-   - Guarino, N. (1998). Formal Ontology and Information Systems.
-Vogt Fair2.0: “The federated interoperability approach, on the other hand, assumes that data formats and  schemata have to be adapted dynamically instead of having a predefined super metamodel.” 
-</t>
+    <t>Definition:
+Interoperability is achieved through an intermediary mediation logic that reconciles semantic heterogeneity between autonomous models by relying on explicit semantic mappings and executing translation or transformation operations.
+Inclusion Criteria:
+1. Explicit mediation logic between heterogeneous models.
+2. Defined semantic correspondences.
+3. Data or messages transformed based on mappings.
+4. Local models remain autonomous.
+Exclusion Criteria:
+1. Mandatory single canonical model (use Conformance-based).
+2. Pure organizational coordination.
+3. Technical conversion without semantic basis.
+Example Quotations:
+1. “Canonical evidence serves as translation of domestic evidence, so automatic processing is enabled.”
+2. “Instead, researchers will have to work with a federated database system in which translation between databases from different domains is mediated at a meta-level.”
+Literature:
+• Euzenat &amp; Shvaiko (2013)
+• Doan et al. (2012)
+• Wache et al. (2001)
+• Guarino (1998)
+• Vogt FAIR 2.0</t>
   </si>
   <si>
     <r>
@@ -2513,6 +2850,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Interoperability is achieved through declarative or logical rules that define how heterogeneous models or data are aligned, transformed, or interpreted at runtime, often in combination with mediation.
+Inclusion Criteria:
+1. Declarative rule sets governing transformation.
+2. Logical inference rules across ontologies.
+3. Rule-driven mediation engines.
+Exclusion Criteria:
+1. Static one-off mappings (use Mediation-based).
+2. Pure conformance regimes (use Conformance-based).
+Example Quotations:
+1. “The mediator ontology is represented by the language CARLIN-ALN. In PICSEL, the domain knowledge is expressed in a declarative manner...”
+Notes:
+Newly defined; closely related to Mediation-based but emphasizes rule-driven rather than mapping-driven logic.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2525,16 +2877,13 @@
   </si>
   <si>
     <t>Definition:
-Solution Level of Shared Meaning refers to the extent and depth of semantic agreement that a solution assumes, establishes, or requires among participating actors. It captures how far shared meaning is institutionalized, ranging from minimal agreement on terminology to full commitment to a unified semantic or ontological framework. This dimension focuses on the ontological commitment implied by a solution, independent of governance structure or technical implementation.
-Inclusion criteria:
-•The solution explicitly or implicitly assumes a particular depth of shared meaning among actors.
-•The level of semantic agreement can be inferred from the proposed models, artefacts, or mechanisms.
-•The solution can be meaningfully classified into one of the subordinate categories.
-•The level of shared meaning influences how interoperability is achieved or constrained.
-Exclusion criteria:
-•Solutions that do not articulate or imply any form of semantic agreement.
-•Purely technical interoperability mechanisms without semantic assumptions.
-•Organizational or governance arrangements that do not address shared meaning.</t>
+Header category. Analytical dimension capturing the extent and depth of semantic agreement that a solution assumes, establishes, or requires among participating actors.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code.</t>
   </si>
   <si>
     <r>
@@ -2544,26 +2893,38 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Level of Shared Meaning: Conceptuel Model</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Level of Shared Meaning: Fully Shared Meaning</t>
     </r>
   </si>
   <si>
     <t>Definition:
 Situations in which all participating parties commit to a single, comprehensive semantic reality that defines domain concepts, relationships, and constraints across use cases and organizational boundaries.
-Inclusion criteria:
-•One unified semantic or conceptual model governs all participants.
-•Strong ontological commitment and centralized governance.
-•Semantic agreement is comprehensive rather than scoped.
-•Local systems conform to or are derived from the shared model.
-Exclusion criteria:
-•Modular, partial, or use-case–specific semantic agreement.
-•Federated or mapping-based interoperability approaches.
-•Upper ontologies without domain-level unification.
+Inclusion Criteria:
+1. One unified semantic model governs all participants.
+2. Strong ontological commitment, centralized governance.
+3. Comprehensive semantic agreement.
+Exclusion Criteria:
+1. Modular or scoped semantic agreement (use Shared Meaning on Core Elements).
+2. Federated or mapping-based interoperability.
+3. Upper ontologies without domain unification.
+Example Quotations:
+1. “A National Effort The goal in the FinnONTO initiative was to develop a national ontology and content infrastructure...”
 Literature:
 • Uschold &amp; Gruninger
-• Wache et al. 
-• Kubicek 
-In Fair 2.0 by Vogt this level of interoperability is a form of “schema interoperability”</t>
+• Wache et al
+• Kubicek
+• FAIR 2.0 (Vogt) as 'schema interoperability'</t>
   </si>
   <si>
     <r>
@@ -2577,6 +2938,22 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Parties share identifiers (URIs, codes, persistent identifiers) without sharing an explicit conceptualization of the underlying domain. Agreement enables linking but not interpretation.
+Inclusion Criteria:
+1. Shared URIs across systems.
+2. Persistent identifiers as ground for linking.
+3. Linked Data ecosystems with shared identifier schemes.
+Exclusion Criteria:
+1. Shared definitions of concepts (use Terminological or Core Elements).
+2. Shared metadata schemas (use Shared Metadata).
+Example Quotations:
+1. “The second principle points to the 'use HTTP URIs so that people can look up those names'.”
+2. “All addresses and streets were given a universally unique identifier which can be looked up via the web.”
+Notes:
+Newly defined. Boundary with Terminological: Identifiers are bare references; Terminological adds labels and codes.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2588,19 +2965,20 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Situations in which parties share a partial semantic reality by agreeing on a bounded set of domain concepts or data elements with explicit meaning. Semantic overlap is intentional, scoped, and sufficient for specific interoperability purposes.
-Inclusion criteria:
-•Common Data Elements (CDEs) with agreed definitions.
-•Domain-specific or modular semantic models that do not need to form a coherent model model.
-•Common Data Models (CDMs) used for reporting, analytics, or exchange.
-•Reference models adopted within a defined scope or use case.
-Exclusion criteria:
-•Purely terminological artifacts without semantic definitions.
-•Upper ontologies or domain-independent foundational models.
-•Claims of full semantic unification across all domains or actors.
-Literature:
-In Fair 2.0 by Vogt this level of interoperability is a form of “schema interoperability” on the Core Elements only </t>
+    <t>Definition:
+Parties share a partial semantic reality by agreeing on a bounded set of domain concepts or data elements with explicit meaning. Semantic overlap is intentional, scoped, and sufficient for specific purposes.
+Inclusion Criteria:
+1. Common Data Elements with agreed definitions.
+2. Domain-specific or modular semantic models.
+3. Reference models adopted within a defined scope.
+Exclusion Criteria:
+1. Purely terminological artefacts.
+2. Upper ontologies.
+3. Claims of full semantic unification.
+Example Quotations:
+1. “OSLO created an ontology in three main domains of interest: persons and organisations, locations, and public services...”
+Literature:
+• FAIR 2.0 (Vogt) 'schema interoperability on the Core Elements only'</t>
   </si>
   <si>
     <r>
@@ -2614,6 +2992,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Parties share metadata schemas and structures that enable interpretation and discovery of data, without sharing the underlying domain conceptualization in full.
+Inclusion Criteria:
+1. Common metadata schemas (e.g., DCAT, ISO 19115).
+2. Shared metadata vocabularies for description.
+3. Federated metadata registries with common profiles.
+Exclusion Criteria:
+1. Shared data models with full conceptual definitions (use Core Elements).
+2. Shared identifiers without metadata schema (use Shared Identifiers).
+Example Quotations:
+1. “Member States ensure that metadata are created for the spatial data sets and services corresponding to one or more of the INSPIRE themes.”
+Notes:
+Newly defined; an empirically distinct level between Shared Identifiers and Shared Meaning on Core Elements.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2626,17 +3019,20 @@
   </si>
   <si>
     <t>Definition:
-Situations in which parties share terminology or identifiers but not an explicit conceptualization of the underlying domain. Agreement is limited to labels, codes, or references.
-Inclusion criteria
-•Use of controlled vocabularies, code lists, thesauri, or identifiers.
-•Agreement addresses naming heterogeneity only.
-•Adoption of Linked Data principles without shared domain models.
-Exclusion criteria
-•Explicit definitions of concepts or data elements.
-•Shared semantic models, reference models, or mappings with semantic intent.
-•Constraints or relationships that define conceptual meaning.
-Literature:
-FAIR 2.0 Vogt</t>
+Parties share terminology, controlled vocabularies, code lists, or thesauri but not an explicit conceptualization of the underlying domain. Agreement is limited to labels, codes, or references.
+Inclusion Criteria:
+1. Controlled vocabularies, code lists, thesauri.
+2. Agreement on naming heterogeneity only.
+3. Linked Data principles without shared models.
+Exclusion Criteria:
+1. Explicit definitions of concepts (use Core Elements).
+2. Mappings with semantic intent.
+3. Constraints defining conceptual meaning.
+Example Quotations:
+1. “A central goal of FinnONTO was to create an interlinked cloud of national ontologies based on existing thesauri.”
+2. “The envisioned enablers would take the form of common standards (taxonomies, controlled vocabularies, thesauri, code lists, etc.)...”
+Literature:
+• FAIR 2.0 (Vogt)</t>
   </si>
   <si>
     <r>
@@ -2650,20 +3046,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Situations in which actors adopt a shared upper ontology consisting of a coherent set of foundational entities and explicitly defined relations, forming a unified ontological framework that constrains and aligns multiple domain models.
-Inclusion criteria:
-•An explicit upper or foundational ontology is adopted.
-•Foundational categories such as object, event, agent, role, or process are: explicitly defined, and systematically related through typed relations.
-•The ontology forms a single, coherent ontological theory.
-•It is intended to structure or align semantics across multiple domains.
-Exclusion criteria
-•Abstract terms are listed without explicit relations.
-•High-level concepts are used informally or heuristically.
-•The artifact functions primarily as a vocabulary, classification, metadata schema, or architectural guideline.
-•Semantic agreement is limited to a single domain or use case..
-Literature:
-In Fair 2.0 by Vogt this level of interoperability is a form of “schema interoperability” on the Upper semantic realisty only </t>
+    <t>Definition:
+Actors adopt a shared upper ontology consisting of foundational entities and explicitly defined relations, forming a unified ontological framework that constrains and aligns multiple domain models.
+Inclusion Criteria:
+1. Explicit upper or foundational ontology.
+2. Foundational categories systematically related.
+3. Unified ontological theory across domains.
+Exclusion Criteria:
+1. Abstract terms without explicit relations.
+2. High-level concepts used informally.
+3. Vocabulary or metadata schema only.
+4. Single domain only.
+Literature:
+• FAIR 2.0 (Vogt) 'schema interoperability on the Upper semantic reality only'
+• No quotations yet
+• retained for analytical completeness</t>
   </si>
   <si>
     <r>
@@ -2677,6 +3074,17 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Header category. Analytical dimension capturing the formal modelling language or paradigm in which a proposed semantic artefact or interoperability solution is expressed (e.g., RDF, OWL, UML, XML Schema). The dimension complements but does not replace Requirement: Semantic: Formal and Shared Syntax for Knowledge Representation, which is the normative requirement; this dimension classifies the actual modelling choice in a described solution.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+2. Do not use for the requirement that a formal syntax must be used (use Formal and Shared Syntax requirement).
+Notes:
+Header / parent code. Subcodes capture concrete modelling choices observed in solutions.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2684,10 +3092,93 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Modelling type: Ontology</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+The solution expresses semantic artefacts as a formal ontology in the OWL family or comparable formalisms, with explicit class hierarchies, properties, axioms, and reasoning support, regardless of whether the serialisation is RDF, Turtle, OWL/XML, or Manchester syntax.
+Inclusion Criteria:
+1. Formal ontologies in OWL, OWL2, or comparable description logic formalisms.
+2. Class and property hierarchies with axioms supporting reasoning.
+3. Use of reasoners (HermiT, Pellet) over the artefact.
+Exclusion Criteria:
+1. Lightweight RDF Linked Data without OWL axioms (use RDF).
+2. Conceptual UML models without formal ontology semantics (use UML).
+Notes:
+Distinguished from RDF: RDF is the data model and serialisation choice, Ontology focuses on the logical formalism and reasoning support.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: OntoUML</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+The solution expresses semantic artefacts in OntoUML, a UML profile grounded in the Unified Foundational Ontology (UFO), supporting rigorous ontological distinctions (kinds, roles, relators, modes) and validation through model-checking tools.
+Inclusion Criteria:
+1. Solutions modelled in OntoUML or with explicit UFO grounding.
+2. Conceptual models that distinguish UFO categories such as kind, role, relator, or mode.
+3. Use of OntoUML tooling for validation or ontology unpacking.
+Exclusion Criteria:
+1. Plain UML class diagrams without UFO grounding (use UML).
+2. Pure RDF/OWL representations without UFO commitments (use RDF).
+Notes:
+OntoUML is increasingly used in semantic interoperability work to surface ontological commitments that plain UML hides; retained as separate subtype.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: OWL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: Paper</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Modelling type: RDF</t>
     </r>
   </si>
   <si>
+    <t>Definition:
+The solution expresses semantic artefacts in RDF or RDF‐derived languages (RDFS, OWL, SKOS), typically serialised as Turtle, RDF/XML, JSON‐LD, or N‐Triples, supporting graph‐based representation, dereferenceable URIs, and SPARQL querying.
+Inclusion Criteria:
+1. Solutions explicitly using RDF, OWL, RDFS, SKOS, or JSON‐LD.
+2. Linked Data implementations relying on triples and URIs.
+3. Use of SPARQL endpoints over RDF data.
+Exclusion Criteria:
+1. Solutions modelled in UML or XML Schema only (use UML or extend the dimension).
+2. Generic statements that a formal syntax is required (use Formal and Shared Syntax requirement).
+Notes:
+Empirically thin in the current dataset, but analytically important to retain because RDF is a defining choice in much of the surveyed Linked Data work.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2695,10 +3186,34 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Modelling type: SHACL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Modelling type: UML</t>
     </r>
   </si>
   <si>
+    <t>Definition:
+The solution expresses semantic artefacts in UML class diagrams, profiles, or related object‐oriented modelling notations, typically supporting conceptual modelling, application profiles, or generation of XML Schemas.
+Inclusion Criteria:
+1. Solutions modelled in UML class diagrams or profiles.
+2. Use of UML to specify INSPIRE or ISA conceptual data models.
+3. UML as the source for derived schemas.
+Exclusion Criteria:
+1. Solutions in RDF/OWL only (use RDF).
+2. Pure XML Schema authored without UML lineage.
+Notes:
+Empirically thin, often present in figures rather than narrative text; retained for completeness because INSPIRE and the OSLO programme make extensive use of UML.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2706,23 +3221,51 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Modelling type: WSDL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: XBRL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: XML</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Scope</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Solution Scope captures the primary contextual breadth at which a proposed solution for semantic interoperability is intended to operate. It specifies the level at which applicability, design assumptions, and constraints are articulated, ranging from highly context-specific settings to context-independent abstractions. The code reflects how explicitly the solution positions itself with respect to domain, jurisdictional, and organizational boundaries.
-Inclusion criteria:
-•The publication explicitly or implicitly defines the contextual level at which the solution is applicable.
-•The scope of applicability can be derived from stated assumptions, design choices, or constraints.
-•The solution can be meaningfully classified into one or more subordinate scope categories, such as Domain/Sector Oriented, Jurisdictional/Geography Oriented, Organizational Oriented, or Generic Scope.
-•The scope influences the design rationale, implementation approach, or governance of the solution.
-Exclusion criteria:
-•Publications that describe isolated technical components without any indication of intended applicability or context.
-•Conceptual discussions of interoperability problems that do not propose or analyze a solution.
-•Empirical case descriptions where no generalization or positioning of the solution scope is provided or inferable.
-Literature:
-</t>
+    <t>Definition:
+Header category. Analytical dimension capturing the primary contextual breadth at which a proposed solution is intended to operate.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code.</t>
   </si>
   <si>
     <r>
@@ -2737,17 +3280,21 @@
   </si>
   <si>
     <t>Definition:
-Solutions are classified as Domain/Sector Oriented when they are explicitly designed to address semantic interoperability within a specific policy domain, functional sector, or thematic area, such as healthcare, social services, justice, education, or energy. 
-Inclusion criteria:
-•The solution targets one clearly identifiable domain or sector.
-•Domain-specific concepts, ontologies, data models, or standards are central to the solution.
-•The solution assumes shared domain knowledge or sector-specific practices.
-Exclusion criteria:
-•Solutions positioned as domain-agnostic or cross-domain by design.
-•Solutions primarily scoped by geography or organizational context rather than by domain.
-•Generic semantic technologies without explicit domain grounding.
-Literature:
-Bontas 2007, Gruninger 2007, Guarino 1998</t>
+Solutions explicitly designed to address semantic interoperability within a specific policy domain, functional sector, or thematic area, such as healthcare, justice, geospatial, or addresses.
+Inclusion Criteria:
+1. Single clearly identifiable domain or sector.
+2. Domain-specific concepts central to design.
+3. Domain-shared knowledge or sector practices assumed.
+Exclusion Criteria:
+1. Domain-agnostic or cross-domain by design (use Generic).
+2. Primarily geographic or organizational scope.
+Example Quotations:
+1. “The Danish Address Programme is a sub-programme of the Basic Data Programme.”
+2. “The Netherlands are going through a similar process. The Cadastre, the Dutch Land Registry and Mapping Agency...”
+Literature:
+• Bontas (2007)
+• Gruninger (2007)
+• Guarino (1998)</t>
   </si>
   <si>
     <r>
@@ -2762,19 +3309,20 @@
   </si>
   <si>
     <t>Definition:
-Solutions are classified as Generic Scope when they are explicitly designed to be broadly applicable across multiple domains, jurisdictions, and organizational contexts without requiring domain-specific semantics, jurisdiction-specific legal assumptions, or organization-specific structures. 
-Inclusion criteria:
-•The solution is explicitly presented as domain-agnostic or cross-domain.
-•No dependency on sector-specific concepts, vocabularies, or workflows is assumed.
-•The solution does not rely on jurisdiction-specific legal or administrative frameworks.
-•The primary is intended for broad reuse.
-Exclusion criteria:
-•Solutions that require adaptation to a specific domain as a core design assumption.
-•Solutions constrained by national, regional, or local legal or policy frameworks.
-•Solutions tailored to the internal structures or processes of specific organizations.
-•Solutions that claim generality but are empirically demonstrated or conceptually grounded in only one domain, jurisdiction, or organizational setting without abstraction.
-Literature:
-Bontas 2007 (mentioned is meta ontology)</t>
+Solutions explicitly designed to be broadly applicable across multiple domains, jurisdictions, and organizational contexts without requiring domain-specific semantics or jurisdiction-specific assumptions.
+Inclusion Criteria:
+1. Domain-agnostic or cross-domain by design.
+2. No sector-specific concepts.
+3. No jurisdiction-specific frameworks.
+Exclusion Criteria:
+1. Domain-specific design (use Domain).
+2. Jurisdiction-specific (use Jurisdictional).
+Notes:
+consider whether this code is empirically supported
+Literature:
+• Bontas (2007)
+• No quotations directly
+• Retained provisionally</t>
   </si>
   <si>
     <r>
@@ -2788,18 +3336,20 @@
     </r>
   </si>
   <si>
-    <t>Definition
-Solutions are classified as Jurisdictional/Geography Oriented when their design, applicability, or governance is explicitly tied to a specific geographic, legal, or administrative jurisdiction, such as a country, region, municipality, or supranational entity. The scope is primarily determined by jurisdiction-specific legal frameworks, administrative structures, or policy mandates.
-Inclusion criteria:
-•The solution is explicitly developed for a named jurisdiction or geographic area.
-•Legal, regulatory, or administrative constraints of that jurisdiction bind the solution.
-•The solution references jurisdiction-specific policies, laws, or governance arrangements.
-Exclusion criteria:
-•Solutions designed to be globally applicable without jurisdictional assumptions.
-•Domain-oriented solutions that happen to be evaluated in a single country without jurisdictional dependency.
-•Organization-specific solutions without explicit geographic or legal anchoring.
-Literature:
-Gruninger 2007 (not explicitly only mentioned functional)</t>
+    <t>Definition:
+Solutions whose design, applicability, or governance is explicitly tied to a specific geographic, legal, or administrative jurisdiction, such as a country, region, municipality, or supranational entity.
+Inclusion Criteria:
+1. Explicit jurisdiction or geographic area.
+2. Jurisdiction-specific legal frameworks bind solution.
+3. Reference to jurisdiction-specific policies.
+Exclusion Criteria:
+1. Globally applicable without jurisdictional assumptions (use Generic).
+2. Organization-specific without geographic anchoring (use Organizational).
+Example Quotations:
+1. “The new agency launched the programme OSLO that focuses on the semantic interoperability level...”
+2. “The Flemish Government administration aligns its base registries with this definition...”
+Literature:
+• Gruninger (2007)</t>
   </si>
   <si>
     <r>
@@ -2813,18 +3363,17 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Solutions are classified as Organizational Oriented when they are primarily designed to support semantic interoperability within or between specific organizations, focusing on internal structures, processes, information systems, or governance arrangements. The scope is defined by organizational boundaries rather than by domain or jurisdiction.
-Inclusion criteria:
-•The solution targets interoperability within a single organization or a defined set of collaborating organizations.
-•Organizational processes, roles, or information architectures are central design drivers.
-•The solution assumes organization-specific practices, data structures, or governance mechanisms.
-Exclusion criteria:
-•Sector-wide or jurisdiction-wide solutions transcending individual organizational boundaries.
-•Generic frameworks intended for broad adoption across organizations without customization.
-•Purely technical solutions lacking an explicit organizational embedding.
-Literature:
-</t>
+    <t>Definition:
+Solutions primarily designed to support semantic interoperability within or between specific organizations, focusing on internal structures, processes, information systems, or governance arrangements.
+Inclusion Criteria:
+1. Single organization or defined set of collaborating organizations.
+2. Organizational processes and roles central design drivers.
+3. Organization-specific data structures and governance.
+Exclusion Criteria:
+1. Sector- or jurisdiction-wide solutions (use Domain or Jurisdictional).
+2. Generic frameworks for broad adoption.
+Notes:
+Retained for analytical completeness; rare in current dataset.</t>
   </si>
   <si>
     <r>
@@ -2839,19 +3388,19 @@
   </si>
   <si>
     <t>Definition:
-Scope System / Application refers to solutions whose semantic scope is explicitly defined by the requirements of a specific information system or application. Such solutions operationalize domain-level semantics by instantiating or specializing domain ontologies in relation to concrete application tasks, system functionalities, and non-functional constraints. The resulting semantic artefacts are tailored to support particular use cases, workflows, or software components rather than to represent a domain in a general or reusable manner.
-Inclusion criteria:
-•The solution is explicitly designed for a specific information system, software application, or IT solution.
-•Application requirements such as performance, data structures, workflows, or user interactions directly shape the semantic design.
-•The semantic model is intended to support concrete system behavior such as data exchange, validation, querying, or automation within a defined application context.
-•Reuse outside the targeted application is limited, secondary, or not claimed.
-Exclusion criteria:
-•Pure domain ontologies intended to represent a domain independently of any specific application.
-•Generic frameworks, meta-models, or methods that abstract from concrete system implementations.
-•Organization-, jurisdiction-, or sector-scoped solutions that are not tied to a specific application or system.
-•Technical data schemas or APIs that lack an explicit semantic grounding in domain ontologies or conceptual models.
-Literature:
-Bontas 2007, Gruninger 2007</t>
+Solutions whose semantic scope is explicitly defined by the requirements of a specific information system or application, instantiating or specializing domain ontologies to support concrete tasks and workflows.
+Inclusion Criteria:
+1. Specific information system or software.
+2. Application requirements shape semantic design.
+3. Concrete system behaviour supported.
+4. Reuse outside the application is limited.
+Exclusion Criteria:
+1. Pure domain ontologies for general representation.
+2. Generic frameworks abstract from systems.
+3. Organizational scope without specific application.
+Literature:
+• Bontas (2007)
+• Gruninger (2007)</t>
   </si>
   <si>
     <r>
@@ -2865,21 +3414,17 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition
-Solution type refers to the analytical classification of a solution according to the nature of the design artefact that is proposed or described as a response to an identified interoperability challenge. It captures what kind of solution is offered (e.g. semantic asset, standard, implemented solution, service, infrastructure), independent of the specific domain, organizational context, or level of adoption.
-This code is grounded in design science research, where solutions are understood as design artefacts that operationalise requirements by providing a means to address identified problems (Hevner et al., 2004).
-Inclusion criteria:
-– The contribution explicitly or implicitly proposes a solution to a challenge concerning semantic interoperability challenges.
-– The solution can be characterized as a distinct type of design artefact.
-– The description goes beyond problem articulation and specifies how the challenge is addressed.
-– The solution type can be analytically distinguished from other solution types, regardless of implementation context or maturity.
-Exclusion criteria:
-– Pure problem descriptions, challenges, or barriers without a proposed solution.
-– Normative goals or requirements without an accompanying artefact or mechanism.
-– Contextual descriptions of policy, governance, or organizational settings without a solution being proposed.
-– Evaluation results, impact assessments, or performance measurements that do not introduce or describe a solution artefact.
-Literature:
-(Hevner 2004, European Commission EIF Solution Finder), </t>
+    <t>Definition:
+Header category. Analytical classification of solutions according to the nature of the design artefact proposed.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes:
+Header / parent code
+Literature:
+• Hevner et al. (2004)
+• EIF Solution Finder</t>
   </si>
   <si>
     <r>
@@ -2893,6 +3438,23 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Formally negotiated mutual commitments between parties that establish or operationalize interoperability arrangements, such as memoranda of understanding, data-sharing agreements, or steering-committee charters.
+Inclusion Criteria:
+1. Memoranda of understanding.
+2. Data-sharing agreements.
+3. Steering-committee charters and mandates.
+4. Multi-party commitments operationalizing standards.
+Exclusion Criteria:
+1. Statutory legal instruments (use Legal Interoperability Measures).
+2. Frameworks providing reusable structure (use Common Frameworks).
+3. Pure community consensus without formal commitment (use Community Based Governance).
+Example Quotations:
+1. “Governance: as described in the Specification Process, a permanent steering committee was installed, which represents the 'authority'.”
+Notes:
+Newly defined; agreements operationalize legal or organizational requirements, distinct from the legal instruments themselves.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2904,20 +3466,22 @@
     </r>
   </si>
   <si>
-    <t>Definition
-Assessment tools and Evaluation refers to solution artefacts that provide structured methods, instruments, or procedures to assess, evaluate, or measure interoperability-related aspects such as standards, systems, services, or organizational practices. These solutions operationalize evaluation criteria by enabling systematic analysis, comparison, or validation, rather than by directly implementing interoperability.
-Inclusion criteria:
-- The contribution proposes or describes a tool, method, or framework explicitly intended for assessment or evaluation purposes.
-- The solution supports the measurement, validation, or comparison of interoperability characteristics, compliance, or readiness.
-- The solution produces evaluative outputs such as scores, classifications, reports, or compliance assessments.
-- The primary function of the solution is analytical or diagnostic rather than operational.
-Exclusion criteria:
-- Solutions that directly implement or operationalize interoperability (e.g. services, infrastructures, implemented systems).
-- Normative specifications, standards, or semantic models that prescribe how interoperability should be realized without an evaluative function.
-- Generic analytical methods not specifically applied to interoperability assessment.
-- Pure monitoring or reporting results without an underlying assessment instrument.
-Literature:
-(European Commission EIF Solution Finder), (Hevner 2004)</t>
+    <t>Definition:
+Solution artefacts that provide structured methods, instruments, or procedures to assess, evaluate, or measure interoperability-related aspects such as standards, systems, services, or organizational practices.
+Inclusion Criteria:
+1. Tool/method/framework for assessment or evaluation.
+2. Measurement, validation, or comparison of interoperability characteristics.
+3. Evaluative outputs (scores, classifications, reports).
+4. Analytical or diagnostic primary function.
+Exclusion Criteria:
+1. Direct implementation of interoperability (use Implemented Solutions).
+2. Normative specifications (use Standards and Specifications).
+3. Generic analytical methods not specifically applied to interoperability.
+Example Quotations:
+1. “Linked data publications on the SW are typically evaluated with the W3C 5-star deployment scheme, using a quality scale analogous to evaluating hotels.”
+Literature:
+• EIF Solution Finder
+• Hevner (2004)</t>
   </si>
   <si>
     <r>
@@ -2931,20 +3495,23 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Common Frameworks and Tooling refers to solution artefacts that provide reusable conceptual frameworks, methodological approaches, reference models, or structured toolsets intended to guide the design, implementation, coordination, or governance of complex systems or practices. These solutions support consistency, alignment, and comparability across multiple contexts by offering shared structures, principles, or methods rather than delivering operational functionality themselves. 
-This code combines the IOPEU Monitoring solution categories (Common frameworks and Generic tools)
-Inclusion criteria:
-- The contribution proposes or describes a framework, model, methodology, guideline, or integrated toolkit intended for reuse across multiple organizations, projects, or domains.
-- The solution provides structured guidance, abstractions, or organizing principles (e.g. reference architectures, process models, governance frameworks, methodological steps).
-- The solution is designed to be adapted to different contexts rather than instantiated as a single, fixed implementation.
-Exclusion criteria:
-- Operational systems, services, or applications whose primary role is execution or service delivery.
-- Purely technical standards or specifications that focus on syntactic or protocol-level interoperability without broader conceptual or methodological guidance.
-- Isolated tools or software components that lack an explicit framing within a broader framework or methodology.
-- Assessment or evaluation instruments whose primary function is measurement rather than guidance or structuring.
-Literature:
-(European Commission EIF Solution Finder), </t>
+    <t>Definition:
+Solution artefacts that provide reusable conceptual frameworks, methodological approaches, reference models, or structured toolsets intended to guide the design, implementation, coordination, or governance of interoperability.
+Inclusion Criteria:
+1. Reusable framework or reference model.
+2. Methodology providing structured guidance.
+3. Integrated toolkit reusable across contexts.
+Exclusion Criteria:
+1. Operational systems or services (use Implemented Solutions).
+2. Pure technical standards (use Standards and Specifications).
+3. Isolated tools without broader framing.
+Example Quotations:
+1. “The Flemish Government launched an interoperability programme: Open Standards for Linked Organisations (OSLO).”
+2. “OSLO² provides a policy framework for technical topics, including the URI-strategy.”
+Notes:
+Combines the IOPEU Common Frameworks and Generic Tools categories
+Literature:
+• EIF Solution Finder</t>
   </si>
   <si>
     <r>
@@ -2958,6 +3525,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Solution artefacts that consist of explicit, formally documented agreements among multiple parties on shared meaning, classification, or terminology, established through deliberation rather than imposed authority.
+Inclusion Criteria:
+1. Documented multi-party consensus on terminology.
+2. Bottom-up agreement on shared classification.
+3. Deliberative outputs as solution artefacts.
+Exclusion Criteria:
+1. Formal agreements with binding commitment (use Agreements).
+2. Top-down standards (use Standards and Specifications).
+Example Quotations:
+1. “Both the bottom-up and top-down approach were important to create the necessary political support. OSLO was built on consensus, rather than authority.”
+Notes:
+Newly defined; complements Solution Governance Paradigm: Community Based Governance.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2969,6 +3551,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Solution artefacts that consist of explicit guidance documents, technical guidelines, manuals, or non-binding implementation aids supporting the realization of interoperability arrangements.
+Inclusion Criteria:
+1. Technical guideline documents.
+2. Implementation manuals.
+3. Non-binding guidance accompanying standards.
+Exclusion Criteria:
+1. Standards or specifications themselves (use Standards and Specifications).
+2. Methodologies prescribing process (use Methodologies).
+Example Quotations:
+1. “Non-legally binding technical guidance documents illustrate how data providers establish access to metadata for discovery services through CSW.”
+Notes:
+Newly defined; documentation operationalizes standards and frameworks but is itself a distinct artefact.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2981,20 +3578,21 @@
   </si>
   <si>
     <t>Definition:
-Guiding Principles refer to articulated normative statements, values, or high-level design rules that provide direction for decision-making, design, or governance across complex systems or practices. They express desired properties or orientations of solutions and guide how solutions should be conceived, evaluated, or implemented, without prescribing specific structures, models, or technical mechanisms.
-Inclusion criteria:
-- The contribution formulates explicit principles, values, or high-level rules intended to guide design, implementation, or governance decisions.
-- The principles are abstract and broadly applicable across multiple contexts, organizations, or domains.
-- The principles influence or constrain solution development without specifying concrete artefacts or implementation steps.
-- The principles are positioned as foundational orientations rather than operational instructions.
-Exclusion criteria:
-- Concrete frameworks, models, or methodologies that translate principles into structured guidance or procedures.
-- Technical or organizational standards that prescribe specific requirements, formats, or compliance rules.
-- Operational solutions, services, or systems that embody principles without explicitly articulating them.
-- Assessment criteria or metrics that operationalize principles for measurement or evaluation.
-Literature:
-Hevner, A. R., March, S. T., Park, J., &amp; Ram, S. (2004). Design Science in Information Systems Research. MIS Quarterly, 28(1), 75–105.
-Gregor, S., &amp; Jones, D. (2007). The anatomy of a design theory. Journal of the Association for Information Systems, 8(5).</t>
+Articulated normative statements, values, or high-level design rules that provide direction for decision-making, design, or governance, without prescribing specific structures or technical mechanisms.
+Inclusion Criteria:
+1. Explicit principles, values, or high-level rules.
+2. Abstract and broadly applicable.
+3. Foundational orientations rather than instructions.
+Exclusion Criteria:
+1. Concrete frameworks (use Common Frameworks).
+2. Technical or organizational standards (use Standards or Methodologies).
+3. Operational systems.
+Example Quotations:
+1. “The first principle states 'Use URIs as names for things'.”
+2. “Here using the FAIR principles for creating Findable, Accessible, Interoperable, and Re-usable data are recommended.”
+Literature:
+• Hevner (2004)
+• Gregor &amp; Jones (2007)</t>
   </si>
   <si>
     <r>
@@ -3008,21 +3606,21 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Implemented Solutions are interoperability-related solutions that have been technically realized and deployed in an operational context and are actively used in practice. They deliver concrete interoperability effects within a specific organizational or system setting, without being explicitly designed or governed as reusable services, shared infrastructure, or generic building blocks.
-Inclusion criteria:
-– The solution is technically implemented and operational (not only specified or conceptual).
-– The solution is in actual use by one or more organisations.
-– The solution is realised within a specific organisational, legal, or technical context.
-– The solution enables or supports interoperability in practice (explicitly or implicitly).
-Exclusion criteria:
-– Solutions explicitly designed as reusable services or building blocks (e.g. Common Services, Common Infrastructure).
-– Normative or declarative artefacts such as standards, frameworks, vocabularies, or data models.
-– Concepts, pilots, prototypes, or design proposals without operational deployment.
-– Pure assessment or evaluation instruments without operational interoperability effects.
-Literature:
-(Hevner 2004) as instantiated artefact
-</t>
+    <t>Definition:
+Interoperability-related solutions that have been technically realized and deployed in an operational context and are actively used in practice. They deliver concrete interoperability effects within a specific setting.
+Inclusion Criteria:
+1. Technically implemented and operational.
+2. In actual use by one or more organizations.
+3. Realized within specific organizational, legal, or technical context.
+Exclusion Criteria:
+1. Reusable services or building blocks (use Common Frameworks).
+2. Normative artefacts (Standards, Frameworks, Vocabularies, Data Models).
+3. Concepts, pilots, prototypes, design proposals.
+Example Quotations:
+1. “The CRAB Address registry is embedded into the core processes of government administrations.”
+2. “The Address Registry is deployed on a cloud infrastructure: Microsoft Azure.”
+Literature:
+• Hevner (2004) instantiated artefact</t>
   </si>
   <si>
     <r>
@@ -3036,22 +3634,22 @@
     </r>
   </si>
   <si>
-    <t>Definition
-Legal Interoperability Measures refer to solution artefacts that address interoperability challenges by operating within, on the basis of, or through formal legal instruments. This includes statutory law, regulations, and legally binding policy instruments derived from legislation. These measures enable lawful information exchange, coordination, or cooperation across organisational or jurisdictional boundaries by translating legal norms, rights, obligations, and constraints into forms that support interoperable practice.
-Inclusion criteria:
-- The contribution proposes or describes a solution grounded in legislation, regulations, or formally adopted policy instruments derived from law.
-- The solution explicitly addresses legal or regulatory barriers to interoperability, such as jurisdictional differences, legal mandates, compliance requirements, or rights and obligations.
-- The solution operationalizes legal provisions through mechanisms such as legal identifiers, legal metadata models, legally defined roles or responsibilities, compliance constructs, or legally mandated procedures.
-- The solution is intended to enable or constrain interoperability in a legally valid manner across organizations, sectors, or jurisdictions.
-Exclusion criteria:
-- Purely technical, semantic, or organizational solutions that do not rely on or implement legal norms.
-- High-level policy aspirations or strategic visions that are not formally grounded in legislation or legally binding policy.
-- Organizational governance arrangements or agreements without a clear legal or regulatory basis.
-- Assessment or monitoring instruments that evaluate legal compliance without constituting a legal or policy measure themselves.
-Literature:
-(European Commission EIF Solution Finder), 
-01/02/2026, 12:47, merged with
-Solution type: Policy Measures</t>
+    <t>Definition:
+Solution artefacts that address interoperability challenges by operating within, on the basis of, or through formal legal instruments, including statutory law, regulations, and legally binding policy instruments derived from legislation.
+Inclusion Criteria:
+1. Solution grounded in legislation or regulation.
+2. Addresses legal or regulatory barriers.
+3. Operationalizes legal provisions for interoperability.
+4. Lawful information exchange across boundaries.
+Exclusion Criteria:
+1. Purely technical/semantic/organizational solutions without legal basis.
+2. High-level policy aspirations without legal grounding.
+3. Voluntary agreements (use Agreements).
+Example Quotations:
+1. “The legal framework has been set by the Directive (2007/2/EC) and interdependent legal acts.”
+2. “The new agency launched the programme OSLO.”
+Literature:
+• EIF Solution Finder. 01/02/2026 merged with 'Solution Type: Policy Measures'</t>
   </si>
   <si>
     <r>
@@ -3066,18 +3664,19 @@
   </si>
   <si>
     <t>Definition:
-Methodologies refer to solution artefacts that provide a structured, systematic approach for analyzing, designing, implementing, or governing interoperability-related problems. They specify ordered activities, procedures, or phases that guide how solutions should be developed or applied, without prescribing a specific technical implementation, artefact, or system.
-Inclusion criteria:
-- The contribution proposes or describes a clearly articulated method, procedure, or stepwise approach for addressing interoperability challenges.
-- The methodology defines roles, activities, phases, or decision steps that structure how interoperability solutions are developed, applied, or governed.
-- The methodology is intended to be reusable across multiple contexts, organizations, or problem settings.
-- The methodology supports problem-solving or solution development rather than serving as a concrete operational system.
-Exclusion criteria:
-- Abstract guiding principles or value statements without a defined procedural structure.
-- Frameworks or reference models that provide conceptual structure without specifying procedural steps.
-- Technical standards, specifications, or protocols that prescribe implementation requirements rather than processes.
-- Operational systems, services, or tools that execute functionality rather than guide its development or application.
-- Assessment instruments that evaluate outcomes without defining a development or implementation process.</t>
+Solution artefacts that provide a structured, systematic approach for analyzing, designing, implementing, or governing interoperability-related problems through ordered activities, procedures, or phases.
+Inclusion Criteria:
+1. Structured method or stepwise approach.
+2. Defined roles, activities, phases, decision steps.
+3. Reusable across contexts.
+Exclusion Criteria:
+1. Abstract guiding principles (use Guiding Principles).
+2. Frameworks without procedural structure (use Common Frameworks).
+3. Technical standards (use Standards and Specifications).
+Example Quotations:
+1. “This was achieved by implementing a process and methodology for developing semantic agreements, based on the ISA methodology.”
+Literature:
+• EIF Solution Finder</t>
   </si>
   <si>
     <r>
@@ -3091,6 +3690,21 @@
     </r>
   </si>
   <si>
+    <t>Definition:
+Solution artefacts that achieve interoperability through query-oriented mechanisms, including declarative query languages, federated query infrastructures, or query rewriting against heterogeneous sources.
+Inclusion Criteria:
+1. SPARQL endpoints over heterogeneous sources.
+2. Federated query mechanisms.
+3. Query rewriting against multiple schemas.
+Exclusion Criteria:
+1. Static data transformation (use Mediation-based mechanism).
+2. Pure data transport (use Implemented Solutions).
+Example Quotations:
+1. “The second one concerns the query-oriented approach. This approach uses interpretable languages, most of which are either logical declarative...”
+Notes:
+Newly defined; empirically supported by 10 quotations. Note: hyphen normalized.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3102,21 +3716,23 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition:
-Semantic Assets refer to solution artefacts that define, formalize, or harmonize the meaning of data, concepts, or information elements to enable shared understanding across systems, organizations, or jurisdictions. They provide canonical representations of concepts, data elements, roles, or relationships, independent of specific technical implementations, and support semantic interoperability by reducing ambiguity and interpretive differences.
-Inclusion criteria:
-- The contribution proposes or describes shared conceptual definitions, vocabularies, ontologies, data models, or common data elements.
-- The solution explicitly addresses semantic heterogeneity by aligning or standardizing meanings across contexts.
-- The semantic artefact is intended to be reused as a reference for interpretation, mapping, or implementation by multiple parties.
-- The solution focuses on defining what data means rather than how it is technically exchanged or operationally executed.
-Exclusion criteria:
-- Purely technical standards or specifications that primarily prescribe formats, protocols, or interfaces.
-- Operational systems, services, or infrastructures that implement functionality without explicitly defining shared semantics.
-- Methodologies or frameworks that guide processes without providing concrete semantic definitions.
-- Assessment or evaluation tools that analyse semantics without providing a semantic artefact.
-- Legal instruments whose primary purpose is legal validity or compliance rather than semantic alignment.
-Literature:
-(European Commission EIF Solution Finder),  </t>
+    <t>Definition:
+Solution artefacts that define, formalize, or harmonize the meaning of data, concepts, or information elements to enable shared understanding across systems, organizations, or jurisdictions.
+Inclusion Criteria:
+1. Shared conceptual definitions, vocabularies, ontologies.
+2. Common Data Elements or canonical data models.
+3. Reusable as semantic reference for multiple parties.
+4. Define what data means rather than how it is exchanged.
+Exclusion Criteria:
+1. Pure technical standards (use Standards and Specifications).
+2. Operational systems (use Implemented Solutions).
+3. Methodologies guiding processes (use Methodologies).
+4. Legal instruments (use Legal Interoperability Measures).
+Example Quotations:
+1. “The Flemish Government has adapted the ISA address towards INSPIRE.”
+2. “OSLO created an ontology in three main domains of interest: persons and organisations, locations, and public services.”
+Literature:
+• EIF Solution Finder</t>
   </si>
   <si>
     <r>
@@ -3130,21 +3746,33 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Definition
-Standards and Specifications refer to formally defined, authoritative solution artefacts that prescribe rules, requirements, or constraints for interoperability, such as data structures, interfaces, protocols, conformance criteria, or procedural obligations. Their primary purpose is to ensure consistency, compatibility, and compliance across implementations. Unlike semantic assets, standards and specifications do not primarily define meaning, but establish enforceable or normative prescriptions for how interoperability must be realised.
-Inclusion criteria:
-- The contribution proposes or describes a formally specified standard or technical specification with defined scope, versioning, and governance.
-- The artefact prescribes mandatory or normative requirements (e.g. MUST/SHALL rules, conformance profiles) for interoperability.
-- The artefact is intended to be implemented uniformly across systems or organisations to achieve compatibility or regulatory compliance.
-- The primary function is to standardise how interoperability is implemented, validated, or enforced.
-Exclusion criteria:
-Semantic assets that primarily define shared meaning, concepts, vocabularies, ontologies, or canonical data models.
-Guiding principles, methodologies, or frameworks that provide orientation or process guidance without normative prescriptions.
-Operational services or implemented systems that execute functionality without defining a standard or specification.
-Assessment or evaluation instruments that analyse compliance without constituting a standard themselves.
-Legal instruments whose authority derives from law rather than from technical or procedural standardisation.
-Literature:
-(European Commission EIF Solution Finder),  </t>
+    <t>Definition:
+Formally defined, authoritative solution artefacts that prescribe rules, requirements, or constraints for interoperability, such as data structures, interfaces, protocols, conformance criteria, or procedural obligations.
+Inclusion Criteria:
+1. Formally specified standard with versioning and governance.
+2. Mandatory or normative requirements.
+3. Implemented uniformly across systems for compatibility.
+Exclusion Criteria:
+1. Semantic assets defining shared meaning (use Semantic Assets).
+2. Guiding principles or frameworks (use Guiding Principles or Common Frameworks).
+3. Operational systems (use Implemented Solutions).
+4. Legal instruments deriving authority from law (use Legal Interoperability Measures).
+Example Quotations:
+1. “INSPIRE metadata are based on the well-established EN ISO 19115 and EN ISO 19119 standards.”
+2. “The methodology for the development of individual data specification followed a commonly agreed pattern based on the ISO 19131 standard.”
+Literature:
+• EIF Solution Finder</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Type: Validation</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3633,8 +4261,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ef851959-c551-42c2-8a62-0ed41916ab49}">
-  <dimension ref="A1:E130"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{c4982660-d5c4-4ea4-a21c-63a454417822}">
+  <dimension ref="A1:E147"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="80.42857142857143" customWidth="1"/>
@@ -3743,17 +4371,19 @@
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" ht="14.25">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
@@ -3763,10 +4393,10 @@
     </row>
     <row r="10" spans="1:5" ht="14.25">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>7</v>
@@ -3776,10 +4406,10 @@
     </row>
     <row r="11" spans="1:5" ht="14.25">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>7</v>
@@ -3789,10 +4419,10 @@
     </row>
     <row r="12" spans="1:5" ht="14.25">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>7</v>
@@ -3802,14 +4432,10 @@
     </row>
     <row r="13" spans="1:5" ht="14.25">
       <c r="A13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
@@ -3817,39 +4443,43 @@
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" ht="14.25">
       <c r="A15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="14.25">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" ht="14.25">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
@@ -3859,72 +4489,80 @@
     </row>
     <row r="18" spans="1:5" ht="14.25">
       <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" ht="14.25">
       <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="14.25">
       <c r="A20" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" ht="14.25">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="14.25">
       <c r="A22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" ht="14.25">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
@@ -3934,23 +4572,19 @@
     </row>
     <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
@@ -3960,10 +4594,10 @@
     </row>
     <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
@@ -3973,10 +4607,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
@@ -3986,10 +4620,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
@@ -3999,54 +4633,58 @@
     </row>
     <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:5" ht="14.25">
       <c r="A32" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
@@ -4056,63 +4694,71 @@
     </row>
     <row r="35" spans="1:5" ht="14.25">
       <c r="A35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" ht="14.25">
       <c r="A36" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5" ht="14.25">
       <c r="A37" s="2" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" ht="14.25">
       <c r="A38" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" ht="14.25">
       <c r="A39" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" ht="14.25">
       <c r="A40" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -4122,33 +4768,27 @@
     </row>
     <row r="41" spans="1:5" ht="14.25">
       <c r="A41" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" ht="14.25">
       <c r="A42" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" ht="14.25">
       <c r="A43" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4157,10 +4797,10 @@
     </row>
     <row r="44" spans="1:5" ht="14.25">
       <c r="A44" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
@@ -4170,806 +4810,820 @@
     </row>
     <row r="45" spans="1:5" ht="14.25">
       <c r="A45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" ht="14.25">
       <c r="A46" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5" ht="14.25">
       <c r="A47" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B47" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" ht="14.25">
       <c r="A48" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2" t="s">
-        <v>84</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="2"/>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5" ht="14.25">
       <c r="A49" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D49" s="2"/>
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" ht="14.25">
       <c r="A50" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2"/>
-      <c r="D50" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5" ht="14.25">
       <c r="A51" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D51" s="2"/>
       <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" ht="14.25">
       <c r="A52" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5" ht="14.25">
       <c r="A53" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" ht="14.25">
       <c r="A54" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5" ht="14.25">
       <c r="A55" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>98</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="D55" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D55" s="2"/>
       <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" ht="14.25">
       <c r="A56" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" ht="14.25">
       <c r="A57" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B57" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="D57" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5" ht="14.25">
       <c r="A58" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" ht="14.25">
       <c r="A59" s="2" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" ht="14.25">
       <c r="A60" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5" ht="14.25">
       <c r="A61" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5" ht="14.25">
       <c r="A62" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D62" s="2"/>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" ht="14.25">
       <c r="A63" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" ht="14.25">
       <c r="A64" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B64" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>127</v>
+      </c>
       <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="D64" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5" ht="14.25">
       <c r="A65" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" ht="14.25">
       <c r="A66" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5" ht="14.25">
       <c r="A67" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" ht="14.25">
       <c r="A68" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5" ht="14.25">
       <c r="A69" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D69" s="2"/>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5" ht="14.25">
       <c r="A70" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5" ht="14.25">
       <c r="A71" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5" ht="14.25">
       <c r="A72" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B72" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+      <c r="D72" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:5" ht="14.25">
       <c r="A73" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5" ht="14.25">
       <c r="A74" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5" ht="14.25">
       <c r="A75" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B75" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+      <c r="D75" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5" ht="14.25">
       <c r="A76" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5" ht="14.25">
       <c r="A77" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D77" s="2"/>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5" ht="14.25">
       <c r="A78" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5" ht="14.25">
       <c r="A79" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" ht="14.25">
       <c r="A80" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="C80" s="2"/>
-      <c r="D80" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="D80" s="2"/>
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5" ht="14.25">
       <c r="A81" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" ht="14.25">
       <c r="A82" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:5" ht="14.25">
       <c r="A83" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" ht="14.25">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" ht="14.25">
       <c r="A85" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" ht="14.25">
       <c r="A86" s="2" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:5" ht="14.25">
       <c r="A87" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" ht="14.25">
       <c r="A88" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" ht="14.25">
       <c r="A89" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5" ht="14.25">
       <c r="A90" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="D90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5" ht="14.25">
       <c r="A91" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="D91" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5" ht="14.25">
       <c r="A92" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="D92" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E92" s="2"/>
     </row>
     <row r="93" spans="1:5" ht="14.25">
       <c r="A93" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="D93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93" s="2"/>
     </row>
     <row r="94" spans="1:5" ht="14.25">
       <c r="A94" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="D94" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E94" s="2"/>
     </row>
     <row r="95" spans="1:5" ht="14.25">
       <c r="A95" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E95" s="2"/>
     </row>
     <row r="96" spans="1:5" ht="14.25">
       <c r="A96" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.25">
       <c r="A97" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="14.25">
       <c r="A98" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="14.25">
       <c r="A99" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
+      <c r="E99" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="100" spans="1:5" ht="14.25">
       <c r="A100" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="14.25">
       <c r="A101" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B101" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
+      <c r="E101" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="102" spans="1:5" ht="14.25">
       <c r="A102" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="14.25">
       <c r="A103" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="14.25">
       <c r="A104" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B104" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
+      <c r="E104" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="105" spans="1:5" ht="14.25">
       <c r="A105" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="14.25">
       <c r="A106" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B106" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="1:5" ht="14.25">
       <c r="A107" s="2" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="14.25">
       <c r="A108" s="2" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E108" s="2"/>
     </row>
     <row r="109" spans="1:5" ht="14.25">
       <c r="A109" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B109" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>216</v>
+      </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
+      <c r="E109" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="110" spans="1:5" ht="14.25">
       <c r="A110" s="2" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4978,151 +5632,143 @@
     </row>
     <row r="111" spans="1:5" ht="14.25">
       <c r="A111" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
+      <c r="E111" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="112" spans="1:5" ht="14.25">
       <c r="A112" s="2" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E112" s="2"/>
     </row>
     <row r="113" spans="1:5" ht="14.25">
       <c r="A113" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="14.25">
       <c r="A114" s="2" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E114" s="2"/>
     </row>
     <row r="115" spans="1:5" ht="14.25">
       <c r="A115" s="2" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="14.25">
       <c r="A116" s="2" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="14.25">
       <c r="A117" s="2" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E117" s="2"/>
     </row>
     <row r="118" spans="1:5" ht="14.25">
       <c r="A118" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E118" s="2"/>
     </row>
     <row r="119" spans="1:5" ht="14.25">
       <c r="A119" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B119" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5" ht="14.25">
       <c r="A120" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>218</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5" ht="14.25">
       <c r="A121" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>220</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E121" s="2"/>
     </row>
     <row r="122" spans="1:5" ht="14.25">
       <c r="A122" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B122" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5" ht="14.25">
       <c r="A123" s="2" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5131,90 +5777,289 @@
     </row>
     <row r="124" spans="1:5" ht="14.25">
       <c r="A124" s="2" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
-      <c r="E124" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E124" s="2"/>
     </row>
     <row r="125" spans="1:5" ht="14.25">
       <c r="A125" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>226</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E125" s="2"/>
     </row>
     <row r="126" spans="1:5" ht="14.25">
       <c r="A126" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E126" s="2"/>
     </row>
     <row r="127" spans="1:5" ht="14.25">
       <c r="A127" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>230</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="2" t="s">
-        <v>163</v>
-      </c>
+      <c r="E127" s="2"/>
     </row>
     <row r="128" spans="1:5" ht="14.25">
       <c r="A128" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B128" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="E128" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="129" spans="1:5" ht="14.25">
       <c r="A129" s="2" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2" t="s">
-        <v>163</v>
+        <v>190</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="14.25">
       <c r="A130" s="2" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2" t="s">
-        <v>163</v>
-      </c>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="14.25">
+      <c r="A131" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="14.25">
+      <c r="A132" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="14.25">
+      <c r="A133" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="14.25">
+      <c r="A134" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="14.25">
+      <c r="A135" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2"/>
+    </row>
+    <row r="136" spans="1:5" ht="14.25">
+      <c r="A136" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="14.25">
+      <c r="A137" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="14.25">
+      <c r="A138" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+    </row>
+    <row r="139" spans="1:5" ht="14.25">
+      <c r="A139" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2"/>
+    </row>
+    <row r="140" spans="1:5" ht="14.25">
+      <c r="A140" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="14.25">
+      <c r="A141" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="14.25">
+      <c r="A142" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="14.25">
+      <c r="A143" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="14.25">
+      <c r="A144" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2"/>
+    </row>
+    <row r="145" spans="1:5" ht="14.25">
+      <c r="A145" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="14.25">
+      <c r="A146" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" ht="14.25">
+      <c r="A147" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
+++ b/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="289">
   <si>
     <t>Code</t>
   </si>
@@ -2754,6 +2754,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Interoperability Mechanism: Deep learning / AI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Interoperability Mechanism: Hybrid</t>
     </r>
   </si>
@@ -3092,6 +3103,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Modelling type: EDI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Modelling type: Ontology</t>
     </r>
   </si>
@@ -3186,6 +3208,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Modelling type: RosettaNet</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Modelling type: SHACL</t>
     </r>
   </si>
@@ -3212,6 +3245,17 @@
 2. Pure XML Schema authored without UML lineage.
 Notes:
 Empirically thin, often present in figures rather than narrative text; retained for completeness because INSPIRE and the OSLO programme make extensive use of UML.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Modelling type: Vector Database</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4261,8 +4305,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{c4982660-d5c4-4ea4-a21c-63a454417822}">
-  <dimension ref="A1:E147"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{e7ff6755-9d12-41ad-97f8-04e95bd17a8d}">
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="80.42857142857143" customWidth="1"/>
@@ -5564,139 +5608,135 @@
       <c r="A105" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>208</v>
-      </c>
+      <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E105" s="2"/>
     </row>
     <row r="106" spans="1:5" ht="14.25">
       <c r="A106" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
+      <c r="E106" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="107" spans="1:5" ht="14.25">
       <c r="A107" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E107" s="2"/>
     </row>
     <row r="108" spans="1:5" ht="14.25">
       <c r="A108" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
+      <c r="E108" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="109" spans="1:5" ht="14.25">
       <c r="A109" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E109" s="2"/>
     </row>
     <row r="110" spans="1:5" ht="14.25">
       <c r="A110" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
+      <c r="E110" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="111" spans="1:5" ht="14.25">
       <c r="A111" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>219</v>
-      </c>
+      <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E111" s="2"/>
     </row>
     <row r="112" spans="1:5" ht="14.25">
       <c r="A112" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
+      <c r="E112" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="113" spans="1:5" ht="14.25">
       <c r="A113" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
-      <c r="E113" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E113" s="2"/>
     </row>
     <row r="114" spans="1:5" ht="14.25">
       <c r="A114" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
+      <c r="E114" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="115" spans="1:5" ht="14.25">
       <c r="A115" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
-      <c r="E115" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E115" s="2"/>
     </row>
     <row r="116" spans="1:5" ht="14.25">
       <c r="A116" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -5706,21 +5746,23 @@
     </row>
     <row r="117" spans="1:5" ht="14.25">
       <c r="A117" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
+      <c r="E117" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="118" spans="1:5" ht="14.25">
       <c r="A118" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
@@ -5728,29 +5770,31 @@
     </row>
     <row r="119" spans="1:5" ht="14.25">
       <c r="A119" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>235</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
     </row>
     <row r="120" spans="1:5" ht="14.25">
       <c r="A120" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B120" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>235</v>
+      </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
     </row>
     <row r="121" spans="1:5" ht="14.25">
       <c r="A121" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
@@ -5759,16 +5803,14 @@
       <c r="A122" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>239</v>
-      </c>
+      <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
     </row>
     <row r="123" spans="1:5" ht="14.25">
       <c r="A123" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5777,10 +5819,10 @@
     </row>
     <row r="124" spans="1:5" ht="14.25">
       <c r="A124" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -5788,7 +5830,7 @@
     </row>
     <row r="125" spans="1:5" ht="14.25">
       <c r="A125" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -5797,7 +5839,7 @@
     </row>
     <row r="126" spans="1:5" ht="14.25">
       <c r="A126" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -5806,9 +5848,11 @@
     </row>
     <row r="127" spans="1:5" ht="14.25">
       <c r="A127" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
@@ -5817,60 +5861,44 @@
       <c r="A128" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>247</v>
-      </c>
+      <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E128" s="2"/>
     </row>
     <row r="129" spans="1:5" ht="14.25">
       <c r="A129" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>249</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E129" s="2"/>
     </row>
     <row r="130" spans="1:5" ht="14.25">
       <c r="A130" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>251</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E130" s="2"/>
     </row>
     <row r="131" spans="1:5" ht="14.25">
       <c r="A131" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>253</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
-      <c r="E131" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E131" s="2"/>
     </row>
     <row r="132" spans="1:5" ht="14.25">
       <c r="A132" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
@@ -5880,10 +5908,10 @@
     </row>
     <row r="133" spans="1:5" ht="14.25">
       <c r="A133" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
@@ -5893,10 +5921,10 @@
     </row>
     <row r="134" spans="1:5" ht="14.25">
       <c r="A134" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -5906,21 +5934,23 @@
     </row>
     <row r="135" spans="1:5" ht="14.25">
       <c r="A135" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
+      <c r="E135" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="136" spans="1:5" ht="14.25">
       <c r="A136" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -5930,10 +5960,10 @@
     </row>
     <row r="137" spans="1:5" ht="14.25">
       <c r="A137" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -5943,21 +5973,23 @@
     </row>
     <row r="138" spans="1:5" ht="14.25">
       <c r="A138" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
+      <c r="E138" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="139" spans="1:5" ht="14.25">
       <c r="A139" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -5965,10 +5997,10 @@
     </row>
     <row r="140" spans="1:5" ht="14.25">
       <c r="A140" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -5978,10 +6010,10 @@
     </row>
     <row r="141" spans="1:5" ht="14.25">
       <c r="A141" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
@@ -5991,47 +6023,45 @@
     </row>
     <row r="142" spans="1:5" ht="14.25">
       <c r="A142" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
-      <c r="E142" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E142" s="2"/>
     </row>
     <row r="143" spans="1:5" ht="14.25">
       <c r="A143" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="E143" s="2"/>
     </row>
     <row r="144" spans="1:5" ht="14.25">
       <c r="A144" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="E144" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="145" spans="1:5" ht="14.25">
       <c r="A145" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
@@ -6041,10 +6071,10 @@
     </row>
     <row r="146" spans="1:5" ht="14.25">
       <c r="A146" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
@@ -6054,12 +6084,62 @@
     </row>
     <row r="147" spans="1:5" ht="14.25">
       <c r="A147" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B147" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="E147" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" ht="14.25">
+      <c r="A148" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2"/>
+    </row>
+    <row r="149" spans="1:5" ht="14.25">
+      <c r="A149" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="14.25">
+      <c r="A150" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="14.25">
+      <c r="A151" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
+++ b/05_coding/atlas/Literature Review MDIMs – Code List.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="276">
   <si>
     <t>Code</t>
   </si>
@@ -43,14 +43,27 @@
     </r>
   </si>
   <si>
-    <t>Definition:
+    <t xml:space="preserve">Definition:
 Header category. Legal interoperability concerns the extent to which binding legal instruments enable, constrain or structurally condition interoperability across domains and organizations. Use the subcodes for actual coding; this header should not be applied directly to fragments.
 Inclusion Criteria:
 1. Use as analytical container only.
 Exclusion Criteria:
 1. Do not code fragments directly with the parent.
 Notes:
-Header / parent code; not used for fragment-level coding.</t>
+Header / parent code; not used for fragment-level coding.
+Literature:
+Grounding: Scholl &amp; Klischewski (2007), constraints 1 and 2, pp. 893–894; Kubicek et al. (2011), on the EIF 2.0 legal interoperability layer; Navarrete et al. (2010), section 4.4 and pp. 6–7.
+Scholl &amp; Klischewski identify constitutional and legal constraints, where the constitutional division of powers can itself bar integration, and jurisdictional constraints, where constituencies own their information and processes and participation cannot be imposed. Kubicek et al. record that EIF 2.0 adds a distinct legal interoperability layer on top of the original three. Navarrete et al. add distinctive national legislation, issues of sovereignty, and privacy legislation as recurring cross-border barriers. 
+The constitutional and jurisdictional constraints are strongly tied to the US constitutional setting; the codebook reasonably handles the jurisdictional theme of voluntary participation and independent ownership through organizational codes rather than legal ones, and this choice should be documented.
+Codes (consolidated from six to five): Legal incompatibility; Legal restrictions on access and reuse, with Licensing folded in, or kept separate as a sixth code if the licensing instrument is to remain explicit; Legal clarity, that is, ambiguity over rights, responsibilities, and liability; Legal instability; Juridical overhead.
+References
+Dawes, S. S. (1996). Interagency information sharing: Expected benefits, manageable risks. Journal of Policy Analysis and Management, 15(3), 377–394.
+European Commission. (2017). New European Interoperability Framework: Promoting seamless services and data flows for European public administrations. Publications Office.
+Kubicek, H., Cimander, R., &amp; Scholl, H. J. (2011). Organizational Interoperability in E-Government: Lessons from 77 European Good-Practice Cases. Springer.
+Navarrete, C., Gil-Garcia, J. R., Mellouli, S., Pardo, T. A., &amp; Scholl, H. J. (2010). Multinational E-Government Collaboration, Information Sharing, and Interoperability: An Integrative Model. Proceedings of the 43rd Hawaii International Conference on System Sciences.
+Scholl, H. J. (2005). Interoperability in E-Government: More than Just Smart Middleware. Proceedings of the 38th Hawaii International Conference on System Sciences.
+Scholl, H. J., &amp; Klischewski, R. (2007). E-Government Integration and Interoperability: Framing the Research Agenda. International Journal of Public Administration, 30(8–9), 889–920.
+</t>
   </si>
   <si>
     <t>Challenges</t>
@@ -198,27 +211,31 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Legal: Privacy</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Privacy and personal‐data protection obligations, derived from data protection law (such as the GDPR), that constrain the collection, sharing, processing, or reuse of data identifying or relating to individuals; the primary aim of the constraint is the protection of personal data and individual privacy rights, not generic confidentiality or commercial protection.
-Inclusion Criteria:
-1. Restrictions traceable to data protection law (GDPR, national equivalents).
-2. Constraints rooted in protection of identifiable individuals.
-3. Requirements for purpose limitation, minimisation, lawful basis, or consent affecting interoperability.
-4. Pseudonymisation or anonymisation obligations limiting reuse.
-Exclusion Criteria:
-1. Generic confidentiality not aimed at personal data (use Restrictions).
-2. Commercial or state secrecy regimes (use Restrictions).
-3. Licensing terms (use Licensing).
-4. Ambiguity in liability or responsibility (use Clarity).
-5. Technical security weaknesses without legal grounding (use Technical: Security Issues).
-Example Quotations:
-1. “Some of these challenges were discussed by Alshehab et al. in their study, which summarized these challenges as the lack of awareness of privacy and security...”
+      <t>Challenge: Legal: Privacy and other restrictions</t>
+    </r>
+  </si>
+  <si>
+    <t>Challenge: Legal: Restrictions
+Definition:
+Jurisdictional or statutory restrictions on data access, storage, sharing, or reuse that are grounded in law rather than in technical or organisational factors. This covers both restrictions whose primary aim is the protection of personal data and individual privacy rights, derived from data protection law such as the GDPR, and restrictions whose aim is generic confidentiality or secrecy; for example confidentiality of state security data, classification regimes, commercial confidentiality, statutory access limitations, or sectoral disclosure prohibitions.
+Inclusion Criteria:
+1. Restrictions traceable to data protection law (GDPR, national equivalents), or otherwise rooted in the protection of identifiable individuals.
+2. Requirements for purpose limitation, data minimisation, lawful basis, or consent that constrain interoperability.
+3. Pseudonymisation or anonymisation obligations that limit reuse.
+4. Confidentiality regulations blocking access for reasons other than personal data protection.
+5. Classification or state security regimes.
+6. Commercial confidentiality limitations.
+7. Statutory disclosure prohibitions within a single jurisdiction.
+Exclusion Criteria:
+1. Conflicts between legal regimes (use Incompatibility).
+2. Licensing terms specifically (use Licensing).
+3. Ambiguity rather than prohibition, including ambiguity in liability or responsibility (use Clarity).
+4. Technical security weaknesses without legal grounding (use Technical: Security Issues).
+Example Quotations:
+1. "Data-sharing was also hampered by cultural and institutional barriers, including closed or non-existent data policies."
+2. "Some of these challenges were discussed by Alshehab et al. in their study, which summarized these challenges as the lack of awareness of privacy and security..."
 Notes:
-Privacy is distinct from Restrictions in legal source and protective object: privacy law operates from the rights of natural persons, whereas Restrictions cover all other access or reuse limitations rooted in jurisdictional or statutory law. When in doubt, ask whether the limitation exists primarily to protect identifiable individuals; if yes, code Privacy.</t>
+This code merges the former Challenge: Legal: Privacy into Challenge: Legal: Restrictions. It now covers all legally grounded limitations on data access or reuse, regardless of whether the protective object is the natural person (privacy, data protection law) or a broader confidentiality or secrecy interest (state security, classification, commercial confidentiality, statutory disclosure prohibitions). If the distinction between privacy and other confidentiality needs to stay analytically visible, capture it through a quotation attribute or a sub-code rather than through two separate top-level codes. Boundaries with neighbouring codes are unchanged: legal regime conflicts go to Incompatibility, license terms to Licensing, ambiguity to Clarity, and technical security weaknesses without legal grounding to Technical: Security Issues. 10/05/2026, 15:41, merged with Challenge: Legal: Privacy</t>
   </si>
   <si>
     <r>
@@ -228,40 +245,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Legal: Restrictions</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Jurisdictional or statutory restrictions on data access, storage, sharing, or reuse other than those primarily aimed at protecting personal data; for example confidentiality of state security data, classification regimes, commercial confidentiality, statutory access limitations, or sectoral disclosure prohibitions.
-Inclusion Criteria:
-1. Confidentiality regulations blocking access (non‐privacy).
-2. Classification or state security regimes.
-3. Commercial confidentiality limitations.
-4. Statutory disclosure prohibitions in a single jurisdiction.
-Exclusion Criteria:
-1. Conflicts between legal regimes (use Incompatibility).
-2. License terms specifically (use Licensing).
-3. Ambiguity rather than prohibition (use Clarity).
-4. Restrictions specifically protecting personal data or individual privacy (use Privacy).
-Example Quotations:
-1. “Data-sharing was also hampered by cultural and institutional barriers, including closed or non-existent data policies.”
-Notes:
-Boundary with Privacy: Privacy is reserved for restrictions whose primary aim is protection of personal data and individual privacy rights; Restrictions covers all other access or reuse limitations.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Challenge: Organizational</t>
     </r>
   </si>
   <si>
-    <t>Definition:
+    <t xml:space="preserve">Definition:
 Header category. Organizational interoperability challenges concern persistent misalignments in roles, structures, processes, governance, capacity, and culture that hinder cross‐organizational interoperability.
 Inclusion Criteria:
 1. Use as analytical container only.
@@ -270,8 +258,31 @@
 Notes:
 Header / parent code
 Literature:
-• EIF
-• Scholl &amp; Klischewski (2007)</t>
+Five families, recorded as Code Groups under the EIF Organizational layer. This consolidates roughly fifteen codes to about thirteen, but the real result is that they fall into five principled families instead of a flat list.
+Collaborative
+Grounding: Scholl &amp; Klischewski (2007), constraint 3, p. 894; Navarrete et al. (2010), the collaboration factors in section 4.1, pp. 4–7, and section 4.4; Scholl (2005), on pre-disposition and leadership support, p. 2.
+Scholl &amp; Klischewski's collaborative constraint holds that organizations differ in their disposition and readiness to cooperate, and that past experience, socio-political organization, and leadership style shape how amenable a collaboration is. Navarrete et al. develop these collaboration factors further, building on Faerman et al. and Ansell &amp; Gash, into initial disposition, variety of participants, institutional design, facilitative leadership, incentives, and power and resource imbalances; they note that &lt;q&gt;different leadership styles between organizations can guide integration projects to failure&lt;/q&gt;. Scholl (2005) adds the pre-disposition for collaboration and the need for leadership support and involvement.
+Codes: Cultural differences; No joint action (formerly Lack of Collaboration); Limited awareness and support (a merge of Little Awareness and Lack of Support, since both concern disposition and socio-political backing); Personal biases is an open question, to be folded in here as disposition or dropped.
+Organizational and structural
+Grounding: Scholl &amp; Klischewski (2007), constraint 4, p. 894; Navarrete et al. (2010), section 4.4, p. 7; Kubicek et al. (2011), on the coordination of workflows.
+Scholl &amp; Klischewski's organizational constraint holds that organizational processes and resources may differ between organizations to such an extent that interoperation is hard to achieve without standardizing on processes, systems, and policies. Navarrete et al. restate this as the challenge of standardizing business processes. Kubicek et al. emphasize that without agreement among the units involved on the rules to adhere to, coordination between workflows will not occur.
+Codes: Organizational diversity; Lack of architecture; No shared agreement (formerly Absence of agreement); No operational uptake (formerly Lack of implementation).
+Managerial
+Grounding: Scholl &amp; Klischewski (2007), constraint 6, p. 895; Navarrete et al. (2010), section 4.4, p. 7.
+Scholl &amp; Klischewski's managerial constraint holds that interoperation becomes inherently more complex as more parties with incongruent interests and needs become involved, so that the demands of the management task may exceed the management capacity of the partners. Navarrete et al. restate this as the difficulty of managing information integration when the actors involved hold different interests and expectations.
+Codes: Lack of governance; Coordination overhead (formerly Overhead Costs).
+Capacity and cost
+Grounding: Scholl &amp; Klischewski (2007), constraint 7, p. 895; Scholl (2005), on the heterogeneity of infrastructures, resources, and skills, p. 5.
+Scholl &amp; Klischewski's cost constraint holds that integration between diverse constituencies may be limited to the lowest common denominator in available funds, and that unexpected budget constraints place long-term projects under pressure. Scholl (2005), in the Justice Information Network case, shows how uneven infrastructure, resources, and skills among participating governments constrain collaboration, since the weakest link limits the network. This family deliberately widens Scholl &amp; Klischewski's narrow cost constraint to absorb the codebook's capacity cluster; that widening should be documented as a deviation. The alternative is to keep cost and capability as two separate families.
+Codes: Shortage in capacity; Lack of expertise; Lack of instrumentarium.
+References
+Dawes, S. S. (1996). Interagency information sharing: Expected benefits, manageable risks. Journal of Policy Analysis and Management, 15(3), 377–394.
+European Commission. (2017). New European Interoperability Framework: Promoting seamless services and data flows for European public administrations. Publications Office.
+Kubicek, H., Cimander, R., &amp; Scholl, H. J. (2011). Organizational Interoperability in E-Government: Lessons from 77 European Good-Practice Cases. Springer.
+Navarrete, C., Gil-Garcia, J. R., Mellouli, S., Pardo, T. A., &amp; Scholl, H. J. (2010). Multinational E-Government Collaboration, Information Sharing, and Interoperability: An Integrative Model. Proceedings of the 43rd Hawaii International Conference on System Sciences.
+Scholl, H. J. (2005). Interoperability in E-Government: More than Just Smart Middleware. Proceedings of the 38th Hawaii International Conference on System Sciences.
+Scholl, H. J., &amp; Klischewski, R. (2007). E-Government Integration and Interoperability: Framing the Research Agenda. International Journal of Public Administration, 30(8–9), 889–920.
+</t>
   </si>
   <si>
     <r>
@@ -281,23 +292,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Absence of agreement</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Absence of shared organizational agreements on the interpretation, use, or governance of semantic constructs, processes, or data, despite the availability of common models or standards.
-Inclusion Criteria:
-1. Missing administrative consensus on use of a shared model.
-2. Lack of formal agreement among partners about implementation.
-3. Standards adopted in name but without operational agreement.
-Exclusion Criteria:
-1. Lack of governance structures (use Lack of Governance).
-2. Voluntary collaboration that simply did not occur (use Lack of Collaboration).
-Example Quotations:
-1. “Lack of semantic agreement at the administrative level of public service providers — for example, the object Address has an attribute, AdminUnitL2...”
+      <t>Challenge: Organizational: Capacity and cost: Lack of Expertise</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Insufficient domain, semantic, technical, or interoperability expertise required to design, implement, interpret, and sustain interoperability solutions, including ontologies and linked data.
+Inclusion Criteria:
+1. Insufficient ontology engineering skills.
+2. Inability to interpret structured semantic data.
+3. Difficulty coping with semantic complexity.
+Exclusion Criteria:
+1. Insufficient time, funding or staffing (use Shortage in Capacity).
+2. Absence of tools or methods (use Little or no Instrumentarium).
+Example Quotations:
+1. “A key problem to be solved in FinnONTO was that large cross-domain thesauri, especially the General Finnish Thesaurus YSA, could not anymore be maintained easily...”
 Notes:
-Boundary with Lack of Governance: Absence of Agreement is the missing consensus, Lack of Governance is the missing structural mechanism.</t>
+Together with Shortage in Capacity and Little or no Instrumentarium, this forms the capacity sub-cluster.
+Literature:
+• Scholl &amp; Klischewski (2007): Cost constraints</t>
   </si>
   <si>
     <r>
@@ -307,7 +320,91 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Cultural Differences</t>
+      <t>Challenge: Organizational: Capacity and cost: Lack of Instrumentarium</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Absence or insufficient availability of appropriate tools, methods, or operational practices required to design, implement, manage, or apply interoperability and semantic solutions.
+Inclusion Criteria:
+1. Missing modelling tools.
+2. Inadequate methods for semantic alignment.
+3. Absence of operational templates and patterns.
+Exclusion Criteria:
+1. Insufficient skills to use existing tools (use Lack of Expertise).
+2. Insufficient infrastructure investments (use Shortage in Capacity).
+Example Quotations:
+1. “While the varying levels of access to technological means (and thus e-education) is another soft challenge.”
+Notes:
+Capacity dimension complement to Lack of Expertise (people) and Shortage in Capacity (resources).
+Literature:
+• Scholl &amp; Klischewski (2007): Cost constraints</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Capacity and cost: Overhead Costs</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Coordination, governance, and management overhead required to align multiple organizations, processes, and responsibilities, where the organizational effort itself becomes a bottleneck to interoperability.
+Inclusion Criteria:
+1. Excessive coordination meetings without progress.
+2. High agreement maintenance costs.
+3. Disproportionate effort relative to benefit.
+Exclusion Criteria:
+1. Legal negotiation overhead (use Legal: Overhead).
+2. Insufficient resources to begin with (use Shortage in Capacity).
+Example Quotations:
+1. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
+Notes:
+Distinguishable from Shortage in Capacity: Overhead is the cost of coordination effort itself, not the absence of resources.
+Literature:
+• Scholl &amp; Klischewski (2007): Cost constraints</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Capacity and cost: Shortage in capacity</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Insufficient structural capacity, including lack of time, funding, staffing, or institutional support, to implement and sustain interoperability solutions.
+Inclusion Criteria:
+1. Insufficient funding for interoperability projects.
+2. Understaffed interoperability units.
+3. Insufficient sustained institutional support.
+Exclusion Criteria:
+1. Skill gaps (use Lack of Expertise).
+2. Tool gaps (use Little or no Instrumentarium).
+Example Quotations:
+1. “A mundane challenge of developing large domain ontologies, at least in Finland, is how to convince the funding organizations, year after year, that this never-ending task is essential...”
+Notes:
+Capacity dimension complement to Expertise and Instrumentarium
+Literature:
+• Scholl &amp; Klischewski (2007): Cost constraints</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Collaborative: Cultural Differences</t>
     </r>
   </si>
   <si>
@@ -334,8 +431,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Data Fragmentation</t>
-    </r>
+      <t>Challenge: Organizational: Collaborative: Lack of Awareness</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Limited awareness, understanding, or recognition among relevant actors of the importance, methods, or benefits of interoperability and shared semantic artefacts.
+Inclusion Criteria:
+1. Stakeholders unaware of available standards.
+2. Decision makers unfamiliar with interoperability concepts.
+3. Organizations not recognizing data as a shared concern.
+Exclusion Criteria:
+1. Lack of training capacity (use Lack of Expertise).
+2. Cultural resistance (use Cultural Differences).
+Example Quotations:
+1. “This ontology building, however, is not being undertaken by Geoconnections, the Canadian federal body responsible for spatial data infrastructure. Instead, isolated initiatives...”
+Notes:
+Newly defined; precedes Lack of Expertise as a precondition: awareness must exist before expertise is sought.
+Literature:
+• Scholl &amp; Klischewski (2007), labelled as collaborative challenge</t>
   </si>
   <si>
     <r>
@@ -345,7 +459,180 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Diversity</t>
+      <t>Challenge: Organizational: Collaborative: Lack of Operational Cooperation</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+The joint action, coordination, or cooperative work needed to implement or sustain interoperability is not taking place, regardless of whether the parties agree or could agree. The gap is one of activity, not of position: even where a shared position exists and governance structures are in place, the cooperative work is not done.
+Inclusion Criteria:
+Actors do not engage in joint development, coordination, or maintenance despite the need.
+Cooperation fails to materialise even though a mandate or an agreed position exists.
+Organizational silos prevent operational cooperation between actors.
+Exclusion Criteria:
+Parties have not reached a shared position on meaning, use, or governance (use Lack of substantive agreement).
+The absence of decision rights, ownership, or steering structures (use Lack of Governance).
+Cooperation withheld for reasons of differing norms, values, or attitudes (use Cultural Differences).
+Example Quotations:
+“The evaluation highlighted some ongoing challenges that include the need for coordination on multiple levels, as well as a more profound role of the private sector.”
+Notes:
+Boundary with Lack of substantive agreement: this code is the missing joint action, a behaviour; Lack of substantive agreement is the missing converged position, a state. The two are independent: parties can cooperate actively yet reach no agreement, and can agree formally yet do no joint work. Boundary with Lack of Governance: cooperation is the behaviour, governance is the structural arrangement that would organise it. The current example quotation is weak, since it states that coordination is needed rather than showing that cooperation demonstrably fails; replace it with a fragment showing actors not engaging while they could.
+Literature:
+Scholl &amp; Klischewski (2007), collaborative constraint
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Collaborative: Lack of Stakeholder Support</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Insufficient political, executive, or stakeholder backing required to authorize, fund, sustain, or legitimize interoperability initiatives.
+Inclusion Criteria:
+1. Missing political endorsement.
+2. Lack of executive sponsorship.
+3. Stakeholder resistance to adoption.
+Exclusion Criteria:
+1. Absence of formal governance (use Lack of Governance).
+2. Funding and staffing constraints (use Shortage in Capacity).
+Example Quotations:
+1. “OSLO applied a generic process and methodology and provided practical insights on how to overcome the encountered hurdles: political support and adoption...”
+Notes:
+Newly defined; relates inversely to the Requirement: Organizational: Political Support.
+Literature:
+• Scholl &amp; Klischewski (2007), labelled as collaborative challenge</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Managerial: Lack of Governance</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Absence of explicit governance arrangements, ownership, or managerial steering for interoperability, leading to ad hoc handling within technical or business silos and unclear allocation of decision rights.
+Inclusion Criteria:
+1. Unclear ownership of shared semantic artefacts.
+2. Missing decision rights or escalation mechanisms.
+3. Misaligned business processes due to absent governance.
+Exclusion Criteria:
+1. Failure of operational cooperation while structures exist (use Collaborative: Lack of Operational Cooperation).
+2. Substantive missing agreements on interpretation (use Organisational and Structural: No shared agreement).
+Example Quotations:
+1. “The FinnONTO initiative pointed out that lots of redundant work had been done in developing the thesauri in Finland as they shared lots similar concepts...”
+Literature:
+• Scholl &amp; Klischewski (2007), labelled managerial constraints</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Organisational and Structural: Lack of Architecture</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Absence or insufficient maturity of an enterprise or interoperability architecture at organizational, sectoral, or jurisdictional level, leading to ad hoc integration and fragmented technical-organizational design.
+Inclusion Criteria:
+1. Missing enterprise architecture for cross-organizational services.
+2. Absence of architectural patterns for shared services.
+3. Scarcity of web-oriented architecture for data exchange.
+Exclusion Criteria:
+1. Technical incompatibility specifically (use Technical: Incompatible Technique).
+2. Lack of governance separately (use Lack of Governance).
+Example Quotations:
+1. “Due to interoperability problems, including adequate semantic standards and scarcity of web-oriented architecture, private partners struggle to reuse Public Sector Information.”
+Notes:
+Newly defined; sits between organizational and technical layer because architecture is an organizational capability with technical manifestations.
+Literature:
+• Scholl &amp; Klischewski (2007), labelled as Organizational constraints
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Organisational and Structural: No Operational Uptake</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Definition:
+An agreed model, standard, or interoperability arrangement exists and has been formally adopted, but it is not put into operational use in everyday processes and systems. The gap is one of execution, not of position: the shared position has been reached, yet it does not translate into practice.
+Inclusion Criteria:
+- Standards or models adopted on paper but not operationalised in processes or systems.
+- Pilots or commitments that do not scale into routine practice.
+- Documented intentions without operational follow-through.
+Exclusion Criteria:
+- No converged, committed position has been reached in the first place (use No shared agreement).
+- The joint cooperative work between actors is not happening (use No joint action).
+- The absence of decision rights, ownership, or steering to drive uptake (use Lack of Governance).
+Example Quotations:
+“It has to be mentioned, that there are several serious problem areas, like documentation (intelligibility), implementation, quality of interoperability...”
+Notes:
+Boundary with No shared agreement, within the same family: No shared agreement is the missing converged position, No operational uptake is the agreed position that fails to reach practice. Sits opposite the requirement Operational Use and Institutional Embedding. Boundary with No joint action: uptake concerns whether an agreed arrangement is applied in practice, not whether actors cooperate to produce it.
+Literature:
+Scholl &amp; Klischewski (2007), organizational constraint</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Organisational and Structural: No shared agreement</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition:
+Parties have not converged on a shared, committed position about the meaning, use, or governance of semantic constructs, processes, or data, even though common models or standards are available to build on. The gap is one of alignment of intent and interpretation, not of activity: the joint position itself has not been reached.
+Inclusion Criteria:
+No administrative or political consensus on how a shared model or construct should be interpreted.
+Partners actively cooperate but arrive at no agreed position on use or governance.
+Standards adopted in name, without a committed agreement on what they mean or how they bind.
+Exclusion Criteria:
+The joint work itself is not happening, regardless of whether a position could be reached (use Lack of operational cooperation).
+The absence of decision rights, ownership, or steering needed to reach or enforce a position (use Lack of Governance).
+Divergence rooted in differing norms, values, or attitudes rather than an unreached position (use Cultural Differences).
+Example Quotations:
+“Lack of semantic agreement at the administrative level of public service providers — for example, the object Address has an attribute, AdminUnitL2...”
+Notes:
+Boundary with Lack of operational cooperation: this code is the missing converged position, a state; Lack of operational cooperation is the missing joint action, a behaviour. The two are independent: parties can agree without cooperating, and cooperate without agreeing. Boundary with Lack of Governance: agreement is the content of alignment, governance is the structural mechanism that would enable or enforce it.
+Literature:
+Scholl &amp; Klischewski (2007), organizational constraint
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Organizational: Organisational and Structural: Organisational Diversity</t>
     </r>
   </si>
   <si>
@@ -361,7 +648,9 @@
 Example Quotations:
 1. “As 80% of the informational needs are related to geographic location and spatial data often uses domain specific standards, address information is scattered on different information systems.”
 Notes:
-Diversity is structural; Cultural Differences is normative and attitudinal.</t>
+Diversity is structural; Cultural Differences is normative and attitudinal.
+Literature:
+• Scholl &amp; Klischewski (2007), labelled as Organizational constraints</t>
   </si>
   <si>
     <r>
@@ -371,310 +660,11 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Organizational: Lack of Architecture</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Absence or insufficient maturity of an enterprise or interoperability architecture at organizational, sectoral, or jurisdictional level, leading to ad hoc integration and fragmented technical-organizational design.
-Inclusion Criteria:
-1. Missing enterprise architecture for cross-organizational services.
-2. Absence of architectural patterns for shared services.
-3. Scarcity of web-oriented architecture for data exchange.
-Exclusion Criteria:
-1. Technical incompatibility specifically (use Technical: Incompatible Technique).
-2. Lack of governance separately (use Lack of Governance).
-Example Quotations:
-1. “Due to interoperability problems, including adequate semantic standards and scarcity of web-oriented architecture, private partners struggle to reuse Public Sector Information.”
-Notes:
-Newly defined; sits between organizational and technical layer because architecture is an organizational capability with technical manifestations.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Lack of Collaboration</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Absence of operational cooperation, joint action, or coordination between actors needed to implement or sustain interoperability, even when governance structures may exist.
-Inclusion Criteria:
-1. Stakeholders failing to engage in joint development.
-2. Coordination not happening despite mandate.
-3. Silos preventing operational cooperation.
-Exclusion Criteria:
-1. Missing governance arrangements (use Lack of Governance).
-2. Cultural reasons for not collaborating (use Cultural Differences).
-Example Quotations:
-1. “The evaluation highlighted some ongoing challenges that include the need for coordination on multiple levels, as well as a more profound role of the private sector.”
-Notes:
-Closely related to Lack of Governance; here the focus is operational cooperation between actors, not the structural arrangement.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Lack of Expertise</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Insufficient domain, semantic, technical, or interoperability expertise required to design, implement, interpret, and sustain interoperability solutions, including ontologies and linked data.
-Inclusion Criteria:
-1. Insufficient ontology engineering skills.
-2. Inability to interpret structured semantic data.
-3. Difficulty coping with semantic complexity.
-Exclusion Criteria:
-1. Insufficient time, funding or staffing (use Shortage in Capacity).
-2. Absence of tools or methods (use Little or no Instrumentarium).
-Example Quotations:
-1. “A key problem to be solved in FinnONTO was that large cross-domain thesauri, especially the General Finnish Thesaurus YSA, could not anymore be maintained easily...”
-Notes:
-Together with Shortage in Capacity and Little or no Instrumentarium, this forms the capacity sub-cluster.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Lack of Governance</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Absence of explicit governance arrangements, ownership, or managerial steering for interoperability, leading to ad hoc handling within technical or business silos and unclear allocation of decision rights.
-Inclusion Criteria:
-1. Unclear ownership of shared semantic artefacts.
-2. Missing decision rights or escalation mechanisms.
-3. Misaligned business processes due to absent governance.
-Exclusion Criteria:
-1. Failure of operational cooperation while structures exist (use Lack of Collaboration).
-2. Substantive missing agreements on interpretation (use Absence of Agreement).
-Example Quotations:
-1. “The FinnONTO initiative pointed out that lots of redundant work had been done in developing the thesauri in Finland as they shared lots similar concepts...”
-Literature:
-• Scholl &amp; Klischewski (2007), labelled managerial</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Lack of implementation</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Adoption of standards, models, or interoperability arrangements remains nominal or partial, with insufficient operational implementation in everyday processes and systems.
-Inclusion Criteria:
-1. Standards adopted on paper but not operationalized.
-2. Pilots that fail to scale.
-3. Documented intentions without operational uptake.
-Exclusion Criteria:
-1. Quality issues in implementation (use Data Quality).
-2. Absence of agreement preceding implementation (use Absence of Agreement).
-Example Quotations:
-1. “It has to be mentioned, that there are several serious problem areas, like documentation (intelligibility), implementation, quality of interoperability...”
-Notes:
-Newly defined; complements Operational Use and Institutional Embedding (a Requirement).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Lack of Support</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Insufficient political, executive, or stakeholder backing required to authorize, fund, sustain, or legitimize interoperability initiatives.
-Inclusion Criteria:
-1. Missing political endorsement.
-2. Lack of executive sponsorship.
-3. Stakeholder resistance to adoption.
-Exclusion Criteria:
-1. Absence of formal governance (use Lack of Governance).
-2. Funding and staffing constraints (use Shortage in Capacity).
-Example Quotations:
-1. “OSLO applied a generic process and methodology and provided practical insights on how to overcome the encountered hurdles: political support and adoption...”
-Notes:
-Newly defined; relates inversely to the Requirement: Organizational: Political Support.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Little Awareness</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Limited awareness, understanding, or recognition among relevant actors of the importance, methods, or benefits of interoperability and shared semantic artefacts.
-Inclusion Criteria:
-1. Stakeholders unaware of available standards.
-2. Decision makers unfamiliar with interoperability concepts.
-3. Organizations not recognizing data as a shared concern.
-Exclusion Criteria:
-1. Lack of training capacity (use Lack of Expertise).
-2. Cultural resistance (use Cultural Differences).
-Example Quotations:
-1. “This ontology building, however, is not being undertaken by Geoconnections, the Canadian federal body responsible for spatial data infrastructure. Instead, isolated initiatives...”
-Notes:
-Newly defined; precedes Lack of Expertise as a precondition: awareness must exist before expertise is sought.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Little or no Instrumentarium</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Absence or insufficient availability of appropriate tools, methods, or operational practices required to design, implement, manage, or apply interoperability and semantic solutions.
-Inclusion Criteria:
-1. Missing modelling tools.
-2. Inadequate methods for semantic alignment.
-3. Absence of operational templates and patterns.
-Exclusion Criteria:
-1. Insufficient skills to use existing tools (use Lack of Expertise).
-2. Insufficient infrastructure investments (use Shortage in Capacity).
-Example Quotations:
-1. “While the varying levels of access to technological means (and thus e-education) is another soft challenge.”
-Notes:
-Capacity dimension complement to Lack of Expertise (people) and Shortage in Capacity (resources).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: No Availability of data</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Relevant data are not available to relevant actors due to organizational decisions, gaps in collection, or absence of publication mechanisms, irrespective of legal or technical permissibility.
-Inclusion Criteria:
-1. Data exist but are not published.
-2. Required datasets simply not collected.
-3. Insufficient release of needed data.
-Exclusion Criteria:
-1. Legal restrictions blocking access (use Legal: Restrictions).
-2. Findability problems (use Technical: Findable, Searchable and Visible as inverse).
-Example Quotations:
-1. “Looking back twenty years to the 1990s, the accessibility and online sharing of public sector data were minimal...”
-Notes:
-Newly defined; an organizational antecedent to technical findability.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Overhead Costs</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Coordination, governance, and management overhead required to align multiple organizations, processes, and responsibilities, where the organizational effort itself becomes a bottleneck to interoperability.
-Inclusion Criteria:
-1. Excessive coordination meetings without progress.
-2. High agreement maintenance costs.
-3. Disproportionate effort relative to benefit.
-Exclusion Criteria:
-1. Legal negotiation overhead (use Legal: Overhead).
-2. Insufficient resources to begin with (use Shortage in Capacity).
-Example Quotations:
-1. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
-Notes:
-Distinguishable from Shortage in Capacity: Overhead is the cost of coordination effort itself, not the absence of resources.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Personal biases</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Organizational: Shortage in capacity</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Insufficient structural capacity, including lack of time, funding, staffing, or institutional support, to implement and sustain interoperability solutions.
-Inclusion Criteria:
-1. Insufficient funding for interoperability projects.
-2. Understaffed interoperability units.
-3. Insufficient sustained institutional support.
-Exclusion Criteria:
-1. Skill gaps (use Lack of Expertise).
-2. Tool gaps (use Little or no Instrumentarium).
-Example Quotations:
-1. “A mundane challenge of developing large domain ontologies, at least in Finland, is how to convince the funding organizations, year after year, that this never-ending task is essential...”
-Notes:
-Capacity dimension complement to Expertise and Instrumentarium
-Literature:
-• Scholl &amp; Klischewski (2007)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Challenge: Semantic</t>
     </r>
   </si>
   <si>
-    <t>Definition:
+    <t xml:space="preserve">Definition:
 Header category. Semantic interoperability challenges concern the shared interpretation and consistent meaning of data across organisations. Challenges arise when conceptual structures, meaning assumptions, or representational conventions diverge across domains or contexts.
 Inclusion Criteria:
 1. Use as analytical container only.
@@ -682,9 +672,44 @@
 1. Do not code fragments directly with the parent.
 Notes:
 Header / parent code
-Literature:
-• EIF
-• Scholl &amp; Klischewski (2007)</t>
+Challenge Codeset: Literature Grounding, Semantic Layer
+Scope: this document grounds the Semantic layer of the challenge codeset. It is the counterpart to the Legal and Organizational grounding document; the Technical layer is still pending.
+Why a separate backbone: the four core e-government papers used for the Legal, Organizational, and Technical layers (Scholl &amp; Klischewski 2007; Navarrete et al. 2010; Scholl 2005; Kubicek et al. 2011) do not decompose semantic challenges. None of them carries a semantic constraint or a semantic-challenge taxonomy. The Semantic layer therefore rests on a different set of sources: Euzenat &amp; Shvaiko (2013), Peristeras et al. (2008), Maratsi et al. (2023), Guarino (1998), and Vogt et al. (2024).
+A note on quotations: direct quotes are kept short and limited to one per source, the rest is paraphrased, and precise locations are given so that fuller passages can be extracted directly from the source PDFs where needed for the manuscript.
+Top frame: two organizing axes, five families
+The three backbone papers cut along two different axes. Euzenat &amp; Shvaiko and Peristeras et al. both organize semantic problems by the type of mismatch: what kind of difference holds between two or more models or representations. Maratsi et al. organize by a different axis, the artefact layer or source: they categorize challenges &lt;q&gt;according to the source where the issue usually stems from&lt;/q&gt;, namely the ontology layer, the metadata layer, the core data components, and a residual category. Neither axis is a complete container for the twelve codes on its own, so the five families below synthesize across them: the heterogeneity family follows the mismatch axis and is the most strongly grounded, and the remaining four families pick up the codes that the mismatch axis does not reach.
+The five families: Semantic heterogeneity; Underspecified meaning; Representational limits; Semantic dynamics; Instance-level meaning fidelity. Recorded as Code Groups under the EIF Semantic layer.
+Semantic heterogeneity
+Codes: Conceptual Divergence; Data Heterogeneity; Lack of shared Syntax; Multi Language.
+Grounding: Euzenat &amp; Shvaiko (2013), pp. 37–39, on the types of heterogeneity; Peristeras et al. (2008), section 5, on data-level and schema-level conflicts.
+This is the spine of the layer and the most strongly grounded family. Euzenat &amp; Shvaiko distinguish four types of heterogeneity, and three of them map almost one to one onto codes here. Syntactic heterogeneity, which occurs when ontologies are expressed in different representation languages, is Lack of shared Syntax. Terminological heterogeneity, which Euzenat &amp; Shvaiko attribute explicitly to the use of different natural languages, is Multi Language. Conceptual heterogeneity, which they also call semantic heterogeneity and describe as &lt;q&gt;the differences in modelling the same domain of interest&lt;/q&gt;, is Conceptual Divergence; they further decompose it into difference in coverage, granularity, and perspective. Data Heterogeneity corresponds to conceptual heterogeneity in its difference-in-coverage form, where distinct domains are involved. Their fourth type, semiotic heterogeneity, has no code, and Euzenat &amp; Shvaiko themselves set it aside as out of computational reach; this is a deliberate non-code rather than an omission. Peristeras et al. add the typology that operates within this family: data-level conflicts, in particular data-value conflicts, and schema-level conflicts, namely naming, entity identifier, schema-isomorphism, generalization, aggregation, and schematic discrepancies.
+Underspecified meaning
+Codes: Lack of Semantic Standards; Underspecified Meaning; Metadata Insufficiency.
+Grounding: Maratsi et al. (2023), the Ontological and Metadata-Related categories; Guarino (1998).
+This family is not about mismatch but about deficit: something needed to anchor or interpret meaning is absent or left implicit. Maratsi et al.'s Ontological category names the inability to express knowledge formally and straightforwardly and the absence of domain-specific and common core ontologies; their Metadata-Related category names poor and non-standardized metadata and disabled discoverability. Guarino's formal-ontology programme is concerned with making an implicit conceptualization explicit, which is precisely what Underspecified Meaning lacks. The family holds three distinct deficits: Lack of Semantic Standards, where no agreed standards exist at all; Underspecified Meaning, where representations exist but meaning is left implicit; and Metadata Insufficiency, where the descriptive context needed to interpret data is missing. One option to keep in view: Maratsi et al. treat metadata as a separate top-level category, so Metadata Insufficiency could be split off into its own family if that proves analytically useful.
+Representational limits
+Codes: Expressiveness Limit; Semantic Complexity and Scale.
+Grounding: Maratsi et al. (2023), the Ontological category, specifically lightweight and large ontologies; Guarino (1998).
+This family is distinct from Underspecified meaning: there the anchoring is absent, here the representation or its scale is itself inadequate. Maratsi et al. name the difficulty of producing lightweight ontologies, and the literature they review records very large ontologies that cannot be maintained. Expressiveness Limit is the case where the formalism cannot capture fuzzy or context-dependent meaning. Semantic Complexity and Scale is the case where the size or intricacy of the models or domains exceeds the capacity to represent and maintain them coherently. The family borders the Organizational capacity cluster, since scale also has a capacity dimension; the codebook's exclusion criteria already route skill shortages to Organizational: Lack of Expertise, which keeps the boundary clean.
+Semantic dynamics
+Code: Instability of Meaning.
+Grounding: weak, and this should be stated openly. None of the three backbone papers has a temporal category: Euzenat &amp; Shvaiko, Peristeras et al., and Maratsi et al. all treat semantic problems at a single point in time. Instability of Meaning is the codebook's own analytical addition, capturing the temporal dimension. It can remain a singleton family, which is consistent with the Organizational layer where Managerial now holds a single code. If it is retained, it should be grounded on literature outside the three backbones, for example work on concept drift, or it can lean on the digital-data argument already present in the code's own example quotation.
+Instance-level meaning fidelity
+Codes: Data Quality; Redundant and repeated data.
+Grounding: Maratsi et al. (2023), the Core Components category.
+The challenge in this family is located in the data itself, at the instance level, not in the model above it. Maratsi et al.'s Core Components category explicitly names the perils of faulty information and fragmentation. Data Quality is the case where fidelity is degraded by errors. Redundant and repeated data is the case where fidelity is degraded by drift between duplicates, shadow databases, and inconsistent copies of authoritative data. In both, the model may be sound while the data no longer carries the intended meaning reliably. This family exists because the codebook deliberately keeps both codes under Semantic rather than moving them to an informational or organizational family. One boundary to keep explicit in the definitions: Redundant and repeated data is the observable semantic symptom at the instance level, while its organizational cause, the absence of steering, stays under Organizational: Lack of Governance.
+The Semantic and Technical boundary
+Peristeras et al. (2008), section 5.2.6, supply the rule that polices the boundary between the Semantic and Technical layers. They classify data representation, data unit, and data precision conflicts as technical rather than semantic, and treat only data-value conflicts as genuinely semantic at the data level, while noting that &lt;q&gt;the boundary between the two interoperability types is not always clear&lt;/q&gt;. This confirms two choices already made in the codebook: Lack of shared Syntax stays in the Semantic layer because it concerns modelling and representation languages, not data formats, and Different encoding and font types correctly sits under the Technical layer. Peristeras et al. also observe that schema-level conflicts frequently carry an organizational dimension as well; this is a co-occurrence signal for Conceptual Divergence and Data Heterogeneity, not a reason to reclassify them.
+Parent code
+The parent code Challenge: Semantic currently cites only EIF and Scholl &amp; Klischewski (2007). Since Scholl &amp; Klischewski carry no semantic constraint, that grounding line is weak and should be replaced with Euzenat &amp; Shvaiko (2013), Maratsi et al. (2023), Peristeras et al. (2008), Guarino (1998), and Vogt et al. (2024).
+References
+European Commission. (2017). New European Interoperability Framework: Promoting seamless services and data flows for European public administrations. Publications Office.
+Euzenat, J., &amp; Shvaiko, P. (2013). Ontology Matching (2nd ed.). Springer.
+Guarino, N. (1998). Formal Ontology in Information Systems. In N. Guarino (Ed.), Formal Ontology in Information Systems (FOIS'98). IOS Press.
+Maratsi, M. I., Charalabidis, Y., &amp; Alexopoulos, C. (2023). A Categorization of Cross-Domain Semantic Interoperability Challenges for Open (Government) Data. EGOV-CeDEM-EPart 2023.
+Peristeras, V., Loutas, N., Goudos, S. K., &amp; Tarabanis, K. (2008). A conceptual analysis of semantic conflicts in pan-European e-government services. Journal of Information Science, 34(6), 877–891.
+Vogt, L., Strömert, P., Matentzoglu, N., Karam, N., Konrad, M., Prinz, M., &amp; Baum, R. (2024). FAIR 2.0: Extending the FAIR Guiding Principles to Address Semantic Interoperability.
+</t>
   </si>
   <si>
     <r>
@@ -694,7 +719,62 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Conceptual Divergence</t>
+      <t>Challenge: Semantic: Data-level fidelity: Data Quality</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data contain errors or otherwise fail to accurately convey their intended meaning, resulting in inconsistent interpretation, reduced usability, or loss of conceptual fidelity across contexts.
+Inclusion Criteria:
+1. Errors degrading semantic interpretation.
+2. Incomplete or inaccurate data hindering meaning.
+3. Loss of conceptual fidelity through transformation.
+Exclusion Criteria:
+1. Heterogeneity across domains (use Data Heterogeneity).
+2. Missing metadata (use Metadata Insufficiency).
+Example Quotations:
+1. “When developing ontology-based applications in FinnONTO, much of the time of the developers was 'wasted' in cleaning and aligning the data from different organizations for interoperability.”
+2. “What the underlying data actually means is not always clear and issues of Big Data quality, such as completeness, veracity, skewness, uncertainty, fuzziness, and errors of data arise.”
+Literature:
+• Vogt (2024)
+• Scholl &amp; Klischewski (2007), labelled collaborative</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Data-level fidelity: Redundant and repeated data</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Same or near-identical data are produced and maintained in multiple places, leading to inconsistency, drift, and resource waste; a downstream symptom of organizational and semantic misalignment.
+Inclusion Criteria:
+1. Shadow databases.
+2. Duplicate data across registries.
+3. Inconsistent copies of authoritative data.
+Exclusion Criteria:
+1. Underlying organizational misalignment (use Organizational: Lack of Governance).
+2. Conceptual differences (use Conceptual Divergence).
+Example Quotations:
+1. “A lack of interoperable information products at local level, has led to redundant and repeated data.”
+2. “The processes that drive these products are often digitalized in separate systems. Due to this, shadow databases arise...”
+Notes:
+Newly defined; often co-occurs with Lack of Governance and Conceptual Divergence as a symptom.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Heterogeneity: Conceptual Divergence</t>
     </r>
   </si>
   <si>
@@ -706,14 +786,14 @@
 3. Divergent semantic granularity.
 4. Homonym or synonym conflicts in models.
 Exclusion Criteria:
-1. Differences across distinct domains (use Data Heterogenity).
+1. Differences across distinct domains (use Data Heterogeneity).
 2. Insufficient or implicit conceptualization (use Underspecified Meaning).
 3. Different formal languages used (use Lack of shared Syntax).
 Example Quotations:
 1. “However, in practice one also has to deal with national level issues and data available that are represented using national languages, data models, vocabularies...”
 2. “Public Sector Information is often modelled from a single perspective and therefore cannot be integrated with other information sources...”
 Notes:
-Boundary with Data Heterogenity: Conceptual Divergence is about the conceptualization of comparable phenomena, Data Heterogenity is about differences between distinct problem domains
+Boundary with Data Heterogeneity: Conceptual Divergence is about the conceptualization of comparable phenomena, Data Heterogeneity is about differences between distinct problem domains
 Literature:
 • Vogt (2024)
 • Euzenat &amp; Shvaiko (2013, p38)</t>
@@ -726,7 +806,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Data Heterogenity</t>
+      <t>Challenge: Semantic: Heterogeneity: Data Heterogeneity</t>
     </r>
   </si>
   <si>
@@ -743,7 +823,7 @@
 1. “The obstacles: (i) address data fragmentation (ii) heterogeneous address data formats and (iii) a lack of common identifiers.”
 2. “The European Commission wanted to overcome the fragmentation of the address data.”
 Notes:
-Heterogenity refers to distinct domains; Conceptual Divergence refers to differing conceptualizations of comparable phenomena.</t>
+Heterogeneity refers to distinct domains; Conceptual Divergence refers to differing conceptualizations of comparable phenomena.</t>
   </si>
   <si>
     <r>
@@ -753,114 +833,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Data Quality</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data contain errors or otherwise fail to accurately convey their intended meaning, resulting in inconsistent interpretation, reduced usability, or loss of conceptual fidelity across contexts.
-Inclusion Criteria:
-1. Errors degrading semantic interpretation.
-2. Incomplete or inaccurate data hindering meaning.
-3. Loss of conceptual fidelity through transformation.
-Exclusion Criteria:
-1. Heterogeneity across domains (use Data Heterogenity).
-2. Missing metadata (use Metadata Insufficiency).
-Example Quotations:
-1. “When developing ontology-based applications in FinnONTO, much of the time of the developers was 'wasted' in cleaning and aligning the data from different organizations for interoperability.”
-2. “What the underlying data actually means is not always clear and issues of Big Data quality, such as completeness, veracity, skewness, uncertainty, fuzziness, and errors of data arise.”
-Literature:
-• Vogt (2024)
-• Scholl &amp; Klischewski (2007), labelled collaborative</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Semantic: Expressiveness Limit</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Limitations in the expressive power or representational adequacy of ontology-based formalisms, where formal structures cannot fully capture complex, fuzzy, or context-dependent meanings.
-Inclusion Criteria:
-1. Class hierarchies cannot represent the needed nuances.
-2. Formal language insufficient for fuzzy categories.
-3. Context dependency lost in formal representation.
-Exclusion Criteria:
-1. Insufficient formalization at all (use Underspecified Meaning).
-2. Different formal languages used (use Lack of shared Syntax).
-Example Quotations:
-1. “As ISA limits itself to an address-as-an-attribute, certain properties of structured addresses are missing in the Core Location Vocabulary. Most noteworthy is address position...”
-Notes:
-The formal language exists but is too limited; not absence of formalization.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Semantic: Instability of Meaning</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Instability or fluidity of meaning over time, such that previously agreed semantic content shifts, drifts, or is reinterpreted, undermining sustained interoperability.
-Inclusion Criteria:
-1. Concept drift in evolving domains.
-2. Reinterpretation of agreed terms.
-3. Fluid digital data eroding stable meaning.
-Exclusion Criteria:
-1. Differences in meaning at one point in time (use Conceptual Divergence).
-2. Changes in legal definitions (use Legal: Instability).
-Example Quotations:
-1. “This view fails to take into account the changes wrought by digital data, which are fluid, unstable, and mobile.”
-Notes:
-Newly defined; the temporal dimension of semantic challenges.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Semantic: Lack of Semantic Standards</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Absence or insufficient maturity of agreed semantic standards (vocabularies, ontologies, code lists, reference models) within a domain or jurisdiction, leaving meaning unanchored across actors.
-Inclusion Criteria:
-1. No agreed vocabulary in a domain.
-2. Sectoral standards do not exist or are immature.
-3. Lack of common reference models.
-Exclusion Criteria:
-1. Standards exist but are underspecified (use Underspecified Meaning).
-2. Standards exist but in different formal languages (use Lack of shared Syntax).
-3. Standards exist but vary across organizations (use Conceptual Divergence).
-Example Quotations:
-1. “Due to interoperability problems, including adequate semantic standards and scarcity of web-oriented architecture, private partners struggle to reuse Public Sector Information.”
-Notes:
-Newly defined and distinguished from Underspecified Meaning: Lack of Semantic Standards is the absence of standards, Underspecified Meaning is insufficient explicit conceptualization within available representations.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Semantic: Lack of shared Syntax</t>
+      <t>Challenge: Semantic: Heterogeneity: Lack of shared Syntax</t>
     </r>
   </si>
   <si>
@@ -886,33 +859,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Metadata Insufficiency</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Metadata are incomplete, inaccurate, or missing, such that the meaning, context, or constraints of data cannot be reliably understood or interpreted.
-Inclusion Criteria:
-1. Missing provenance.
-2. Absent context descriptions.
-3. Inaccurate metadata records.
-Exclusion Criteria:
-1. Quality of the data itself (use Data Quality).
-2. Absent semantic standards (use Lack of Semantic Standards).
-Example Quotations:
-1. “When re-using public sector information, until now Postbuzz had to look-up the coordinates... Because of a lack of context, the developers of Postbuzz missed out this valuable clue.”
-Notes:
-The receiving system lacks the descriptive context needed to interpret data.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Semantic: Multi Language</t>
+      <t>Challenge: Semantic: Heterogeneity: Multi Language</t>
     </r>
   </si>
   <si>
@@ -936,24 +883,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Redundant and repeated data</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Same or near-identical data are produced and maintained in multiple places, leading to inconsistency, drift, and resource waste; a downstream symptom of organizational and semantic misalignment.
-Inclusion Criteria:
-1. Shadow databases.
-2. Duplicate data across registries.
-3. Inconsistent copies of authoritative data.
-Exclusion Criteria:
-1. Underlying organizational misalignment (use Organizational: Lack of Governance).
-2. Conceptual differences (use Conceptual Divergence).
-Example Quotations:
-1. “A lack of interoperable information products at local level, has led to redundant and repeated data.”
-2. “The processes that drive these products are often digitalized in separate systems. Due to this, shadow databases arise...”
+      <t>Challenge: Semantic: Representational Limitations: Expressiveness Limit</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Limitations in the expressive power or representational adequacy of ontology-based formalisms, where formal structures cannot fully capture complex, fuzzy, or context-dependent meanings.
+Inclusion Criteria:
+1. Class hierarchies cannot represent the needed nuances.
+2. Formal language insufficient for fuzzy categories.
+3. Context dependency lost in formal representation.
+Exclusion Criteria:
+1. Insufficient formalization at all (use Underspecified Meaning).
+2. Different formal languages used (use Lack of shared Syntax).
+Example Quotations:
+1. “As ISA limits itself to an address-as-an-attribute, certain properties of structured addresses are missing in the Core Location Vocabulary. Most noteworthy is address position...”
 Notes:
-Newly defined; often co-occurs with Lack of Governance and Conceptual Divergence as a symptom.</t>
+The formal language exists but is too limited; not absence of formalization.</t>
   </si>
   <si>
     <r>
@@ -963,12 +909,12 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Semantic Complexity and Scale</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-The intrinsic complexity and scale of semantic models or domains exceeds the capacity to represent, maintain, or interpret them coherently, leading to fragmentation or untractable mappings.
+      <t>Challenge: Semantic: Representational Limitations: Semantic Complexity and Scale</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+The intrinsic complexity and scale of semantic models or domains exceeds the capacity to represent, maintain, or interpret them coherently, leading to fragmentation or intractable mappings.
 Inclusion Criteria:
 1. Very large ontologies that cannot be maintained.
 2. Fine-grained classifications that fragment communities.
@@ -990,7 +936,86 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Semantic: Underspecified Meaning</t>
+      <t>Challenge: Semantic: Semantic Dynamics: Instability of Meaning</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Instability or fluidity of meaning over time, such that previously agreed semantic content shifts, drifts, or is reinterpreted, undermining sustained interoperability.
+Inclusion Criteria:
+1. Concept drift in evolving domains.
+2. Reinterpretation of agreed terms.
+3. Fluid digital data eroding stable meaning.
+Exclusion Criteria:
+1. Differences in meaning at one point in time (use Conceptual Divergence).
+2. Changes in legal definitions (use Legal: Instability).
+Example Quotations:
+1. “This view fails to take into account the changes wrought by digital data, which are fluid, unstable, and mobile.”
+Notes:
+Newly defined; the temporal dimension of semantic challenges.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Underspecification: Lack of Semantic Standards</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Absence or insufficient maturity of agreed semantic standards (vocabularies, ontologies, code lists, reference models) within a domain or jurisdiction, leaving meaning unanchored across actors.
+Inclusion Criteria:
+1. No agreed vocabulary in a domain.
+2. Sectoral standards do not exist or are immature.
+3. Lack of common reference models.
+Exclusion Criteria:
+1. Standards exist but are underspecified (use Underspecified Meaning).
+2. Standards exist but in different formal languages (use Lack of shared Syntax).
+3. Standards exist but vary across organizations (use Conceptual Divergence).
+Example Quotations:
+1. “Due to interoperability problems, including adequate semantic standards and scarcity of web-oriented architecture, private partners struggle to reuse Public Sector Information.”
+Notes:
+Newly defined and distinguished from Underspecified Meaning: Lack of Semantic Standards is the absence of standards, Underspecified Meaning is insufficient explicit conceptualization within available representations.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Underspecification: Metadata Insufficiency</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Metadata are incomplete, inaccurate, or missing, such that the meaning, context, or constraints of data cannot be reliably understood or interpreted.
+Inclusion Criteria:
+1. Missing provenance.
+2. Absent context descriptions.
+3. Inaccurate metadata records.
+Exclusion Criteria:
+1. Quality of the data itself (use Data Quality).
+2. Absent semantic standards (use Lack of Semantic Standards).
+Example Quotations:
+1. “When re-using public sector information, until now Postbuzz had to look-up the coordinates... Because of a lack of context, the developers of Postbuzz missed out this valuable clue.”
+Notes:
+The receiving system lacks the descriptive context needed to interpret data.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Semantic: Underspecification: Underspecified Meaning</t>
     </r>
   </si>
   <si>
@@ -1031,7 +1056,10 @@
 Notes:
 Header / parent code
 Literature:
-• Scholl &amp; Klischewski (2007)</t>
+- European Commission (2017), EIF, technical interoperability layer
+- Scholl &amp; Klischewski (2007), constraints 8 and 9
+- Kubicek et al. (2011), ch. 7 on technical interoperability
+- Scholl (2005), heterogeneity of infrastructures and scalability</t>
   </si>
   <si>
     <r>
@@ -1041,8 +1069,14 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Different encoding and font types</t>
-    </r>
+      <t>Challenge: Technical: Connectivity and Performance: Performance problems and scalability</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Literature:
+- Scholl &amp; Klischewski (2007), constraint 8 (technological), networking aspect, p. 895
+- Navarrete et al. (2010), section 4.3, technical barriers in cross-border integration</t>
   </si>
   <si>
     <r>
@@ -1052,22 +1086,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Genral Technical Limitations</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Generic or composite technical limitations that do not cleanly fall into one specific subcode but jointly hinder system-to-system interoperability.
-Inclusion Criteria:
-1. Composite technical barriers without single dominant cause.
-2. Multiple technical limitations described jointly.
-Exclusion Criteria:
-1. Specific incompatibilities (use Incompatible Technique).
-2. Specific interface or transport problems (use Interfacing or Transportation).
-Example Quotations:
-1. “Back in the 1990s, there were several barriers for accessing and using the spatial data and information necessary for environmental management...”
+      <t>Challenge: Technical: Connectivity and Performance: Transportation Problems</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Limitations in discoverability, data transport, service connectivity, authentication, or authorization mechanisms that hinder secure and stable communication across systems.
+Inclusion Criteria:
+1. Unstable connectivity.
+2. Failures in service discovery.
+3. Authentication mechanisms blocking transport.
+Exclusion Criteria:
+1. Format-level interfacing problems (use Interfacing Problems).
+2. Pure security limitations (use Security Issues).
+Example Quotations:
+1. “The infrastructure should adapt to changing technological trends. In that respect, new guidance may be produced...”
 Notes:
-Use sparingly; prefer the more specific subcodes whenever possible. Note: original spelling 'Genral' corrected to 'General'.</t>
+Original definition retained.</t>
   </si>
   <si>
     <r>
@@ -1077,18 +1112,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Identification and authentication issues</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF7800"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Challenge: Technical: Incompatible Technique</t>
+      <t>Challenge: Technical: Technical heterogeneity: Incompatible Technique</t>
     </r>
   </si>
   <si>
@@ -1100,11 +1124,13 @@
 3. Architectural lock-in preventing exchange.
 Exclusion Criteria:
 1. Missing or inconsistent shared standards (use Interfacing Problems).
-2. Validation failures (use Machine Readability problems).
+2. Validation failures (use Machine readability and encoding problems).
 Example Quotations:
 1. “The infrastructure should adapt to changing technological trends... encoding of data through GeoJSON, or JSON-LD...”
 Literature:
-• Scholl &amp; Klischewski (2007)</t>
+- Scholl &amp; Klischewski (2007), constraint 8 (technological), p. 895
+- Scholl (2005), heterogeneity of infrastructures, p. 5
+- Navarrete et al. (2010), reuses technological constraint</t>
   </si>
   <si>
     <r>
@@ -1114,7 +1140,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Interfacing Problems</t>
+      <t>Challenge: Technical: Technical heterogeneity: Interfacing Problems</t>
     </r>
   </si>
   <si>
@@ -1130,7 +1156,10 @@
 Example Quotations:
 1. “In general the discoverability of geospatial data on the web remains a challenge. Being based on OGC standards, data in INSPIRE is accessed through the interaction with different services...”
 Notes:
-Boundary with Incompatible Technique: Interfacing concerns the interface contract; Incompatible Technique concerns the underlying platform/architecture.</t>
+Boundary with Incompatible Technique: Interfacing concerns the interface contract; Incompatible Technique concerns the underlying platform/architecture.
+Literature:
+- Kubicek et al. (2011), ch. 7 on acknowledged technical standards
+- Scholl &amp; Klischewski (2007), constraint 8 (technological), p. 895</t>
   </si>
   <si>
     <r>
@@ -1140,23 +1169,29 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Machine Readability problems</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Failures in syntactic validation, schema conformance, or machine-level processability of exchanged data, including query language limitations.
-Inclusion Criteria:
-1. Parsing failures.
-2. Schema validation errors.
-3. Query language unsuited to the data.
-Exclusion Criteria:
-1. Conceptual issues affecting interpretation (use Semantic: Underspecified Meaning).
-2. Format incompatibility (use Interfacing Problems).
-Example Quotations:
-1. “The infrastructure should adapt to changing technological trends... establishment of RESTful web services, use of asynchronous event-based architectures...”
-Notes:
-Includes query languages.</t>
+      <t>Challenge: Technical: Technical heterogeneity: Machine Readability and Encoding Problems</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Definition: Failures in the machine-level processability of exchanged data, covering both the syntactic side, parsing and schema validation and query-language fit, and the encoding side, character sets, encodings and font representations that prevent reliable interpretation by receiving systems. The challenge is technical, not semantic: the receiving system cannot reliably process the bytes or parse the structure, regardless of whether the meaning would have been interpretable if it could.
+Inclusion Criteria:
+1Parsing failures or malformed exchanged data.
+2Schema validation errors or non-conformant payloads.
+3Query language not suited to the structure or contents of the data.
+4Character-set, encoding, or font mismatches between sender and receiver.
+5Loss of fidelity in the textual or symbolic representation of data due to encoding incompatibility.
+Exclusion Criteria:
+1The exchanged data is technically processable but its meaning is left implicit (use Semantic: Underspecification: Underspecified Meaning).
+2The interface contract or shared standard for exchange is missing or inconsistently adopted (use Technical heterogeneity: Interface and standards mismatch).
+3The underlying platform or architecture is incompatible (use Technical heterogeneity: Incompatible Technique).
+4Different formal modelling languages are used, for example RDF versus UML (use Semantic: Heterogeneity: Lack of shared Syntax).
+Example Quotations: (retain the existing example quotation and add an encoding-specific fragment when one is identified during the cross-coding pass)
+Notes: This code merges the former Machine Readability problems and Different encoding and font types. It covers two related technical concerns: the machine-syntactic side, including parsing, validation and query languages, and the byte- and character-level encoding side. Peristeras et al. supply the boundary rule that places encoding conflicts in the technical layer rather than the semantic; that boundary is what holds the merged code together. The boundary with Lack of shared Syntax in the Semantic layer should be kept sharp: Lack of shared Syntax concerns modelling and representation languages, while this code concerns the syntactic and encoding processability of the exchanged data itself.
+Literature:
+•Peristeras et al. (2008), section 5.2.2, data representation as technical
+•Kubicek et al. (2011), ch. 7 on syntactic interoperability layer
+•Scholl &amp; Klischewski (2007), constraint 8 (technological), p. 895
+</t>
   </si>
   <si>
     <r>
@@ -1166,7 +1201,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Security issues</t>
+      <t>Challenge: Technical: Trust and Security: Identification and authentication issues</t>
+    </r>
+  </si>
+  <si>
+    <t>Literature:
+- European Commission (2017), EIF, trust frameworks in technical layer
+- Kubicek et al. (2011), ch. 7 on technical interoperability</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7800"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Challenge: Technical: Trust and Security: Security issues</t>
     </r>
   </si>
   <si>
@@ -1182,7 +1233,10 @@
 Example Quotations:
 1. “Some of these challenges were discussed by Alshehab et al. in their study, which summarized these challenges as the lack of awareness... and security.”
 Notes:
-Newly defined; complements Requirement: Technical: Security and Privacy.</t>
+Newly defined; complements Requirement: Technical: Security and Privacy.
+Literature:
+- European Commission (2017), EIF, security in technical interoperability
+- Kubicek et al. (2011), ch. 7 on technical interoperability</t>
   </si>
   <si>
     <r>
@@ -1192,23 +1246,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Challenge: Technical: Transportation Problems</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Limitations in discoverability, data transport, service connectivity, authentication, or authorization mechanisms that hinder secure and stable communication across systems.
-Inclusion Criteria:
-1. Unstable connectivity.
-2. Failures in service discovery.
-3. Authentication mechanisms blocking transport.
-Exclusion Criteria:
-1. Format-level interfacing problems (use Interfacing Problems).
-2. Pure security limitations (use Security Issues).
-Example Quotations:
-1. “The infrastructure should adapt to changing technological trends. In that respect, new guidance may be produced...”
+      <t>Challenge: Technical: Unspecified Technical Limitations</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Generic or composite technical limitations that do not cleanly fall into one specific subcode but jointly hinder system-to-system interoperability.
+Inclusion Criteria:
+1. Composite technical barriers without single dominant cause.
+2. Multiple technical limitations described jointly.
+Exclusion Criteria:
+1. Specific incompatibilities (use Incompatible Technique).
+2. Specific interface or transport problems (use Interfacing or Transportation).
+Example Quotations:
+1. “Back in the 1990s, there were several barriers for accessing and using the spatial data and information necessary for environmental management...”
 Notes:
-Original definition retained.</t>
+Use sparingly; prefer the more specific subcodes whenever possible. Note: original spelling 'Genral' corrected to 'General'.
+Literature:
+- Maratsi et al. (2023), residual category as analytical parallel
+- Analytical code; grounding in the meta-finding on unspecified technical reporting in the reviewed literature</t>
   </si>
   <si>
     <r>
@@ -1236,20 +1292,6 @@
 Highest-frequency code in dataset (146 quotations). Definition added; previously empty. Recommend using as a multi-value tag with the domain string in a free-text comment in ATLAS.ti.</t>
   </si>
   <si>
-    <t>Imported annotation</t>
-  </si>
-  <si>
-    <t>Definition:
-Meta-code reserved for annotations imported from other coding systems or external sources during data ingestion. Use as a flag, not as an analytical category.
-Inclusion Criteria:
-1. Annotations carried over from previous coding rounds.
-2. External annotations imported with the document.
-Exclusion Criteria:
-1. Substantive analytical observations (use Remark).
-Notes:
-System / housekeeping code. Consider whether to retain or replace with a metadata field.</t>
-  </si>
-  <si>
     <t>Remark</t>
   </si>
   <si>
@@ -1296,7 +1338,62 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Legal: Clear Copyright and Licensing Statements</t>
+      <t>Requirement: Legal: Competent authorities: Statutory Interoperability Authority</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+A legally established and formally authorized public body must be designated to coordinate, regulate, or oversee interoperability arrangements across organizational or jurisdictional boundaries.
+Inclusion Criteria:
+1. Legally mandated coordinating body.
+2. Statutory authority with interoperability competence.
+3. Designated regulator for interoperability.
+Exclusion Criteria:
+1. Voluntary coordinating bodies (use Communities of Interest).
+2. Internal organizational governance (use Governance and Institutional Alignment).
+Example Quotations:
+1. “Two groups of stakeholders were identified: Legally Mandated Organisations (LMOs) and Spatial Data Interest Community (SDIC).”
+Literature:
+• Wimmer et al. (2018)
+• Scott (2014)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Legal: Compliance and enforcement: Compliance and Enforcement Mechanisms</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Formal mechanisms must exist to ensure adherence to interoperability-related legal and regulatory arrangements through monitoring, oversight, incentives, and sanctioning instruments.
+Inclusion Criteria:
+1. Mandatory compliance regimes.
+2. Audit and reporting mechanisms.
+3. Sanctions for non-compliance.
+Exclusion Criteria:
+1. Internal organizational adherence (use Organizational: Compliance Mechanisms).
+2. Voluntary coordination.
+Example Quotations:
+1. “As a Directive, the legal obligations did not come into force immediately but had to be transposed into national law.”
+Literature:
+• Baldwin et al. (2012)
+• Ayres &amp; Braithwaite (1992)
+• EIF Recommendation 1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Legal: Ownership and evidentiary status: Clear Copyright and Licensing Statements</t>
     </r>
   </si>
   <si>
@@ -1326,25 +1423,22 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Legal: Compliance and Enforcement Mechanisms</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Formal mechanisms must exist to ensure adherence to interoperability-related legal and regulatory arrangements through monitoring, oversight, incentives, and sanctioning instruments.
-Inclusion Criteria:
-1. Mandatory compliance regimes.
-2. Audit and reporting mechanisms.
-3. Sanctions for non-compliance.
-Exclusion Criteria:
-1. Internal organizational adherence (use Organizational: Compliance Mechanisms).
-2. Voluntary coordination.
-Example Quotations:
-1. “As a Directive, the legal obligations did not come into force immediately but had to be transposed into national law.”
-Literature:
-• Baldwin et al. (2012)
-• Ayres &amp; Braithwaite (1992)
-• EIF Recommendation 1</t>
+      <t>Requirement: Legal: Ownership and evidentiary status: Information serves as legal evidence</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Data and metadata must possess the evidentiary properties required to serve as legal evidence in administrative or judicial proceedings, including integrity, authenticity, traceability and non-repudiation.
+Inclusion Criteria:
+1. Audit-trailed data with verifiable integrity.
+2. Authenticated origin and chain of custody.
+3. Long-term preservation suited to evidentiary use.
+4. Non-repudiation mechanisms for transactions.
+Exclusion Criteria:
+1. General data quality without evidentiary framing (use Adequate Data Quality).
+2. Legal access permissions (use Public Regulation).
+Literature:
+- EIF Recommendations on trust and evidentiary records
+- Archival science on records authenticity (general grounding)</t>
   </si>
   <si>
     <r>
@@ -1354,18 +1448,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Legal: Information serves as legal evidence</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Legal: Public Policy for Interoperability</t>
+      <t>Requirement: Legal: Regulatory foundation: Public Policy for Interoperability</t>
     </r>
   </si>
   <si>
@@ -1393,7 +1476,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Legal: Public Regulation for Interoperability</t>
+      <t>Requirement: Legal: Regulatory foundation: Public Regulation for Interoperability</t>
     </r>
   </si>
   <si>
@@ -1411,33 +1494,6 @@
 Literature:
 • EIF Recommendation 27
 • Baldwin et al. (2012)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Legal: Statutory Interoperability Authority</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-A legally established and formally authorized public body must be designated to coordinate, regulate, or oversee interoperability arrangements across organizational or jurisdictional boundaries.
-Inclusion Criteria:
-1. Legally mandated coordinating body.
-2. Statutory authority with interoperability competence.
-3. Designated regulator for interoperability.
-Exclusion Criteria:
-1. Voluntary coordinating bodies (use Communities of Interest).
-2. Internal organizational governance (use Governance and Institutional Alignment).
-Example Quotations:
-1. “Two groups of stakeholders were identified: Legally Mandated Organisations (LMOs) and Spatial Data Interest Community (SDIC).”
-Literature:
-• Wimmer et al. (2018)
-• Scott (2014)</t>
   </si>
   <si>
     <r>
@@ -1473,7 +1529,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Capability and Learning Infrastructure</t>
+      <t>Requirement: Organizational: Collaboration and capacity: Capability and Learning Infrastructure</t>
     </r>
   </si>
   <si>
@@ -1503,7 +1559,70 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Clear Terms and Conditions of Use</t>
+      <t>Requirement: Organizational: Collaboration and capacity: Collaboration</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Generic collaboration requirement: interoperability requires that relevant actors, including domain experts, technical specialists, public administrations, citizens, and businesses, actively work together, share knowledge, and align their efforts. Use this code for statements that emphasise the need for collaboration as such, without specifying institutional structures, formalised communities, or sustained governance arrangements.
+Inclusion Criteria:
+1. Calls for collaboration between government, industry, researchers, citizens.
+2. Need for joint working between domain and technical experts.
+3. Generic invocations of cooperation as a precondition for interoperability.
+Exclusion Criteria:
+1. Structured, sustained, multi‐stakeholder collaboration with institutional embedding (use Communities of Interest and Collaboration).
+2. Internal organisational coordination (use Governance and Institutional Alignment).
+3. Process alignment across organisations (use Structural Process Alignment).
+Example Quotations:
+1. “Finally, they concluded the article by highlighting the need for collaboration between government agencies, IT professionals, researchers, and citizens to overcome the challenges...”
+2. “They also emphasize the need for effective collaboration between domain experts and technical specialists to develop accurate and useful ontologies.”
+Notes:
+Boundary with Communities of Interest and Collaboration: Collaboration is the generic call for working together; Communities of Interest is the institutionalised, sustained collaboration via formal structures.
+Literature:
+• When the source describes formal working groups, sector forums, or governance bodies, use the latter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Collaboration and capacity: Communities of Interest and Collaboration</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Sustained semantic interoperability depends on structured cross-organizational collaboration mechanisms that bring together stakeholders around shared semantic artefacts, standards, and interoperability objectives.
+Inclusion Criteria:
+1. Formal cross-organizational collaboration structures.
+2. Multi-stakeholder communities co-developing standards.
+3. Institutionalized working groups.
+4. Cross-sector or cross-border forums.
+Exclusion Criteria:
+1. Informal communication.
+2. Temporary project groups without institutional embedding.
+3. Legal mandates without collaborative practice.
+Example Quotations:
+1. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
+2. “Stakeholders, who participated in the development and implementation process, have a sense of stewardship of the results.”
+Notes:
+ABSORBS: Requirement: Organizational: Collaboration. The original 'Collaboration' code is empirically a subset of this code; recommend folding all quotes here. Note: original spelling 'Communuities' corrected to 'Communities'
+Literature:
+• EIF Recommendation 32
+• Scholl &amp; Klischewski (2007)
+• Baldwin et al. (2012)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Compliance and incentives: Clear Terms and Conditions of Use</t>
     </r>
   </si>
   <si>
@@ -1531,70 +1650,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Collaboration</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Generic collaboration requirement: interoperability requires that relevant actors, including domain experts, technical specialists, public administrations, citizens, and businesses, actively work together, share knowledge, and align their efforts. Use this code for statements that emphasise the need for collaboration as such, without specifying institutional structures, formalised communities, or sustained governance arrangements.
-Inclusion Criteria:
-1. Calls for collaboration between government, industry, researchers, citizens.
-2. Need for joint working between domain and technical experts.
-3. Generic invocations of cooperation as a precondition for interoperability.
-Exclusion Criteria:
-1. Structured, sustained, multi‐stakeholder collaboration with institutional embedding (use Communities of Interest and Collaboration).
-2. Internal organisational coordination (use Governance and Institutional Alignment).
-3. Process alignment across organisations (use Structural Process Alignment).
-Example Quotations:
-1. “Finally, they concluded the article by highlighting the need for collaboration between government agencies, IT professionals, researchers, and citizens to overcome the challenges...”
-2. “They also emphasize the need for effective collaboration between domain experts and technical specialists to develop accurate and useful ontologies.”
-Notes:
-Boundary with Communities of Interest and Collaboration: Collaboration is the generic call for working together; Communities of Interest is the institutionalised, sustained collaboration via formal structures.
-Literature:
-• When the source describes formal working groups, sector forums, or governance bodies, use the latter</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Organizational: Communuities of Interest and Collaboration</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Sustained semantic interoperability depends on structured cross-organizational collaboration mechanisms that bring together stakeholders around shared semantic artefacts, standards, and interoperability objectives.
-Inclusion Criteria:
-1. Formal cross-organizational collaboration structures.
-2. Multi-stakeholder communities co-developing standards.
-3. Institutionalized working groups.
-4. Cross-sector or cross-border forums.
-Exclusion Criteria:
-1. Informal communication.
-2. Temporary project groups without institutional embedding.
-3. Legal mandates without collaborative practice.
-Example Quotations:
-1. “Beyond these legal and technical aspects it was recognised that appropriate coordination mechanisms would be needed on multiple levels.”
-2. “Stakeholders, who participated in the development and implementation process, have a sense of stewardship of the results.”
-Notes:
-ABSORBS: Requirement: Organizational: Collaboration. The original 'Collaboration' code is empirically a subset of this code; recommend folding all quotes here. Note: original spelling 'Communuities' corrected to 'Communities'
-Literature:
-• EIF Recommendation 32
-• Scholl &amp; Klischewski (2007)
-• Baldwin et al. (2012)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Organizational: Compliance Mechanismes</t>
+      <t>Requirement: Organizational: Compliance and incentives: Compliance Mechanisms</t>
     </r>
   </si>
   <si>
@@ -1626,7 +1682,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Evaluation and Feedback Mechanisms</t>
+      <t>Requirement: Organizational: Compliance and incentives: Evaluation and Feedback Mechanisms</t>
     </r>
   </si>
   <si>
@@ -1655,7 +1711,36 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Governance and Institutional Alignment</t>
+      <t>Requirement: Organizational: Compliance and incentives: Incentive Strategies</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Public authorities must establish structured motivational and alignment mechanisms that encourage organizations and stakeholders to adopt, implement, and sustain interoperability standards.
+Inclusion Criteria:
+1. Funding linked to interoperability adoption.
+2. Performance benchmarking influencing reputation.
+3. Certification or recognition schemes.
+4. Strategic benefits structured to encourage adherence.
+Exclusion Criteria:
+1. Legal sanctions (use Legal: Compliance and Enforcement).
+2. Internal monitoring (use Compliance Mechanisms).
+Example Quotations:
+1. “The collaboration between experts in Member States' public and private sectors, software solution providers, open source communities...”
+Literature:
+• Baldwin et al. (2012)
+• Pardo &amp; Tayi (2007)
+• EIF (2017)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Governance and standardisation: Governance and Institutional Alignment</t>
     </r>
   </si>
   <si>
@@ -1687,26 +1772,28 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Incentive Strategies</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Public authorities must establish structured motivational and alignment mechanisms that encourage organizations and stakeholders to adopt, implement, and sustain interoperability standards.
-Inclusion Criteria:
-1. Funding linked to interoperability adoption.
-2. Performance benchmarking influencing reputation.
-3. Certification or recognition schemes.
-4. Strategic benefits structured to encourage adherence.
-Exclusion Criteria:
-1. Legal sanctions (use Legal: Compliance and Enforcement).
-2. Internal monitoring (use Compliance Mechanisms).
-Example Quotations:
-1. “The collaboration between experts in Member States' public and private sectors, software solution providers, open source communities...”
-Literature:
-• Baldwin et al. (2012)
-• Pardo &amp; Tayi (2007)
-• EIF (2017)</t>
+      <t>Requirement: Organizational: Governance and standardisation: Semantic Construct Design and Maintenance</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Public authorities must establish structured processes for the systematic design, specification, revision, and long-term maintenance of shared semantic artefacts used for interoperability.
+Inclusion Criteria:
+1. Formal modeling methodologies for construct development.
+2. Versioning and change management procedures.
+3. Impact analysis before changes.
+4. Long-term stewardship responsibilities.
+Exclusion Criteria:
+1. Mere selection of standards (use Standardization and Semantic Control).
+2. Operational use without lifecycle management (use Operational Use).
+Example Quotations:
+1. “This was achieved by implementing a process and methodology for developing semantic agreements, based on the ISA methodology.”
+Literature:
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013)
+• Kubicek et al. (2011)
+• EIF
+• EOSC</t>
   </si>
   <si>
     <r>
@@ -1716,7 +1803,37 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Operational Use and Institutional Embedding</t>
+      <t>Requirement: Organizational: Governance and standardisation: Standardization and Semantic Control</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Public authorities must systematically govern the selection, adoption, documentation, versioning, alignment, and compliance monitoring of interoperability-relevant artefacts across organizations and jurisdictions.
+Inclusion Criteria:
+1. Selection processes for standards.
+2. Alignment with national or EU catalogues.
+3. Reference data governance.
+4. Versioning and change governance.
+Exclusion Criteria:
+1. Purely technical infrastructure (use Technical: Existence of Shared Technical Standards).
+2. Legislative rule-setting (use Public Regulation).
+Example Quotations:
+1. “This has led to a demand for stable, governed data standards.”
+2. “While implementing the address vocabulary, we stumbled on competing international semantic standards and difficult choices on how to extend them to fit the local context.”
+Literature:
+• Wimmer et al. (2018)
+• EOSC
+• EIF Recommendations 21, 22, 23, 24</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Operational uptake and process alignment: Operational Use and Institutional Embedding</t>
     </r>
   </si>
   <si>
@@ -1745,7 +1862,39 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Political Support</t>
+      <t>Requirement: Organizational: Operational uptake and process alignment: Structural Process Alignment</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Public authorities must institutionalize coherent organizational structures and aligned operational procedures to enable interoperability across organizational, sectoral, administrative, or national boundaries.
+Inclusion Criteria:
+1. Institutional coordination across boundaries.
+2. Harmonized business processes.
+3. Aligned data submission and validation procedures.
+4. Joint decision-making mechanisms.
+Exclusion Criteria:
+1. Internal improvements without coordination relevance.
+2. Purely technical connectivity.
+3. Informal collaboration.
+Example Quotations:
+1. “The streamlined data governance approach leads to the establishment of an efficient governance structure. In some cases, such as the Dutch 'public geo datasets at your service – PDOK'...”
+Literature:
+• Pardo &amp; Tayi (2007)
+• Scholl &amp; Klischewski (2007)
+• Maheshwari &amp; Janssen (2014)
+• Scholl (2005)
+• EIF (2017)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Organizational: Political and strategic foundation: Political Support</t>
     </r>
   </si>
   <si>
@@ -1772,7 +1921,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Organizational: Public Asset Orientation Toward Data</t>
+      <t>Requirement: Organizational: Political and strategic foundation: Public Asset Orientation Toward Data</t>
     </r>
   </si>
   <si>
@@ -1792,99 +1941,6 @@
 • EIF Recommendation 30
 • No quotations in current dataset
 • retained because of strong theoretical grounding</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Organizational: Semantic Construct Design and Maintenance</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Public authorities must establish structured processes for the systematic design, specification, revision, and long-term maintenance of shared semantic artefacts used for interoperability.
-Inclusion Criteria:
-1. Formal modeling methodologies for construct development.
-2. Versioning and change management procedures.
-3. Impact analysis before changes.
-4. Long-term stewardship responsibilities.
-Exclusion Criteria:
-1. Mere selection of standards (use Standardization and Semantic Control).
-2. Operational use without lifecycle management (use Operational Use).
-Example Quotations:
-1. “This was achieved by implementing a process and methodology for developing semantic agreements, based on the ISA methodology.”
-Literature:
-• Guarino (1998)
-• Euzenat &amp; Shvaiko (2013)
-• Kubicek et al. (2011)
-• EIF
-• EOSC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Organizational: Standardization and Semantic Control</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Public authorities must systematically govern the selection, adoption, documentation, versioning, alignment, and compliance monitoring of interoperability-relevant artefacts across organizations and jurisdictions.
-Inclusion Criteria:
-1. Selection processes for standards.
-2. Alignment with national or EU catalogues.
-3. Reference data governance.
-4. Versioning and change governance.
-Exclusion Criteria:
-1. Purely technical infrastructure (use Technical: Existence of Shared Technical Standards).
-2. Legislative rule-setting (use Public Regulation).
-Example Quotations:
-1. “This has led to a demand for stable, governed data standards.”
-2. “While implementing the address vocabulary, we stumbled on competing international semantic standards and difficult choices on how to extend them to fit the local context.”
-Literature:
-• Wimmer et al. (2018)
-• EOSC
-• EIF Recommendations 21, 22, 23, 24</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Organizational: Structural Process Alignment</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Public authorities must institutionalize coherent organizational structures and aligned operational procedures to enable interoperability across organizational, sectoral, administrative, or national boundaries.
-Inclusion Criteria:
-1. Institutional coordination across boundaries.
-2. Harmonized business processes.
-3. Aligned data submission and validation procedures.
-4. Joint decision-making mechanisms.
-Exclusion Criteria:
-1. Internal improvements without coordination relevance.
-2. Purely technical connectivity.
-3. Informal collaboration.
-Example Quotations:
-1. “The streamlined data governance approach leads to the establishment of an efficient governance structure. In some cases, such as the Dutch 'public geo datasets at your service – PDOK'...”
-Literature:
-• Pardo &amp; Tayi (2007)
-• Scholl &amp; Klischewski (2007)
-• Maheshwari &amp; Janssen (2014)
-• Scholl (2005)
-• EIF (2017)</t>
   </si>
   <si>
     <r>
@@ -1922,7 +1978,97 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Semantic: Adequate Data Quality</t>
+      <t>Requirement: Semantic: Alignment: Modelling Flexibility</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Semantic models and modelling environments must allow for context-sensitive variation and extension without breaking interoperability, in order to accommodate divergent and evolving domain requirements.
+Inclusion Criteria:
+1. Extension mechanisms in shared models.
+2. Application profiles built on top of core models.
+3. Allowance for jurisdictional or sectoral variation.
+Exclusion Criteria:
+1. Strict conformance regimes that prohibit variation (use Conformance-based mechanism for related solution context).
+2. Ad hoc undocumented modelling differences.
+Example Quotations:
+1. “Analyzing the situation at ECDC it became clear, that implementing simply a rigorous data modeling rule set plus introducing obligatory mappings is insufficient...”
+2. “The core data models as contained in the legal framework can be extended, following the rules defined by the generic conceptual model.”
+Notes:
+Newly defined; complement of Semantic Modelling Alignment, addressing how flexibility is institutionalized.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Alignment: Semantic Mapping and Alignment capabilities</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+An interoperability ecosystem must enable the formal specification, representation, and maintenance of explicit correspondences between heterogeneous semantic artefacts (post hoc alignment).
+Inclusion Criteria:
+1. Cross-schema mappings or crosswalks.
+2. Equivalence, subsumption, transformation rules.
+3. Semantic mediation via formal mappings.
+4. Multi-standard environments requiring correspondence.
+Exclusion Criteria:
+1. Single shared model mandated (use Semantic Modelling Alignment).
+2. Syntactic format conversion only.
+Example Quotations:
+1. “In order to achieve a feasible model, and to benefit from the best of both worlds, the Flemish Government has adapted the ISA address towards INSPIRE.”
+Literature:
+• Euzenat &amp; Shvaiko (2013)
+• Peristeras et al. (2009)
+• FAIR I1-I2 and R1.3
+• FAIR 2.0
+• Guarino (1998)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Alignment: Semantic Modelling Alignment</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Participating actors must adopt and apply a shared conceptualization approach, modelling methodology, naming conventions, and structural design logic when developing semantic artefacts (ex ante alignment).
+Inclusion Criteria:
+1. Common conceptual modelling methodology.
+2. Agreed abstraction levels and granularity.
+3. Harmonized modelling guidelines.
+4. Shared reference architecture or meta-model.
+Exclusion Criteria:
+1. Post hoc mapping (use Semantic Mapping and Alignment).
+2. Syntactic format choice only.
+3. Single shared artefact without modelling principles.
+Example Quotations:
+1. “The base registries are part of a semantic coherent system of uniform identified base-objects and relations, which are in line with the OSLO-standards.”
+Literature:
+• FAIR 2.0 (Vogt et al. 2024)
+• FAIR I1-I2, R1.3
+• Euzenat &amp; Shvaiko (2013)
+• Guarino (1998)
+• Peristeras et al. (2009)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Data-level fidelity: Adequate Data Quality</t>
     </r>
   </si>
   <si>
@@ -1953,7 +2099,184 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Semantic: Existence and Use of Domain-Relevant Semantic Standards</t>
+      <t>Requirement: Semantic: Metadata and provenance: Explicit Provenance Documentation</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be accompanied by structured and sufficiently detailed documentation of their origin, creation process, transformation history, and responsible actors.
+Inclusion Criteria:
+1. Documented data origin.
+2. Recorded transformation steps.
+3. Identified responsible actors.
+4. Lineage linked to resources.
+Exclusion Criteria:
+1. General reliability claims without lineage.
+2. Quality without origin information.
+Example Quotations:
+1. “The Model of the Flemish Address Register applies the W3C PROV ontology for modeling provenance.”
+2. “Core Objects contain provenance information, which defines when the information was registered and for which period of time it is valid.”
+Literature:
+• FAIR R1.2
+• Buneman et al. (2001)
+• Moreau &amp; Missier (2013)
+• Wang &amp; Strong (1996)
+• Peristeras et al. (2009)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Metadata and provenance: Metadata Availability</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data resources must be accompanied by metadata, irrespective of structuring or independence; this is the precondition for the more demanding requirement of structured and independently accessible metadata.
+Inclusion Criteria:
+1. Presence of any metadata for data resources.
+2. Documented existence of metadata.
+Exclusion Criteria:
+1. Structured metadata accessible independently (use Structured and Independently Accessible Metadata).
+Example Quotations:
+1. “The Directive does not require a collection of new data, instead existing data should be transformed to fit agreed data models.”
+Notes:
+Newly defined as a baseline precondition. Note: original spelling 'Meta-data' standardized to 'Metadata'.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Metadata and provenance: Structured and Independently Accessible Metadata</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data resources must be accompanied by formally structured metadata that provide explicit descriptions of their content, context, structure, provenance, and conditions of use, retrievable independently of the data they describe.
+Inclusion Criteria:
+1. Formally defined metadata schema.
+2. Contextual metadata for interpretation.
+3. Metadata documenting provenance and usage conditions.
+4. Metadata persistent even when data are restricted.
+Exclusion Criteria:
+1. Informal narrative documentation.
+2. Implicit context embedded in data.
+Example Quotations:
+1. “Member States ensure that metadata are created for the spatial data sets and services corresponding to one or more of the INSPIRE themes.”
+Literature:
+• FAIR F2, F3, A2
+• Guarino (1998)
+• Guizzardi &amp; Guarino (2024)
+• Peristeras et al. (2009)
+• EIF Recommendations 39, 42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Representation: Formal and Shared Syntax for Knowledge Representation</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be expressed using formally defined, publicly specified, and widely recognized syntactic languages for knowledge representation.
+Inclusion Criteria:
+1. Use of RDF, OWL, XML Schema or similar.
+2. Public documentation of representation languages.
+3. Formal structural constraints.
+Exclusion Criteria:
+1. Free text without formal structure.
+2. Proprietary or undocumented syntactic formats.
+Example Quotations:
+1. “When someone looks up a URI, provide useful information, using the standards RDF and SPARQL.”
+Literature:
+• FAIR I1, I2, R1.3
+• Guarino (1998)
+• Euzenat &amp; Shvaiko (2013)
+• Peristeras et al. (2009)
+• EIF Recommendation 42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Representation: Multilingual Representation</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Information systems, data models, and semantic artefacts must support representation and interpretation of information across multiple natural languages, preserving conceptual equivalence.
+Inclusion Criteria:
+1. Multilingual labels in semantic artefacts.
+2. Concept identifiers separated from labels.
+3. Multilingual metadata mandated.
+Exclusion Criteria:
+1. UI translation only.
+2. Informal translation without semantic linkage.
+Example Quotations:
+1. “All the semantics included in the legal text have been translated into 24 languages and are now accessible via the INSPIRE registry service.”
+Notes:
+Note: original spelling 'Mutlilingual' corrected
+Literature:
+• Guarino (1998)
+• EIF Recommendation 16</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Representation: Rich and Accurate Conceptual Description</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be described with a plurality of accurate, relevant, and sufficiently detailed attributes that make their meaning understandable within and beyond their original context.
+Inclusion Criteria:
+1. Multiple relevant descriptive attributes.
+2. Contextual qualifiers (scope, units, temporal coverage).
+3. Definitions accurate and non-ambiguous.
+Exclusion Criteria:
+1. Minimal or generic descriptions.
+2. Formal ontological modelling specifically (use Semantic Standards or Modelling Alignment).
+Example Quotations:
+1. “Linked address data provides context information via the dereferenceable address identifiers (URIs) including a reference to the vocabulary...”
+Literature:
+• FAIR R1
+• Park (2006)
+• Peristeras et al. (2009)
+• Batini &amp; Scannapieco (2016)
+• EOSC
+• EIF Recommendation 38</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Semantic: Standards: Domain-Relevant Semantic Standards</t>
     </r>
   </si>
   <si>
@@ -1985,273 +2308,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Semantic: Existence of Meta-data</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data resources must be accompanied by metadata, irrespective of structuring or independence; this is the precondition for the more demanding requirement of structured and independently accessible metadata.
-Inclusion Criteria:
-1. Presence of any metadata for data resources.
-2. Documented existence of metadata.
-Exclusion Criteria:
-1. Structured metadata accessible independently (use Structured and Independently Accessible Metadata).
-Example Quotations:
-1. “The Directive does not require a collection of new data, instead existing data should be transformed to fit agreed data models.”
-Notes:
-Newly defined as a baseline precondition. Note: original spelling 'Meta-data' standardized to 'Metadata'.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Explicit Provenance Documentation</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data and metadata must be accompanied by structured and sufficiently detailed documentation of their origin, creation process, transformation history, and responsible actors.
-Inclusion Criteria:
-1. Documented data origin.
-2. Recorded transformation steps.
-3. Identified responsible actors.
-4. Lineage linked to resources.
-Exclusion Criteria:
-1. General reliability claims without lineage.
-2. Quality without origin information.
-Example Quotations:
-1. “The Model of the Flemish Address Register applies the W3C PROV ontology for modeling provenance.”
-2. “Core Objects contain provenance information, which defines when the information was registered and for which period of time it is valid.”
-Literature:
-• FAIR R1.2
-• Buneman et al. (2001)
-• Moreau &amp; Missier (2013)
-• Wang &amp; Strong (1996)
-• Peristeras et al. (2009)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Formal and Shared Syntax for Knowledge Representation</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data and metadata must be expressed using formally defined, publicly specified, and widely recognized syntactic languages for knowledge representation.
-Inclusion Criteria:
-1. Use of RDF, OWL, XML Schema or similar.
-2. Public documentation of representation languages.
-3. Formal structural constraints.
-Exclusion Criteria:
-1. Free text without formal structure.
-2. Proprietary or undocumented syntactic formats.
-Example Quotations:
-1. “When someone looks up a URI, provide useful information, using the standards RDF and SPARQL.”
-Literature:
-• FAIR I1, I2, R1.3
-• Guarino (1998)
-• Euzenat &amp; Shvaiko (2013)
-• Peristeras et al. (2009)
-• EIF Recommendation 42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Modelling Flexibility</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Semantic models and modelling environments must allow for context-sensitive variation and extension without breaking interoperability, in order to accommodate divergent and evolving domain requirements.
-Inclusion Criteria:
-1. Extension mechanisms in shared models.
-2. Application profiles built on top of core models.
-3. Allowance for jurisdictional or sectoral variation.
-Exclusion Criteria:
-1. Strict conformance regimes that prohibit variation (use Conformance-based mechanism for related solution context).
-2. Ad hoc undocumented modelling differences.
-Example Quotations:
-1. “Analyzing the situation at ECDC it became clear, that implementing simply a rigorous data modeling rule set plus introducing obligatory mappings is insufficient...”
-2. “The core data models as contained in the legal framework can be extended, following the rules defined by the generic conceptual model.”
-Notes:
-Newly defined; complement of Semantic Modelling Alignment, addressing how flexibility is institutionalized.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Mutlilingual Representation</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Information systems, data models, and semantic artefacts must support representation and interpretation of information across multiple natural languages, preserving conceptual equivalence.
-Inclusion Criteria:
-1. Multilingual labels in semantic artefacts.
-2. Concept identifiers separated from labels.
-3. Multilingual metadata mandated.
-Exclusion Criteria:
-1. UI translation only.
-2. Informal translation without semantic linkage.
-Example Quotations:
-1. “All the semantics included in the legal text have been translated into 24 languages and are now accessible via the INSPIRE registry service.”
-Notes:
-Note: original spelling 'Mutlilingual' corrected
-Literature:
-• Guarino (1998)
-• EIF Recommendation 16</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Rich and Accurate Conceptual Description</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data and metadata must be described with a plurality of accurate, relevant, and sufficiently detailed attributes that make their meaning understandable within and beyond their original context.
-Inclusion Criteria:
-1. Multiple relevant descriptive attributes.
-2. Contextual qualifiers (scope, units, temporal coverage).
-3. Definitions accurate and non-ambiguous.
-Exclusion Criteria:
-1. Minimal or generic descriptions.
-2. Formal ontological modelling specifically (use Semantic Standards or Modelling Alignment).
-Example Quotations:
-1. “Linked address data provides context information via the dereferenceable address identifiers (URIs) including a reference to the vocabulary...”
-Literature:
-• FAIR R1
-• Park (2006)
-• Peristeras et al. (2009)
-• Batini &amp; Scannapieco (2016)
-• EOSC
-• EIF Recommendation 38</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Semantic Mapping and Alignment capabilities</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-An interoperability ecosystem must enable the formal specification, representation, and maintenance of explicit correspondences between heterogeneous semantic artefacts (post hoc alignment).
-Inclusion Criteria:
-1. Cross-schema mappings or crosswalks.
-2. Equivalence, subsumption, transformation rules.
-3. Semantic mediation via formal mappings.
-4. Multi-standard environments requiring correspondence.
-Exclusion Criteria:
-1. Single shared model mandated (use Semantic Modelling Alignment).
-2. Syntactic format conversion only.
-Example Quotations:
-1. “In order to achieve a feasible model, and to benefit from the best of both worlds, the Flemish Government has adapted the ISA address towards INSPIRE.”
-Literature:
-• Euzenat &amp; Shvaiko (2013)
-• Peristeras et al. (2009)
-• FAIR I1-I2 and R1.3
-• FAIR 2.0
-• Guarino (1998)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Semantic Modelling Alignment</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Participating actors must adopt and apply a shared conceptualization approach, modelling methodology, naming conventions, and structural design logic when developing semantic artefacts (ex ante alignment).
-Inclusion Criteria:
-1. Common conceptual modelling methodology.
-2. Agreed abstraction levels and granularity.
-3. Harmonized modelling guidelines.
-4. Shared reference architecture or meta-model.
-Exclusion Criteria:
-1. Post hoc mapping (use Semantic Mapping and Alignment).
-2. Syntactic format choice only.
-3. Single shared artefact without modelling principles.
-Example Quotations:
-1. “The base registries are part of a semantic coherent system of uniform identified base-objects and relations, which are in line with the OSLO-standards.”
-Literature:
-• FAIR 2.0 (Vogt et al. 2024)
-• FAIR I1-I2, R1.3
-• Euzenat &amp; Shvaiko (2013)
-• Guarino (1998)
-• Peristeras et al. (2009)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Semantic: Structured and Independently Accessible Metadata</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data resources must be accompanied by formally structured metadata that provide explicit descriptions of their content, context, structure, provenance, and conditions of use, retrievable independently of the data they describe.
-Inclusion Criteria:
-1. Formally defined metadata schema.
-2. Contextual metadata for interpretation.
-3. Metadata documenting provenance and usage conditions.
-4. Metadata persistent even when data are restricted.
-Exclusion Criteria:
-1. Informal narrative documentation.
-2. Implicit context embedded in data.
-Example Quotations:
-1. “Member States ensure that metadata are created for the spatial data sets and services corresponding to one or more of the INSPIRE themes.”
-Literature:
-• FAIR F2, F3, A2
-• Guarino (1998)
-• Guizzardi &amp; Guarino (2024)
-• Peristeras et al. (2009)
-• EIF Recommendations 39, 42</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Requirement: Technical</t>
     </r>
   </si>
@@ -2279,25 +2335,22 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Technical: Existence of Shared Technical Standards</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Interoperable public services must rely on commonly agreed and publicly available technical specifications, preferably open, to ensure compatibility of systems, interfaces, protocols, and infrastructural components.
-Inclusion Criteria:
-1. Open specifications for interoperability.
-2. Common technical standards for interfaces.
-3. Standardized communication protocols.
-4. Vendor-neutral technical specifications.
-Exclusion Criteria:
-1. Semantic standards (use Semantic: Existence and Use of Domain-Relevant Semantic Standards).
-2. Governance of selection (use Standardization and Semantic Control).
-Example Quotations:
-1. “INSPIRE metadata are based on the well-established EN ISO 19115 and EN ISO 19119 standards.”
-Literature:
-• EIF Recommendation 33
-• Peristeras et al. (2009)</t>
+      <t>Requirement: Technical: Access and trust: Integration of services and applications</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Interoperability requires that services and applications can be composed and integrated into wider workflows or service chains, beyond pairwise data exchange, including orchestration and choreography of services across organizational boundaries.
+Inclusion Criteria:
+1. Composability of services into end-to-end processes.
+2. Orchestration and choreography mechanisms.
+3. Service chains crossing organizational boundaries.
+4. Application-level integration patterns.
+Exclusion Criteria:
+1. Pure data exchange without service composition (use Technical Interconnection).
+2. Workflow alignment as organizational requirement (use Structural Process Alignment).
+Literature:
+- Scholl &amp; Klischewski (2007), constraints 4 and 8
+- Kubicek et al. (2011), ch. 7 on technical interoperability</t>
   </si>
   <si>
     <r>
@@ -2307,7 +2360,140 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Technical: Findable, Searchable and Visible</t>
+      <t>Requirement: Technical: Access and trust: Security and Privacy</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Interoperable public services must operate within a coherent framework of technical, organizational, and procedural safeguards that ensure secure, trustworthy, and legally compliant data exchange.
+Inclusion Criteria:
+1. Common security and privacy framework.
+2. Trust services (eID, e-signatures).
+3. Risk-based protection measures.
+4. Embedded privacy in interoperability architectures.
+Exclusion Criteria:
+1. Pure legal data protection (use Legal: Restrictions).
+2. Generic trust references without mechanisms.
+Literature:
+• EIF Recommendations 15, 37, 46, 47</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Access and trust: Standardized and Formally Governed Accessibility</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Data and metadata must be retrievable through standardized, documented, and interoperable communication protocols that ensure predictable access conditions across organizational and technical boundaries.
+Inclusion Criteria:
+1. Documented standardized access protocols.
+2. Stable access mechanisms.
+3. Formally specified authentication and authorization.
+Exclusion Criteria:
+1. Manual or informal access.
+2. Undocumented or proprietary mechanisms.
+Example Quotations:
+1. “Geospatial data is made available 'online first', thus unlocking it as is for further use.”
+Literature:
+• FAIR A1, A1.1, A1.2
+• Peristeras et al. (2009)
+• Wimmer et al. (2018)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Connectivity and performance: Scalable and Performant</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Interoperability infrastructures must scale to handle expected volumes of data, users and transactions while maintaining acceptable performance characteristics in terms of response time, throughput and availability.
+Inclusion Criteria:
+1. Architectures supporting growth in data volume and user load.
+2. Defined performance and availability targets.
+3. Mechanisms to handle peak load and federation across nodes.
+Exclusion Criteria:
+1. Pure technical interconnection without performance dimension (use Technical Interconnection).
+2. Sustainability of infrastructure governance (use Sustainable and Trusted Infrastructure for Data Availability).
+Literature:
+- Scholl &amp; Klischewski (2007), constraint 9 (performance)
+- Scholl (2005), on scalability and latency</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Connectivity and performance: Sustainable and Trusted Infrastructure for Data Availability</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+A federated data ecosystem must include stable, trusted, and sustainably governed infrastructure components that ensure long-term availability, accessibility, and operational continuity.
+Inclusion Criteria:
+1. Persistent repositories.
+2. Long-term availability guarantees.
+3. Federated infrastructures for cross-community interoperability.
+4. Certified or governed technical services.
+Exclusion Criteria:
+1. Trust as social claim only.
+2. Governance without technical service provision.
+Example Quotations:
+1. “The Address Registry is deployed on a cloud infrastructure: Microsoft Azure. All the components are available as runnable services using Docker.”
+Literature:
+• EOSC IF
+• FAIR A
+• Wimmer et al. (2018)
+• Peristeras et al. (2009)
+• EIF Recommendations 6, 35, 36, 37, 38, 39, 44</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Connectivity and performance: Technical Interconnection</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Systems must be technically connectable through compatible network and communication infrastructure, including network protocols, transport mechanisms and connectivity arrangements that enable data to move between systems.
+Inclusion Criteria:
+1. Compatible network and transport protocols.
+2. Connectivity arrangements between participating systems.
+3. Service reachability across organizational boundaries.
+Exclusion Criteria:
+1. Performance and scalability of the connection (use Scalable and Performant).
+2. Application-level service integration (use Integration of services and applications).
+3. Access protocols and contracts (use Standardized and Formally Governed Accessibility).
+Literature:
+- Scholl &amp; Klischewski (2007), constraint 8 (technological)
+- Kubicek et al. (2011), ch. 7 on technical interoperability</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8C32A0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Requirement: Technical: Identification and findability: Findable, Searchable and Visible</t>
     </r>
   </si>
   <si>
@@ -2338,18 +2524,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Technical: Integration of services and applications</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Technical: Persistent and Globally Unique Identification</t>
+      <t>Requirement: Technical: Identification and findability: Persistent and Globally Unique Identification</t>
     </r>
   </si>
   <si>
@@ -2378,7 +2553,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Technical: Presence of Common Semantic Tooling</t>
+      <t>Requirement: Technical: Standards and tooling: Common Semantic Tooling</t>
     </r>
   </si>
   <si>
@@ -2408,92 +2583,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Requirement: Technical: Security and Privacy</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Interoperable public services must operate within a coherent framework of technical, organizational, and procedural safeguards that ensure secure, trustworthy, and legally compliant data exchange.
-Inclusion Criteria:
-1. Common security and privacy framework.
-2. Trust services (eID, e-signatures).
-3. Risk-based protection measures.
-4. Embedded privacy in interoperability architectures.
-Exclusion Criteria:
-1. Pure legal data protection (use Legal: Restrictions).
-2. Generic trust references without mechanisms.
-Literature:
-• EIF Recommendations 15, 37, 46, 47</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Technical: Standardized and Formally Governed Accessibility</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Data and metadata must be retrievable through standardized, documented, and interoperable communication protocols that ensure predictable access conditions across organizational and technical boundaries.
-Inclusion Criteria:
-1. Documented standardized access protocols.
-2. Stable access mechanisms.
-3. Formally specified authentication and authorization.
-Exclusion Criteria:
-1. Manual or informal access.
-2. Undocumented or proprietary mechanisms.
-Example Quotations:
-1. “Geospatial data is made available 'online first', thus unlocking it as is for further use.”
-Literature:
-• FAIR A1, A1.1, A1.2
-• Peristeras et al. (2009)
-• Wimmer et al. (2018)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Technical: Sustainable and Trusted Infrastructure for Data Availability</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-A federated data ecosystem must include stable, trusted, and sustainably governed infrastructure components that ensure long-term availability, accessibility, and operational continuity.
-Inclusion Criteria:
-1. Persistent repositories.
-2. Long-term availability guarantees.
-3. Federated infrastructures for cross-community interoperability.
-4. Certified or governed technical services.
-Exclusion Criteria:
-1. Trust as social claim only.
-2. Governance without technical service provision.
-Example Quotations:
-1. “The Address Registry is deployed on a cloud infrastructure: Microsoft Azure. All the components are available as runnable services using Docker.”
-Literature:
-• EOSC IF
-• FAIR A
-• Wimmer et al. (2018)
-• Peristeras et al. (2009)
-• EIF Recommendations 6, 35, 36, 37, 38, 39, 44</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF8C32A0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Requirement: Technical: Technical Interconnection</t>
-    </r>
+      <t>Requirement: Technical: Standards and tooling: Shared Technical Standards</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Interoperable public services must rely on commonly agreed and publicly available technical specifications, preferably open, to ensure compatibility of systems, interfaces, protocols, and infrastructural components.
+Inclusion Criteria:
+1. Open specifications for interoperability.
+2. Common technical standards for interfaces.
+3. Standardized communication protocols.
+4. Vendor-neutral technical specifications.
+Exclusion Criteria:
+1. Semantic standards (use Semantic: Existence and Use of Domain-Relevant Semantic Standards).
+2. Governance of selection (use Standardization and Semantic Control).
+Example Quotations:
+1. “INSPIRE metadata are based on the well-established EN ISO 19115 and EN ISO 19119 standards.”
+Literature:
+• EIF Recommendation 33
+• Peristeras et al. (2009)</t>
   </si>
   <si>
     <r>
@@ -2642,33 +2750,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Governance Paradigm: Hybrid Governance</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-A governance paradigm in which multiple governance logics coexist, combining elements of central, federated, community-based, and/or decentralized approaches within a single solution or ecosystem.
-Inclusion Criteria:
-1. Multiple governance paradigms explicitly combined.
-2. Different layers, phases, or components follow different logics.
-3. Trade-offs consciously articulated.
-Exclusion Criteria:
-1. One paradigm dominates clearly.
-2. Apparent hybridity from ambiguity rather than design.
-Example Quotations:
-1. “Two groups of stakeholders were identified: Legally Mandated Organisations (LMOs) and Spatial Data Interest Community (SDIC).”
-Literature:
-• Kubicek (2008)
-• Gruninger (2008)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Solution Interoperability Mechanism</t>
     </r>
   </si>
@@ -2745,45 +2826,6 @@
 Literature:
 • Wimmer et al. (2018)
 • Kubicek (2009)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Interoperability Mechanism: Deep learning / AI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Interoperability Mechanism: Hybrid</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Interoperability is achieved through a deliberate combination of two or more distinct interoperability mechanisms applied at different layers, scopes, or phases.
-Inclusion Criteria:
-1. Multiple mechanisms explicitly combined.
-2. Combination intentional and articulated.
-3. No single dominant mechanism.
-Exclusion Criteria:
-1. Vague or accidental hybridity.
-2. Multiple mechanisms mentioned without integration rationale.
-Literature:
-• Wache et al. (2001)
-• Uschold &amp; Gruninger (2004)
-• Doan et al. (2012)
-• No quotations yet
-• retained for analytical completeness</t>
   </si>
   <si>
     <r>
@@ -2857,6 +2899,32 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Interoperability Mechanism: Query based</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition:
+Solution artefacts that achieve interoperability through query-oriented mechanisms, including declarative query languages, federated query infrastructures, or query rewriting against heterogeneous sources.
+Inclusion Criteria:
+1. SPARQL endpoints over heterogeneous sources.
+2. Federated query mechanisms.
+3. Query rewriting against multiple schemas.
+Exclusion Criteria:
+1. Static data transformation (use Mediation-based mechanism).
+2. Pure data transport (use Implemented Solutions).
+Example Quotations:
+1. “The second one concerns the query-oriented approach. This approach uses interpretable languages, most of which are either logical declarative...”
+Notes:
+Newly defined; empirically supported by 10 quotations. Note: hyphen normalized.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Interoperability Mechanism: Rule-based</t>
     </r>
   </si>
@@ -2895,17 +2963,6 @@
 1. Do not code fragments directly with the parent.
 Notes:
 Header / parent code.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Level of Shared Meaning: Conceptuel Model</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3081,6 +3138,131 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>Solution Maturity</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Orthogonal dimension that records how mature or far-realized a solution is at the time it is described in the source. Coded in addition to Solution Type, not instead of it: the same artefact can be at any maturity level. Captures the literature-level meta-finding of how much of the field reports proposed versus realized solutions.
+Inclusion Criteria:
+1. Use as analytical container only.
+Exclusion Criteria:
+1. Do not code fragments directly with the parent.
+Notes: Header and parent code. The four values below are mutually exclusive: each solution-describing fragment is coded with exactly one Solution Maturity value when maturity is identifiable. Fragments that describe a solution without giving any indication of maturity are left uncoded on this dimension.
+Literature:
+- Analytical dimension; grounded in the GCSR meta-finding on the gap between proposed and realized solutions in interoperability literature</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Maturity: Conceptual proposal</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions described at the level of a concept, idea or design proposal, without implementation. The artefact exists as a written or modelled proposition; no working version has been built.
+Inclusion Criteria:
+1. Solutions presented as design proposals or conceptual frameworks.
+2. Position papers and vision documents proposing a way forward.
+3. Architectural designs without realization.
+Exclusion Criteria:
+1. A working implementation, however limited (use Prototype or Operational).
+2. A solution that exists primarily as evaluation of an existing one (use Operational or Evaluated).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Prototype: a prototype implements at least part of the proposal in working form; a conceptual proposal does not. When a fragment is ambiguous about whether implementation occurred, this code applies by default.
+Literature:
+- Analytical maturity value; specific instances per fragment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Maturity: Evaluated</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions described primarily through ex-post evaluation, where the source reports outcomes, lessons learned, residual challenges or measured effects of an already-deployed solution. The maturity claim is that the solution has been used long enough to evaluate.
+Inclusion Criteria:
+1. Sources reporting evaluation outcomes of deployed solutions.
+2. Lessons-learned studies and retrospective analyses.
+3. Empirical assessments of solution effectiveness.
+Exclusion Criteria:
+1. Operational solutions described without evaluative content (use Operational).
+2. Assessment frameworks as artefacts rather than evaluation results (use Solution Type: Assessment frameworks and tools).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This value captures the highest-maturity stage where outcomes are reported, not just deployment. It links directly to the GCSR Residue analysis: evaluated solutions are the ones from which residue can most reliably be read. Boundary with Operational: a solution described as in use is Operational; a solution described in terms of evaluated outcomes is Evaluated.
+Literature:
+- Analytical maturity value; specific instances per fragment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Maturity: Operational</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions in routine operational use, serving real users or processes in production environments. Includes pilots and limited deployments that nonetheless serve real operational purposes, as well as full production systems.
+Inclusion Criteria:
+1. Solutions deployed in production environments.
+2. Pilots and limited deployments serving real users or processes.
+3. Operational rollouts at any scale, from single organization to multinational.
+Exclusion Criteria:
+1. Prototypes that demonstrate feasibility without operational use (use Prototype).
+2. Solutions described primarily through ex-post evaluation (use Evaluated).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This value merges what could conceptually be split into Pilot and Production deployment, because the distinction is rarely clear in the literature and rarely analytically decisive. The unifying criterion is that the solution serves real users or processes, regardless of scale. Boundary with Evaluated: an operational solution is described in terms of what it does; an evaluated solution is described in terms of what it has achieved or fallen short of.
+Literature:
+- Analytical maturity value; specific instances per fragment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Solution Maturity: Prototype</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions realized as working prototypes, demonstrators or proof-of-concept implementations, intended to show feasibility but not deployed for routine use.
+Inclusion Criteria:
+1. Proof-of-concept implementations.
+2. Research demonstrators and laboratory builds.
+3. Limited-scope working versions not intended for production.
+Exclusion Criteria:
+1. Conceptual proposals without working implementation (use Conceptual proposal).
+2. Solutions deployed for routine operational use (use Operational).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Operational: a prototype demonstrates feasibility within a controlled scope; an operational deployment serves real users in real processes. When a pilot is described as serving real users at limited scale, prefer Operational.
+Literature:
+- Analytical maturity value; specific instances per fragment</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF46AA00"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>Solution Modelling type</t>
     </r>
   </si>
@@ -3103,8 +3285,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Modelling type: EDI</t>
-    </r>
+      <t>Solution Modelling type: Conceptual modelling</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions that model a domain through conceptual abstractions, typically using object-oriented or ontologically grounded modelling languages, where the focus is on capturing entities, relationships and constraints at a conceptual rather than purely syntactic or operational level.
+Inclusion Criteria:
+1. UML class diagrams or comparable object-oriented conceptual models.
+2. OntoUML or other ontologically grounded conceptual modelling languages.
+3. Ontologies described conceptually without specific commitment to a Semantic Web implementation.
+Exclusion Criteria:
+1. RDF-based ontologies expressed in OWL or comparable Semantic Web standards (use Semantic web formalisms).
+2. Schema definitions whose purpose is exchange rather than conceptualization (use Schema and exchange formats).
+3. Paper-based or vector-based representations (use Other modelling forms).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This code merges the former UML, OntoUML and Ontology sub-codes. The unifying property is that the modelling intent is conceptual: capturing the structure of a domain rather than specifying an exchange or implementation artefact. The same content expressed in OWL would belong under Semantic web formalisms; the boundary is the formalism, not the subject matter. When a source describes an ontology without specifying its formal expression, this code applies unless the source makes a Semantic Web commitment explicit.
+Literature:
+- Guarino (1998), on formal ontology as conceptual modelling
+- Euzenat &amp; Shvaiko (2013), pp. 37–39, on the distinction between conceptual and syntactic representations</t>
   </si>
   <si>
     <r>
@@ -3114,21 +3313,23 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Modelling type: Ontology</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-The solution expresses semantic artefacts as a formal ontology in the OWL family or comparable formalisms, with explicit class hierarchies, properties, axioms, and reasoning support, regardless of whether the serialisation is RDF, Turtle, OWL/XML, or Manchester syntax.
-Inclusion Criteria:
-1. Formal ontologies in OWL, OWL2, or comparable description logic formalisms.
-2. Class and property hierarchies with axioms supporting reasoning.
-3. Use of reasoners (HermiT, Pellet) over the artefact.
-Exclusion Criteria:
-1. Lightweight RDF Linked Data without OWL axioms (use RDF).
-2. Conceptual UML models without formal ontology semantics (use UML).
-Notes:
-Distinguished from RDF: RDF is the data model and serialisation choice, Ontology focuses on the logical formalism and reasoning support.</t>
+      <t>Solution Modelling type: Other</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions whose modelling form falls outside the three established families above, either because they involve no formal modelling at all or because they rely on a fundamentally different representational paradigm such as vector-based embeddings.
+Inclusion Criteria:
+1. Paper-based or narrative descriptions used as the modelling substrate.
+2. Vector databases and embedding-based representations as the substrate.
+3. Other emerging or non-standard modelling forms that do not fit the three established families.
+Exclusion Criteria:
+1. Any of the formalisms covered by the three other Modelling type codes.
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This code merges the former Paper and Vector Database sub-codes, and serves as a residual category for modelling forms that do not fit the three established families. Two members are conceptually quite verschillend: Paper represents the absence of formal modelling, while Vector Database represents an alternative representational paradigm based on numeric embeddings rather than symbolic structures. If during coding these two prove to behave very differently in your analysis, splitting this code into Informal or non-formal modelling and Vector-based modelling remains an option. For now they are pragmatically grouped.
+Literature:
+- Vogt et al. (2024), FAIR 2.0, on representational paradigms beyond classical formal modelling
+- Analytical residual category</t>
   </si>
   <si>
     <r>
@@ -3138,21 +3339,28 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Modelling type: OntoUML</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-The solution expresses semantic artefacts in OntoUML, a UML profile grounded in the Unified Foundational Ontology (UFO), supporting rigorous ontological distinctions (kinds, roles, relators, modes) and validation through model-checking tools.
-Inclusion Criteria:
-1. Solutions modelled in OntoUML or with explicit UFO grounding.
-2. Conceptual models that distinguish UFO categories such as kind, role, relator, or mode.
-3. Use of OntoUML tooling for validation or ontology unpacking.
-Exclusion Criteria:
-1. Plain UML class diagrams without UFO grounding (use UML).
-2. Pure RDF/OWL representations without UFO commitments (use RDF).
-Notes:
-OntoUML is increasingly used in semantic interoperability work to surface ontological commitments that plain UML hides; retained as separate subtype.</t>
+      <t>Solution Modelling type: Schema and exchange formats</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions that model and exchange data through syntactic schemas, structured exchange formats or relational structures, where interoperability rests on agreed structure and field-level conformance rather than on formally expressed semantics.
+Inclusion Criteria:
+1. XML, including domain-specific XML dialects.
+2. XBRL for structured business reporting.
+3. WSDL or comparable web service description languages.
+4. EDI standards for electronic data interchange.
+5. RosettaNet and similar industry-specific exchange standards.
+6. Relational database schemas as the modelling substrate.
+Exclusion Criteria:
+1. RDF-based representations where semantics is carried by the Semantic Web stack (use Semantic web formalisms).
+2. Conceptual models such as UML or OntoUML that describe a domain rather than an exchange format (use Conceptual modelling).
+3. Paper-based or vector-based representations (use Other modelling forms).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This code merges the former XML, XBRL, WSDL, EDI, RosettaNet and Relational Database sub-codes. The unifying property is that interoperability is achieved through syntactic structure and schema conformance, not through formally expressed meaning. Peristeras' boundary rule places format and representation conflicts in the technical layer; this code captures the artefact side of that family on the solution side. An XML payload annotated with semantic metadata that pushes it into the RDF stack should be coded under Semantic web formalisms instead.
+Literature:
+- Kubicek et al. (2011), ch. 7, on syntactic interoperability standards
+- Peristeras et al. (2008), section 5.2.2, on data representation as syntactic layer</t>
   </si>
   <si>
     <r>
@@ -3162,133 +3370,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Modelling type: OWL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: Paper</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: RDF</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-The solution expresses semantic artefacts in RDF or RDF‐derived languages (RDFS, OWL, SKOS), typically serialised as Turtle, RDF/XML, JSON‐LD, or N‐Triples, supporting graph‐based representation, dereferenceable URIs, and SPARQL querying.
-Inclusion Criteria:
-1. Solutions explicitly using RDF, OWL, RDFS, SKOS, or JSON‐LD.
-2. Linked Data implementations relying on triples and URIs.
-3. Use of SPARQL endpoints over RDF data.
-Exclusion Criteria:
-1. Solutions modelled in UML or XML Schema only (use UML or extend the dimension).
-2. Generic statements that a formal syntax is required (use Formal and Shared Syntax requirement).
-Notes:
-Empirically thin in the current dataset, but analytically important to retain because RDF is a defining choice in much of the surveyed Linked Data work.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: RosettaNet</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: SHACL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: UML</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-The solution expresses semantic artefacts in UML class diagrams, profiles, or related object‐oriented modelling notations, typically supporting conceptual modelling, application profiles, or generation of XML Schemas.
-Inclusion Criteria:
-1. Solutions modelled in UML class diagrams or profiles.
-2. Use of UML to specify INSPIRE or ISA conceptual data models.
-3. UML as the source for derived schemas.
-Exclusion Criteria:
-1. Solutions in RDF/OWL only (use RDF).
-2. Pure XML Schema authored without UML lineage.
-Notes:
-Empirically thin, often present in figures rather than narrative text; retained for completeness because INSPIRE and the OSLO programme make extensive use of UML.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: Vector Database</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: WSDL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: XBRL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Modelling type: XML</t>
-    </r>
+      <t>Solution Modelling type: Semantic web formalisms</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Solutions that model and exchange data using Semantic Web standards built on RDF, where meaning is expressed through typed resources, properties and relationships, and where formal vocabularies, validation constraints or graph structures carry the semantics.
+Inclusion Criteria:
+1. RDF, RDF Schema and related core standards.
+2. OWL ontologies of any expressiveness.
+3. SHACL or other RDF-based constraint and validation languages.
+4. Knowledge graphs built on RDF or comparable graph-based semantic technologies.
+Exclusion Criteria:
+1. Conceptual models that are not RDF-based, such as UML or OntoUML (use Conceptual modelling).
+2. XML, XBRL, WSDL or other schema and exchange formats not built on RDF semantics (use Schema and exchange formats).
+3. Vector embeddings or paper-based descriptions (use Other modelling forms).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This code merges the former RDF, OWL, SHACL and Knowledge graph sub-codes. The unifying property is that meaning is carried by an RDF-based semantic stack, not by syntactic schema definitions alone. A knowledge graph that is not RDF-based but conceptually similar can be coded here; the formalism rather than the vendor implementation determines the placement.
+Literature:
+- Euzenat &amp; Shvaiko (2013), on the Semantic Web stack as semantic interoperability infrastructure
+- W3C standards for RDF, OWL, SHACL as defining sources</t>
   </si>
   <si>
     <r>
@@ -3482,21 +3583,20 @@
     </r>
   </si>
   <si>
-    <t>Definition:
-Formally negotiated mutual commitments between parties that establish or operationalize interoperability arrangements, such as memoranda of understanding, data-sharing agreements, or steering-committee charters.
-Inclusion Criteria:
-1. Memoranda of understanding.
-2. Data-sharing agreements.
-3. Steering-committee charters and mandates.
-4. Multi-party commitments operationalizing standards.
-Exclusion Criteria:
-1. Statutory legal instruments (use Legal Interoperability Measures).
-2. Frameworks providing reusable structure (use Common Frameworks).
-3. Pure community consensus without formal commitment (use Community Based Governance).
-Example Quotations:
-1. “Governance: as described in the Specification Process, a permanent steering committee was installed, which represents the 'authority'.”
-Notes:
-Newly defined; agreements operationalize legal or organizational requirements, distinct from the legal instruments themselves.</t>
+    <t>Definition: Formal or informal arrangements between specific parties that establish how they will cooperate on interoperability. The artefact form is bilateral or multilateral and bound to identified participants.
+Inclusion Criteria:
+1. Inter-organizational agreements on data sharing or interoperability.
+2. Memoranda of understanding, covenants and similar instruments.
+3. Service-level agreements specific to interoperability arrangements.
+Exclusion Criteria:
+1. Industry-wide standards (use Standards and Specifications).
+2. Legal instruments with statutory force (use Legal Interoperability Measures).
+3. The substantive shared position that an agreement records (use Challenge: Organisational and Structural: No shared agreement, inverted).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Standards and Specifications: agreements bind specific parties; standards apply to anyone who adopts them. Boundary with Legal Interoperability Measures: agreements are negotiated instruments between parties; legal measures derive from statutory or regulatory authority.
+Literature:
+- Scholl &amp; Klischewski (2007), constraint 3, on inter-organizational arrangements</t>
   </si>
   <si>
     <r>
@@ -3510,22 +3610,23 @@
     </r>
   </si>
   <si>
-    <t>Definition:
-Solution artefacts that provide structured methods, instruments, or procedures to assess, evaluate, or measure interoperability-related aspects such as standards, systems, services, or organizational practices.
-Inclusion Criteria:
-1. Tool/method/framework for assessment or evaluation.
-2. Measurement, validation, or comparison of interoperability characteristics.
-3. Evaluative outputs (scores, classifications, reports).
-4. Analytical or diagnostic primary function.
-Exclusion Criteria:
-1. Direct implementation of interoperability (use Implemented Solutions).
-2. Normative specifications (use Standards and Specifications).
-3. Generic analytical methods not specifically applied to interoperability.
-Example Quotations:
-1. “Linked data publications on the SW are typically evaluated with the W3C 5-star deployment scheme, using a quality scale analogous to evaluating hotels.”
-Literature:
-• EIF Solution Finder
-• Hevner (2004)</t>
+    <t>Definition: Artefacts designed to evaluate or verify interoperability properties, including maturity models, conformance test suites, validation rule sets, metrics frameworks and benchmark instruments. The artefact form is evaluative: the artefact exists to measure or check something against an explicit standard.
+Inclusion Criteria:
+1. Maturity models for interoperability or related properties.
+2. Conformance test suites and validation rule sets, including SHACL shapesets, XML Schema validators and unit-test suites published as artefacts.
+3. Metrics frameworks for interoperability, FAIRness, data quality or comparable properties.
+4. Benchmarks and assessment instruments published for reuse by others.
+Exclusion Criteria:
+1. A fragment describing only that an evaluation took place, without naming a reusable instrument (do not code under this dimension; consider whether another dimension applies).
+2. Standards that prescribe behaviour rather than evaluate it (use Standards and Specifications).
+3. Software tooling that supports interoperability creation rather than evaluation (use Common Frameworks and Tooling).
+4. Methodological procedures that include evaluation as one step (use Methodologies).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: This code merges the former Assessment tools and Evaluation and Validation sub-codes, and renames to make the artefact focus explicit. The unifying property is that the artefact exists to measure or verify something. Validation is included as a specific case of assessment focused on conformance. Boundary with Common Frameworks and Tooling: assessment frameworks measure; common frameworks enable building. Boundary with Standards and Specifications: a standard prescribes what should hold; an assessment framework measures whether it does.
+Literature:
+- Wilkinson et al. (2016), FAIR Guiding Principles, as basis for FAIR assessment frameworks
+- Vogt et al. (2024), FAIR 2.0, on assessment of semantic interoperability</t>
   </si>
   <si>
     <r>
@@ -3539,23 +3640,22 @@
     </r>
   </si>
   <si>
-    <t>Definition:
-Solution artefacts that provide reusable conceptual frameworks, methodological approaches, reference models, or structured toolsets intended to guide the design, implementation, coordination, or governance of interoperability.
-Inclusion Criteria:
-1. Reusable framework or reference model.
-2. Methodology providing structured guidance.
-3. Integrated toolkit reusable across contexts.
-Exclusion Criteria:
-1. Operational systems or services (use Implemented Solutions).
-2. Pure technical standards (use Standards and Specifications).
-3. Isolated tools without broader framing.
-Example Quotations:
-1. “The Flemish Government launched an interoperability programme: Open Standards for Linked Organisations (OSLO).”
-2. “OSLO² provides a policy framework for technical topics, including the URI-strategy.”
-Notes:
-Combines the IOPEU Common Frameworks and Generic Tools categories
-Literature:
-• EIF Solution Finder</t>
+    <t>Definition: Reusable technical or organizational frameworks and software tools that support the creation, deployment or maintenance of interoperable solutions. The artefact form is enabling: it does not solve a specific case but provides infrastructure for solving many.
+Inclusion Criteria:
+1. Software frameworks for building interoperable systems.
+2. Tooling for modelling, transformation or integration.
+3. Reusable infrastructure components.
+4. Reference architectures intended for adaptation.
+Exclusion Criteria:
+1. Specific assessment instruments (use Assessment frameworks and tools).
+2. Methodological descriptions of how to use the framework (use Methodologies).
+3. The semantic content carried by the framework (use Semantic Assets).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Assessment frameworks and tools: this code is for frameworks that enable building; assessment frameworks measure or evaluate. A framework that contains assessment functionality as one component is coded here unless the assessment role dominates the fragment.
+Literature:
+- Kubicek et al. (2011), on common frameworks emerging from cross-case analysis
+- Analytical artefact category; specific instances established in the reference-architecture tradition</t>
   </si>
   <si>
     <r>
@@ -3565,23 +3665,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Type: Consensus</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Solution artefacts that consist of explicit, formally documented agreements among multiple parties on shared meaning, classification, or terminology, established through deliberation rather than imposed authority.
-Inclusion Criteria:
-1. Documented multi-party consensus on terminology.
-2. Bottom-up agreement on shared classification.
-3. Deliberative outputs as solution artefacts.
-Exclusion Criteria:
-1. Formal agreements with binding commitment (use Agreements).
-2. Top-down standards (use Standards and Specifications).
-Example Quotations:
-1. “Both the bottom-up and top-down approach were important to create the necessary political support. OSLO was built on consensus, rather than authority.”
-Notes:
-Newly defined; complements Solution Governance Paradigm: Community Based Governance.</t>
+      <t>Solution Type: Guiding Principles</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Articulated principles, values or design philosophies that guide how interoperability should be approached, without prescribing specific technical implementations. The artefact form is conceptual: principles that others can adopt, reference or build upon.
+Inclusion Criteria:
+1. Sets of design principles for interoperability or data sharing.
+2. Articulated philosophies such as FAIR, Common Ground, or comparable principle-based frameworks.
+3. High-level guidance documents that establish values rather than specifications.
+Exclusion Criteria:
+1. Concrete specifications, schemas or formats (use Standards and Specifications).
+2. Step-by-step working procedures (use Methodologies).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Methodologies: principles state what should hold; methodologies state how to do something. Boundary with Standards and Specifications: principles are abstract and reusable across contexts; standards prescribe concrete form. A document that combines principles with specifications is coded under whichever element carries the analytical weight in the fragment.
+Literature:
+- Wilkinson et al. (2016), FAIR Guiding Principles as canonical principle-based artefact
+- Vogt et al. (2024), FAIR 2.0, on principles as design object
+- European Commission (2017), EIF, principle-based interoperability framework</t>
   </si>
   <si>
     <r>
@@ -3591,23 +3693,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Type: Documentation</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Solution artefacts that consist of explicit guidance documents, technical guidelines, manuals, or non-binding implementation aids supporting the realization of interoperability arrangements.
-Inclusion Criteria:
-1. Technical guideline documents.
-2. Implementation manuals.
-3. Non-binding guidance accompanying standards.
-Exclusion Criteria:
-1. Standards or specifications themselves (use Standards and Specifications).
-2. Methodologies prescribing process (use Methodologies).
-Example Quotations:
-1. “Non-legally binding technical guidance documents illustrate how data providers establish access to metadata for discovery services through CSW.”
-Notes:
-Newly defined; documentation operationalizes standards and frameworks but is itself a distinct artefact.</t>
+      <t>Solution Type: Legal Interoperability Measures</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Legal and regulatory instruments that enable, mandate or constrain interoperability, including statutes, regulations, directives, and binding policy instruments. The artefact form is statutory.
+Inclusion Criteria:
+1. Laws and regulations enabling or mandating interoperability.
+2. EU directives and similar supranational instruments.
+3. Binding policy instruments with regulatory effect.
+Exclusion Criteria:
+1. Negotiated agreements between specific parties (use Agreements).
+2. Legal challenges or obstacles encountered (use the Challenge: Legal family).
+3. Non-binding policy documents (use Guiding Principles).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Agreements: legal measures have statutory force; agreements are negotiated. Boundary with Challenge: Legal: this code captures legal instruments as enablers or solutions; the Challenge: Legal family captures legal obstacles. The same statute can appear in both roles in different fragments, and is coded according to the role it plays in the fragment.
+Literature:
+- Kubicek et al. (2011), on the legal interoperability layer
+- Scholl &amp; Klischewski (2007), constraint 1, on constitutional and legal aspects</t>
   </si>
   <si>
     <r>
@@ -3617,26 +3721,25 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Type: Guiding Principles</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Articulated normative statements, values, or high-level design rules that provide direction for decision-making, design, or governance, without prescribing specific structures or technical mechanisms.
-Inclusion Criteria:
-1. Explicit principles, values, or high-level rules.
-2. Abstract and broadly applicable.
-3. Foundational orientations rather than instructions.
-Exclusion Criteria:
-1. Concrete frameworks (use Common Frameworks).
-2. Technical or organizational standards (use Standards or Methodologies).
-3. Operational systems.
-Example Quotations:
-1. “The first principle states 'Use URIs as names for things'.”
-2. “Here using the FAIR principles for creating Findable, Accessible, Interoperable, and Re-usable data are recommended.”
-Literature:
-• Hevner (2004)
-• Gregor &amp; Jones (2007)</t>
+      <t>Solution Type: Methodologies</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Documented working procedures that prescribe how to approach interoperability challenges, intended for reuse and adaptation by others. The artefact form is procedural: a sequence of steps, roles or activities that can be applied across cases.
+Inclusion Criteria:
+1. Step-by-step methods for designing, building or governing interoperable solutions.
+2. Process models, lifecycles or workflows for interoperability work.
+3. Documented approaches that combine principles, activities and deliverables into a reusable whole.
+Exclusion Criteria:
+1. Abstract principles without procedural detail (use Guiding Principles).
+2. Software tooling that implements a methodology (use Common Frameworks and Tooling).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Guiding Principles: methodologies prescribe how to do something; principles state what should hold. Boundary with Common Frameworks and Tooling: a methodology is a procedure; a framework is the infrastructure that may support that procedure. A documented methodology that ships with supporting tooling is coded under both, with the dominant role determining the primary code.
+Literature:
+- Peffers et al. (2007), DSRM as methodological artefact
+- Hevner et al. (2004), design science methodology
+- Vogt et al. (2024), FAIR 2.0, on methodological articulation</t>
   </si>
   <si>
     <r>
@@ -3646,25 +3749,26 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Type: Implemented Solutions</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Interoperability-related solutions that have been technically realized and deployed in an operational context and are actively used in practice. They deliver concrete interoperability effects within a specific setting.
-Inclusion Criteria:
-1. Technically implemented and operational.
-2. In actual use by one or more organizations.
-3. Realized within specific organizational, legal, or technical context.
-Exclusion Criteria:
-1. Reusable services or building blocks (use Common Frameworks).
-2. Normative artefacts (Standards, Frameworks, Vocabularies, Data Models).
-3. Concepts, pilots, prototypes, design proposals.
-Example Quotations:
-1. “The CRAB Address registry is embedded into the core processes of government administrations.”
-2. “The Address Registry is deployed on a cloud infrastructure: Microsoft Azure.”
-Literature:
-• Hevner (2004) instantiated artefact</t>
+      <t>Solution Type: Semantic Assets</t>
+    </r>
+  </si>
+  <si>
+    <t>Definition: Reusable semantic artefacts that capture shared meaning for use across systems or organizations, such as vocabularies, taxonomies, ontologies, code lists, reference data and identifier registries.
+Inclusion Criteria:
+1. Controlled vocabularies and taxonomies.
+2. Ontologies published as reusable artefacts.
+3. Reference data, code lists and identifier registries.
+4. Thesauri and other terminological resources.
+Exclusion Criteria:
+1. The formalism in which the asset is expressed (use the appropriate Modelling type code).
+2. Standards that specify exchange or interface contracts rather than shared meaning (use Standards and Specifications).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Modelling type: Semantic Assets is the kind of artefact; the Modelling type dimension records its formalism. The two are coded together when both apply. Boundary with Standards and Specifications: a vocabulary is a semantic asset; a specification that mandates its use is a standard. When a fragment describes both the asset and its standardized status, both codes apply.
+Literature:
+- Guarino (1998), formal ontology as reusable semantic artefact
+- Euzenat &amp; Shvaiko (2013), vocabularies and ontologies as reusable artefacts
+- European Commission SEMIC initiative, Core Vocabularies as practical instantiation</t>
   </si>
   <si>
     <r>
@@ -3674,149 +3778,24 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Solution Type: Legal Interoperability Measures</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Solution artefacts that address interoperability challenges by operating within, on the basis of, or through formal legal instruments, including statutory law, regulations, and legally binding policy instruments derived from legislation.
-Inclusion Criteria:
-1. Solution grounded in legislation or regulation.
-2. Addresses legal or regulatory barriers.
-3. Operationalizes legal provisions for interoperability.
-4. Lawful information exchange across boundaries.
-Exclusion Criteria:
-1. Purely technical/semantic/organizational solutions without legal basis.
-2. High-level policy aspirations without legal grounding.
-3. Voluntary agreements (use Agreements).
-Example Quotations:
-1. “The legal framework has been set by the Directive (2007/2/EC) and interdependent legal acts.”
-2. “The new agency launched the programme OSLO.”
-Literature:
-• EIF Solution Finder. 01/02/2026 merged with 'Solution Type: Policy Measures'</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Type: Methodologies</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Solution artefacts that provide a structured, systematic approach for analyzing, designing, implementing, or governing interoperability-related problems through ordered activities, procedures, or phases.
-Inclusion Criteria:
-1. Structured method or stepwise approach.
-2. Defined roles, activities, phases, decision steps.
-3. Reusable across contexts.
-Exclusion Criteria:
-1. Abstract guiding principles (use Guiding Principles).
-2. Frameworks without procedural structure (use Common Frameworks).
-3. Technical standards (use Standards and Specifications).
-Example Quotations:
-1. “This was achieved by implementing a process and methodology for developing semantic agreements, based on the ISA methodology.”
-Literature:
-• EIF Solution Finder</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Type: Query based</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Solution artefacts that achieve interoperability through query-oriented mechanisms, including declarative query languages, federated query infrastructures, or query rewriting against heterogeneous sources.
-Inclusion Criteria:
-1. SPARQL endpoints over heterogeneous sources.
-2. Federated query mechanisms.
-3. Query rewriting against multiple schemas.
-Exclusion Criteria:
-1. Static data transformation (use Mediation-based mechanism).
-2. Pure data transport (use Implemented Solutions).
-Example Quotations:
-1. “The second one concerns the query-oriented approach. This approach uses interpretable languages, most of which are either logical declarative...”
-Notes:
-Newly defined; empirically supported by 10 quotations. Note: hyphen normalized.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Type: Semantic Assets</t>
-    </r>
-  </si>
-  <si>
-    <t>Definition:
-Solution artefacts that define, formalize, or harmonize the meaning of data, concepts, or information elements to enable shared understanding across systems, organizations, or jurisdictions.
-Inclusion Criteria:
-1. Shared conceptual definitions, vocabularies, ontologies.
-2. Common Data Elements or canonical data models.
-3. Reusable as semantic reference for multiple parties.
-4. Define what data means rather than how it is exchanged.
-Exclusion Criteria:
-1. Pure technical standards (use Standards and Specifications).
-2. Operational systems (use Implemented Solutions).
-3. Methodologies guiding processes (use Methodologies).
-4. Legal instruments (use Legal Interoperability Measures).
-Example Quotations:
-1. “The Flemish Government has adapted the ISA address towards INSPIRE.”
-2. “OSLO created an ontology in three main domains of interest: persons and organisations, locations, and public services.”
-Literature:
-• EIF Solution Finder</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Solution Type: Standards and Specifications</t>
     </r>
   </si>
   <si>
-    <t>Definition:
-Formally defined, authoritative solution artefacts that prescribe rules, requirements, or constraints for interoperability, such as data structures, interfaces, protocols, conformance criteria, or procedural obligations.
-Inclusion Criteria:
-1. Formally specified standard with versioning and governance.
-2. Mandatory or normative requirements.
-3. Implemented uniformly across systems for compatibility.
-Exclusion Criteria:
-1. Semantic assets defining shared meaning (use Semantic Assets).
-2. Guiding principles or frameworks (use Guiding Principles or Common Frameworks).
-3. Operational systems (use Implemented Solutions).
-4. Legal instruments deriving authority from law (use Legal Interoperability Measures).
-Example Quotations:
-1. “INSPIRE metadata are based on the well-established EN ISO 19115 and EN ISO 19119 standards.”
-2. “The methodology for the development of individual data specification followed a commonly agreed pattern based on the ISO 19131 standard.”
-Literature:
-• EIF Solution Finder</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF46AA00"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Solution Type: Validation</t>
-    </r>
+    <t>Definition: Formal artefacts that prescribe how something should be structured, expressed, exchanged or implemented, intended for adoption by multiple parties. The artefact form is normative and concrete.
+Inclusion Criteria:
+1. Formal standards from recognised standards bodies.
+2. Domain-specific specifications, profiles or application schemas.
+3. Conformance requirements that prescribe how a solution should behave.
+Exclusion Criteria:
+1. High-level principles rather than concrete prescription (use Guiding Principles).
+2. The semantic content the standard references rather than the standard itself (use Semantic Assets).
+3. Formal agreements that are not industry standards (use Agreements).
+Example Quotations:
+1. (to be added during the cross-coding pass)
+Notes: Boundary with Guiding Principles: standards prescribe concrete form; principles articulate values. Boundary with Agreements: standards apply across an industry or domain; agreements are bilateral or multilateral between specific parties.
+Literature:
+- Kubicek et al. (2011), ch. 7, on standards as the mechanism of technical interoperability</t>
   </si>
 </sst>
 </file>
@@ -4305,11 +4284,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{e7ff6755-9d12-41ad-97f8-04e95bd17a8d}">
-  <dimension ref="A1:E151"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00a1bc99-7232-4d03-bee2-e4136662d5b8}">
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="80.42857142857143" customWidth="1"/>
+    <col min="1" max="1" width="110.28571428571429" customWidth="1"/>
     <col min="2" max="2" width="255.71428571428572" customWidth="1"/>
     <col min="3" max="3" width="14.285714285714286" customWidth="1"/>
     <col min="4" max="4" width="14.428571428571429" customWidth="1"/>
@@ -4418,7 +4397,9 @@
       <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
@@ -4478,17 +4459,21 @@
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" ht="14.25">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>7</v>
@@ -4498,32 +4483,36 @@
     </row>
     <row r="15" spans="1:5" ht="14.25">
       <c r="A15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="14.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" ht="14.25">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
@@ -4533,10 +4522,10 @@
     </row>
     <row r="18" spans="1:5" ht="14.25">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>7</v>
@@ -4546,43 +4535,49 @@
     </row>
     <row r="19" spans="1:5" ht="14.25">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="14.25">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" ht="14.25">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" ht="14.25">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>7</v>
@@ -4592,21 +4587,23 @@
     </row>
     <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" ht="14.25">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>7</v>
@@ -4616,19 +4613,23 @@
     </row>
     <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
     <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>7</v>
@@ -4638,10 +4639,10 @@
     </row>
     <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>7</v>
@@ -4651,10 +4652,10 @@
     </row>
     <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>7</v>
@@ -4664,10 +4665,10 @@
     </row>
     <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>7</v>
@@ -4677,10 +4678,10 @@
     </row>
     <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>7</v>
@@ -4690,10 +4691,10 @@
     </row>
     <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>7</v>
@@ -4703,32 +4704,36 @@
     </row>
     <row r="32" spans="1:5" ht="14.25">
       <c r="A32" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>7</v>
@@ -4738,10 +4743,10 @@
     </row>
     <row r="35" spans="1:5" ht="14.25">
       <c r="A35" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>7</v>
@@ -4751,10 +4756,10 @@
     </row>
     <row r="36" spans="1:5" ht="14.25">
       <c r="A36" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>7</v>
@@ -4764,32 +4769,36 @@
     </row>
     <row r="37" spans="1:5" ht="14.25">
       <c r="A37" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" ht="14.25">
       <c r="A38" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" ht="14.25">
       <c r="A39" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>7</v>
@@ -4799,10 +4808,10 @@
     </row>
     <row r="40" spans="1:5" ht="14.25">
       <c r="A40" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>7</v>
@@ -4812,39 +4821,49 @@
     </row>
     <row r="41" spans="1:5" ht="14.25">
       <c r="A41" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" ht="14.25">
       <c r="A42" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
     </row>
     <row r="43" spans="1:5" ht="14.25">
       <c r="A43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
     </row>
     <row r="44" spans="1:5" ht="14.25">
       <c r="A44" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>7</v>
@@ -4854,1292 +4873,1182 @@
     </row>
     <row r="45" spans="1:5" ht="14.25">
       <c r="A45" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
     <row r="46" spans="1:5" ht="14.25">
       <c r="A46" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:5" ht="14.25">
       <c r="A47" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
+      <c r="D47" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48" spans="1:5" ht="14.25">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49" spans="1:5" ht="14.25">
       <c r="A49" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="D49" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50" spans="1:5" ht="14.25">
       <c r="A50" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
       <c r="E50" s="2"/>
     </row>
     <row r="51" spans="1:5" ht="14.25">
       <c r="A51" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="D51" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52" spans="1:5" ht="14.25">
       <c r="A52" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53" spans="1:5" ht="14.25">
       <c r="A53" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54" spans="1:5" ht="14.25">
       <c r="A54" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55" spans="1:5" ht="14.25">
       <c r="A55" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>114</v>
+      </c>
       <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="D55" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56" spans="1:5" ht="14.25">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57" spans="1:5" ht="14.25">
       <c r="A57" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58" spans="1:5" ht="14.25">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59" spans="1:5" ht="14.25">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60" spans="1:5" ht="14.25">
       <c r="A60" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61" spans="1:5" ht="14.25">
       <c r="A61" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62" spans="1:5" ht="14.25">
       <c r="A62" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63" spans="1:5" ht="14.25">
       <c r="A63" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" ht="14.25">
       <c r="A64" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65" spans="1:5" ht="14.25">
       <c r="A65" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" ht="14.25">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67" spans="1:5" ht="14.25">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" ht="14.25">
       <c r="A68" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E68" s="2"/>
     </row>
     <row r="69" spans="1:5" ht="14.25">
       <c r="A69" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+      <c r="D69" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E69" s="2"/>
     </row>
     <row r="70" spans="1:5" ht="14.25">
       <c r="A70" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E70" s="2"/>
     </row>
     <row r="71" spans="1:5" ht="14.25">
       <c r="A71" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E71" s="2"/>
     </row>
     <row r="72" spans="1:5" ht="14.25">
       <c r="A72" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E72" s="2"/>
     </row>
     <row r="73" spans="1:5" ht="14.25">
       <c r="A73" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E73" s="2"/>
     </row>
     <row r="74" spans="1:5" ht="14.25">
       <c r="A74" s="2" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E74" s="2"/>
     </row>
     <row r="75" spans="1:5" ht="14.25">
       <c r="A75" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E75" s="2"/>
     </row>
     <row r="76" spans="1:5" ht="14.25">
       <c r="A76" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E76" s="2"/>
     </row>
     <row r="77" spans="1:5" ht="14.25">
       <c r="A77" s="2" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
+      <c r="D77" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5" ht="14.25">
       <c r="A78" s="2" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E78" s="2"/>
     </row>
     <row r="79" spans="1:5" ht="14.25">
       <c r="A79" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" ht="14.25">
       <c r="A80" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
+      <c r="D80" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E80" s="2"/>
     </row>
     <row r="81" spans="1:5" ht="14.25">
       <c r="A81" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" ht="14.25">
       <c r="A82" s="2" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E82" s="2"/>
     </row>
     <row r="83" spans="1:5" ht="14.25">
       <c r="A83" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E83" s="2"/>
     </row>
     <row r="84" spans="1:5" ht="14.25">
       <c r="A84" s="2" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:5" ht="14.25">
       <c r="A85" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E85" s="2"/>
     </row>
     <row r="86" spans="1:5" ht="14.25">
       <c r="A86" s="2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E86" s="2"/>
     </row>
     <row r="87" spans="1:5" ht="14.25">
       <c r="A87" s="2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E87" s="2"/>
     </row>
     <row r="88" spans="1:5" ht="14.25">
       <c r="A88" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E88" s="2"/>
     </row>
     <row r="89" spans="1:5" ht="14.25">
       <c r="A89" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="D89" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E89" s="2"/>
     </row>
     <row r="90" spans="1:5" ht="14.25">
       <c r="A90" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E90" s="2"/>
     </row>
     <row r="91" spans="1:5" ht="14.25">
       <c r="A91" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E91" s="2"/>
     </row>
     <row r="92" spans="1:5" ht="14.25">
       <c r="A92" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C92" s="2"/>
-      <c r="D92" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="93" spans="1:5" ht="14.25">
       <c r="A93" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C93" s="2"/>
-      <c r="D93" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="94" spans="1:5" ht="14.25">
       <c r="A94" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C94" s="2"/>
-      <c r="D94" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="95" spans="1:5" ht="14.25">
       <c r="A95" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B95" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>195</v>
+      </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="E95" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="14.25">
       <c r="A96" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="14.25">
       <c r="A97" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="14.25">
       <c r="A98" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="14.25">
       <c r="A99" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="14.25">
       <c r="A100" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="14.25">
       <c r="A101" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="14.25">
       <c r="A102" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="14.25">
       <c r="A103" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="14.25">
       <c r="A104" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="14.25">
       <c r="A105" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B105" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
+      <c r="E105" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="106" spans="1:5" ht="14.25">
       <c r="A106" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="14.25">
       <c r="A107" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
+      <c r="E107" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="108" spans="1:5" ht="14.25">
       <c r="A108" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="14.25">
       <c r="A109" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
+      <c r="E109" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="110" spans="1:5" ht="14.25">
       <c r="A110" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="14.25">
       <c r="A111" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
+      <c r="E111" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="112" spans="1:5" ht="14.25">
       <c r="A112" s="2" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="14.25">
       <c r="A113" s="2" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
+      <c r="E113" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="114" spans="1:5" ht="14.25">
       <c r="A114" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="14.25">
       <c r="A115" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
+      <c r="E115" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="116" spans="1:5" ht="14.25">
       <c r="A116" s="2" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="14.25">
       <c r="A117" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="14.25">
       <c r="A118" s="2" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
+      <c r="E118" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="119" spans="1:5" ht="14.25">
       <c r="A119" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B119" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>243</v>
+      </c>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
+      <c r="E119" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="120" spans="1:5" ht="14.25">
       <c r="A120" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
+      <c r="E120" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="121" spans="1:5" ht="14.25">
       <c r="A121" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
+      <c r="E121" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="122" spans="1:5" ht="14.25">
       <c r="A122" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B122" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
+      <c r="E122" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="123" spans="1:5" ht="14.25">
       <c r="A123" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B123" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>251</v>
+      </c>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
+      <c r="E123" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="124" spans="1:5" ht="14.25">
       <c r="A124" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
+      <c r="E124" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="125" spans="1:5" ht="14.25">
       <c r="A125" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B125" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
+      <c r="E125" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="126" spans="1:5" ht="14.25">
       <c r="A126" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B126" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
+      <c r="E126" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="127" spans="1:5" ht="14.25">
       <c r="A127" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
+      <c r="E127" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="128" spans="1:5" ht="14.25">
       <c r="A128" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B128" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="E128" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="129" spans="1:5" ht="14.25">
       <c r="A129" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B129" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>263</v>
+      </c>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
+      <c r="E129" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="130" spans="1:5" ht="14.25">
       <c r="A130" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B130" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
+      <c r="E130" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="131" spans="1:5" ht="14.25">
       <c r="A131" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B131" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>267</v>
+      </c>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="E131" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="132" spans="1:5" ht="14.25">
       <c r="A132" s="2" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="14.25">
       <c r="A133" s="2" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="14.25">
       <c r="A134" s="2" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="14.25">
       <c r="A135" s="2" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="14.25">
-      <c r="A136" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="14.25">
-      <c r="A137" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" ht="14.25">
-      <c r="A138" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" ht="14.25">
-      <c r="A139" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-    </row>
-    <row r="140" spans="1:5" ht="14.25">
-      <c r="A140" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="14.25">
-      <c r="A141" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="14.25">
-      <c r="A142" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-    </row>
-    <row r="143" spans="1:5" ht="14.25">
-      <c r="A143" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
-    </row>
-    <row r="144" spans="1:5" ht="14.25">
-      <c r="A144" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="14.25">
-      <c r="A145" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="14.25">
-      <c r="A146" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="14.25">
-      <c r="A147" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="14.25">
-      <c r="A148" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
-    </row>
-    <row r="149" spans="1:5" ht="14.25">
-      <c r="A149" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="14.25">
-      <c r="A150" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" ht="14.25">
-      <c r="A151" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
+        <v>189</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
